--- a/Audit/JJ_PD_IP_A02_기능구조도_v1.5_이노팸.xlsx
+++ b/Audit/JJ_PD_IP_A02_기능구조도_v1.5_이노팸.xlsx
@@ -3375,7 +3375,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>개발 결과 현행화 + 화면설계서 v1.5 검수본 반영(알림 기준 설정 팝업, 격자 크기, 구역 추천 방식, 투자우선순위 가중치·지표, 명칭 통일)</t>
+          <t>개발 결과 현행화 + 화면설계서 v1.5 검수본 반영(알림 기준 설정 팝업, 격자 크기, 구역추천 방식, 투자우선순위 가중치·지표), 메뉴 명칭은 구현 화면 기준</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="G12" s="15" t="inlineStr">
         <is>
-          <t>최근 정책 시뮬레이션 목록 표시. 목록이 비면 빈 상태 안내 문구 표시. 전체 → 정책 시뮬레이션 이동</t>
+          <t>최근 정책 효과 시뮬레이션 목록 표시. 목록이 비면 빈 상태 안내 문구 표시. 전체 → 정책 효과 시뮬레이션 이동</t>
         </is>
       </c>
       <c r="H12" s="14" t="inlineStr">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
-          <t>집중구역분석</t>
+          <t>불법 주차 집중 구역 분석</t>
         </is>
       </c>
       <c r="D22" s="16" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="C23" s="32" t="inlineStr">
         <is>
-          <t>집중구역분석</t>
+          <t>불법 주차 집중 구역 분석</t>
         </is>
       </c>
       <c r="D23" s="32" t="inlineStr">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="C24" s="32" t="inlineStr">
         <is>
-          <t>집중구역분석</t>
+          <t>불법 주차 집중 구역 분석</t>
         </is>
       </c>
       <c r="D24" s="32" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="C25" s="34" t="inlineStr">
         <is>
-          <t>집중구역분석</t>
+          <t>불법 주차 집중 구역 분석</t>
         </is>
       </c>
       <c r="D25" s="34" t="inlineStr">
@@ -4813,7 +4813,7 @@
       </c>
       <c r="C26" s="16" t="inlineStr">
         <is>
-          <t>정책 시뮬레이션</t>
+          <t>정책 효과 시뮬레이션</t>
         </is>
       </c>
       <c r="D26" s="16" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="C27" s="32" t="inlineStr">
         <is>
-          <t>정책 시뮬레이션</t>
+          <t>정책 효과 시뮬레이션</t>
         </is>
       </c>
       <c r="D27" s="32" t="inlineStr">
@@ -4919,7 +4919,7 @@
       </c>
       <c r="C28" s="32" t="inlineStr">
         <is>
-          <t>정책 시뮬레이션</t>
+          <t>정책 효과 시뮬레이션</t>
         </is>
       </c>
       <c r="D28" s="32" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="C29" s="32" t="inlineStr">
         <is>
-          <t>정책 시뮬레이션</t>
+          <t>정책 효과 시뮬레이션</t>
         </is>
       </c>
       <c r="D29" s="32" t="inlineStr">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="C30" s="32" t="inlineStr">
         <is>
-          <t>정책 시뮬레이션</t>
+          <t>정책 효과 시뮬레이션</t>
         </is>
       </c>
       <c r="D30" s="14" t="inlineStr">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="C31" s="32" t="inlineStr">
         <is>
-          <t>정책 시뮬레이션</t>
+          <t>정책 효과 시뮬레이션</t>
         </is>
       </c>
       <c r="D31" s="14" t="inlineStr">
@@ -5408,7 +5408,7 @@
       </c>
       <c r="C37" s="16" t="inlineStr">
         <is>
-          <t>구역 추천</t>
+          <t>구역추천</t>
         </is>
       </c>
       <c r="D37" s="16" t="inlineStr">
@@ -5461,7 +5461,7 @@
       </c>
       <c r="C38" s="32" t="inlineStr">
         <is>
-          <t>구역 추천</t>
+          <t>구역추천</t>
         </is>
       </c>
       <c r="D38" s="14" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="C39" s="32" t="inlineStr">
         <is>
-          <t>구역 추천</t>
+          <t>구역추천</t>
         </is>
       </c>
       <c r="D39" s="14" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="C40" s="52" t="inlineStr">
         <is>
-          <t>구역 추천</t>
+          <t>구역추천</t>
         </is>
       </c>
       <c r="D40" s="51" t="inlineStr">

--- a/Audit/JJ_PD_IP_A02_기능구조도_v1.5_이노팸.xlsx
+++ b/Audit/JJ_PD_IP_A02_기능구조도_v1.5_이노팸.xlsx
@@ -3375,7 +3375,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>개발 결과 현행화 + 화면설계서 v1.5 검수본 반영(알림 기준 설정 팝업, 격자 크기, 구역추천 방식, 투자우선순위 가중치·지표), 메뉴 명칭은 구현 화면 기준</t>
+          <t>개발 결과 현행화 + 화면설계서 v1.5 검수본 반영(알림 기준 설정 팝업, 격자 크기, 구역추천 방식, 투자우선순위 가중치·지표), 메뉴 명칭은 구현 화면 기준, 내보내기 기능을 공통에서 분석 화면별 기능으로 분리</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -3542,7 +3542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K74"/>
+  <dimension ref="A1:K78"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.875" defaultRowHeight="68.09999999999999" customHeight="1"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3688,173 +3688,173 @@
       <c r="K4" s="24" t="n"/>
     </row>
     <row r="5" ht="32.1" customHeight="1">
-      <c r="A5" s="25" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-10</t>
-        </is>
-      </c>
-      <c r="B5" s="14" t="inlineStr">
-        <is>
-          <t>FN-PAR-C01-02</t>
-        </is>
-      </c>
-      <c r="C5" s="31" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>REQ-SFR-005-07</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>FN-PAR-C01-03</t>
+        </is>
+      </c>
+      <c r="C5" s="33" t="inlineStr">
         <is>
           <t>공통</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
-        <is>
-          <t>내보내기</t>
-        </is>
-      </c>
-      <c r="E5" s="14" t="inlineStr">
-        <is>
-          <t>PDF/Excel 내보내기</t>
-        </is>
-      </c>
-      <c r="F5" s="14" t="inlineStr">
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>AI 대화 시작하기</t>
+        </is>
+      </c>
+      <c r="E5" s="18" t="inlineStr">
+        <is>
+          <t>AI 어시스턴트 바로가기</t>
+        </is>
+      </c>
+      <c r="F5" s="18" t="inlineStr">
         <is>
           <t>공통</t>
         </is>
       </c>
-      <c r="G5" s="15" t="inlineStr">
-        <is>
-          <t>각 화면의 데이터를 PDF/DOCX로 내보내는 기능 버튼, 직접 생성 보고서 목록에 업데이트</t>
-        </is>
-      </c>
-      <c r="H5" s="14" t="inlineStr">
+      <c r="G5" s="19" t="inlineStr">
+        <is>
+          <t>AI 어시스턴트 화면으로 바로 이동하는 버튼</t>
+        </is>
+      </c>
+      <c r="H5" s="18" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I5" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J5" s="14" t="inlineStr">
+      <c r="I5" s="39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J5" s="18" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K5" s="26" t="n"/>
+      <c r="K5" s="28" t="n"/>
     </row>
     <row r="6" ht="32.1" customHeight="1">
-      <c r="A6" s="27" t="inlineStr">
-        <is>
-          <t>REQ-SFR-005-07</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>FN-PAR-C01-03</t>
-        </is>
-      </c>
-      <c r="C6" s="33" t="inlineStr">
-        <is>
-          <t>공통</t>
-        </is>
-      </c>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>AI 대화 시작하기</t>
-        </is>
-      </c>
-      <c r="E6" s="18" t="inlineStr">
-        <is>
-          <t>AI 어시스턴트 바로가기</t>
-        </is>
-      </c>
-      <c r="F6" s="18" t="inlineStr">
-        <is>
-          <t>공통</t>
-        </is>
-      </c>
-      <c r="G6" s="19" t="inlineStr">
-        <is>
-          <t>AI 어시스턴트 화면으로 바로 이동하는 버튼</t>
-        </is>
-      </c>
-      <c r="H6" s="18" t="inlineStr">
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>REQ-SFR-003-07</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>FN-PAR-01-01</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>대시보드</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>조회 단위 필터</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>기간 탭 및 상세 필터</t>
+        </is>
+      </c>
+      <c r="F6" s="16" t="inlineStr">
+        <is>
+          <t>UI-PAR-001</t>
+        </is>
+      </c>
+      <c r="G6" s="17" t="inlineStr">
+        <is>
+          <t>이제/주간/월간 탭 및 상세 필터(날짜 범위) 설정 기능</t>
+        </is>
+      </c>
+      <c r="H6" s="16" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I6" s="39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J6" s="18" t="inlineStr">
+      <c r="I6" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J6" s="16" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K6" s="28" t="n"/>
+      <c r="K6" s="24" t="n"/>
     </row>
     <row r="7" ht="32.1" customHeight="1">
-      <c r="A7" s="23" t="inlineStr">
+      <c r="A7" s="25" t="inlineStr">
         <is>
           <t>REQ-SFR-003-07</t>
         </is>
       </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>FN-PAR-01-01</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>FN-PAR-01-02</t>
+        </is>
+      </c>
+      <c r="C7" s="31" t="inlineStr">
         <is>
           <t>대시보드</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>조회 단위 필터</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>기간 탭 및 상세 필터</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>KPI 요약</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>KPI 카드</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
         <is>
           <t>UI-PAR-001</t>
         </is>
       </c>
-      <c r="G7" s="17" t="inlineStr">
-        <is>
-          <t>이제/주간/월간 탭 및 상세 필터(날짜 범위) 설정 기능</t>
-        </is>
-      </c>
-      <c r="H7" s="16" t="inlineStr">
+      <c r="G7" s="15" t="inlineStr">
+        <is>
+          <t>총 민원 건수·공영주차장 현황(개소)·위험단계알림 건수 카드 (단속 건수는 월 1회 갱신으로 제외)</t>
+        </is>
+      </c>
+      <c r="H7" s="14" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I7" s="37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J7" s="16" t="inlineStr">
+      <c r="I7" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J7" s="14" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K7" s="24" t="n"/>
+      <c r="K7" s="26" t="n"/>
     </row>
     <row r="8" ht="32.1" customHeight="1">
       <c r="A8" s="25" t="inlineStr">
         <is>
-          <t>REQ-SFR-003-07</t>
+          <t>REQ-SFR-003-01</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>FN-PAR-01-02</t>
+          <t>FN-PAR-01-03</t>
         </is>
       </c>
       <c r="C8" s="31" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>KPI 요약</t>
+          <t>민원 발생 추이</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>KPI 카드</t>
+          <t>시간대별 라인 차트</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="G8" s="15" t="inlineStr">
         <is>
-          <t>총 민원 건수·공영주차장 현황(개소)·위험단계알림 건수 카드 (단속 건수는 월 1회 갱신으로 제외)</t>
+          <t>시간대별(00~22시) 민원 유형 라인 차트 — 어제/주간/월간 조회 단위 모두 시간대별 집계, 단위에 따라 집계 규모 변경</t>
         </is>
       </c>
       <c r="H8" s="14" t="inlineStr">
@@ -3902,12 +3902,12 @@
     <row r="9" ht="32.1" customHeight="1">
       <c r="A9" s="25" t="inlineStr">
         <is>
-          <t>REQ-SFR-003-01</t>
+          <t>REQ-SFR-003-02</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>FN-PAR-01-03</t>
+          <t>FN-PAR-01-04</t>
         </is>
       </c>
       <c r="C9" s="31" t="inlineStr">
@@ -3917,12 +3917,12 @@
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>민원 발생 추이</t>
+          <t>민원 집중구역 순위</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>시간대별 라인 차트</t>
+          <t>Top5 목록 + GIS 보기</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
-          <t>시간대별(00~22시) 민원 유형 라인 차트 — 어제/주간/월간 조회 단위 모두 시간대별 집계, 단위에 따라 집계 규모 변경</t>
+          <t>불법주차 집중구역 Top5 목록(최근 1개월 기준), 위험 등급 배지(심각/경고/주의), '자세히 보기'로 집중 구역 분석 이동</t>
         </is>
       </c>
       <c r="H9" s="14" t="inlineStr">
@@ -3955,12 +3955,12 @@
     <row r="10" ht="32.1" customHeight="1">
       <c r="A10" s="25" t="inlineStr">
         <is>
-          <t>REQ-SFR-003-02</t>
+          <t>REQ-SFR-003-03</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>FN-PAR-01-04</t>
+          <t>FN-PAR-01-05</t>
         </is>
       </c>
       <c r="C10" s="31" t="inlineStr">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>민원 집중구역 순위</t>
+          <t>읍·면·동 민원 순위</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>Top5 목록 + GIS 보기</t>
+          <t>읍면동 Top5 카드</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="G10" s="15" t="inlineStr">
         <is>
-          <t>불법주차 집중구역 Top5 목록(최근 1개월 기준), 위험 등급 배지(심각/경고/주의), '자세히 보기'로 집중 구역 분석 이동</t>
+          <t>읍·면·동 Top5 민원 건수 카드, 전일 대비 증감률·순위 변동·유형별 건수 및 스택바 표시. 전체 보기 링크</t>
         </is>
       </c>
       <c r="H10" s="14" t="inlineStr">
@@ -4008,12 +4008,12 @@
     <row r="11" ht="32.1" customHeight="1">
       <c r="A11" s="25" t="inlineStr">
         <is>
-          <t>REQ-SFR-003-03</t>
+          <t>REQ-SFR-003-10</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>FN-PAR-01-05</t>
+          <t>FN-PAR-01-06</t>
         </is>
       </c>
       <c r="C11" s="31" t="inlineStr">
@@ -4023,12 +4023,12 @@
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>읍·면·동 민원 순위</t>
+          <t>최근 분석 요약</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>읍면동 Top5 카드</t>
+          <t>분석 상태 목록 위젯</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>읍·면·동 Top5 민원 건수 카드, 전일 대비 증감률·순위 변동·유형별 건수 및 스택바 표시. 전체 보기 링크</t>
+          <t>최근 정책 효과 시뮬레이션 목록 표시. 목록이 비면 빈 상태 안내 문구 표시. 전체 → 정책 효과 시뮬레이션 이동</t>
         </is>
       </c>
       <c r="H11" s="14" t="inlineStr">
@@ -4061,12 +4061,12 @@
     <row r="12" ht="32.1" customHeight="1">
       <c r="A12" s="25" t="inlineStr">
         <is>
-          <t>REQ-SFR-003-10</t>
+          <t>REQ-SFR-005-05</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>FN-PAR-01-06</t>
+          <t>FN-PAR-01-07</t>
         </is>
       </c>
       <c r="C12" s="31" t="inlineStr">
@@ -4076,12 +4076,12 @@
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>최근 분석 요약</t>
+          <t>최근 보고서 요약</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>분석 상태 목록 위젯</t>
+          <t>보고서 목록 위젯</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="G12" s="15" t="inlineStr">
         <is>
-          <t>최근 정책 효과 시뮬레이션 목록 표시. 목록이 비면 빈 상태 안내 문구 표시. 전체 → 정책 효과 시뮬레이션 이동</t>
+          <t>최근 생성 보고서 목록(제목·일시). 항목 클릭 시 보고서 목록의 해당 행으로 이동·강조. 빈 상태 안내 포함</t>
         </is>
       </c>
       <c r="H12" s="14" t="inlineStr">
@@ -4112,135 +4112,135 @@
       <c r="K12" s="26" t="n"/>
     </row>
     <row r="13" ht="32.1" customHeight="1">
-      <c r="A13" s="25" t="inlineStr">
-        <is>
-          <t>REQ-SFR-005-05</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>FN-PAR-01-07</t>
-        </is>
-      </c>
-      <c r="C13" s="31" t="inlineStr">
+      <c r="A13" s="27" t="inlineStr">
+        <is>
+          <t>REQ-SFR-005-07</t>
+        </is>
+      </c>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>FN-PAR-01-08</t>
+        </is>
+      </c>
+      <c r="C13" s="33" t="inlineStr">
         <is>
           <t>대시보드</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
-        <is>
-          <t>최근 보고서 요약</t>
-        </is>
-      </c>
-      <c r="E13" s="14" t="inlineStr">
-        <is>
-          <t>보고서 목록 위젯</t>
-        </is>
-      </c>
-      <c r="F13" s="14" t="inlineStr">
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>AI 어시스턴트 패널</t>
+        </is>
+      </c>
+      <c r="E13" s="18" t="inlineStr">
+        <is>
+          <t>빠른 질문 입력창</t>
+        </is>
+      </c>
+      <c r="F13" s="18" t="inlineStr">
         <is>
           <t>UI-PAR-001</t>
         </is>
       </c>
-      <c r="G13" s="15" t="inlineStr">
-        <is>
-          <t>최근 생성 보고서 목록(제목·일시). 항목 클릭 시 보고서 목록의 해당 행으로 이동·강조. 빈 상태 안내 포함</t>
-        </is>
-      </c>
-      <c r="H13" s="14" t="inlineStr">
+      <c r="G13" s="19" t="inlineStr">
+        <is>
+          <t>AI 어시스턴트 빠른 질문 입력창 및 추천 질문 3개 표시. 대화 열기 버튼 → AI 어시스턴트 화면 이동</t>
+        </is>
+      </c>
+      <c r="H13" s="18" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I13" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J13" s="14" t="inlineStr">
+      <c r="I13" s="39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J13" s="18" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K13" s="26" t="n"/>
+      <c r="K13" s="28" t="n"/>
     </row>
     <row r="14" ht="32.1" customHeight="1">
-      <c r="A14" s="27" t="inlineStr">
-        <is>
-          <t>REQ-SFR-005-07</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>FN-PAR-01-08</t>
-        </is>
-      </c>
-      <c r="C14" s="33" t="inlineStr">
-        <is>
-          <t>대시보드</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>AI 어시스턴트 패널</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>빠른 질문 입력창</t>
-        </is>
-      </c>
-      <c r="F14" s="18" t="inlineStr">
-        <is>
-          <t>UI-PAR-001</t>
-        </is>
-      </c>
-      <c r="G14" s="19" t="inlineStr">
-        <is>
-          <t>AI 어시스턴트 빠른 질문 입력창 및 추천 질문 3개 표시. 대화 열기 버튼 → AI 어시스턴트 화면 이동</t>
-        </is>
-      </c>
-      <c r="H14" s="18" t="inlineStr">
+      <c r="A14" s="23" t="inlineStr">
+        <is>
+          <t>REQ-SFR-003-03</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>FN-PAR-02-01</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>민원현황</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="inlineStr">
+        <is>
+          <t>조회 단위 필터</t>
+        </is>
+      </c>
+      <c r="E14" s="16" t="inlineStr">
+        <is>
+          <t>기간 탭 및 상세 필터</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>UI-PAR-002</t>
+        </is>
+      </c>
+      <c r="G14" s="17" t="inlineStr">
+        <is>
+          <t>어제/주간/월간 탭 및 상세 필터(행정구역/민원유형/위험단계) 설정</t>
+        </is>
+      </c>
+      <c r="H14" s="16" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I14" s="39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J14" s="18" t="inlineStr">
+      <c r="I14" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J14" s="16" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K14" s="28" t="n"/>
+      <c r="K14" s="24" t="n"/>
     </row>
     <row r="15" ht="32.1" customHeight="1">
-      <c r="A15" s="23" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-03</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>FN-PAR-02-01</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="A15" s="29" t="inlineStr">
+        <is>
+          <t>REQ-SFR-003-07</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>FN-PAR-02-02</t>
+        </is>
+      </c>
+      <c r="C15" s="32" t="inlineStr">
         <is>
           <t>민원현황</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>조회 단위 필터</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>기간 탭 및 상세 필터</t>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>KPI 요약</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>KPI 카드</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -4248,37 +4248,37 @@
           <t>UI-PAR-002</t>
         </is>
       </c>
-      <c r="G15" s="17" t="inlineStr">
-        <is>
-          <t>어제/주간/월간 탭 및 상세 필터(행정구역/민원유형/위험단계) 설정</t>
-        </is>
-      </c>
-      <c r="H15" s="16" t="inlineStr">
+      <c r="G15" s="21" t="inlineStr">
+        <is>
+          <t>KPI 카드(총 민원 건수 / 민원 감정 분석(긍정·보통·부정) / 단속 집중 지역 / 수요 부족 지역). 전기 대비 증감 표시</t>
+        </is>
+      </c>
+      <c r="H15" s="20" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I15" s="37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J15" s="16" t="inlineStr">
+      <c r="I15" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J15" s="20" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K15" s="24" t="n"/>
+      <c r="K15" s="30" t="n"/>
     </row>
     <row r="16" ht="32.1" customHeight="1">
-      <c r="A16" s="29" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-07</t>
+      <c r="A16" s="25" t="inlineStr">
+        <is>
+          <t>REQ-SFR-003-09</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>FN-PAR-02-02</t>
+          <t>FN-PAR-02-03</t>
         </is>
       </c>
       <c r="C16" s="32" t="inlineStr">
@@ -4286,27 +4286,27 @@
           <t>민원현황</t>
         </is>
       </c>
-      <c r="D16" s="20" t="inlineStr">
-        <is>
-          <t>KPI 요약</t>
-        </is>
-      </c>
-      <c r="E16" s="20" t="inlineStr">
-        <is>
-          <t>KPI 카드</t>
-        </is>
-      </c>
-      <c r="F16" s="20" t="inlineStr">
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>GIS 지도</t>
+        </is>
+      </c>
+      <c r="E16" s="14" t="inlineStr">
+        <is>
+          <t>민원 히트맵 레이어</t>
+        </is>
+      </c>
+      <c r="F16" s="14" t="inlineStr">
         <is>
           <t>UI-PAR-002</t>
         </is>
       </c>
-      <c r="G16" s="21" t="inlineStr">
-        <is>
-          <t>KPI 카드(총 민원 건수 / 민원 감정 분석(긍정·보통·부정) / 단속 집중 지역 / 수요 부족 지역). 전기 대비 증감 표시</t>
-        </is>
-      </c>
-      <c r="H16" s="20" t="inlineStr">
+      <c r="G16" s="15" t="inlineStr">
+        <is>
+          <t>민원 히트맵 표시, 히트맵 중심점 동단위 건수 표기.</t>
+        </is>
+      </c>
+      <c r="H16" s="14" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
@@ -4316,12 +4316,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J16" s="20" t="inlineStr">
+      <c r="J16" s="14" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K16" s="30" t="n"/>
+      <c r="K16" s="26" t="n"/>
     </row>
     <row r="17" ht="32.1" customHeight="1">
       <c r="A17" s="25" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="B17" s="20" t="inlineStr">
         <is>
-          <t>FN-PAR-02-03</t>
+          <t>FN-PAR-02-04</t>
         </is>
       </c>
       <c r="C17" s="32" t="inlineStr">
@@ -4339,14 +4339,14 @@
           <t>민원현황</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D17" s="31" t="inlineStr">
         <is>
           <t>GIS 지도</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>민원 히트맵 레이어</t>
+          <t>레이어 설정 패널</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="G17" s="15" t="inlineStr">
         <is>
-          <t>민원 히트맵 표시, 히트맵 중심점 동단위 건수 표기.</t>
+          <t>지도 레이어 패널 — 민원 다발/단속 집중/수요 부족(택1 라디오) + 공영주차장·행정동 경계 토글. 레이어 선택에 따라 우측 순위 카드 연동 전환</t>
         </is>
       </c>
       <c r="H17" s="14" t="inlineStr">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>FN-PAR-02-04</t>
+          <t>FN-PAR-02-05</t>
         </is>
       </c>
       <c r="C18" s="32" t="inlineStr">
@@ -4399,7 +4399,7 @@
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>레이어 설정 패널</t>
+          <t>지도 범례</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
@@ -4409,7 +4409,7 @@
       </c>
       <c r="G18" s="15" t="inlineStr">
         <is>
-          <t>지도 레이어 패널 — 민원 다발/단속 집중/수요 부족(택1 라디오) + 공영주차장·행정동 경계 토글. 레이어 선택에 따라 우측 순위 카드 연동 전환</t>
+          <t>히트맵 색상 범례 표시</t>
         </is>
       </c>
       <c r="H18" s="14" t="inlineStr">
@@ -4432,12 +4432,12 @@
     <row r="19" ht="32.1" customHeight="1">
       <c r="A19" s="25" t="inlineStr">
         <is>
-          <t>REQ-SFR-003-09</t>
+          <t>REQ-SFR-003-01</t>
         </is>
       </c>
       <c r="B19" s="20" t="inlineStr">
         <is>
-          <t>FN-PAR-02-05</t>
+          <t>FN-PAR-02-06</t>
         </is>
       </c>
       <c r="C19" s="32" t="inlineStr">
@@ -4445,14 +4445,14 @@
           <t>민원현황</t>
         </is>
       </c>
-      <c r="D19" s="31" t="inlineStr">
-        <is>
-          <t>GIS 지도</t>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>지역별 민원 현황</t>
         </is>
       </c>
       <c r="E19" s="14" t="inlineStr">
         <is>
-          <t>지도 범례</t>
+          <t>읍면동 순위 목록</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>히트맵 색상 범례 표시</t>
+          <t>읍·면·동 민원/단속/수요부족 순위(선택 레이어 연동). 범례 등급(심각·경고·주의)에 해당하는 지역만 표출, 행 클릭 시 지도 이동·팝업</t>
         </is>
       </c>
       <c r="H19" s="14" t="inlineStr">
@@ -4483,67 +4483,67 @@
       <c r="K19" s="26" t="n"/>
     </row>
     <row r="20" ht="32.1" customHeight="1">
-      <c r="A20" s="25" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-01</t>
-        </is>
-      </c>
-      <c r="B20" s="20" t="inlineStr">
-        <is>
-          <t>FN-PAR-02-06</t>
-        </is>
-      </c>
-      <c r="C20" s="32" t="inlineStr">
+      <c r="A20" s="27" t="inlineStr">
+        <is>
+          <t>REQ-SFR-003-02</t>
+        </is>
+      </c>
+      <c r="B20" s="40" t="inlineStr">
+        <is>
+          <t>FN-PAR-02-07</t>
+        </is>
+      </c>
+      <c r="C20" s="34" t="inlineStr">
         <is>
           <t>민원현황</t>
         </is>
       </c>
-      <c r="D20" s="14" t="inlineStr">
-        <is>
-          <t>지역별 민원 현황</t>
-        </is>
-      </c>
-      <c r="E20" s="14" t="inlineStr">
+      <c r="D20" s="18" t="inlineStr">
+        <is>
+          <t>부정 민원 상위 지역</t>
+        </is>
+      </c>
+      <c r="E20" s="18" t="inlineStr">
         <is>
           <t>읍면동 순위 목록</t>
         </is>
       </c>
-      <c r="F20" s="14" t="inlineStr">
+      <c r="F20" s="18" t="inlineStr">
         <is>
           <t>UI-PAR-002</t>
         </is>
       </c>
-      <c r="G20" s="15" t="inlineStr">
-        <is>
-          <t>읍·면·동 민원/단속/수요부족 순위(선택 레이어 연동). 범례 등급(심각·경고·주의)에 해당하는 지역만 표출, 행 클릭 시 지도 이동·팝업</t>
-        </is>
-      </c>
-      <c r="H20" s="14" t="inlineStr">
+      <c r="G20" s="19" t="inlineStr">
+        <is>
+          <t>읍·면·동 기준 부정 민원 상위 지역 순위. 긍정·보통·부정 구성비 막대 차트​. 더보기 클릭 하면 최대 15개 목록 노출</t>
+        </is>
+      </c>
+      <c r="H20" s="18" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I20" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J20" s="14" t="inlineStr">
+      <c r="I20" s="39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J20" s="18" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K20" s="26" t="n"/>
+      <c r="K20" s="28" t="n"/>
     </row>
     <row r="21" ht="32.1" customHeight="1">
       <c r="A21" s="27" t="inlineStr">
         <is>
-          <t>REQ-SFR-003-02</t>
+          <t>REQ-SFR-003-10</t>
         </is>
       </c>
       <c r="B21" s="40" t="inlineStr">
         <is>
-          <t>FN-PAR-02-07</t>
+          <t>FN-PAR-02-08</t>
         </is>
       </c>
       <c r="C21" s="34" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="D21" s="18" t="inlineStr">
         <is>
-          <t>부정 민원 상위 지역</t>
+          <t>내보내기</t>
         </is>
       </c>
       <c r="E21" s="18" t="inlineStr">
         <is>
-          <t>읍면동 순위 목록</t>
+          <t>PDF/DOCX 내보내기</t>
         </is>
       </c>
       <c r="F21" s="18" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="G21" s="19" t="inlineStr">
         <is>
-          <t>읍·면·동 기준 부정 민원 상위 지역 순위. 긍정·보통·부정 구성비 막대 차트​. 더보기 클릭 하면 최대 15개 목록 노출</t>
+          <t>조회 결과(KPI·지도·순위)를 PDF/DOCX로 내보내기 — 직접 생성 보고서 목록에 추가</t>
         </is>
       </c>
       <c r="H21" s="18" t="inlineStr">
@@ -4586,7 +4586,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="K21" s="28" t="n"/>
+      <c r="K21" s="28" t="inlineStr"/>
     </row>
     <row r="22" ht="32.1" customHeight="1">
       <c r="A22" s="23" t="inlineStr">
@@ -4801,110 +4801,110 @@
       <c r="K25" s="28" t="n"/>
     </row>
     <row r="26" ht="32.1" customHeight="1">
-      <c r="A26" s="23" t="inlineStr">
+      <c r="A26" s="27" t="inlineStr">
+        <is>
+          <t>REQ-SFR-003-10</t>
+        </is>
+      </c>
+      <c r="B26" s="18" t="inlineStr">
+        <is>
+          <t>FN-PAR-03-01-05</t>
+        </is>
+      </c>
+      <c r="C26" s="34" t="inlineStr">
+        <is>
+          <t>불법 주차 집중 구역 분석</t>
+        </is>
+      </c>
+      <c r="D26" s="34" t="inlineStr">
+        <is>
+          <t>내보내기</t>
+        </is>
+      </c>
+      <c r="E26" s="18" t="inlineStr">
+        <is>
+          <t>PDF/DOCX 내보내기</t>
+        </is>
+      </c>
+      <c r="F26" s="18" t="inlineStr">
+        <is>
+          <t>UI-PAR-003-01</t>
+        </is>
+      </c>
+      <c r="G26" s="19" t="inlineStr">
+        <is>
+          <t>분석 결과(집중구역 순위·지도)를 PDF/DOCX로 내보내기 — 결과 패널에 배치, 직접 생성 보고서 목록에 추가</t>
+        </is>
+      </c>
+      <c r="H26" s="18" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I26" s="39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J26" s="18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K26" s="28" t="inlineStr"/>
+    </row>
+    <row r="27" ht="32.1" customHeight="1">
+      <c r="A27" s="23" t="inlineStr">
         <is>
           <t>REQ-SFR-003-05</t>
         </is>
       </c>
-      <c r="B26" s="16" t="inlineStr">
+      <c r="B27" s="16" t="inlineStr">
         <is>
           <t>FN-PAR-03-02-01</t>
         </is>
       </c>
-      <c r="C26" s="16" t="inlineStr">
+      <c r="C27" s="16" t="inlineStr">
         <is>
           <t>정책 효과 시뮬레이션</t>
         </is>
       </c>
-      <c r="D26" s="16" t="inlineStr">
+      <c r="D27" s="16" t="inlineStr">
         <is>
           <t>정책 변수 설정</t>
         </is>
       </c>
-      <c r="E26" s="16" t="inlineStr">
+      <c r="E27" s="16" t="inlineStr">
         <is>
           <t>정책 유형 탭 선택</t>
         </is>
       </c>
-      <c r="F26" s="16" t="inlineStr">
+      <c r="F27" s="16" t="inlineStr">
         <is>
           <t>UI-PAR-003-02</t>
         </is>
       </c>
-      <c r="G26" s="17" t="inlineStr">
+      <c r="G27" s="17" t="inlineStr">
         <is>
           <t>정책 유형 탭 전환: 주차장 확충 / 이면도로 정비 / 요금제 적용 3종 탭 선택</t>
         </is>
       </c>
-      <c r="H26" s="16" t="inlineStr">
+      <c r="H27" s="16" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I26" s="37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J26" s="16" t="inlineStr">
+      <c r="I27" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J27" s="16" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K26" s="24" t="n"/>
-    </row>
-    <row r="27" ht="32.1" customHeight="1">
-      <c r="A27" s="25" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-05</t>
-        </is>
-      </c>
-      <c r="B27" s="14" t="inlineStr">
-        <is>
-          <t>FN-PAR-03-02-02</t>
-        </is>
-      </c>
-      <c r="C27" s="32" t="inlineStr">
-        <is>
-          <t>정책 효과 시뮬레이션</t>
-        </is>
-      </c>
-      <c r="D27" s="32" t="inlineStr">
-        <is>
-          <t>정책 변수 설정</t>
-        </is>
-      </c>
-      <c r="E27" s="14" t="inlineStr">
-        <is>
-          <t>주차장 확충 파라미터</t>
-        </is>
-      </c>
-      <c r="F27" s="14" t="inlineStr">
-        <is>
-          <t>UI-PAR-003-02</t>
-        </is>
-      </c>
-      <c r="G27" s="15" t="inlineStr">
-        <is>
-          <t>[주차장 확충] 대상 지역·확충 방식(공한지 조성/복층화/신규 조성)·주차면 증설 수 입력 후 시뮬레이션 실행</t>
-        </is>
-      </c>
-      <c r="H27" s="14" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I27" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J27" s="14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K27" s="26" t="n"/>
+      <c r="K27" s="24" t="n"/>
     </row>
     <row r="28" ht="32.1" customHeight="1">
       <c r="A28" s="25" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>FN-PAR-03-02-03</t>
+          <t>FN-PAR-03-02-02</t>
         </is>
       </c>
       <c r="C28" s="32" t="inlineStr">
@@ -4929,17 +4929,17 @@
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>이면도로 정비 파라미터</t>
+          <t>주차장 확충 파라미터</t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
         <is>
-          <t>UI-PAR-003-02-1</t>
+          <t>UI-PAR-003-02</t>
         </is>
       </c>
       <c r="G28" s="15" t="inlineStr">
         <is>
-          <t>[이면도로 정비] 대상 지역·정비 방식(상업지역형(주차환경개선지구)/주거지역형(주민참여형))·정비 구간 연장(m) 입력</t>
+          <t>[주차장 확충] 대상 지역·확충 방식(공한지 조성/복층화/신규 조성)·주차면 증설 수 입력 후 시뮬레이션 실행</t>
         </is>
       </c>
       <c r="H28" s="14" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>FN-PAR-03-02-04</t>
+          <t>FN-PAR-03-02-03</t>
         </is>
       </c>
       <c r="C29" s="32" t="inlineStr">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="E29" s="14" t="inlineStr">
         <is>
-          <t>요금제 적용 파라미터</t>
+          <t>이면도로 정비 파라미터</t>
         </is>
       </c>
       <c r="F29" s="14" t="inlineStr">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="G29" s="15" t="inlineStr">
         <is>
-          <t>[요금제 적용] 대상 지역·적용 방식(요금 인상/무료→유료 전환)·적용 급지(전체/1급지(동)/2급지(읍·면), 제주 전체·시 전체 선택 시에만)·인상률(+10/20/30%, 요금 인상 시)</t>
+          <t>[이면도로 정비] 대상 지역·정비 방식(상업지역형(주차환경개선지구)/주거지역형(주민참여형))·정비 구간 연장(m) 입력</t>
         </is>
       </c>
       <c r="H29" s="14" t="inlineStr">
@@ -5010,21 +5010,17 @@
           <t>O</t>
         </is>
       </c>
-      <c r="K29" s="26" t="inlineStr">
-        <is>
-          <t>설계감리 시정 완료</t>
-        </is>
-      </c>
+      <c r="K29" s="26" t="n"/>
     </row>
     <row r="30" ht="32.1" customHeight="1">
       <c r="A30" s="25" t="inlineStr">
         <is>
-          <t>REQ-SFR-003-10</t>
+          <t>REQ-SFR-003-05</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>FN-PAR-03-02-05</t>
+          <t>FN-PAR-03-02-04</t>
         </is>
       </c>
       <c r="C30" s="32" t="inlineStr">
@@ -5032,24 +5028,24 @@
           <t>정책 효과 시뮬레이션</t>
         </is>
       </c>
-      <c r="D30" s="14" t="inlineStr">
-        <is>
-          <t>효과 예측 결과</t>
+      <c r="D30" s="32" t="inlineStr">
+        <is>
+          <t>정책 변수 설정</t>
         </is>
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>효과 예측 KPI 카드</t>
+          <t>요금제 적용 파라미터</t>
         </is>
       </c>
       <c r="F30" s="14" t="inlineStr">
         <is>
-          <t>UI-PAR-003-02</t>
+          <t>UI-PAR-003-02-1</t>
         </is>
       </c>
       <c r="G30" s="15" t="inlineStr">
         <is>
-          <t>효과 예측 KPI: 민원 감소 예측·혼잡도 개선(혼잡 지수 = (정상 이용+불법주차)÷공급 면수). 분석 근거 ⓘ 팝오버(가정값 기반 고지 포함)</t>
+          <t>[요금제 적용] 대상 지역·적용 방식(요금 인상/무료→유료 전환)·적용 급지(전체/1급지(동)/2급지(읍·면), 제주 전체·시 전체 선택 시에만)·인상률(+10/20/30%, 요금 인상 시)</t>
         </is>
       </c>
       <c r="H30" s="14" t="inlineStr">
@@ -5067,180 +5063,184 @@
           <t>O</t>
         </is>
       </c>
-      <c r="K30" s="26" t="n"/>
+      <c r="K30" s="26" t="inlineStr">
+        <is>
+          <t>설계감리 시정 완료</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="32.1" customHeight="1" thickBot="1">
       <c r="A31" s="25" t="inlineStr">
         <is>
+          <t>REQ-SFR-003-10</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>FN-PAR-03-02-05</t>
+        </is>
+      </c>
+      <c r="C31" s="32" t="inlineStr">
+        <is>
+          <t>정책 효과 시뮬레이션</t>
+        </is>
+      </c>
+      <c r="D31" s="14" t="inlineStr">
+        <is>
+          <t>효과 예측 결과</t>
+        </is>
+      </c>
+      <c r="E31" s="14" t="inlineStr">
+        <is>
+          <t>효과 예측 KPI 카드</t>
+        </is>
+      </c>
+      <c r="F31" s="14" t="inlineStr">
+        <is>
+          <t>UI-PAR-003-02</t>
+        </is>
+      </c>
+      <c r="G31" s="15" t="inlineStr">
+        <is>
+          <t>효과 예측 KPI: 민원 감소 예측·혼잡도 개선(혼잡 지수 = (정상 이용+불법주차)÷공급 면수). 분석 근거 ⓘ 팝오버(가정값 기반 고지 포함)</t>
+        </is>
+      </c>
+      <c r="H31" s="14" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I31" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J31" s="14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K31" s="26" t="n"/>
+    </row>
+    <row r="32" ht="32.1" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
           <t>REQ-SFR-003-12</t>
         </is>
       </c>
-      <c r="B31" s="14" t="inlineStr">
+      <c r="B32" s="14" t="inlineStr">
         <is>
           <t>FN-PAR-03-02-06</t>
         </is>
       </c>
-      <c r="C31" s="32" t="inlineStr">
+      <c r="C32" s="32" t="inlineStr">
         <is>
           <t>정책 효과 시뮬레이션</t>
         </is>
       </c>
-      <c r="D31" s="14" t="inlineStr">
+      <c r="D32" s="14" t="inlineStr">
         <is>
           <t>시나리오 비교 테이블</t>
         </is>
       </c>
-      <c r="E31" s="14" t="inlineStr">
+      <c r="E32" s="14" t="inlineStr">
         <is>
           <t>비교 결과 PDF 다운로드</t>
         </is>
       </c>
-      <c r="F31" s="14" t="inlineStr">
+      <c r="F32" s="14" t="inlineStr">
         <is>
           <t>UI-PAR-003-02</t>
         </is>
       </c>
-      <c r="G31" s="15" t="inlineStr">
+      <c r="G32" s="15" t="inlineStr">
         <is>
           <t>시나리오 비교 테이블 — 정책 유형 필터 칩(건수 병기), 체크박스 선택 내보내기(PDF/DOCX, 비교 차트 포함), 행 삭제(확인 모달)</t>
         </is>
       </c>
-      <c r="H31" s="14" t="inlineStr">
+      <c r="H32" s="14" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I31" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J31" s="14" t="inlineStr">
+      <c r="I32" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J32" s="14" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K31" s="26" t="inlineStr">
+      <c r="K32" s="26" t="inlineStr">
         <is>
           <t>설계감리 시정 완료</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="32.1" customHeight="1">
-      <c r="A32" s="23" t="inlineStr">
+    <row r="33" ht="32.1" customHeight="1">
+      <c r="A33" s="23" t="inlineStr">
         <is>
           <t>REQ-SFR-003-04</t>
         </is>
       </c>
-      <c r="B32" s="16" t="inlineStr">
+      <c r="B33" s="16" t="inlineStr">
         <is>
           <t>FN-PAR-03-03-01</t>
         </is>
       </c>
-      <c r="C32" s="16" t="inlineStr">
+      <c r="C33" s="16" t="inlineStr">
         <is>
           <t>생활권 시뮬레이션</t>
         </is>
       </c>
-      <c r="D32" s="16" t="inlineStr">
+      <c r="D33" s="16" t="inlineStr">
         <is>
           <t>생활권 분석 설정</t>
         </is>
       </c>
-      <c r="E32" s="16" t="inlineStr">
+      <c r="E33" s="16" t="inlineStr">
         <is>
           <t>분석 조건 설정 패널</t>
         </is>
       </c>
-      <c r="F32" s="16" t="inlineStr">
+      <c r="F33" s="16" t="inlineStr">
         <is>
           <t>UI-PAR-003-03</t>
         </is>
       </c>
-      <c r="G32" s="17" t="inlineStr">
+      <c r="G33" s="17" t="inlineStr">
         <is>
           <t>분석 내용 선택·분석 지역·분석 기간(최근1/3/6개월·직접 설정·날짜 범위)·격자 크기(1km/500m/250m/100m) 설정 후 생활권 분석 실행</t>
         </is>
       </c>
-      <c r="H32" s="16" t="inlineStr">
+      <c r="H33" s="16" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I32" s="37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J32" s="16" t="inlineStr">
+      <c r="I33" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J33" s="16" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K32" s="24" t="n"/>
-    </row>
-    <row r="33" ht="32.1" customHeight="1">
-      <c r="A33" s="25" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-09</t>
-        </is>
-      </c>
-      <c r="B33" s="14" t="inlineStr">
-        <is>
-          <t>FN-PAR-03-03-02</t>
-        </is>
-      </c>
-      <c r="C33" s="32" t="inlineStr">
-        <is>
-          <t>생활권 시뮬레이션</t>
-        </is>
-      </c>
-      <c r="D33" s="14" t="inlineStr">
-        <is>
-          <t>격자 GIS 지도</t>
-        </is>
-      </c>
-      <c r="E33" s="14" t="inlineStr">
-        <is>
-          <t>격자 히트맵 시각화</t>
-        </is>
-      </c>
-      <c r="F33" s="14" t="inlineStr">
-        <is>
-          <t>UI-PAR-003-03</t>
-        </is>
-      </c>
-      <c r="G33" s="15" t="inlineStr">
-        <is>
-          <t>격자(100m~1km) 기반 GIS 히트맵 — 5단계 색상(심각/경고/주의/보통/낮음). 민원·수급은 백분위, 혼잡도는 절대 기준(지수 1.0=100점)</t>
-        </is>
-      </c>
-      <c r="H33" s="14" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I33" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J33" s="14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K33" s="26" t="n"/>
+      <c r="K33" s="24" t="n"/>
     </row>
     <row r="34" ht="32.1" customHeight="1">
       <c r="A34" s="25" t="inlineStr">
         <is>
-          <t>REQ-SFR-003-04</t>
+          <t>REQ-SFR-003-09</t>
         </is>
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>FN-PAR-03-03-03</t>
+          <t>FN-PAR-03-03-02</t>
         </is>
       </c>
       <c r="C34" s="32" t="inlineStr">
@@ -5248,14 +5248,14 @@
           <t>생활권 시뮬레이션</t>
         </is>
       </c>
-      <c r="D34" s="32" t="inlineStr">
+      <c r="D34" s="14" t="inlineStr">
         <is>
           <t>격자 GIS 지도</t>
         </is>
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>격자 팝업</t>
+          <t>격자 히트맵 시각화</t>
         </is>
       </c>
       <c r="F34" s="14" t="inlineStr">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="G34" s="15" t="inlineStr">
         <is>
-          <t>선택 격자 클릭 시 팝업: 위치명·총 건수·기간· 유형별 건수 상세 표시</t>
+          <t>격자(100m~1km) 기반 GIS 히트맵 — 5단계 색상(심각/경고/주의/보통/낮음). 민원·수급은 백분위, 혼잡도는 절대 기준(지수 1.0=100점)</t>
         </is>
       </c>
       <c r="H34" s="14" t="inlineStr">
@@ -5293,635 +5293,627 @@
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
+          <t>FN-PAR-03-03-03</t>
+        </is>
+      </c>
+      <c r="C35" s="32" t="inlineStr">
+        <is>
+          <t>생활권 시뮬레이션</t>
+        </is>
+      </c>
+      <c r="D35" s="32" t="inlineStr">
+        <is>
+          <t>격자 GIS 지도</t>
+        </is>
+      </c>
+      <c r="E35" s="14" t="inlineStr">
+        <is>
+          <t>격자 팝업</t>
+        </is>
+      </c>
+      <c r="F35" s="14" t="inlineStr">
+        <is>
+          <t>UI-PAR-003-03</t>
+        </is>
+      </c>
+      <c r="G35" s="15" t="inlineStr">
+        <is>
+          <t>선택 격자 클릭 시 팝업: 위치명·총 건수·기간· 유형별 건수 상세 표시</t>
+        </is>
+      </c>
+      <c r="H35" s="14" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I35" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J35" s="14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K35" s="26" t="n"/>
+    </row>
+    <row r="36" ht="32.1" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>REQ-SFR-003-04</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
           <t>FN-PAR-03-03-04</t>
         </is>
       </c>
-      <c r="C35" s="32" t="inlineStr">
+      <c r="C36" s="32" t="inlineStr">
         <is>
           <t>생활권 시뮬레이션</t>
         </is>
       </c>
-      <c r="D35" s="14" t="inlineStr">
+      <c r="D36" s="14" t="inlineStr">
         <is>
           <t>분석 결과 요약</t>
         </is>
       </c>
-      <c r="E35" s="14" t="inlineStr">
+      <c r="E36" s="14" t="inlineStr">
         <is>
           <t>격자 기반 분석 요약 패널</t>
         </is>
       </c>
-      <c r="F35" s="14" t="inlineStr">
+      <c r="F36" s="14" t="inlineStr">
         <is>
           <t>UI-PAR-003-03</t>
         </is>
       </c>
-      <c r="G35" s="15" t="inlineStr">
+      <c r="G36" s="15" t="inlineStr">
         <is>
           <t>총 분석 격자 수 + 5단계 격자 수 요약, 격자 크기 칩·등급 산정 기준 ⓘ 팝오버</t>
         </is>
       </c>
-      <c r="H35" s="14" t="inlineStr">
+      <c r="H36" s="14" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I35" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J35" s="14" t="inlineStr">
+      <c r="I36" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J36" s="14" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K35" s="26" t="inlineStr">
+      <c r="K36" s="26" t="inlineStr">
         <is>
           <t>설계감리 시정 완료</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="32.1" customHeight="1">
-      <c r="A36" s="27" t="inlineStr">
+    <row r="37" ht="32.1" customHeight="1">
+      <c r="A37" s="27" t="inlineStr">
         <is>
           <t>REQ-SFR-003-04</t>
         </is>
       </c>
-      <c r="B36" s="18" t="inlineStr">
+      <c r="B37" s="18" t="inlineStr">
         <is>
           <t>FN-PAR-03-03-05</t>
         </is>
       </c>
-      <c r="C36" s="34" t="inlineStr">
+      <c r="C37" s="34" t="inlineStr">
         <is>
           <t>생활권 시뮬레이션</t>
         </is>
       </c>
-      <c r="D36" s="18" t="inlineStr">
+      <c r="D37" s="18" t="inlineStr">
         <is>
           <t>민원 집중구역 목록</t>
         </is>
       </c>
-      <c r="E36" s="18" t="inlineStr">
+      <c r="E37" s="18" t="inlineStr">
         <is>
           <t>격자 기반 집중구역 Top 목록</t>
         </is>
       </c>
-      <c r="F36" s="18" t="inlineStr">
+      <c r="F37" s="18" t="inlineStr">
         <is>
           <t>UI-PAR-003-03</t>
         </is>
       </c>
-      <c r="G36" s="19" t="inlineStr">
+      <c r="G37" s="19" t="inlineStr">
         <is>
           <t>격자 분석 집중 구역 Top8(심각·경고·주의) 목록 — 동 + 격자 중심 POI 명칭으로 표시. 행 클릭 시 지도 이동·팝업. 혼잡도 모드는 혼잡 점수 안내 ⓘ 제공</t>
         </is>
       </c>
-      <c r="H36" s="18" t="inlineStr">
+      <c r="H37" s="18" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I36" s="39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J36" s="18" t="inlineStr">
+      <c r="I37" s="39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J37" s="18" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K36" s="28" t="n"/>
-    </row>
-    <row r="37" ht="32.1" customHeight="1">
-      <c r="A37" s="23" t="inlineStr">
+      <c r="K37" s="28" t="n"/>
+    </row>
+    <row r="38" ht="32.1" customHeight="1">
+      <c r="A38" s="27" t="inlineStr">
+        <is>
+          <t>REQ-SFR-003-10</t>
+        </is>
+      </c>
+      <c r="B38" s="18" t="inlineStr">
+        <is>
+          <t>FN-PAR-03-03-06</t>
+        </is>
+      </c>
+      <c r="C38" s="34" t="inlineStr">
+        <is>
+          <t>생활권 시뮬레이션</t>
+        </is>
+      </c>
+      <c r="D38" s="18" t="inlineStr">
+        <is>
+          <t>내보내기</t>
+        </is>
+      </c>
+      <c r="E38" s="18" t="inlineStr">
+        <is>
+          <t>PDF/DOCX 내보내기</t>
+        </is>
+      </c>
+      <c r="F38" s="18" t="inlineStr">
+        <is>
+          <t>UI-PAR-003-03</t>
+        </is>
+      </c>
+      <c r="G38" s="19" t="inlineStr">
+        <is>
+          <t>격자 분석 결과(요약·집중 구역 목록)를 PDF/DOCX로 내보내기 — 결과 패널에 배치, 직접 생성 보고서 목록에 추가</t>
+        </is>
+      </c>
+      <c r="H38" s="18" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I38" s="39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J38" s="18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K38" s="28" t="inlineStr"/>
+    </row>
+    <row r="39" ht="32.1" customHeight="1">
+      <c r="A39" s="23" t="inlineStr">
         <is>
           <t>REQ-SFR-003-06</t>
         </is>
       </c>
-      <c r="B37" s="16" t="inlineStr">
+      <c r="B39" s="16" t="inlineStr">
         <is>
           <t>FN-PAR-03-04-01</t>
         </is>
       </c>
-      <c r="C37" s="16" t="inlineStr">
+      <c r="C39" s="16" t="inlineStr">
         <is>
           <t>구역추천</t>
         </is>
       </c>
-      <c r="D37" s="16" t="inlineStr">
+      <c r="D39" s="16" t="inlineStr">
         <is>
           <t>구역 추천 설정</t>
         </is>
       </c>
-      <c r="E37" s="16" t="inlineStr">
+      <c r="E39" s="16" t="inlineStr">
         <is>
           <t>추천 조건 설정 패널</t>
         </is>
       </c>
-      <c r="F37" s="16" t="inlineStr">
+      <c r="F39" s="16" t="inlineStr">
         <is>
           <t>UI-PAR-003-04</t>
         </is>
       </c>
-      <c r="G37" s="17" t="inlineStr">
+      <c r="G39" s="17" t="inlineStr">
         <is>
           <t>분석 내용(요금제 적용/공유주차제 적용)·분석 지역·분석 기간(월 단위) 설정 후 구역 추천 실행</t>
         </is>
       </c>
-      <c r="H37" s="16" t="inlineStr">
+      <c r="H39" s="16" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I37" s="37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J37" s="16" t="inlineStr">
+      <c r="I39" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J39" s="16" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K37" s="24" t="n"/>
-    </row>
-    <row r="38" ht="32.1" customHeight="1">
-      <c r="A38" s="25" t="inlineStr">
+      <c r="K39" s="24" t="n"/>
+    </row>
+    <row r="40" ht="32.1" customHeight="1" thickBot="1">
+      <c r="A40" s="25" t="inlineStr">
         <is>
           <t>REQ-SFR-003-06</t>
         </is>
       </c>
-      <c r="B38" s="14" t="inlineStr">
+      <c r="B40" s="14" t="inlineStr">
         <is>
           <t>FN-PAR-03-04-02</t>
         </is>
       </c>
-      <c r="C38" s="32" t="inlineStr">
+      <c r="C40" s="32" t="inlineStr">
         <is>
           <t>구역추천</t>
         </is>
       </c>
-      <c r="D38" s="14" t="inlineStr">
+      <c r="D40" s="14" t="inlineStr">
         <is>
           <t>구역 추천 GIS</t>
         </is>
       </c>
-      <c r="E38" s="14" t="inlineStr">
+      <c r="E40" s="14" t="inlineStr">
         <is>
           <t>GIS 지도 + 순위 마커</t>
         </is>
       </c>
-      <c r="F38" s="14" t="inlineStr">
+      <c r="F40" s="14" t="inlineStr">
         <is>
           <t>UI-PAR-003-04</t>
         </is>
       </c>
-      <c r="G38" s="15" t="inlineStr">
+      <c r="G40" s="15" t="inlineStr">
         <is>
           <t>제주 전역 GIS 지도에 추천 구역 순위 핀 마커 표시 — 우선순위(높음/중간/낮음) 범례 색상, 핀 클릭 시 상세 팝업</t>
         </is>
       </c>
-      <c r="H38" s="14" t="inlineStr">
+      <c r="H40" s="14" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I38" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J38" s="14" t="inlineStr">
+      <c r="I40" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J40" s="14" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K38" s="26" t="n"/>
-    </row>
-    <row r="39" ht="32.1" customHeight="1">
-      <c r="A39" s="25" t="inlineStr">
+      <c r="K40" s="26" t="n"/>
+    </row>
+    <row r="41" ht="32.1" customHeight="1">
+      <c r="A41" s="25" t="inlineStr">
         <is>
           <t>REQ-SFR-003-06</t>
         </is>
       </c>
-      <c r="B39" s="14" t="inlineStr">
+      <c r="B41" s="14" t="inlineStr">
         <is>
           <t>FN-PAR-03-04-03</t>
         </is>
       </c>
-      <c r="C39" s="32" t="inlineStr">
+      <c r="C41" s="32" t="inlineStr">
         <is>
           <t>구역추천</t>
         </is>
       </c>
-      <c r="D39" s="14" t="inlineStr">
+      <c r="D41" s="14" t="inlineStr">
         <is>
           <t>분석 결과 요약</t>
         </is>
       </c>
-      <c r="E39" s="14" t="inlineStr">
+      <c r="E41" s="14" t="inlineStr">
         <is>
           <t>격자 기반 분석 요약 패널</t>
         </is>
       </c>
-      <c r="F39" s="14" t="inlineStr">
+      <c r="F41" s="14" t="inlineStr">
         <is>
           <t>UI-PAR-003-04</t>
         </is>
       </c>
-      <c r="G39" s="15" t="inlineStr">
+      <c r="G41" s="15" t="inlineStr">
         <is>
           <t>총 분석 격자 수·단계별(심각/경고/주의/양호) 격자 수 요약 패널</t>
         </is>
       </c>
-      <c r="H39" s="14" t="inlineStr">
+      <c r="H41" s="14" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I39" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J39" s="14" t="inlineStr">
+      <c r="I41" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J41" s="14" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K39" s="26" t="n"/>
-    </row>
-    <row r="40" ht="32.1" customHeight="1" thickBot="1">
-      <c r="A40" s="50" t="inlineStr">
+      <c r="K41" s="26" t="n"/>
+    </row>
+    <row r="42" ht="32.1" customHeight="1">
+      <c r="A42" s="50" t="inlineStr">
         <is>
           <t>REQ-SFR-003-06</t>
         </is>
       </c>
-      <c r="B40" s="51" t="inlineStr">
+      <c r="B42" s="51" t="inlineStr">
         <is>
           <t>FN-PAR-03-04-04</t>
         </is>
       </c>
-      <c r="C40" s="52" t="inlineStr">
+      <c r="C42" s="52" t="inlineStr">
         <is>
           <t>구역추천</t>
         </is>
       </c>
-      <c r="D40" s="51" t="inlineStr">
+      <c r="D42" s="51" t="inlineStr">
         <is>
           <t>요금제 적용 추천 구역 순위</t>
         </is>
       </c>
-      <c r="E40" s="51" t="inlineStr">
+      <c r="E42" s="51" t="inlineStr">
         <is>
           <t>구역 추천 결과 Top 목록</t>
         </is>
       </c>
-      <c r="F40" s="51" t="inlineStr">
+      <c r="F42" s="51" t="inlineStr">
         <is>
           <t>UI-PAR-003-04</t>
         </is>
       </c>
-      <c r="G40" s="53" t="inlineStr">
+      <c r="G42" s="53" t="inlineStr">
         <is>
           <t>[요금제 적용] 무료 공영주차장(20면 이상) 대상 — 민원 1건을 300m 내 최근접 후보에 배정, 배정 민원 많은 순(동률 시 면수 순), 우선순위(높음/중간/낮음) 범례. [공유주차제 적용] 검토 지수(월평균 민원·100면당 민원 기반)에 민원 증가 추세 계수를 반영한 추세 반영 지수 순 추천. 순위 산정 기준 ⓘ 팝오버, 목록-지도 연동</t>
         </is>
       </c>
-      <c r="H40" s="51" t="inlineStr">
+      <c r="H42" s="51" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I40" s="54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J40" s="51" t="inlineStr">
+      <c r="I42" s="54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J42" s="51" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K40" s="55" t="n"/>
-    </row>
-    <row r="41" ht="32.1" customHeight="1">
-      <c r="A41" s="23" t="inlineStr">
+      <c r="K42" s="55" t="n"/>
+    </row>
+    <row r="43" ht="32.1" customHeight="1">
+      <c r="A43" s="50" t="inlineStr">
+        <is>
+          <t>REQ-SFR-003-10</t>
+        </is>
+      </c>
+      <c r="B43" s="51" t="inlineStr">
+        <is>
+          <t>FN-PAR-03-04-05</t>
+        </is>
+      </c>
+      <c r="C43" s="52" t="inlineStr">
+        <is>
+          <t>구역추천</t>
+        </is>
+      </c>
+      <c r="D43" s="51" t="inlineStr">
+        <is>
+          <t>내보내기</t>
+        </is>
+      </c>
+      <c r="E43" s="51" t="inlineStr">
+        <is>
+          <t>PDF/DOCX 내보내기</t>
+        </is>
+      </c>
+      <c r="F43" s="51" t="inlineStr">
+        <is>
+          <t>UI-PAR-003-04</t>
+        </is>
+      </c>
+      <c r="G43" s="53" t="inlineStr">
+        <is>
+          <t>추천 결과(순위 표·차트)를 PDF/DOCX로 내보내기 — 결과 패널에 배치, 직접 생성 보고서 목록에 추가</t>
+        </is>
+      </c>
+      <c r="H43" s="51" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I43" s="54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J43" s="51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K43" s="55" t="inlineStr"/>
+    </row>
+    <row r="44" ht="32.1" customHeight="1" thickBot="1">
+      <c r="A44" s="23" t="inlineStr">
         <is>
           <t>REQ-SFR-005-04</t>
         </is>
       </c>
-      <c r="B41" s="16" t="inlineStr">
+      <c r="B44" s="16" t="inlineStr">
         <is>
           <t>FN-PAR-03-05-01</t>
         </is>
       </c>
-      <c r="C41" s="16" t="inlineStr">
+      <c r="C44" s="16" t="inlineStr">
         <is>
           <t>투자우선순위 보드</t>
         </is>
       </c>
-      <c r="D41" s="16" t="inlineStr">
+      <c r="D44" s="16" t="inlineStr">
         <is>
           <t>KPI 요약</t>
         </is>
       </c>
-      <c r="E41" s="16" t="inlineStr">
+      <c r="E44" s="16" t="inlineStr">
         <is>
           <t>KPI 카드</t>
         </is>
       </c>
-      <c r="F41" s="16" t="inlineStr">
+      <c r="F44" s="16" t="inlineStr">
         <is>
           <t>UI-PAR-003-05</t>
         </is>
       </c>
-      <c r="G41" s="17" t="inlineStr">
+      <c r="G44" s="17" t="inlineStr">
         <is>
           <t>분석 대상 주차장 수·높음 우선순위 개소·최근 3개월 사고 건수 KPI 카드 표시</t>
         </is>
       </c>
-      <c r="H41" s="16" t="inlineStr">
+      <c r="H44" s="16" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I41" s="37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J41" s="16" t="inlineStr">
+      <c r="I44" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J44" s="16" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K41" s="24" t="inlineStr">
+      <c r="K44" s="24" t="inlineStr">
         <is>
           <t>설계감리 시정 완료</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="32.1" customHeight="1">
-      <c r="A42" s="25" t="inlineStr">
+    <row r="45" ht="32.1" customHeight="1">
+      <c r="A45" s="25" t="inlineStr">
         <is>
           <t>REQ-SFR-005-04</t>
         </is>
       </c>
-      <c r="B42" s="14" t="inlineStr">
+      <c r="B45" s="14" t="inlineStr">
         <is>
           <t>FN-PAR-03-05-02</t>
         </is>
       </c>
-      <c r="C42" s="31" t="inlineStr">
+      <c r="C45" s="31" t="inlineStr">
         <is>
           <t>투자우선순위 보드</t>
         </is>
       </c>
-      <c r="D42" s="14" t="inlineStr">
+      <c r="D45" s="14" t="inlineStr">
         <is>
           <t>투자우선순위 GIS</t>
         </is>
       </c>
-      <c r="E42" s="14" t="inlineStr">
+      <c r="E45" s="14" t="inlineStr">
         <is>
           <t>GIS 지도 + 우선순위 마커</t>
         </is>
       </c>
-      <c r="F42" s="14" t="inlineStr">
+      <c r="F45" s="14" t="inlineStr">
         <is>
           <t>UI-PAR-003-05</t>
         </is>
       </c>
-      <c r="G42" s="15" t="inlineStr">
+      <c r="G45" s="15" t="inlineStr">
         <is>
           <t>제주 전역 GIS 지도에 공영주차장 위치별 우선순위(높음/중간/낮음) 색상 마커 표시. 선택 시 주차장 상세 팝업(위치·총 면수·준공연도·경과연수)</t>
         </is>
       </c>
-      <c r="H42" s="14" t="inlineStr">
+      <c r="H45" s="14" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I42" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J42" s="14" t="inlineStr">
+      <c r="I45" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J45" s="14" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K42" s="26" t="inlineStr">
+      <c r="K45" s="26" t="inlineStr">
         <is>
           <t>설계감리 시정 완료</t>
         </is>
       </c>
-    </row>
-    <row r="43" ht="32.1" customHeight="1">
-      <c r="A43" s="25" t="inlineStr">
-        <is>
-          <t>REQ-SFR-005-04</t>
-        </is>
-      </c>
-      <c r="B43" s="14" t="inlineStr">
-        <is>
-          <t>FN-PAR-03-05-03</t>
-        </is>
-      </c>
-      <c r="C43" s="31" t="inlineStr">
-        <is>
-          <t>투자우선순위 보드</t>
-        </is>
-      </c>
-      <c r="D43" s="31" t="inlineStr">
-        <is>
-          <t>투자우선순위 GIS</t>
-        </is>
-      </c>
-      <c r="E43" s="14" t="inlineStr">
-        <is>
-          <t>주차장 상세 팝업</t>
-        </is>
-      </c>
-      <c r="F43" s="14" t="inlineStr">
-        <is>
-          <t>UI-PAR-003-05</t>
-        </is>
-      </c>
-      <c r="G43" s="15" t="inlineStr">
-        <is>
-          <t>선택 주차장 팝업: 주차장명·주소·총 면수·준공연도·경과연수 및 안전위험도·민원 빈도·이용 패턴·단속 건수 4개 지표 게이지 표시</t>
-        </is>
-      </c>
-      <c r="H43" s="14" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I43" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J43" s="14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K43" s="26" t="inlineStr">
-        <is>
-          <t>설계감리 시정 완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="32.1" customHeight="1" thickBot="1">
-      <c r="A44" s="27" t="inlineStr">
-        <is>
-          <t>REQ-SFR-005-04</t>
-        </is>
-      </c>
-      <c r="B44" s="18" t="inlineStr">
-        <is>
-          <t>FN-PAR-03-05-04</t>
-        </is>
-      </c>
-      <c r="C44" s="33" t="inlineStr">
-        <is>
-          <t>투자우선순위 보드</t>
-        </is>
-      </c>
-      <c r="D44" s="18" t="inlineStr">
-        <is>
-          <t>투자·보강 우선순위 목록</t>
-        </is>
-      </c>
-      <c r="E44" s="18" t="inlineStr">
-        <is>
-          <t>종합점수 기반 순위 Top 목록</t>
-        </is>
-      </c>
-      <c r="F44" s="18" t="inlineStr">
-        <is>
-          <t>UI-PAR-003-05</t>
-        </is>
-      </c>
-      <c r="G44" s="19" t="inlineStr">
-        <is>
-          <t>종합점수(안전위험도 25%·민원 빈도 25%·이용 패턴 20%·단속 건수 25% — 설정에서 가중치 변경 가능) 기준 우선순위 목록 — 행 클릭 시 지도 확대 이동·팝업, 등급(높음/중간/낮음) 점 표시</t>
-        </is>
-      </c>
-      <c r="H44" s="18" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I44" s="39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J44" s="18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K44" s="28" t="inlineStr">
-        <is>
-          <t>설계감리 시정 완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="32.1" customHeight="1">
-      <c r="A45" s="29" t="inlineStr">
-        <is>
-          <t>REQ-SFR-005-05</t>
-        </is>
-      </c>
-      <c r="B45" s="20" t="inlineStr">
-        <is>
-          <t>FN-PAR-04-01-01</t>
-        </is>
-      </c>
-      <c r="C45" s="20" t="inlineStr">
-        <is>
-          <t>보고서 목록</t>
-        </is>
-      </c>
-      <c r="D45" s="20" t="inlineStr">
-        <is>
-          <t>자동 생성 보고서 목록</t>
-        </is>
-      </c>
-      <c r="E45" s="20" t="inlineStr">
-        <is>
-          <t>자동 생성 보고서 목록</t>
-        </is>
-      </c>
-      <c r="F45" s="20" t="inlineStr">
-        <is>
-          <t>UI-PAR-004-01</t>
-        </is>
-      </c>
-      <c r="G45" s="21" t="inlineStr">
-        <is>
-          <t>자동 생성된 보고서 목록 조회.</t>
-        </is>
-      </c>
-      <c r="H45" s="20" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I45" s="56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J45" s="20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K45" s="30" t="n"/>
     </row>
     <row r="46" ht="32.1" customHeight="1">
       <c r="A46" s="25" t="inlineStr">
         <is>
-          <t>REQ-SFR-003-11</t>
+          <t>REQ-SFR-005-04</t>
         </is>
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>FN-PAR-04-01-02</t>
+          <t>FN-PAR-03-05-03</t>
         </is>
       </c>
       <c r="C46" s="31" t="inlineStr">
         <is>
-          <t>보고서 목록</t>
-        </is>
-      </c>
-      <c r="D46" s="14" t="inlineStr">
-        <is>
-          <t>직접 생성 보고서 목록</t>
+          <t>투자우선순위 보드</t>
+        </is>
+      </c>
+      <c r="D46" s="31" t="inlineStr">
+        <is>
+          <t>투자우선순위 GIS</t>
         </is>
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>직접 생성 보고서 목록</t>
+          <t>주차장 상세 팝업</t>
         </is>
       </c>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>UI-PAR-004-01</t>
+          <t>UI-PAR-003-05</t>
         </is>
       </c>
       <c r="G46" s="15" t="inlineStr">
         <is>
-          <t>직접 생성 보고서 목록 — 보고서명 검색·출처·생성일 필터, 행 삭제(확인 모달)</t>
+          <t>선택 주차장 팝업: 주차장명·주소·총 면수·준공연도·경과연수 및 안전위험도·민원 빈도·이용 패턴·단속 건수 4개 지표 게이지 표시</t>
         </is>
       </c>
       <c r="H46" s="14" t="inlineStr">
@@ -5946,651 +5938,659 @@
       </c>
     </row>
     <row r="47" ht="32.1" customHeight="1">
-      <c r="A47" s="25" t="inlineStr">
-        <is>
-          <t>REQ-SFR-005-05</t>
-        </is>
-      </c>
-      <c r="B47" s="14" t="inlineStr">
-        <is>
-          <t>FN-PAR-04-02-01</t>
-        </is>
-      </c>
-      <c r="C47" s="14" t="inlineStr">
-        <is>
-          <t>보고서 관리</t>
-        </is>
-      </c>
-      <c r="D47" s="14" t="inlineStr">
-        <is>
-          <t>자동 생성 설정 목록</t>
-        </is>
-      </c>
-      <c r="E47" s="14" t="inlineStr">
-        <is>
-          <t>자동 생성 설정 목록</t>
-        </is>
-      </c>
-      <c r="F47" s="14" t="inlineStr">
-        <is>
-          <t>UI-PAR-004-02</t>
-        </is>
-      </c>
-      <c r="G47" s="15" t="inlineStr">
-        <is>
-          <t>보고서 자동 생성 설정에서 확인된 목록 조회, 수정 버튼 클릭시 배포부서/배포주기/배포일자 수정</t>
-        </is>
-      </c>
-      <c r="H47" s="14" t="inlineStr">
+      <c r="A47" s="27" t="inlineStr">
+        <is>
+          <t>REQ-SFR-005-04</t>
+        </is>
+      </c>
+      <c r="B47" s="18" t="inlineStr">
+        <is>
+          <t>FN-PAR-03-05-04</t>
+        </is>
+      </c>
+      <c r="C47" s="33" t="inlineStr">
+        <is>
+          <t>투자우선순위 보드</t>
+        </is>
+      </c>
+      <c r="D47" s="18" t="inlineStr">
+        <is>
+          <t>투자·보강 우선순위 목록</t>
+        </is>
+      </c>
+      <c r="E47" s="18" t="inlineStr">
+        <is>
+          <t>종합점수 기반 순위 Top 목록</t>
+        </is>
+      </c>
+      <c r="F47" s="18" t="inlineStr">
+        <is>
+          <t>UI-PAR-003-05</t>
+        </is>
+      </c>
+      <c r="G47" s="19" t="inlineStr">
+        <is>
+          <t>종합점수(안전위험도 25%·민원 빈도 25%·이용 패턴 20%·단속 건수 25% — 설정에서 가중치 변경 가능) 기준 우선순위 목록 — 행 클릭 시 지도 확대 이동·팝업, 등급(높음/중간/낮음) 점 표시</t>
+        </is>
+      </c>
+      <c r="H47" s="18" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I47" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J47" s="14" t="inlineStr">
+      <c r="I47" s="39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J47" s="18" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K47" s="26" t="n"/>
+      <c r="K47" s="28" t="inlineStr">
+        <is>
+          <t>설계감리 시정 완료</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="32.1" customHeight="1">
       <c r="A48" s="27" t="inlineStr">
         <is>
+          <t>REQ-SFR-003-10</t>
+        </is>
+      </c>
+      <c r="B48" s="18" t="inlineStr">
+        <is>
+          <t>FN-PAR-03-05-05</t>
+        </is>
+      </c>
+      <c r="C48" s="33" t="inlineStr">
+        <is>
+          <t>투자우선순위 보드</t>
+        </is>
+      </c>
+      <c r="D48" s="18" t="inlineStr">
+        <is>
+          <t>내보내기</t>
+        </is>
+      </c>
+      <c r="E48" s="18" t="inlineStr">
+        <is>
+          <t>PDF/DOCX 내보내기</t>
+        </is>
+      </c>
+      <c r="F48" s="18" t="inlineStr">
+        <is>
+          <t>UI-PAR-003-05</t>
+        </is>
+      </c>
+      <c r="G48" s="19" t="inlineStr">
+        <is>
+          <t>우선순위 분석 결과(순위·지표)를 PDF/DOCX로 내보내기 — 결과 패널에 배치, 직접 생성 보고서 목록에 추가</t>
+        </is>
+      </c>
+      <c r="H48" s="18" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I48" s="39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J48" s="18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K48" s="28" t="inlineStr"/>
+    </row>
+    <row r="49" ht="32.1" customHeight="1">
+      <c r="A49" s="29" t="inlineStr">
+        <is>
+          <t>REQ-SFR-005-05</t>
+        </is>
+      </c>
+      <c r="B49" s="20" t="inlineStr">
+        <is>
+          <t>FN-PAR-04-01-01</t>
+        </is>
+      </c>
+      <c r="C49" s="20" t="inlineStr">
+        <is>
+          <t>보고서 목록</t>
+        </is>
+      </c>
+      <c r="D49" s="20" t="inlineStr">
+        <is>
+          <t>자동 생성 보고서 목록</t>
+        </is>
+      </c>
+      <c r="E49" s="20" t="inlineStr">
+        <is>
+          <t>자동 생성 보고서 목록</t>
+        </is>
+      </c>
+      <c r="F49" s="20" t="inlineStr">
+        <is>
+          <t>UI-PAR-004-01</t>
+        </is>
+      </c>
+      <c r="G49" s="21" t="inlineStr">
+        <is>
+          <t>자동 생성된 보고서 목록 조회.</t>
+        </is>
+      </c>
+      <c r="H49" s="20" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I49" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J49" s="20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K49" s="30" t="n"/>
+    </row>
+    <row r="50" ht="32.1" customHeight="1">
+      <c r="A50" s="25" t="inlineStr">
+        <is>
+          <t>REQ-SFR-003-11</t>
+        </is>
+      </c>
+      <c r="B50" s="14" t="inlineStr">
+        <is>
+          <t>FN-PAR-04-01-02</t>
+        </is>
+      </c>
+      <c r="C50" s="31" t="inlineStr">
+        <is>
+          <t>보고서 목록</t>
+        </is>
+      </c>
+      <c r="D50" s="14" t="inlineStr">
+        <is>
+          <t>직접 생성 보고서 목록</t>
+        </is>
+      </c>
+      <c r="E50" s="14" t="inlineStr">
+        <is>
+          <t>직접 생성 보고서 목록</t>
+        </is>
+      </c>
+      <c r="F50" s="14" t="inlineStr">
+        <is>
+          <t>UI-PAR-004-01</t>
+        </is>
+      </c>
+      <c r="G50" s="15" t="inlineStr">
+        <is>
+          <t>직접 생성 보고서 목록 — 보고서명 검색·출처·생성일 필터, 행 삭제(확인 모달)</t>
+        </is>
+      </c>
+      <c r="H50" s="14" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I50" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J50" s="14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K50" s="26" t="inlineStr">
+        <is>
+          <t>설계감리 시정 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="32.1" customHeight="1">
+      <c r="A51" s="25" t="inlineStr">
+        <is>
+          <t>REQ-SFR-005-05</t>
+        </is>
+      </c>
+      <c r="B51" s="14" t="inlineStr">
+        <is>
+          <t>FN-PAR-04-02-01</t>
+        </is>
+      </c>
+      <c r="C51" s="14" t="inlineStr">
+        <is>
+          <t>보고서 관리</t>
+        </is>
+      </c>
+      <c r="D51" s="14" t="inlineStr">
+        <is>
+          <t>자동 생성 설정 목록</t>
+        </is>
+      </c>
+      <c r="E51" s="14" t="inlineStr">
+        <is>
+          <t>자동 생성 설정 목록</t>
+        </is>
+      </c>
+      <c r="F51" s="14" t="inlineStr">
+        <is>
+          <t>UI-PAR-004-02</t>
+        </is>
+      </c>
+      <c r="G51" s="15" t="inlineStr">
+        <is>
+          <t>보고서 자동 생성 설정에서 확인된 목록 조회, 수정 버튼 클릭시 배포부서/배포주기/배포일자 수정</t>
+        </is>
+      </c>
+      <c r="H51" s="14" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I51" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J51" s="14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K51" s="26" t="n"/>
+    </row>
+    <row r="52" ht="32.1" customHeight="1">
+      <c r="A52" s="27" t="inlineStr">
+        <is>
           <t>REQ-SFR-005-06</t>
         </is>
       </c>
-      <c r="B48" s="18" t="inlineStr">
+      <c r="B52" s="18" t="inlineStr">
         <is>
           <t>FN-PAR-04-02-02</t>
         </is>
       </c>
-      <c r="C48" s="33" t="inlineStr">
+      <c r="C52" s="33" t="inlineStr">
         <is>
           <t>보고서 관리</t>
         </is>
       </c>
-      <c r="D48" s="18" t="inlineStr">
+      <c r="D52" s="18" t="inlineStr">
         <is>
           <t>보고서 자동 생성 설정</t>
         </is>
       </c>
-      <c r="E48" s="18" t="inlineStr">
+      <c r="E52" s="18" t="inlineStr">
         <is>
           <t>배포 부서·배포 주기·배포 일자 설정</t>
         </is>
       </c>
-      <c r="F48" s="18" t="inlineStr">
+      <c r="F52" s="18" t="inlineStr">
         <is>
           <t>UI-PAR-004-02</t>
         </is>
       </c>
-      <c r="G48" s="19" t="inlineStr">
+      <c r="G52" s="19" t="inlineStr">
         <is>
           <t>배포 부서, 배포 주기, 배포 일자, 보고서 자동생성버튼</t>
         </is>
       </c>
-      <c r="H48" s="18" t="inlineStr">
+      <c r="H52" s="18" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I48" s="39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J48" s="18" t="inlineStr">
+      <c r="I52" s="39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J52" s="18" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K48" s="28" t="inlineStr">
+      <c r="K52" s="28" t="inlineStr">
         <is>
           <t>REQ-SFR-005-05 
 설계감리 시정 완료</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="32.1" customHeight="1">
-      <c r="A49" s="29" t="inlineStr">
+    <row r="53" ht="32.1" customHeight="1">
+      <c r="A53" s="29" t="inlineStr">
         <is>
           <t>REQ-SFR-003-08</t>
         </is>
       </c>
-      <c r="B49" s="20" t="inlineStr">
+      <c r="B53" s="20" t="inlineStr">
         <is>
           <t>FN-PAR-04-03-01</t>
         </is>
       </c>
-      <c r="C49" s="20" t="inlineStr">
+      <c r="C53" s="20" t="inlineStr">
         <is>
           <t>위험단계 알림 조회</t>
         </is>
       </c>
-      <c r="D49" s="20" t="inlineStr">
+      <c r="D53" s="20" t="inlineStr">
         <is>
           <t>조회 단위 필터</t>
         </is>
       </c>
-      <c r="E49" s="20" t="inlineStr">
+      <c r="E53" s="20" t="inlineStr">
         <is>
           <t>기간 탭 및 상세 필터</t>
         </is>
       </c>
-      <c r="F49" s="20" t="inlineStr">
+      <c r="F53" s="20" t="inlineStr">
         <is>
           <t>UI-PAR-004-03</t>
         </is>
       </c>
-      <c r="G49" s="21" t="inlineStr">
+      <c r="G53" s="21" t="inlineStr">
         <is>
           <t>단계(전체/심각/경고/주의), 지역,기간 선택</t>
         </is>
       </c>
-      <c r="H49" s="20" t="inlineStr">
+      <c r="H53" s="20" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I49" s="56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J49" s="20" t="inlineStr">
+      <c r="I53" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J53" s="20" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K49" s="30" t="n"/>
-    </row>
-    <row r="50" ht="32.1" customHeight="1">
-      <c r="A50" s="25" t="inlineStr">
+      <c r="K53" s="30" t="n"/>
+    </row>
+    <row r="54" ht="32.1" customHeight="1">
+      <c r="A54" s="25" t="inlineStr">
         <is>
           <t>REQ-SFR-003-08</t>
         </is>
       </c>
-      <c r="B50" s="14" t="inlineStr">
+      <c r="B54" s="14" t="inlineStr">
         <is>
           <t>FN-PAR-04-03-02</t>
         </is>
       </c>
-      <c r="C50" s="32" t="inlineStr">
+      <c r="C54" s="32" t="inlineStr">
         <is>
           <t>위험단계 알림 조회</t>
         </is>
       </c>
-      <c r="D50" s="14" t="inlineStr">
+      <c r="D54" s="14" t="inlineStr">
         <is>
           <t>KPI 요약</t>
         </is>
       </c>
-      <c r="E50" s="14" t="inlineStr">
+      <c r="E54" s="14" t="inlineStr">
         <is>
           <t>KPI 카드</t>
         </is>
       </c>
-      <c r="F50" s="14" t="inlineStr">
+      <c r="F54" s="14" t="inlineStr">
         <is>
           <t>UI-PAR-004-03</t>
         </is>
       </c>
-      <c r="G50" s="15" t="inlineStr">
+      <c r="G54" s="15" t="inlineStr">
         <is>
           <t>KPI 카드(조회 알림 건수/위험 알림 건수/누적 민원 수) 표시</t>
         </is>
       </c>
-      <c r="H50" s="14" t="inlineStr">
+      <c r="H54" s="14" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I50" s="14" t="n"/>
-      <c r="J50" s="14" t="inlineStr">
+      <c r="I54" s="14" t="n"/>
+      <c r="J54" s="14" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K50" s="26" t="n"/>
-    </row>
-    <row r="51" ht="32.1" customHeight="1">
-      <c r="A51" s="25" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-08</t>
-        </is>
-      </c>
-      <c r="B51" s="14" t="inlineStr">
-        <is>
-          <t>FN-PAR-04-03-03</t>
-        </is>
-      </c>
-      <c r="C51" s="32" t="inlineStr">
-        <is>
-          <t>위험단계 알림 조회</t>
-        </is>
-      </c>
-      <c r="D51" s="14" t="inlineStr">
-        <is>
-          <t>알림 이력 조회</t>
-        </is>
-      </c>
-      <c r="E51" s="14" t="inlineStr">
-        <is>
-          <t>알림 이력 테이블</t>
-        </is>
-      </c>
-      <c r="F51" s="14" t="inlineStr">
-        <is>
-          <t>UI-PAR-004-03</t>
-        </is>
-      </c>
-      <c r="G51" s="15" t="inlineStr">
-        <is>
-          <t>발송된 위험단계 알림 이력 테이블 — 단계(심각/경고/주의 배지)·지역·내용·일시·민원 수</t>
-        </is>
-      </c>
-      <c r="H51" s="14" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I51" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J51" s="14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K51" s="26" t="n"/>
-    </row>
-    <row r="52" ht="32.1" customHeight="1">
-      <c r="A52" s="25" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-08</t>
-        </is>
-      </c>
-      <c r="B52" s="14" t="inlineStr">
-        <is>
-          <t>FN-PAR-04-04-01</t>
-        </is>
-      </c>
-      <c r="C52" s="14" t="inlineStr">
-        <is>
-          <t>위험단계 알림 관리</t>
-        </is>
-      </c>
-      <c r="D52" s="14" t="inlineStr">
-        <is>
-          <t>알림 기준 설정</t>
-        </is>
-      </c>
-      <c r="E52" s="14" t="inlineStr">
-        <is>
-          <t>단계별 임계값 설정</t>
-        </is>
-      </c>
-      <c r="F52" s="14" t="inlineStr">
-        <is>
-          <t>UI-PAR-004-04</t>
-        </is>
-      </c>
-      <c r="G52" s="15" t="inlineStr">
-        <is>
-          <t>민원 증가율 기준 단계별 알림 기준 카드 — 심각 30%/경고 20%/주의 10% 이상 + 최소 건수 10건 표시. 설정 버튼 → 알림 기준 설정 팝업에서 단계별 증가율(%)·최소 건수 입력 후 저장(서비스 공통 반영, 다음날부터 적용, 민원 건수가 최소 건수 미만이면 알림 미발생)</t>
-        </is>
-      </c>
-      <c r="H52" s="14" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I52" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J52" s="14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K52" s="26" t="n"/>
-    </row>
-    <row r="53" ht="32.1" customHeight="1">
-      <c r="A53" s="27" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-08</t>
-        </is>
-      </c>
-      <c r="B53" s="18" t="inlineStr">
-        <is>
-          <t>FN-PAR-04-04-02</t>
-        </is>
-      </c>
-      <c r="C53" s="34" t="inlineStr">
-        <is>
-          <t>위험단계 알림 관리</t>
-        </is>
-      </c>
-      <c r="D53" s="18" t="inlineStr">
-        <is>
-          <t>수신자 관리</t>
-        </is>
-      </c>
-      <c r="E53" s="18" t="inlineStr">
-        <is>
-          <t>수신자 목록</t>
-        </is>
-      </c>
-      <c r="F53" s="18" t="inlineStr">
-        <is>
-          <t>UI-PAR-004-04</t>
-        </is>
-      </c>
-      <c r="G53" s="19" t="inlineStr">
-        <is>
-          <t>수신자 목록 및 추가 팝업 — 기본 정보는 로그인 사용자 자동 입력(사용자 목록 불러오기 전환 가능), 지역 다중 추가(+버튼·칩), 알림 단계 누적 선택. 삭제 시 확인 모달</t>
-        </is>
-      </c>
-      <c r="H53" s="18" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I53" s="39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J53" s="18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K53" s="28" t="n"/>
-    </row>
-    <row r="54" ht="32.1" customHeight="1">
-      <c r="A54" s="23" t="inlineStr">
-        <is>
-          <t>REQ-SFR-005-07</t>
-        </is>
-      </c>
-      <c r="B54" s="16" t="inlineStr">
-        <is>
-          <t>FN-PAR-05-01-01</t>
-        </is>
-      </c>
-      <c r="C54" s="16" t="inlineStr">
-        <is>
-          <t>AI 어시스턴트</t>
-        </is>
-      </c>
-      <c r="D54" s="16" t="inlineStr">
-        <is>
-          <t>AI 채팅</t>
-        </is>
-      </c>
-      <c r="E54" s="16" t="inlineStr">
-        <is>
-          <t>질문·답변 인터페이스</t>
-        </is>
-      </c>
-      <c r="F54" s="16" t="inlineStr">
-        <is>
-          <t>UI-PAR-005-01</t>
-        </is>
-      </c>
-      <c r="G54" s="17" t="inlineStr">
-        <is>
-          <t>sLLM 기반 대화형 인터페이스. 인사말 그리팅 표시. 자연어 질의응답·파일 첨부 지원. 행정 정보 검색·민원 분석 요청 처리</t>
-        </is>
-      </c>
-      <c r="H54" s="16" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I54" s="16" t="inlineStr">
-        <is>
-          <t>sLLM(EXAONE)</t>
-        </is>
-      </c>
-      <c r="J54" s="16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K54" s="24" t="n"/>
+      <c r="K54" s="26" t="n"/>
     </row>
     <row r="55" ht="32.1" customHeight="1">
       <c r="A55" s="25" t="inlineStr">
         <is>
-          <t>REQ-SFR-005-08</t>
+          <t>REQ-SFR-003-08</t>
         </is>
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>FN-PAR-05-01-02</t>
+          <t>FN-PAR-04-03-03</t>
         </is>
       </c>
       <c r="C55" s="32" t="inlineStr">
         <is>
+          <t>위험단계 알림 조회</t>
+        </is>
+      </c>
+      <c r="D55" s="14" t="inlineStr">
+        <is>
+          <t>알림 이력 조회</t>
+        </is>
+      </c>
+      <c r="E55" s="14" t="inlineStr">
+        <is>
+          <t>알림 이력 테이블</t>
+        </is>
+      </c>
+      <c r="F55" s="14" t="inlineStr">
+        <is>
+          <t>UI-PAR-004-03</t>
+        </is>
+      </c>
+      <c r="G55" s="15" t="inlineStr">
+        <is>
+          <t>발송된 위험단계 알림 이력 테이블 — 단계(심각/경고/주의 배지)·지역·내용·일시·민원 수</t>
+        </is>
+      </c>
+      <c r="H55" s="14" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I55" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J55" s="14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K55" s="26" t="n"/>
+    </row>
+    <row r="56" ht="32.1" customHeight="1">
+      <c r="A56" s="25" t="inlineStr">
+        <is>
+          <t>REQ-SFR-003-08</t>
+        </is>
+      </c>
+      <c r="B56" s="14" t="inlineStr">
+        <is>
+          <t>FN-PAR-04-04-01</t>
+        </is>
+      </c>
+      <c r="C56" s="14" t="inlineStr">
+        <is>
+          <t>위험단계 알림 관리</t>
+        </is>
+      </c>
+      <c r="D56" s="14" t="inlineStr">
+        <is>
+          <t>알림 기준 설정</t>
+        </is>
+      </c>
+      <c r="E56" s="14" t="inlineStr">
+        <is>
+          <t>단계별 임계값 설정</t>
+        </is>
+      </c>
+      <c r="F56" s="14" t="inlineStr">
+        <is>
+          <t>UI-PAR-004-04</t>
+        </is>
+      </c>
+      <c r="G56" s="15" t="inlineStr">
+        <is>
+          <t>민원 증가율 기준 단계별 알림 기준 카드 — 심각 30%/경고 20%/주의 10% 이상 + 최소 건수 10건 표시. 설정 버튼 → 알림 기준 설정 팝업에서 단계별 증가율(%)·최소 건수 입력 후 저장(서비스 공통 반영, 다음날부터 적용, 민원 건수가 최소 건수 미만이면 알림 미발생)</t>
+        </is>
+      </c>
+      <c r="H56" s="14" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I56" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J56" s="14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K56" s="26" t="n"/>
+    </row>
+    <row r="57" ht="32.1" customHeight="1">
+      <c r="A57" s="27" t="inlineStr">
+        <is>
+          <t>REQ-SFR-003-08</t>
+        </is>
+      </c>
+      <c r="B57" s="18" t="inlineStr">
+        <is>
+          <t>FN-PAR-04-04-02</t>
+        </is>
+      </c>
+      <c r="C57" s="34" t="inlineStr">
+        <is>
+          <t>위험단계 알림 관리</t>
+        </is>
+      </c>
+      <c r="D57" s="18" t="inlineStr">
+        <is>
+          <t>수신자 관리</t>
+        </is>
+      </c>
+      <c r="E57" s="18" t="inlineStr">
+        <is>
+          <t>수신자 목록</t>
+        </is>
+      </c>
+      <c r="F57" s="18" t="inlineStr">
+        <is>
+          <t>UI-PAR-004-04</t>
+        </is>
+      </c>
+      <c r="G57" s="19" t="inlineStr">
+        <is>
+          <t>수신자 목록 및 추가 팝업 — 기본 정보는 로그인 사용자 자동 입력(사용자 목록 불러오기 전환 가능), 지역 다중 추가(+버튼·칩), 알림 단계 누적 선택. 삭제 시 확인 모달</t>
+        </is>
+      </c>
+      <c r="H57" s="18" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I57" s="39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J57" s="18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K57" s="28" t="n"/>
+    </row>
+    <row r="58" ht="32.1" customHeight="1">
+      <c r="A58" s="23" t="inlineStr">
+        <is>
+          <t>REQ-SFR-005-07</t>
+        </is>
+      </c>
+      <c r="B58" s="16" t="inlineStr">
+        <is>
+          <t>FN-PAR-05-01-01</t>
+        </is>
+      </c>
+      <c r="C58" s="16" t="inlineStr">
+        <is>
           <t>AI 어시스턴트</t>
         </is>
       </c>
-      <c r="D55" s="32" t="inlineStr">
+      <c r="D58" s="16" t="inlineStr">
         <is>
           <t>AI 채팅</t>
         </is>
       </c>
-      <c r="E55" s="14" t="inlineStr">
-        <is>
-          <t>조례 검색·RAG 연계 답변</t>
-        </is>
-      </c>
-      <c r="F55" s="14" t="inlineStr">
+      <c r="E58" s="16" t="inlineStr">
+        <is>
+          <t>질문·답변 인터페이스</t>
+        </is>
+      </c>
+      <c r="F58" s="16" t="inlineStr">
         <is>
           <t>UI-PAR-005-01</t>
         </is>
       </c>
-      <c r="G55" s="15" t="inlineStr">
-        <is>
-          <t>민원 관련 행정 정보(조례 등) RAG 기반 검색 및 답변 생성. 조례명·원문 보기 링크 카드 형태 응답</t>
-        </is>
-      </c>
-      <c r="H55" s="14" t="inlineStr">
+      <c r="G58" s="17" t="inlineStr">
+        <is>
+          <t>sLLM 기반 대화형 인터페이스. 인사말 그리팅 표시. 자연어 질의응답·파일 첨부 지원. 행정 정보 검색·민원 분석 요청 처리</t>
+        </is>
+      </c>
+      <c r="H58" s="16" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I55" s="14" t="inlineStr">
-        <is>
-          <t>RAG·Vector DB</t>
-        </is>
-      </c>
-      <c r="J55" s="14" t="inlineStr">
+      <c r="I58" s="16" t="inlineStr">
+        <is>
+          <t>sLLM(EXAONE)</t>
+        </is>
+      </c>
+      <c r="J58" s="16" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K55" s="26" t="n"/>
-    </row>
-    <row r="56" ht="32.1" customHeight="1">
-      <c r="A56" s="41" t="inlineStr">
-        <is>
-          <t>REQ-SFR-005-09</t>
-        </is>
-      </c>
-      <c r="B56" s="42" t="inlineStr">
-        <is>
-          <t>FN-PAR-05-05</t>
-        </is>
-      </c>
-      <c r="C56" s="57" t="inlineStr">
-        <is>
-          <t>AI 어시스턴트</t>
-        </is>
-      </c>
-      <c r="D56" s="32" t="inlineStr">
-        <is>
-          <t>AI 채팅</t>
-        </is>
-      </c>
-      <c r="E56" s="42" t="inlineStr">
-        <is>
-          <t>대량 민원 자동 요약</t>
-        </is>
-      </c>
-      <c r="F56" s="42" t="inlineStr">
-        <is>
-          <t>UI-PAR-005-02</t>
-        </is>
-      </c>
-      <c r="G56" s="43" t="inlineStr">
-        <is>
-          <t>대량 민원 내용을 sLLM으로 자동 요약하여 보고용 리포트 생성. AI 응답 하단 리포트 생성 버튼 제공</t>
-        </is>
-      </c>
-      <c r="H56" s="42" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I56" s="42" t="inlineStr">
-        <is>
-          <t>sLLM(EXAONE)</t>
-        </is>
-      </c>
-      <c r="J56" s="42" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K56" s="44" t="n"/>
-    </row>
-    <row r="57" ht="32.1" customHeight="1">
-      <c r="A57" s="41" t="inlineStr">
-        <is>
-          <t>REQ-SFR-005-05</t>
-        </is>
-      </c>
-      <c r="B57" s="42" t="inlineStr">
-        <is>
-          <t>FN-PAR-05-06</t>
-        </is>
-      </c>
-      <c r="C57" s="57" t="inlineStr">
-        <is>
-          <t>AI 어시스턴트</t>
-        </is>
-      </c>
-      <c r="D57" s="32" t="inlineStr">
-        <is>
-          <t>AI 채팅</t>
-        </is>
-      </c>
-      <c r="E57" s="42" t="inlineStr">
-        <is>
-          <t>리포트 미리보기·다운로드</t>
-        </is>
-      </c>
-      <c r="F57" s="42" t="inlineStr">
-        <is>
-          <t>UI-PAR-005-03</t>
-        </is>
-      </c>
-      <c r="G57" s="43" t="inlineStr">
-        <is>
-          <t>AI 생성 민원 요약 보고서 미리보기 및 다운로드(PDF/DOCX)</t>
-        </is>
-      </c>
-      <c r="H57" s="42" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I57" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J57" s="42" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K57" s="44" t="n"/>
-    </row>
-    <row r="58" ht="32.1" customHeight="1">
-      <c r="A58" s="41" t="inlineStr">
-        <is>
-          <t>REQ-SFR-005-01</t>
-        </is>
-      </c>
-      <c r="B58" s="42" t="inlineStr">
-        <is>
-          <t>FN-PAR-05-07</t>
-        </is>
-      </c>
-      <c r="C58" s="57" t="inlineStr">
-        <is>
-          <t>AI 어시스턴트</t>
-        </is>
-      </c>
-      <c r="D58" s="32" t="inlineStr">
-        <is>
-          <t>AI 채팅</t>
-        </is>
-      </c>
-      <c r="E58" s="42" t="inlineStr">
-        <is>
-          <t>융합 데이터 통합 분석 답변</t>
-        </is>
-      </c>
-      <c r="F58" s="42" t="inlineStr">
-        <is>
-          <t>UI-PAR-005-04</t>
-        </is>
-      </c>
-      <c r="G58" s="43" t="inlineStr">
-        <is>
-          <t>민원 데이터와 감시(화재·안전) 데이터를 결합해야 답이 나오는 질문에 AI 에이전트를 호출, 융합 데이터에서 종합 인사이트를 도출하여 AI 어시스턴트 답변으로 표시. 리포트 생성 버튼 제공</t>
-        </is>
-      </c>
-      <c r="H58" s="42" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I58" s="42" t="inlineStr">
-        <is>
-          <t>AI 에이전트</t>
-        </is>
-      </c>
-      <c r="J58" s="42" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K58" s="44" t="n"/>
+      <c r="K58" s="24" t="n"/>
     </row>
     <row r="59" ht="32.1" customHeight="1">
       <c r="A59" s="25" t="inlineStr">
         <is>
-          <t>REQ-SFR-005-07</t>
+          <t>REQ-SFR-005-08</t>
         </is>
       </c>
       <c r="B59" s="14" t="inlineStr">
         <is>
-          <t>FN-PAR-05-02</t>
+          <t>FN-PAR-05-01-02</t>
         </is>
       </c>
       <c r="C59" s="32" t="inlineStr">
@@ -6598,14 +6598,14 @@
           <t>AI 어시스턴트</t>
         </is>
       </c>
-      <c r="D59" s="14" t="inlineStr">
-        <is>
-          <t>최근 대화</t>
+      <c r="D59" s="32" t="inlineStr">
+        <is>
+          <t>AI 채팅</t>
         </is>
       </c>
       <c r="E59" s="14" t="inlineStr">
         <is>
-          <t>대화 이력 목록</t>
+          <t>조례 검색·RAG 연계 답변</t>
         </is>
       </c>
       <c r="F59" s="14" t="inlineStr">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="G59" s="15" t="inlineStr">
         <is>
-          <t>최근 대화 목록(제목·일시) — 항목 클릭 시 대화 재개, 새 대화 버튼, 행별 X 삭제(확인 모달)</t>
+          <t>민원 관련 행정 정보(조례 등) RAG 기반 검색 및 답변 생성. 조례명·원문 보기 링크 카드 형태 응답</t>
         </is>
       </c>
       <c r="H59" s="14" t="inlineStr">
@@ -6623,9 +6623,9 @@
           <t>신규</t>
         </is>
       </c>
-      <c r="I59" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I59" s="14" t="inlineStr">
+        <is>
+          <t>RAG·Vector DB</t>
         </is>
       </c>
       <c r="J59" s="14" t="inlineStr">
@@ -6636,145 +6636,145 @@
       <c r="K59" s="26" t="n"/>
     </row>
     <row r="60" ht="32.1" customHeight="1">
-      <c r="A60" s="25" t="inlineStr">
+      <c r="A60" s="41" t="inlineStr">
         <is>
           <t>REQ-SFR-005-09</t>
         </is>
       </c>
-      <c r="B60" s="14" t="inlineStr">
-        <is>
-          <t>FN-PAR-05-03</t>
-        </is>
-      </c>
-      <c r="C60" s="32" t="inlineStr">
+      <c r="B60" s="42" t="inlineStr">
+        <is>
+          <t>FN-PAR-05-05</t>
+        </is>
+      </c>
+      <c r="C60" s="57" t="inlineStr">
         <is>
           <t>AI 어시스턴트</t>
         </is>
       </c>
-      <c r="D60" s="14" t="inlineStr">
-        <is>
-          <t>최근 리포트</t>
-        </is>
-      </c>
-      <c r="E60" s="14" t="inlineStr">
-        <is>
-          <t>리포트 목록 및 다운로드</t>
-        </is>
-      </c>
-      <c r="F60" s="14" t="inlineStr">
-        <is>
-          <t>UI-PAR-005-01</t>
-        </is>
-      </c>
-      <c r="G60" s="15" t="inlineStr">
-        <is>
-          <t>AI 생성 민원 요약 리포트 목록(제목·날짜) 조회 및 개별 다운로드(↓) 기능</t>
-        </is>
-      </c>
-      <c r="H60" s="14" t="inlineStr">
+      <c r="D60" s="32" t="inlineStr">
+        <is>
+          <t>AI 채팅</t>
+        </is>
+      </c>
+      <c r="E60" s="42" t="inlineStr">
+        <is>
+          <t>대량 민원 자동 요약</t>
+        </is>
+      </c>
+      <c r="F60" s="42" t="inlineStr">
+        <is>
+          <t>UI-PAR-005-02</t>
+        </is>
+      </c>
+      <c r="G60" s="43" t="inlineStr">
+        <is>
+          <t>대량 민원 내용을 sLLM으로 자동 요약하여 보고용 리포트 생성. AI 응답 하단 리포트 생성 버튼 제공</t>
+        </is>
+      </c>
+      <c r="H60" s="42" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I60" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J60" s="14" t="inlineStr">
+      <c r="I60" s="42" t="inlineStr">
+        <is>
+          <t>sLLM(EXAONE)</t>
+        </is>
+      </c>
+      <c r="J60" s="42" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K60" s="26" t="n"/>
+      <c r="K60" s="44" t="n"/>
     </row>
     <row r="61" ht="32.1" customHeight="1">
-      <c r="A61" s="50" t="inlineStr">
-        <is>
-          <t>REQ-SFR-005-07</t>
-        </is>
-      </c>
-      <c r="B61" s="51" t="inlineStr">
-        <is>
-          <t>FN-PAR-05-04</t>
-        </is>
-      </c>
-      <c r="C61" s="52" t="inlineStr">
+      <c r="A61" s="41" t="inlineStr">
+        <is>
+          <t>REQ-SFR-005-05</t>
+        </is>
+      </c>
+      <c r="B61" s="42" t="inlineStr">
+        <is>
+          <t>FN-PAR-05-06</t>
+        </is>
+      </c>
+      <c r="C61" s="57" t="inlineStr">
         <is>
           <t>AI 어시스턴트</t>
         </is>
       </c>
-      <c r="D61" s="51" t="inlineStr">
-        <is>
-          <t>자주 하는 질문(FAQ)</t>
-        </is>
-      </c>
-      <c r="E61" s="51" t="inlineStr">
-        <is>
-          <t>FAQ 목록</t>
-        </is>
-      </c>
-      <c r="F61" s="14" t="inlineStr">
-        <is>
-          <t>UI-PAR-005-01</t>
-        </is>
-      </c>
-      <c r="G61" s="53" t="inlineStr">
-        <is>
-          <t>이번 달 민원 현황 요약·불법주차 단속 관련 행정 절차·공유주차제 도입 요건 등 자주 사용 질문 목록. 클릭 시 입력창 자동 입력</t>
-        </is>
-      </c>
-      <c r="H61" s="51" t="inlineStr">
+      <c r="D61" s="32" t="inlineStr">
+        <is>
+          <t>AI 채팅</t>
+        </is>
+      </c>
+      <c r="E61" s="42" t="inlineStr">
+        <is>
+          <t>리포트 미리보기·다운로드</t>
+        </is>
+      </c>
+      <c r="F61" s="42" t="inlineStr">
+        <is>
+          <t>UI-PAR-005-03</t>
+        </is>
+      </c>
+      <c r="G61" s="43" t="inlineStr">
+        <is>
+          <t>AI 생성 민원 요약 보고서 미리보기 및 다운로드(PDF/DOCX)</t>
+        </is>
+      </c>
+      <c r="H61" s="42" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I61" s="54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J61" s="51" t="inlineStr">
+      <c r="I61" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J61" s="42" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K61" s="55" t="n"/>
+      <c r="K61" s="44" t="n"/>
     </row>
     <row r="62" ht="30.95" customHeight="1">
       <c r="A62" s="41" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>REQ-SFR-005-01</t>
         </is>
       </c>
       <c r="B62" s="42" t="inlineStr">
         <is>
-          <t>FN-PAR-06-01</t>
-        </is>
-      </c>
-      <c r="C62" s="32" t="inlineStr">
-        <is>
-          <t>설정</t>
-        </is>
-      </c>
-      <c r="D62" s="42" t="inlineStr">
-        <is>
-          <t>메뉴 권한 관리</t>
+          <t>FN-PAR-05-07</t>
+        </is>
+      </c>
+      <c r="C62" s="57" t="inlineStr">
+        <is>
+          <t>AI 어시스턴트</t>
+        </is>
+      </c>
+      <c r="D62" s="32" t="inlineStr">
+        <is>
+          <t>AI 채팅</t>
         </is>
       </c>
       <c r="E62" s="42" t="inlineStr">
         <is>
-          <t>메뉴별 권한 그룹 지정</t>
+          <t>융합 데이터 통합 분석 답변</t>
         </is>
       </c>
       <c r="F62" s="42" t="inlineStr">
         <is>
-          <t>UI-PAR-006-01</t>
+          <t>UI-PAR-005-04</t>
         </is>
       </c>
       <c r="G62" s="43" t="inlineStr">
         <is>
-          <t>메뉴별 권한 그룹 지정 — 시스템 관리자 항상 허용(해제 불가), 일반 사용자는 관리 메뉴 부여 불가, 서비스 관리자 해제 시 일반 사용자 동시 해제</t>
+          <t>민원 데이터와 감시(화재·안전) 데이터를 결합해야 답이 나오는 질문에 AI 에이전트를 호출, 융합 데이터에서 종합 인사이트를 도출하여 AI 어시스턴트 답변으로 표시. 리포트 생성 버튼 제공</t>
         </is>
       </c>
       <c r="H62" s="42" t="inlineStr">
@@ -6784,7 +6784,7 @@
       </c>
       <c r="I62" s="42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AI 에이전트</t>
         </is>
       </c>
       <c r="J62" s="42" t="inlineStr">
@@ -6792,683 +6792,895 @@
           <t>O</t>
         </is>
       </c>
-      <c r="K62" s="44" t="inlineStr">
-        <is>
-          <t>관리자</t>
-        </is>
-      </c>
+      <c r="K62" s="44" t="n"/>
     </row>
     <row r="63" ht="30.95" customHeight="1">
-      <c r="A63" s="41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B63" s="42" t="inlineStr">
-        <is>
-          <t>FN-PAR-06-02</t>
-        </is>
-      </c>
-      <c r="C63" s="31" t="inlineStr">
-        <is>
-          <t>설정</t>
-        </is>
-      </c>
-      <c r="D63" s="42" t="inlineStr">
-        <is>
-          <t>메뉴 권한 관리</t>
-        </is>
-      </c>
-      <c r="E63" s="42" t="inlineStr">
-        <is>
-          <t>권한 저장</t>
-        </is>
-      </c>
-      <c r="F63" s="42" t="inlineStr">
-        <is>
-          <t>UI-PAR-006-01</t>
-        </is>
-      </c>
-      <c r="G63" s="43" t="inlineStr">
-        <is>
-          <t>메뉴별 권한 설정 저장(메뉴 단위 저장)</t>
-        </is>
-      </c>
-      <c r="H63" s="42" t="inlineStr">
+      <c r="A63" s="25" t="inlineStr">
+        <is>
+          <t>REQ-SFR-005-07</t>
+        </is>
+      </c>
+      <c r="B63" s="14" t="inlineStr">
+        <is>
+          <t>FN-PAR-05-02</t>
+        </is>
+      </c>
+      <c r="C63" s="32" t="inlineStr">
+        <is>
+          <t>AI 어시스턴트</t>
+        </is>
+      </c>
+      <c r="D63" s="14" t="inlineStr">
+        <is>
+          <t>최근 대화</t>
+        </is>
+      </c>
+      <c r="E63" s="14" t="inlineStr">
+        <is>
+          <t>대화 이력 목록</t>
+        </is>
+      </c>
+      <c r="F63" s="14" t="inlineStr">
+        <is>
+          <t>UI-PAR-005-01</t>
+        </is>
+      </c>
+      <c r="G63" s="15" t="inlineStr">
+        <is>
+          <t>최근 대화 목록(제목·일시) — 항목 클릭 시 대화 재개, 새 대화 버튼, 행별 X 삭제(확인 모달)</t>
+        </is>
+      </c>
+      <c r="H63" s="14" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I63" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J63" s="42" t="inlineStr">
+      <c r="I63" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J63" s="14" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K63" s="44" t="inlineStr">
-        <is>
-          <t>관리자</t>
-        </is>
-      </c>
+      <c r="K63" s="26" t="n"/>
     </row>
     <row r="64" ht="30.95" customHeight="1">
-      <c r="A64" s="41" t="inlineStr">
-        <is>
-          <t>REQ-SFR-005-10</t>
-        </is>
-      </c>
-      <c r="B64" s="42" t="inlineStr">
-        <is>
-          <t>FN-PAR-06-03</t>
-        </is>
-      </c>
-      <c r="C64" s="31" t="inlineStr">
-        <is>
-          <t>설정</t>
-        </is>
-      </c>
-      <c r="D64" s="42" t="inlineStr">
-        <is>
-          <t>분석 지표 가중치 설정</t>
-        </is>
-      </c>
-      <c r="E64" s="42" t="inlineStr">
-        <is>
-          <t>종합점수 가중치</t>
-        </is>
-      </c>
-      <c r="F64" s="42" t="inlineStr">
-        <is>
-          <t>UI-PAR-006-02</t>
-        </is>
-      </c>
-      <c r="G64" s="43" t="inlineStr">
-        <is>
-          <t>집중구역 분석/구역 추천/투자·보강 우선순위 3개 모델의 가중치 조정(합 100% 검증)</t>
-        </is>
-      </c>
-      <c r="H64" s="42" t="inlineStr">
+      <c r="A64" s="25" t="inlineStr">
+        <is>
+          <t>REQ-SFR-005-09</t>
+        </is>
+      </c>
+      <c r="B64" s="14" t="inlineStr">
+        <is>
+          <t>FN-PAR-05-03</t>
+        </is>
+      </c>
+      <c r="C64" s="32" t="inlineStr">
+        <is>
+          <t>AI 어시스턴트</t>
+        </is>
+      </c>
+      <c r="D64" s="14" t="inlineStr">
+        <is>
+          <t>최근 리포트</t>
+        </is>
+      </c>
+      <c r="E64" s="14" t="inlineStr">
+        <is>
+          <t>리포트 목록 및 다운로드</t>
+        </is>
+      </c>
+      <c r="F64" s="14" t="inlineStr">
+        <is>
+          <t>UI-PAR-005-01</t>
+        </is>
+      </c>
+      <c r="G64" s="15" t="inlineStr">
+        <is>
+          <t>AI 생성 민원 요약 리포트 목록(제목·날짜) 조회 및 개별 다운로드(↓) 기능</t>
+        </is>
+      </c>
+      <c r="H64" s="14" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I64" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J64" s="42" t="inlineStr">
+      <c r="I64" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J64" s="14" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K64" s="44" t="inlineStr">
-        <is>
-          <t>관리자</t>
-        </is>
-      </c>
+      <c r="K64" s="26" t="n"/>
     </row>
     <row r="65" ht="30.95" customHeight="1">
-      <c r="A65" s="41" t="inlineStr">
-        <is>
-          <t>REQ-SFR-005-10</t>
-        </is>
-      </c>
-      <c r="B65" s="42" t="inlineStr">
-        <is>
-          <t>FN-PAR-06-04</t>
-        </is>
-      </c>
-      <c r="C65" s="31" t="inlineStr">
-        <is>
-          <t>설정</t>
-        </is>
-      </c>
-      <c r="D65" s="42" t="inlineStr">
-        <is>
-          <t>분석 지표 가중치 설정</t>
-        </is>
-      </c>
-      <c r="E65" s="42" t="inlineStr">
-        <is>
-          <t>설정 변경 이력</t>
-        </is>
-      </c>
-      <c r="F65" s="42" t="inlineStr">
-        <is>
-          <t>UI-PAR-006-02</t>
-        </is>
-      </c>
-      <c r="G65" s="43" t="inlineStr">
-        <is>
-          <t>변경일시, 변경자, 변경 항목, 변경 내용에 대한 목록 조회</t>
-        </is>
-      </c>
-      <c r="H65" s="42" t="inlineStr">
+      <c r="A65" s="50" t="inlineStr">
+        <is>
+          <t>REQ-SFR-005-07</t>
+        </is>
+      </c>
+      <c r="B65" s="51" t="inlineStr">
+        <is>
+          <t>FN-PAR-05-04</t>
+        </is>
+      </c>
+      <c r="C65" s="52" t="inlineStr">
+        <is>
+          <t>AI 어시스턴트</t>
+        </is>
+      </c>
+      <c r="D65" s="51" t="inlineStr">
+        <is>
+          <t>자주 하는 질문(FAQ)</t>
+        </is>
+      </c>
+      <c r="E65" s="51" t="inlineStr">
+        <is>
+          <t>FAQ 목록</t>
+        </is>
+      </c>
+      <c r="F65" s="14" t="inlineStr">
+        <is>
+          <t>UI-PAR-005-01</t>
+        </is>
+      </c>
+      <c r="G65" s="53" t="inlineStr">
+        <is>
+          <t>이번 달 민원 현황 요약·불법주차 단속 관련 행정 절차·공유주차제 도입 요건 등 자주 사용 질문 목록. 클릭 시 입력창 자동 입력</t>
+        </is>
+      </c>
+      <c r="H65" s="51" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I65" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J65" s="42" t="inlineStr">
+      <c r="I65" s="54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J65" s="51" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K65" s="44" t="inlineStr">
-        <is>
-          <t>관리자</t>
-        </is>
-      </c>
+      <c r="K65" s="55" t="n"/>
     </row>
     <row r="66" ht="30.95" customHeight="1">
       <c r="A66" s="41" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B66" s="42" t="inlineStr">
+        <is>
+          <t>FN-PAR-06-01</t>
+        </is>
+      </c>
+      <c r="C66" s="32" t="inlineStr">
+        <is>
+          <t>설정</t>
+        </is>
+      </c>
+      <c r="D66" s="42" t="inlineStr">
+        <is>
+          <t>메뉴 권한 관리</t>
+        </is>
+      </c>
+      <c r="E66" s="42" t="inlineStr">
+        <is>
+          <t>메뉴별 권한 그룹 지정</t>
+        </is>
+      </c>
+      <c r="F66" s="42" t="inlineStr">
+        <is>
+          <t>UI-PAR-006-01</t>
+        </is>
+      </c>
+      <c r="G66" s="43" t="inlineStr">
+        <is>
+          <t>메뉴별 권한 그룹 지정 — 시스템 관리자 항상 허용(해제 불가), 일반 사용자는 관리 메뉴 부여 불가, 서비스 관리자 해제 시 일반 사용자 동시 해제</t>
+        </is>
+      </c>
+      <c r="H66" s="42" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I66" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J66" s="42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K66" s="44" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="30.95" customHeight="1">
+      <c r="A67" s="41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B67" s="42" t="inlineStr">
+        <is>
+          <t>FN-PAR-06-02</t>
+        </is>
+      </c>
+      <c r="C67" s="31" t="inlineStr">
+        <is>
+          <t>설정</t>
+        </is>
+      </c>
+      <c r="D67" s="42" t="inlineStr">
+        <is>
+          <t>메뉴 권한 관리</t>
+        </is>
+      </c>
+      <c r="E67" s="42" t="inlineStr">
+        <is>
+          <t>권한 저장</t>
+        </is>
+      </c>
+      <c r="F67" s="42" t="inlineStr">
+        <is>
+          <t>UI-PAR-006-01</t>
+        </is>
+      </c>
+      <c r="G67" s="43" t="inlineStr">
+        <is>
+          <t>메뉴별 권한 설정 저장(메뉴 단위 저장)</t>
+        </is>
+      </c>
+      <c r="H67" s="42" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I67" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J67" s="42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K67" s="44" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="45" customHeight="1">
+      <c r="A68" s="41" t="inlineStr">
+        <is>
           <t>REQ-SFR-005-10</t>
         </is>
       </c>
-      <c r="B66" s="42" t="inlineStr">
+      <c r="B68" s="42" t="inlineStr">
+        <is>
+          <t>FN-PAR-06-03</t>
+        </is>
+      </c>
+      <c r="C68" s="31" t="inlineStr">
+        <is>
+          <t>설정</t>
+        </is>
+      </c>
+      <c r="D68" s="42" t="inlineStr">
+        <is>
+          <t>분석 지표 가중치 설정</t>
+        </is>
+      </c>
+      <c r="E68" s="42" t="inlineStr">
+        <is>
+          <t>종합점수 가중치</t>
+        </is>
+      </c>
+      <c r="F68" s="42" t="inlineStr">
+        <is>
+          <t>UI-PAR-006-02</t>
+        </is>
+      </c>
+      <c r="G68" s="43" t="inlineStr">
+        <is>
+          <t>집중구역 분석/구역 추천/투자·보강 우선순위 3개 모델의 가중치 조정(합 100% 검증)</t>
+        </is>
+      </c>
+      <c r="H68" s="42" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I68" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J68" s="42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K68" s="44" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="30" customHeight="1">
+      <c r="A69" s="41" t="inlineStr">
+        <is>
+          <t>REQ-SFR-005-10</t>
+        </is>
+      </c>
+      <c r="B69" s="42" t="inlineStr">
+        <is>
+          <t>FN-PAR-06-04</t>
+        </is>
+      </c>
+      <c r="C69" s="31" t="inlineStr">
+        <is>
+          <t>설정</t>
+        </is>
+      </c>
+      <c r="D69" s="42" t="inlineStr">
+        <is>
+          <t>분석 지표 가중치 설정</t>
+        </is>
+      </c>
+      <c r="E69" s="42" t="inlineStr">
+        <is>
+          <t>설정 변경 이력</t>
+        </is>
+      </c>
+      <c r="F69" s="42" t="inlineStr">
+        <is>
+          <t>UI-PAR-006-02</t>
+        </is>
+      </c>
+      <c r="G69" s="43" t="inlineStr">
+        <is>
+          <t>변경일시, 변경자, 변경 항목, 변경 내용에 대한 목록 조회</t>
+        </is>
+      </c>
+      <c r="H69" s="42" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I69" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J69" s="42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K69" s="44" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="41" t="inlineStr">
+        <is>
+          <t>REQ-SFR-005-10</t>
+        </is>
+      </c>
+      <c r="B70" s="42" t="inlineStr">
         <is>
           <t>FN-PAR-06-05</t>
         </is>
       </c>
-      <c r="C66" s="31" t="inlineStr">
+      <c r="C70" s="31" t="inlineStr">
         <is>
           <t>설정</t>
         </is>
       </c>
-      <c r="D66" s="42" t="inlineStr">
+      <c r="D70" s="42" t="inlineStr">
         <is>
           <t>분석 지표 가중치 설정</t>
         </is>
       </c>
-      <c r="E66" s="42" t="inlineStr">
+      <c r="E70" s="42" t="inlineStr">
         <is>
           <t>기본값 초기화</t>
         </is>
       </c>
-      <c r="F66" s="42" t="inlineStr">
+      <c r="F70" s="42" t="inlineStr">
         <is>
           <t>UI-PAR-006-02</t>
         </is>
       </c>
-      <c r="G66" s="43" t="inlineStr">
+      <c r="G70" s="43" t="inlineStr">
         <is>
           <t>기존 종합점수 가중치로 초기화</t>
         </is>
       </c>
-      <c r="H66" s="42" t="inlineStr">
+      <c r="H70" s="42" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I66" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J66" s="42" t="inlineStr">
+      <c r="I70" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J70" s="42" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K66" s="44" t="inlineStr">
+      <c r="K70" s="44" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="30.95" customHeight="1">
-      <c r="A67" s="48" t="inlineStr">
+    <row r="71" ht="30" customHeight="1">
+      <c r="A71" s="48" t="inlineStr">
         <is>
           <t>REQ-SFR-005-10</t>
         </is>
       </c>
-      <c r="B67" s="46" t="inlineStr">
+      <c r="B71" s="46" t="inlineStr">
         <is>
           <t>FN-PAR-06-06</t>
         </is>
       </c>
-      <c r="C67" s="33" t="inlineStr">
+      <c r="C71" s="33" t="inlineStr">
         <is>
           <t>설정</t>
         </is>
       </c>
-      <c r="D67" s="46" t="inlineStr">
+      <c r="D71" s="46" t="inlineStr">
         <is>
           <t>분석 지표 가중치 설정</t>
         </is>
       </c>
-      <c r="E67" s="46" t="inlineStr">
+      <c r="E71" s="46" t="inlineStr">
         <is>
           <t>설정 저장</t>
         </is>
       </c>
-      <c r="F67" s="46" t="inlineStr">
+      <c r="F71" s="46" t="inlineStr">
         <is>
           <t>UI-PAR-006-02</t>
         </is>
       </c>
-      <c r="G67" s="47" t="inlineStr">
+      <c r="G71" s="47" t="inlineStr">
         <is>
           <t>변경한 가중치 설정 저장 버튼</t>
         </is>
       </c>
-      <c r="H67" s="46" t="inlineStr">
+      <c r="H71" s="46" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I67" s="46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J67" s="46" t="inlineStr">
+      <c r="I71" s="46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J71" s="46" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K67" s="49" t="inlineStr">
+      <c r="K71" s="49" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="45" customHeight="1">
-      <c r="A68" s="48" t="inlineStr">
+    <row r="72" ht="30.95" customHeight="1" thickBot="1">
+      <c r="A72" s="48" t="inlineStr">
         <is>
           <t>REQ-SFR-003-07</t>
         </is>
       </c>
-      <c r="B68" s="46" t="inlineStr">
+      <c r="B72" s="46" t="inlineStr">
         <is>
           <t>FN-PAR-C01-04</t>
         </is>
       </c>
-      <c r="C68" s="75" t="inlineStr">
+      <c r="C72" s="75" t="inlineStr">
         <is>
           <t>공통</t>
         </is>
       </c>
-      <c r="D68" s="46" t="inlineStr">
+      <c r="D72" s="46" t="inlineStr">
         <is>
           <t>데이터 기준일 안내</t>
         </is>
       </c>
-      <c r="E68" s="46" t="inlineStr">
+      <c r="E72" s="46" t="inlineStr">
         <is>
           <t>데이터 기준일 팝오버</t>
         </is>
       </c>
-      <c r="F68" s="46" t="inlineStr">
+      <c r="F72" s="46" t="inlineStr">
         <is>
           <t>공통</t>
         </is>
       </c>
-      <c r="G68" s="47" t="inlineStr">
+      <c r="G72" s="47" t="inlineStr">
         <is>
           <t>헤더 '최근 갱신' 문구의 ⓘ 호버 시 데이터별 기준일·갱신 주기 팝오버 표시(민원 3종·단속·공영주차장)</t>
         </is>
       </c>
-      <c r="H68" s="46" t="inlineStr">
+      <c r="H72" s="46" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I68" s="46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J68" s="46" t="inlineStr">
+      <c r="I72" s="46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J72" s="46" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K68" s="49" t="inlineStr">
+      <c r="K72" s="49" t="inlineStr">
         <is>
           <t>대시보드·민원현황</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="30" customHeight="1">
-      <c r="A69" s="48" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="48" t="inlineStr">
         <is>
           <t>REQ-SFR-003-10</t>
         </is>
       </c>
-      <c r="B69" s="46" t="inlineStr">
+      <c r="B73" s="46" t="inlineStr">
         <is>
           <t>FN-PAR-C01-05</t>
         </is>
       </c>
-      <c r="C69" s="75" t="inlineStr">
+      <c r="C73" s="75" t="inlineStr">
         <is>
           <t>공통</t>
         </is>
       </c>
-      <c r="D69" s="46" t="inlineStr">
+      <c r="D73" s="46" t="inlineStr">
         <is>
           <t>삭제 확인</t>
         </is>
       </c>
-      <c r="E69" s="46" t="inlineStr">
+      <c r="E73" s="46" t="inlineStr">
         <is>
           <t>삭제 확인 모달</t>
         </is>
       </c>
-      <c r="F69" s="46" t="inlineStr">
+      <c r="F73" s="46" t="inlineStr">
         <is>
           <t>공통</t>
         </is>
       </c>
-      <c r="G69" s="47" t="inlineStr">
+      <c r="G73" s="47" t="inlineStr">
         <is>
           <t>모든 삭제 동작(시나리오·보고서·자동 생성 설정·수신자·최근 대화)에 확인 모달 적용 — '삭제하면 되돌릴 수 없습니다' 경고 및 취소/삭제 버튼</t>
         </is>
       </c>
-      <c r="H69" s="46" t="inlineStr">
+      <c r="H73" s="46" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I69" s="46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J69" s="46" t="inlineStr">
+      <c r="I73" s="46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J73" s="46" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K69" s="49" t="inlineStr"/>
-    </row>
-    <row r="70" ht="30" customHeight="1">
-      <c r="A70" s="29" t="inlineStr">
+      <c r="K73" s="49" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="29" t="inlineStr">
         <is>
           <t>REQ-SFR-003-14</t>
         </is>
       </c>
-      <c r="B70" s="20" t="inlineStr">
+      <c r="B74" s="20" t="inlineStr">
         <is>
           <t>FN-PAR-SYS-01</t>
         </is>
       </c>
-      <c r="C70" s="20" t="n"/>
-      <c r="D70" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E70" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F70" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G70" s="45" t="inlineStr">
+      <c r="C74" s="20" t="n"/>
+      <c r="D74" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E74" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F74" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G74" s="45" t="inlineStr">
         <is>
           <t>분석 모델 재학습은 AI 어시스턴트(sLLM+RAG) 학습으로 대체 수행. 신규 민원 유형·정책 변화·도시 환경 변화 발생 시 조례·정책문서 재색인(Vector DB 갱신), 첨부문서 학습, 대화 이력·FAQ 축적을 통해 지속 고도화. 모델 개선 프로세스는 AI 어시스턴트 운영 절차에 포함</t>
         </is>
       </c>
-      <c r="H70" s="20" t="inlineStr">
+      <c r="H74" s="20" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I70" s="20" t="inlineStr">
+      <c r="I74" s="20" t="inlineStr">
         <is>
           <t>sLLM(EXAONE)·RAG·Vector DB</t>
         </is>
       </c>
-      <c r="J70" s="20" t="inlineStr">
+      <c r="J74" s="20" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K70" s="30" t="inlineStr">
+      <c r="K74" s="30" t="inlineStr">
         <is>
           <t>비화면</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="30" customHeight="1">
-      <c r="A71" s="25" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="25" t="inlineStr">
         <is>
           <t>REQ-SFR-005-02</t>
         </is>
       </c>
-      <c r="B71" s="14" t="inlineStr">
+      <c r="B75" s="14" t="inlineStr">
         <is>
           <t>FN-PAR-SYS-02</t>
         </is>
       </c>
-      <c r="C71" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D71" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E71" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F71" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G71" s="35" t="inlineStr">
+      <c r="C75" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D75" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E75" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F75" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G75" s="35" t="inlineStr">
         <is>
           <t>D-hub에 적제된 통합데이터 활용하여 민원 3종 이상·정책행정문서 12종 이상 데이터의 수집→정제→구조화→적용 전 과정 관리. 데이터 유형별 적용 목적·활용 시나리오 관리</t>
         </is>
       </c>
-      <c r="H71" s="14" t="inlineStr">
+      <c r="H75" s="14" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I71" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J71" s="14" t="inlineStr">
+      <c r="I75" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J75" s="14" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K71" s="26" t="inlineStr">
+      <c r="K75" s="26" t="inlineStr">
         <is>
           <t>비화면</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="30.95" customHeight="1" thickBot="1">
-      <c r="A72" s="25" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="25" t="inlineStr">
         <is>
           <t>REQ-SFR-005-03</t>
         </is>
       </c>
-      <c r="B72" s="14" t="inlineStr">
+      <c r="B76" s="14" t="inlineStr">
         <is>
           <t>FN-PAR-SYS-03</t>
         </is>
       </c>
-      <c r="C72" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D72" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E72" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F72" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G72" s="35" t="inlineStr">
+      <c r="C76" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D76" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E76" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F76" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G76" s="35" t="inlineStr">
         <is>
           <t>비정형 문서·스캔 문서·이미지 기반 행정자료를 AI RPA로 자동 수집하고 AI OCR로 텍스트 추출·정형화·구조화 적재</t>
         </is>
       </c>
-      <c r="H72" s="14" t="inlineStr">
+      <c r="H76" s="14" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I72" s="14" t="inlineStr">
+      <c r="I76" s="14" t="inlineStr">
         <is>
           <t>AI RPA·AI OCR</t>
         </is>
       </c>
-      <c r="J72" s="14" t="inlineStr">
+      <c r="J76" s="14" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K72" s="26" t="inlineStr">
+      <c r="K76" s="26" t="inlineStr">
         <is>
           <t>비화면</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="25" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="25" t="inlineStr">
         <is>
           <t>REQ-SFR-005-01</t>
         </is>
       </c>
-      <c r="B73" s="14" t="inlineStr">
+      <c r="B77" s="14" t="inlineStr">
         <is>
           <t>FN-PAR-SYS-04</t>
         </is>
       </c>
-      <c r="C73" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D73" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E73" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F73" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G73" s="35" t="inlineStr">
+      <c r="C77" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D77" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E77" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F77" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G77" s="35" t="inlineStr">
         <is>
           <t>민원 분석 대응 솔루션과 실시간 공영주차장 감시 대응 솔루션의 수집·분석 데이터를 결합·융합하여 상관관계 분석 및 종합 인사이트 도출. 대시보드·보고서로 반영</t>
         </is>
       </c>
-      <c r="H73" s="14" t="inlineStr">
+      <c r="H77" s="14" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I73" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J73" s="14" t="inlineStr">
+      <c r="I77" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J77" s="14" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K73" s="26" t="inlineStr">
+      <c r="K77" s="26" t="inlineStr">
         <is>
           <t>비화면</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="27" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="27" t="inlineStr">
         <is>
           <t>REQ-SFR-005-10</t>
         </is>
       </c>
-      <c r="B74" s="18" t="inlineStr">
+      <c r="B78" s="18" t="inlineStr">
         <is>
           <t>FN-PAR-SYS-05</t>
         </is>
       </c>
-      <c r="C74" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D74" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E74" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F74" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G74" s="36" t="inlineStr">
+      <c r="C78" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D78" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E78" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F78" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G78" s="36" t="inlineStr">
         <is>
           <t>타 지자체 확산 적용을 위해 데이터 구조·분석 지표·가중치·기능 구성을 지역 여건에 맞게 설정·조정. 오픈 소스 활용. 공통코드 및 지표 가중치 관리</t>
         </is>
       </c>
-      <c r="H74" s="18" t="inlineStr">
+      <c r="H78" s="18" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I74" s="39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J74" s="18" t="inlineStr">
+      <c r="I78" s="39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J78" s="18" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K74" s="28" t="inlineStr">
+      <c r="K78" s="28" t="inlineStr">
         <is>
           <t>비화면</t>
         </is>

--- a/Audit/JJ_PD_IP_A02_기능구조도_v1.5_이노팸.xlsx
+++ b/Audit/JJ_PD_IP_A02_기능구조도_v1.5_이노팸.xlsx
@@ -4568,7 +4568,7 @@
       </c>
       <c r="G21" s="19" t="inlineStr">
         <is>
-          <t>조회 결과(KPI·지도·순위)를 PDF/DOCX로 내보내기 — 직접 생성 보고서 목록에 추가</t>
+          <t>분석 결과를 PDF/DOCX 보고서로 내보내기 — 내보낸 보고서는 보고서 목록의 직접 생성 보고서 목록에 표시</t>
         </is>
       </c>
       <c r="H21" s="18" t="inlineStr">
@@ -4833,7 +4833,7 @@
       </c>
       <c r="G26" s="19" t="inlineStr">
         <is>
-          <t>분석 결과(집중구역 순위·지도)를 PDF/DOCX로 내보내기 — 결과 패널에 배치, 직접 생성 보고서 목록에 추가</t>
+          <t>분석 결과를 PDF/DOCX 보고서로 내보내기 — 내보낸 보고서는 보고서 목록의 직접 생성 보고서 목록에 표시</t>
         </is>
       </c>
       <c r="H26" s="18" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="G38" s="19" t="inlineStr">
         <is>
-          <t>격자 분석 결과(요약·집중 구역 목록)를 PDF/DOCX로 내보내기 — 결과 패널에 배치, 직접 생성 보고서 목록에 추가</t>
+          <t>분석 결과를 PDF/DOCX 보고서로 내보내기 — 내보낸 보고서는 보고서 목록의 직접 생성 보고서 목록에 표시</t>
         </is>
       </c>
       <c r="H38" s="18" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G43" s="53" t="inlineStr">
         <is>
-          <t>추천 결과(순위 표·차트)를 PDF/DOCX로 내보내기 — 결과 패널에 배치, 직접 생성 보고서 목록에 추가</t>
+          <t>분석 결과를 PDF/DOCX 보고서로 내보내기 — 내보낸 보고서는 보고서 목록의 직접 생성 보고서 목록에 표시</t>
         </is>
       </c>
       <c r="H43" s="51" t="inlineStr">
@@ -6027,7 +6027,7 @@
       </c>
       <c r="G48" s="19" t="inlineStr">
         <is>
-          <t>우선순위 분석 결과(순위·지표)를 PDF/DOCX로 내보내기 — 결과 패널에 배치, 직접 생성 보고서 목록에 추가</t>
+          <t>분석 결과를 PDF/DOCX 보고서로 내보내기 — 내보낸 보고서는 보고서 목록의 직접 생성 보고서 목록에 표시</t>
         </is>
       </c>
       <c r="H48" s="18" t="inlineStr">

--- a/Audit/JJ_PD_IP_A02_기능구조도_v1.5_이노팸.xlsx
+++ b/Audit/JJ_PD_IP_A02_기능구조도_v1.5_이노팸.xlsx
@@ -5693,7 +5693,7 @@
       </c>
       <c r="G42" s="53" t="inlineStr">
         <is>
-          <t>[요금제 적용] 무료 공영주차장(20면 이상) 대상 — 민원 1건을 300m 내 최근접 후보에 배정, 배정 민원 많은 순(동률 시 면수 순), 우선순위(높음/중간/낮음) 범례. [공유주차제 적용] 검토 지수(월평균 민원·100면당 민원 기반)에 민원 증가 추세 계수를 반영한 추세 반영 지수 순 추천. 순위 산정 기준 ⓘ 팝오버, 목록-지도 연동</t>
+          <t>민원 증가 추세를 분석하여 요금제·공유주차제 적용 추천 구역 순위 표시 — 산정 기준 ⓘ 팝오버 제공, 목록과 지도 연동</t>
         </is>
       </c>
       <c r="H42" s="51" t="inlineStr">

--- a/Audit/JJ_PD_IP_A02_기능구조도_v1.5_이노팸.xlsx
+++ b/Audit/JJ_PD_IP_A02_기능구조도_v1.5_이노팸.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="38460" yWindow="-21000" windowWidth="39960" windowHeight="28200" tabRatio="710" firstSheet="2" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-50580" yWindow="2360" windowWidth="45860" windowHeight="23080" tabRatio="710" firstSheet="2" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="표지" sheetId="1" state="visible" r:id="rId1"/>
@@ -57,6 +57,139 @@
     <definedName name="\O">'[4]9GNG운반'!#REF!</definedName>
     <definedName name="\P">'[4]9GNG운반'!#REF!</definedName>
     <definedName name="\Q">'[4]9GNG운반'!#REF!</definedName>
+    <definedName name="ㄱ" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="ㄱㄱㄷㄱ">#REF!</definedName>
+    <definedName name="ㄱㅎㄷㄱㅎ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="가" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="개정이력">[6]단계별측정!#REF!</definedName>
+    <definedName name="계획표">#REF!</definedName>
+    <definedName name="공사설명서" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="과업">[7]COST!#REF!</definedName>
+    <definedName name="과업대비표1">#REF!</definedName>
+    <definedName name="국소수_서울">#REF!</definedName>
+    <definedName name="기존프로그램">#REF!</definedName>
+    <definedName name="기준용어">#REF!</definedName>
+    <definedName name="ㄴ" hidden="1">#REF!</definedName>
+    <definedName name="ㄴㄴ">[9]단계별측정!#REF!</definedName>
+    <definedName name="ㄴㄴㄱ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㄴㄹ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㄴ아러" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="나" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="납기1">[11]IN!$B$5</definedName>
+    <definedName name="납기2">[13]IN!$B$5</definedName>
+    <definedName name="납기3">[11]IN!$D$5</definedName>
+    <definedName name="납기4">[13]IN!$D$5</definedName>
+    <definedName name="ㄷ가" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㄷㄷㄷ">#REF!</definedName>
+    <definedName name="다" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="단가">#REF!</definedName>
+    <definedName name="도">#REF!</definedName>
+    <definedName name="두지" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="둑ㅈ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㄹㅇㅁㄴㄹ" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="라" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅁ" hidden="1">#REF!</definedName>
+    <definedName name="ㅁㅁㅁ" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="마" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="문서명">"단위시험 결과서"</definedName>
+    <definedName name="문서번호표시">"Document #: " &amp; DocumentName</definedName>
+    <definedName name="ㅁㄻㄴㄹ" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="ㅂ" hidden="1">#REF!</definedName>
+    <definedName name="ㅂㅂ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="바" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="버전">"Version " &amp; Version</definedName>
+    <definedName name="변경내역" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="보" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="분류">#REF!</definedName>
+    <definedName name="ㅅㅅㅅ" hidden="1">#REF!</definedName>
+    <definedName name="사" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="수" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="수정" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="수정1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="수정2" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="수정3" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="수정4" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="수정5" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="수정6" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="시스템명">"IVR시스템 연계 및 개발"</definedName>
+    <definedName name="신설변경" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="ㅇ45">#REF!</definedName>
+    <definedName name="ㅇ나닐ㄷ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅇㄹㅇ" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="ㅇㄹㅈㄷ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅇㅇㄹㅈㅈ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅇ아" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="ㅇㅀㅇㅁㄹ" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="아" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="아ㅓㄹ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="아ㅓㄹ지" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="아ㅓㅈ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="아ㅓㅗㄹ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="아ㅣㅈ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="아ㅣㅈㅂ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="알람관리">#REF!</definedName>
+    <definedName name="이력">[6]검토측정!#REF!</definedName>
+    <definedName name="이름" hidden="1">#REF!</definedName>
+    <definedName name="이름1">#REF!</definedName>
+    <definedName name="일반현황__2_">#REF!</definedName>
+    <definedName name="일반현황_3">#REF!</definedName>
+    <definedName name="일일대가1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="잊" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅈ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅈㅂㄷㅈㅂㄷ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="자" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="자ㅓㄷ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="재료집계3">#REF!</definedName>
+    <definedName name="전기출력2">[14]ELEC!$B$3:$M$3,[14]ELEC!$B$4:$M$4,[14]ELEC!$B$5:$M$5,[14]ELEC!$B$7:$M$7</definedName>
+    <definedName name="전기출력3">[14]ELEC!$B$3:$M$3,[14]ELEC!$B$6:$M$6,[14]ELEC!$B$8:$M$8</definedName>
+    <definedName name="정" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="제주추가종합수정안" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="중계기현황">#REF!</definedName>
+    <definedName name="지더" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="지두" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="직종">#REF!</definedName>
+    <definedName name="차" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="총괄11" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="충남신설">#REF!</definedName>
+    <definedName name="충북신설">#REF!</definedName>
+    <definedName name="ㅋ">#REF!</definedName>
+    <definedName name="ㅋㅋ">[9]단계별측정!#REF!</definedName>
+    <definedName name="ㅋㅋㅋ">#REF!</definedName>
+    <definedName name="카" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="타" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="특별시방서1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="파" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="표준용어">#REF!</definedName>
+    <definedName name="표준프로세스">#REF!</definedName>
+    <definedName name="프로젝트명">"민원시스템 백업장비 도입 및 노후장비 교체"</definedName>
+    <definedName name="하" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="한" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="합계">#REF!</definedName>
+    <definedName name="협업포탈_1">'[3]예정(3)'!#REF!</definedName>
+    <definedName name="홎ㅅㄱ도" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅏㄷ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅏ도">#REF!</definedName>
+    <definedName name="ㅏ딪" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅏㅇ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅏ아">#REF!</definedName>
+    <definedName name="ㅏ잊" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅏ짇" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅏㅣㄴ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅏㅣㄷ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅓ아ㅣㄷ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅗㄷ">#REF!</definedName>
+    <definedName name="ㅗㅎㄷ">#REF!</definedName>
+    <definedName name="ㅜ다" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅜㅈ다" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅜ자ㅣㅂ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅠ">#REF!</definedName>
+    <definedName name="ㅠㄹㅇ">#REF!</definedName>
+    <definedName name="ㅣ닺" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅣㅇ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅣㅈ다" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅣ잗" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅣ젇" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㄻㄹ" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
     <definedName name="A">#REF!</definedName>
     <definedName name="A000">#REF!</definedName>
     <definedName name="a2121212">'[4]9GNG운반'!#REF!</definedName>
@@ -119,11 +252,11 @@
     <definedName name="EI_first_row">#REF!</definedName>
     <definedName name="EI_Name">#REF!</definedName>
     <definedName name="EI_S">IF( OR(AND(#REF!&lt;2, AND(#REF!&gt;= 1,#REF!&lt;= 50)), AND(AND(#REF!&gt;=2,#REF!&lt;=5), AND(#REF!&gt;= 1,#REF!&lt;= 19)) ),1,0)</definedName>
+    <definedName name="ENG_개체전">#REF!</definedName>
+    <definedName name="ENG_개체후">#REF!</definedName>
     <definedName name="ENG_Data">#REF!</definedName>
     <definedName name="ENG_Data_서울">#REF!</definedName>
     <definedName name="ENG_Data_증설후">#REF!</definedName>
-    <definedName name="ENG_개체전">#REF!</definedName>
-    <definedName name="ENG_개체후">#REF!</definedName>
     <definedName name="ENG11차">#REF!</definedName>
     <definedName name="ENGDATA">#REF!</definedName>
     <definedName name="Entity_List">#REF!</definedName>
@@ -266,139 +399,6 @@
     <definedName name="wte" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="ww" hidden="1">#REF!</definedName>
     <definedName name="zzzzzzzzzzzzzzzzzzz">#REF!</definedName>
-    <definedName name="ㄱ" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="ㄱㄱㄷㄱ">#REF!</definedName>
-    <definedName name="ㄱㅎㄷㄱㅎ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="가" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="개정이력">[6]단계별측정!#REF!</definedName>
-    <definedName name="계획표">#REF!</definedName>
-    <definedName name="공사설명서" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="과업">[7]COST!#REF!</definedName>
-    <definedName name="과업대비표1">#REF!</definedName>
-    <definedName name="국소수_서울">#REF!</definedName>
-    <definedName name="기존프로그램">#REF!</definedName>
-    <definedName name="기준용어">#REF!</definedName>
-    <definedName name="ㄴ" hidden="1">#REF!</definedName>
-    <definedName name="ㄴㄴ">[9]단계별측정!#REF!</definedName>
-    <definedName name="ㄴㄴㄱ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㄴㄹ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㄴ아러" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="나" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="납기1">[11]IN!$B$5</definedName>
-    <definedName name="납기2">[13]IN!$B$5</definedName>
-    <definedName name="납기3">[11]IN!$D$5</definedName>
-    <definedName name="납기4">[13]IN!$D$5</definedName>
-    <definedName name="ㄷ가" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㄷㄷㄷ">#REF!</definedName>
-    <definedName name="다" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="단가">#REF!</definedName>
-    <definedName name="도">#REF!</definedName>
-    <definedName name="두지" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="둑ㅈ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㄹㅇㅁㄴㄹ" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="라" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㄻㄹ" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="ㅁ" hidden="1">#REF!</definedName>
-    <definedName name="ㅁㄻㄴㄹ" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="ㅁㅁㅁ" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="마" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="문서명">"단위시험 결과서"</definedName>
-    <definedName name="문서번호표시">"Document #: " &amp; DocumentName</definedName>
-    <definedName name="ㅂ" hidden="1">#REF!</definedName>
-    <definedName name="ㅂㅂ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="바" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="버전">"Version " &amp; Version</definedName>
-    <definedName name="변경내역" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="보" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="분류">#REF!</definedName>
-    <definedName name="ㅅㅅㅅ" hidden="1">#REF!</definedName>
-    <definedName name="사" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="수" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="수정" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="수정1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="수정2" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="수정3" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="수정4" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="수정5" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="수정6" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="시스템명">"IVR시스템 연계 및 개발"</definedName>
-    <definedName name="신설변경" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="ㅇ45">#REF!</definedName>
-    <definedName name="ㅇ나닐ㄷ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅇㄹㅇ" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="ㅇㄹㅈㄷ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅇㅀㅇㅁㄹ" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="ㅇㅇㄹㅈㅈ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅇ아" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="아" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="아ㅓㄹ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="아ㅓㄹ지" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="아ㅓㅈ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="아ㅓㅗㄹ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="아ㅣㅈ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="아ㅣㅈㅂ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="알람관리">#REF!</definedName>
-    <definedName name="이력">[6]검토측정!#REF!</definedName>
-    <definedName name="이름" hidden="1">#REF!</definedName>
-    <definedName name="이름1">#REF!</definedName>
-    <definedName name="일반현황__2_">#REF!</definedName>
-    <definedName name="일반현황_3">#REF!</definedName>
-    <definedName name="일일대가1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="잊" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅈ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅈㅂㄷㅈㅂㄷ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="자" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="자ㅓㄷ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="재료집계3">#REF!</definedName>
-    <definedName name="전기출력2">[14]ELEC!$B$3:$M$3,[14]ELEC!$B$4:$M$4,[14]ELEC!$B$5:$M$5,[14]ELEC!$B$7:$M$7</definedName>
-    <definedName name="전기출력3">[14]ELEC!$B$3:$M$3,[14]ELEC!$B$6:$M$6,[14]ELEC!$B$8:$M$8</definedName>
-    <definedName name="정" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="제주추가종합수정안" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="중계기현황">#REF!</definedName>
-    <definedName name="지더" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="지두" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="직종">#REF!</definedName>
-    <definedName name="차" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="총괄11" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="충남신설">#REF!</definedName>
-    <definedName name="충북신설">#REF!</definedName>
-    <definedName name="ㅋ">#REF!</definedName>
-    <definedName name="ㅋㅋ">[9]단계별측정!#REF!</definedName>
-    <definedName name="ㅋㅋㅋ">#REF!</definedName>
-    <definedName name="카" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="타" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="특별시방서1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="파" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="표준용어">#REF!</definedName>
-    <definedName name="표준프로세스">#REF!</definedName>
-    <definedName name="프로젝트명">"민원시스템 백업장비 도입 및 노후장비 교체"</definedName>
-    <definedName name="하" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="한" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="합계">#REF!</definedName>
-    <definedName name="협업포탈_1">'[3]예정(3)'!#REF!</definedName>
-    <definedName name="홎ㅅㄱ도" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅏㄷ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅏ도">#REF!</definedName>
-    <definedName name="ㅏ딪" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅏㅇ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅏ아">#REF!</definedName>
-    <definedName name="ㅏ잊" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅏ짇" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅏㅣㄴ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅏㅣㄷ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅓ아ㅣㄷ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅗㄷ">#REF!</definedName>
-    <definedName name="ㅗㅎㄷ">#REF!</definedName>
-    <definedName name="ㅜ다" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅜㅈ다" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅜ자ㅣㅂ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅠ">#REF!</definedName>
-    <definedName name="ㅠㄹㅇ">#REF!</definedName>
-    <definedName name="ㅣ닺" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅣㅇ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅣㅈ다" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅣ잗" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅣ젇" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="_" localSheetId="0">#REF!</definedName>
     <definedName name="__" localSheetId="0">#REF!</definedName>
     <definedName name="_80486SX_25" localSheetId="0">[2]COST!#REF!</definedName>
@@ -415,6 +415,103 @@
     <definedName name="\O" localSheetId="0">'[5]9GNG운반'!#REF!</definedName>
     <definedName name="\P" localSheetId="0">'[5]9GNG운반'!#REF!</definedName>
     <definedName name="\Q" localSheetId="0">'[5]9GNG운반'!#REF!</definedName>
+    <definedName name="ㄱ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="ㄱㅎㄷㄱㅎ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="가" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="계획표" localSheetId="0">#REF!</definedName>
+    <definedName name="공사설명서" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="과업" localSheetId="0">[2]COST!#REF!</definedName>
+    <definedName name="과업대비표1" localSheetId="0">#REF!</definedName>
+    <definedName name="국소수_서울" localSheetId="0">#REF!</definedName>
+    <definedName name="기존프로그램" localSheetId="0">#REF!</definedName>
+    <definedName name="ㄴㄴ" localSheetId="0">[8]단계별측정!#REF!</definedName>
+    <definedName name="ㄴㄴㄱ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㄴㄹ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㄴ아러" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="나" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="납기1" localSheetId="0">[10]IN!$B$5</definedName>
+    <definedName name="납기2" localSheetId="0">[12]IN!$B$5</definedName>
+    <definedName name="납기3" localSheetId="0">[10]IN!$D$5</definedName>
+    <definedName name="납기4" localSheetId="0">[12]IN!$D$5</definedName>
+    <definedName name="ㄷ가" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="다" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="두지" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="둑ㅈ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㄹㅇㅁㄴㄹ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="라" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅁㅁㅁ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="마" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="문서번호표시" localSheetId="0">"Document #: " &amp; DocumentName</definedName>
+    <definedName name="ㅁㄻㄴㄹ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="ㅂㅂ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="바" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="버전" localSheetId="0">"Version " &amp; Version</definedName>
+    <definedName name="변경내역" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="보" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="사" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="수" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="수정" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="수정1" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="수정2" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="수정3" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="수정4" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="수정5" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="수정6" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="신설변경" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="ㅇ나닐ㄷ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅇㄹㅇ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="ㅇㄹㅈㄷ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅇㅇㄹㅈㅈ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅇ아" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="ㅇㅀㅇㅁㄹ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="아" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="아ㅓㄹ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="아ㅓㄹ지" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="아ㅓㅈ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="아ㅓㅗㄹ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="아ㅣㅈ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="아ㅣㅈㅂ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="이름" localSheetId="0" hidden="1">#REF!</definedName>
+    <definedName name="이름1" localSheetId="0">#REF!</definedName>
+    <definedName name="일반현황__2_" localSheetId="0">#REF!</definedName>
+    <definedName name="일일대가1" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="잊" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅈ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅈㅂㄷㅈㅂㄷ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="자" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="자ㅓㄷ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="정" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="제주추가종합수정안" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="지더" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="지두" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="차" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="총괄11" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="ㅋㅋ" localSheetId="0">[8]단계별측정!#REF!</definedName>
+    <definedName name="ㅋㅋㅋ" localSheetId="0">#REF!</definedName>
+    <definedName name="카" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="타" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="특별시방서1" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="파" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="하" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="한" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="홎ㅅㄱ도" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅏㄷ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅏ딪" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅏㅇ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅏ잊" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅏ짇" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅏㅣㄴ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅏㅣㄷ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅓ아ㅣㄷ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅜ다" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅜㅈ다" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅜ자ㅣㅂ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅣ닺" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅣㅇ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅣㅈ다" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅣ잗" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅣ젇" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㄻㄹ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
     <definedName name="A" localSheetId="0">#REF!</definedName>
     <definedName name="A000" localSheetId="0">#REF!</definedName>
     <definedName name="a2121212" localSheetId="0">'[5]9GNG운반'!#REF!</definedName>
@@ -557,103 +654,6 @@
     <definedName name="wrn.aaa." localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="wrn.TEST." localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
     <definedName name="wte" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㄱ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="ㄱㅎㄷㄱㅎ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="가" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="계획표" localSheetId="0">#REF!</definedName>
-    <definedName name="공사설명서" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="과업" localSheetId="0">[2]COST!#REF!</definedName>
-    <definedName name="과업대비표1" localSheetId="0">#REF!</definedName>
-    <definedName name="국소수_서울" localSheetId="0">#REF!</definedName>
-    <definedName name="기존프로그램" localSheetId="0">#REF!</definedName>
-    <definedName name="ㄴㄴ" localSheetId="0">[8]단계별측정!#REF!</definedName>
-    <definedName name="ㄴㄴㄱ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㄴㄹ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㄴ아러" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="나" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="납기1" localSheetId="0">[10]IN!$B$5</definedName>
-    <definedName name="납기2" localSheetId="0">[12]IN!$B$5</definedName>
-    <definedName name="납기3" localSheetId="0">[10]IN!$D$5</definedName>
-    <definedName name="납기4" localSheetId="0">[12]IN!$D$5</definedName>
-    <definedName name="ㄷ가" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="다" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="두지" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="둑ㅈ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㄹㅇㅁㄴㄹ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="라" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㄻㄹ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="ㅁㄻㄴㄹ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="ㅁㅁㅁ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="마" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="문서번호표시" localSheetId="0">"Document #: " &amp; DocumentName</definedName>
-    <definedName name="ㅂㅂ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="바" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="버전" localSheetId="0">"Version " &amp; Version</definedName>
-    <definedName name="변경내역" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="보" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="사" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="수" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="수정" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="수정1" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="수정2" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="수정3" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="수정4" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="수정5" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="수정6" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="신설변경" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="ㅇ나닐ㄷ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅇㄹㅇ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="ㅇㄹㅈㄷ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅇㅀㅇㅁㄹ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="ㅇㅇㄹㅈㅈ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅇ아" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="아" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="아ㅓㄹ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="아ㅓㄹ지" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="아ㅓㅈ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="아ㅓㅗㄹ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="아ㅣㅈ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="아ㅣㅈㅂ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="이름" localSheetId="0" hidden="1">#REF!</definedName>
-    <definedName name="이름1" localSheetId="0">#REF!</definedName>
-    <definedName name="일반현황__2_" localSheetId="0">#REF!</definedName>
-    <definedName name="일일대가1" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="잊" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅈ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅈㅂㄷㅈㅂㄷ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="자" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="자ㅓㄷ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="정" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="제주추가종합수정안" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="지더" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="지두" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="차" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="총괄11" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="ㅋㅋ" localSheetId="0">[8]단계별측정!#REF!</definedName>
-    <definedName name="ㅋㅋㅋ" localSheetId="0">#REF!</definedName>
-    <definedName name="카" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="타" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="특별시방서1" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="파" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="하" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="한" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="홎ㅅㄱ도" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅏㄷ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅏ딪" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅏㅇ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅏ잊" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅏ짇" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅏㅣㄴ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅏㅣㄷ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅓ아ㅣㄷ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅜ다" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅜㅈ다" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅜ자ㅣㅂ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅣ닺" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅣㅇ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅣㅈ다" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅣ잗" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅣ젇" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="_" localSheetId="1">#REF!</definedName>
     <definedName name="__" localSheetId="1">#REF!</definedName>
     <definedName name="_80486SX_25" localSheetId="1">[1]COST!#REF!</definedName>
@@ -662,6 +662,96 @@
     <definedName name="_Table1_Out" localSheetId="1" hidden="1">#REF!</definedName>
     <definedName name="_wo1" localSheetId="1">'[3]예정(3)'!#REF!</definedName>
     <definedName name="\0" localSheetId="1">'[4]9GNG운반'!#REF!</definedName>
+    <definedName name="ㄱ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="ㄱㅎㄷㄱㅎ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="가" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="계획표" localSheetId="1">#REF!</definedName>
+    <definedName name="공사설명서" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="과업" localSheetId="1">[2]COST!#REF!</definedName>
+    <definedName name="과업대비표1" localSheetId="1">#REF!</definedName>
+    <definedName name="국소수_서울" localSheetId="1">#REF!</definedName>
+    <definedName name="기존프로그램" localSheetId="1">#REF!</definedName>
+    <definedName name="ㄴㄴ" localSheetId="1">[8]단계별측정!#REF!</definedName>
+    <definedName name="ㄴㄴㄱ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㄴㄹ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㄴ아러" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="나" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㄷ가" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="다" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="두지" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="둑ㅈ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㄹㅇㅁㄴㄹ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="라" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅁㅁㅁ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="마" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="문서번호표시" localSheetId="1">"Document #: " &amp; DocumentName</definedName>
+    <definedName name="ㅁㄻㄴㄹ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="ㅂㅂ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="바" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="버전" localSheetId="1">"Version " &amp; Version</definedName>
+    <definedName name="변경내역" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="보" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="사" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="수" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="수정" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="수정1" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="수정2" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="수정3" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="수정4" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="수정5" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="수정6" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="신설변경" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="ㅇ나닐ㄷ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅇㄹㅇ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="ㅇㄹㅈㄷ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅇㅇㄹㅈㅈ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅇ아" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="ㅇㅀㅇㅁㄹ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="아" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="아ㅓㄹ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="아ㅓㄹ지" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="아ㅓㅈ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="아ㅓㅗㄹ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="아ㅣㅈ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="아ㅣㅈㅂ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="일일대가1" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="잊" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅈ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅈㅂㄷㅈㅂㄷ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="자" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="자ㅓㄷ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="정" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="제주추가종합수정안" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="지더" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="지두" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="차" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="총괄11" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="ㅋㅋ" localSheetId="1">[8]단계별측정!#REF!</definedName>
+    <definedName name="ㅋㅋㅋ" localSheetId="1">#REF!</definedName>
+    <definedName name="카" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="타" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="특별시방서1" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="파" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="하" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="한" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
+    <definedName name="홎ㅅㄱ도" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅏㄷ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅏ딪" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅏㅇ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅏ잊" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅏ짇" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅏㅣㄴ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅏㅣㄷ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅓ아ㅣㄷ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅜ다" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅜㅈ다" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅜ자ㅣㅂ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅣ닺" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅣㅇ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅣㅈ다" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅣ잗" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㅣ젇" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
+    <definedName name="ㄻㄹ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
     <definedName name="A" localSheetId="1">#REF!</definedName>
     <definedName name="A000" localSheetId="1">#REF!</definedName>
     <definedName name="a2121212" localSheetId="1">'[4]9GNG운반'!#REF!</definedName>
@@ -786,101 +876,11 @@
     <definedName name="wrn.aaa." localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="wrn.TEST." localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
     <definedName name="wte" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㄱ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="ㄱㅎㄷㄱㅎ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="가" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="계획표" localSheetId="1">#REF!</definedName>
-    <definedName name="공사설명서" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="과업" localSheetId="1">[2]COST!#REF!</definedName>
-    <definedName name="과업대비표1" localSheetId="1">#REF!</definedName>
-    <definedName name="국소수_서울" localSheetId="1">#REF!</definedName>
-    <definedName name="기존프로그램" localSheetId="1">#REF!</definedName>
-    <definedName name="ㄴㄴ" localSheetId="1">[8]단계별측정!#REF!</definedName>
-    <definedName name="ㄴㄴㄱ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㄴㄹ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㄴ아러" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="나" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㄷ가" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="다" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="두지" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="둑ㅈ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㄹㅇㅁㄴㄹ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="라" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㄻㄹ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="ㅁㄻㄴㄹ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="ㅁㅁㅁ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="마" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="문서번호표시" localSheetId="1">"Document #: " &amp; DocumentName</definedName>
-    <definedName name="ㅂㅂ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="바" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="버전" localSheetId="1">"Version " &amp; Version</definedName>
-    <definedName name="변경내역" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="보" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="사" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="수" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="수정" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="수정1" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="수정2" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="수정3" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="수정4" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="수정5" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="수정6" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="신설변경" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="ㅇ나닐ㄷ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅇㄹㅇ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="ㅇㄹㅈㄷ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅇㅀㅇㅁㄹ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="ㅇㅇㄹㅈㅈ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅇ아" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="아" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="아ㅓㄹ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="아ㅓㄹ지" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="아ㅓㅈ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="아ㅓㅗㄹ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="아ㅣㅈ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="아ㅣㅈㅂ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="일일대가1" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="잊" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅈ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅈㅂㄷㅈㅂㄷ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="자" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="자ㅓㄷ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="정" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="제주추가종합수정안" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="지더" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="지두" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="차" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="총괄11" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="ㅋㅋ" localSheetId="1">[8]단계별측정!#REF!</definedName>
-    <definedName name="ㅋㅋㅋ" localSheetId="1">#REF!</definedName>
-    <definedName name="카" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="타" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="특별시방서1" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="파" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="하" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="한" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="홎ㅅㄱ도" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅏㄷ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅏ딪" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅏㅇ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅏ잊" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅏ짇" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅏㅣㄴ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅏㅣㄷ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅓ아ㅣㄷ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅜ다" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅜㅈ다" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅜ자ㅣㅂ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅣ닺" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅣㅇ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅣㅈ다" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅣ잗" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="ㅣ젇" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'기능구조도'!$A$3:$K$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'기능구조도'!$1:$3</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'기능구조도'!$C$1:$J$3</definedName>
   </definedNames>
-  <calcPr calcId="191028" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -1462,7 +1462,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="5"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
@@ -1666,12 +1666,20 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1702,17 +1710,13 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="5"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="9">
@@ -3005,63 +3009,63 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:K30"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="17.1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
-    <col width="6.5" customWidth="1" style="61" min="1" max="1"/>
-    <col width="3.875" customWidth="1" style="61" min="2" max="2"/>
-    <col width="9.625" customWidth="1" style="61" min="3" max="4"/>
-    <col width="3.375" customWidth="1" style="61" min="5" max="5"/>
-    <col width="9.625" customWidth="1" style="61" min="6" max="7"/>
-    <col width="3.625" customWidth="1" style="61" min="8" max="8"/>
-    <col width="10.5" customWidth="1" style="61" min="9" max="9"/>
-    <col width="8.375" customWidth="1" style="61" min="10" max="10"/>
-    <col width="7.125" customWidth="1" style="61" min="11" max="11"/>
-    <col width="9" customWidth="1" style="61" min="12" max="12"/>
-    <col width="9" customWidth="1" style="61" min="13" max="16384"/>
+    <col width="6.5" customWidth="1" style="65" min="1" max="1"/>
+    <col width="3.83203125" customWidth="1" style="65" min="2" max="2"/>
+    <col width="9.6640625" customWidth="1" style="65" min="3" max="4"/>
+    <col width="3.33203125" customWidth="1" style="65" min="5" max="5"/>
+    <col width="9.6640625" customWidth="1" style="65" min="6" max="7"/>
+    <col width="3.6640625" customWidth="1" style="65" min="8" max="8"/>
+    <col width="10.5" customWidth="1" style="65" min="9" max="9"/>
+    <col width="8.33203125" customWidth="1" style="65" min="10" max="10"/>
+    <col width="7.1640625" customWidth="1" style="65" min="11" max="11"/>
+    <col width="9" customWidth="1" style="65" min="12" max="13"/>
+    <col width="9" customWidth="1" style="65" min="14" max="16384"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.6" customHeight="1">
+    <row r="2" ht="27.5" customHeight="1" s="60">
       <c r="E2" s="5" t="n"/>
       <c r="F2" s="5" t="n"/>
       <c r="G2" s="5" t="n"/>
-      <c r="H2" s="59" t="inlineStr">
+      <c r="H2" s="62" t="inlineStr">
         <is>
           <t>문서관리번호</t>
         </is>
       </c>
-      <c r="I2" s="71" t="n"/>
-      <c r="J2" s="63" t="inlineStr">
+      <c r="I2" s="63" t="n"/>
+      <c r="J2" s="67" t="inlineStr">
         <is>
           <t>버전</t>
         </is>
       </c>
-      <c r="K2" s="71" t="n"/>
-    </row>
-    <row r="3" ht="27.6" customHeight="1">
+      <c r="K2" s="63" t="n"/>
+    </row>
+    <row r="3" ht="27.5" customHeight="1" s="60">
       <c r="E3" s="5" t="n"/>
       <c r="F3" s="5" t="n"/>
       <c r="G3" s="5" t="n"/>
-      <c r="H3" s="67" t="inlineStr">
+      <c r="H3" s="71" t="inlineStr">
         <is>
           <t>JJ_IP_A02</t>
         </is>
       </c>
-      <c r="I3" s="71" t="n"/>
-      <c r="J3" s="69" t="inlineStr">
+      <c r="I3" s="63" t="n"/>
+      <c r="J3" s="73" t="inlineStr">
         <is>
           <t>v1.5</t>
         </is>
       </c>
-      <c r="K3" s="72" t="n"/>
-    </row>
-    <row r="9" ht="26.25" customHeight="1">
-      <c r="A9" s="66" t="inlineStr">
+      <c r="K3" s="74" t="n"/>
+    </row>
+    <row r="9" ht="26.25" customHeight="1" s="60">
+      <c r="A9" s="70" t="inlineStr">
         <is>
           <t>'25년 제주스마트도시 데이터허브 시범솔루션 발굴사업</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="9.6" customHeight="1">
+    <row r="10" ht="9.5" customHeight="1" s="60">
       <c r="A10" s="6" t="n"/>
       <c r="B10" s="6" t="n"/>
       <c r="C10" s="6" t="n"/>
@@ -3074,14 +3078,14 @@
       <c r="J10" s="6" t="n"/>
       <c r="K10" s="6" t="n"/>
     </row>
-    <row r="11" ht="50.25" customHeight="1">
-      <c r="A11" s="64" t="inlineStr">
+    <row r="11" ht="50.25" customHeight="1" s="60">
+      <c r="A11" s="68" t="inlineStr">
         <is>
           <t>기능구조도</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="1.5" customHeight="1">
+    <row r="12" ht="1.5" customHeight="1" s="60">
       <c r="A12" s="7" t="n"/>
       <c r="B12" s="7" t="n"/>
       <c r="C12" s="7" t="n"/>
@@ -3094,7 +3098,7 @@
       <c r="J12" s="7" t="n"/>
       <c r="K12" s="7" t="n"/>
     </row>
-    <row r="13" ht="9.6" customHeight="1">
+    <row r="13" ht="9.5" customHeight="1" s="60">
       <c r="A13" s="6" t="n"/>
       <c r="B13" s="6" t="n"/>
       <c r="C13" s="6" t="n"/>
@@ -3107,33 +3111,33 @@
       <c r="J13" s="6" t="n"/>
       <c r="K13" s="6" t="n"/>
     </row>
-    <row r="14" ht="24.75" customHeight="1">
-      <c r="A14" s="65" t="inlineStr">
+    <row r="14" ht="24.75" customHeight="1" s="60">
+      <c r="A14" s="69" t="inlineStr">
         <is>
           <t>공영주차장관련민원솔루션</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="43.5" customHeight="1">
-      <c r="B28" s="68" t="n"/>
-      <c r="E28" s="68" t="n"/>
-      <c r="H28" s="62" t="n"/>
-    </row>
-    <row r="29" ht="43.5" customHeight="1">
-      <c r="B29" s="62" t="n"/>
-      <c r="C29" s="60" t="n"/>
-      <c r="E29" s="62" t="n"/>
-      <c r="F29" s="60" t="n"/>
-      <c r="H29" s="62" t="n"/>
-      <c r="I29" s="60" t="n"/>
-    </row>
-    <row r="30" ht="43.5" customHeight="1">
-      <c r="B30" s="62" t="n"/>
-      <c r="C30" s="60" t="n"/>
-      <c r="E30" s="62" t="n"/>
-      <c r="F30" s="60" t="n"/>
-      <c r="H30" s="62" t="n"/>
-      <c r="I30" s="60" t="n"/>
+    <row r="28" ht="43.5" customHeight="1" s="60">
+      <c r="B28" s="72" t="n"/>
+      <c r="E28" s="72" t="n"/>
+      <c r="H28" s="66" t="n"/>
+    </row>
+    <row r="29" ht="43.5" customHeight="1" s="60">
+      <c r="B29" s="66" t="n"/>
+      <c r="C29" s="64" t="n"/>
+      <c r="E29" s="66" t="n"/>
+      <c r="F29" s="64" t="n"/>
+      <c r="H29" s="66" t="n"/>
+      <c r="I29" s="64" t="n"/>
+    </row>
+    <row r="30" ht="43.5" customHeight="1" s="60">
+      <c r="B30" s="66" t="n"/>
+      <c r="C30" s="64" t="n"/>
+      <c r="E30" s="66" t="n"/>
+      <c r="F30" s="64" t="n"/>
+      <c r="H30" s="66" t="n"/>
+      <c r="I30" s="64" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -3142,12 +3146,12 @@
     <mergeCell ref="J3:K3"/>
     <mergeCell ref="E28:G28"/>
     <mergeCell ref="I29:J29"/>
-    <mergeCell ref="C29:D29"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="F30:G30"/>
+    <mergeCell ref="F29:G29"/>
     <mergeCell ref="H28:J28"/>
-    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C29:D29"/>
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="A11:K11"/>
     <mergeCell ref="A14:K14"/>
@@ -3168,24 +3172,24 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A2:E30"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
-    <col width="12" customWidth="1" style="73" min="1" max="1"/>
-    <col width="8.5" customWidth="1" style="73" min="2" max="2"/>
-    <col width="45.5" customWidth="1" style="73" min="3" max="3"/>
-    <col width="8.375" customWidth="1" style="73" min="4" max="5"/>
-    <col width="9" customWidth="1" style="73" min="6" max="6"/>
-    <col width="9" customWidth="1" style="73" min="7" max="16384"/>
+    <col width="12" customWidth="1" style="76" min="1" max="1"/>
+    <col width="8.5" customWidth="1" style="76" min="2" max="2"/>
+    <col width="45.5" customWidth="1" style="76" min="3" max="3"/>
+    <col width="8.33203125" customWidth="1" style="76" min="4" max="5"/>
+    <col width="9" customWidth="1" style="76" min="6" max="7"/>
+    <col width="9" customWidth="1" style="76" min="8" max="16384"/>
   </cols>
   <sheetData>
-    <row r="2" ht="26.25" customHeight="1">
-      <c r="A2" s="70" t="inlineStr">
+    <row r="2" ht="26.25" customHeight="1" s="60">
+      <c r="A2" s="75" t="inlineStr">
         <is>
           <t>개 정 이 력</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="24.75" customHeight="1">
+    <row r="4" ht="24.75" customHeight="1" s="60">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>제 개정일자</t>
@@ -3212,7 +3216,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="24.95" customHeight="1">
+    <row r="5" ht="25" customHeight="1" s="60">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>2026-06-12</t>
@@ -3239,7 +3243,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="24.95" customHeight="1">
+    <row r="6" ht="25" customHeight="1" s="60">
       <c r="A6" s="22" t="n">
         <v>46213</v>
       </c>
@@ -3264,7 +3268,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="24.95" customHeight="1">
+    <row r="7" ht="25" customHeight="1" s="60">
       <c r="A7" s="22" t="n">
         <v>46217</v>
       </c>
@@ -3289,7 +3293,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="24.95" customHeight="1">
+    <row r="8" ht="25" customHeight="1" s="60">
       <c r="A8" s="22" t="n">
         <v>46224</v>
       </c>
@@ -3314,7 +3318,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="24.95" customHeight="1">
+    <row r="9" ht="25" customHeight="1" s="60">
       <c r="A9" s="22" t="n">
         <v>46226</v>
       </c>
@@ -3339,7 +3343,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="24.95" customHeight="1">
+    <row r="10" ht="25" customHeight="1" s="60">
       <c r="A10" s="22" t="n">
         <v>46230</v>
       </c>
@@ -3364,7 +3368,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="24.75" customHeight="1">
+    <row r="11" ht="24.75" customHeight="1" s="60">
       <c r="A11" s="22" t="n">
         <v>46322</v>
       </c>
@@ -3385,134 +3389,134 @@
       </c>
       <c r="E11" s="3" t="n"/>
     </row>
-    <row r="12" ht="24.75" customHeight="1">
-      <c r="A12" s="74" t="n"/>
+    <row r="12" ht="24.75" customHeight="1" s="60">
+      <c r="A12" s="77" t="n"/>
       <c r="B12" s="3" t="n"/>
       <c r="C12" s="3" t="n"/>
       <c r="D12" s="3" t="n"/>
       <c r="E12" s="3" t="n"/>
     </row>
-    <row r="13" ht="24.75" customHeight="1">
-      <c r="A13" s="74" t="n"/>
+    <row r="13" ht="24.75" customHeight="1" s="60">
+      <c r="A13" s="77" t="n"/>
       <c r="B13" s="3" t="n"/>
       <c r="C13" s="3" t="n"/>
       <c r="D13" s="3" t="n"/>
       <c r="E13" s="3" t="n"/>
     </row>
-    <row r="14" ht="24.75" customHeight="1">
-      <c r="A14" s="74" t="n"/>
+    <row r="14" ht="24.75" customHeight="1" s="60">
+      <c r="A14" s="77" t="n"/>
       <c r="B14" s="3" t="n"/>
       <c r="C14" s="3" t="n"/>
       <c r="D14" s="3" t="n"/>
       <c r="E14" s="3" t="n"/>
     </row>
-    <row r="15" ht="24.75" customHeight="1">
-      <c r="A15" s="74" t="n"/>
+    <row r="15" ht="24.75" customHeight="1" s="60">
+      <c r="A15" s="77" t="n"/>
       <c r="B15" s="3" t="n"/>
       <c r="C15" s="3" t="n"/>
       <c r="D15" s="3" t="n"/>
       <c r="E15" s="3" t="n"/>
     </row>
-    <row r="16" ht="24.75" customHeight="1">
-      <c r="A16" s="74" t="n"/>
+    <row r="16" ht="24.75" customHeight="1" s="60">
+      <c r="A16" s="77" t="n"/>
       <c r="B16" s="3" t="n"/>
       <c r="C16" s="3" t="n"/>
       <c r="D16" s="3" t="n"/>
       <c r="E16" s="3" t="n"/>
     </row>
-    <row r="17" ht="24.75" customHeight="1">
-      <c r="A17" s="74" t="n"/>
+    <row r="17" ht="24.75" customHeight="1" s="60">
+      <c r="A17" s="77" t="n"/>
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="n"/>
       <c r="D17" s="3" t="n"/>
       <c r="E17" s="3" t="n"/>
     </row>
-    <row r="18" ht="24.75" customHeight="1">
-      <c r="A18" s="74" t="n"/>
+    <row r="18" ht="24.75" customHeight="1" s="60">
+      <c r="A18" s="77" t="n"/>
       <c r="B18" s="3" t="n"/>
       <c r="C18" s="3" t="n"/>
       <c r="D18" s="3" t="n"/>
       <c r="E18" s="3" t="n"/>
     </row>
-    <row r="19" ht="24.75" customHeight="1">
-      <c r="A19" s="74" t="n"/>
+    <row r="19" ht="24.75" customHeight="1" s="60">
+      <c r="A19" s="77" t="n"/>
       <c r="B19" s="3" t="n"/>
       <c r="C19" s="3" t="n"/>
       <c r="D19" s="3" t="n"/>
       <c r="E19" s="3" t="n"/>
     </row>
-    <row r="20" ht="24.75" customHeight="1">
-      <c r="A20" s="74" t="n"/>
+    <row r="20" ht="24.75" customHeight="1" s="60">
+      <c r="A20" s="77" t="n"/>
       <c r="B20" s="3" t="n"/>
       <c r="C20" s="3" t="n"/>
       <c r="D20" s="3" t="n"/>
       <c r="E20" s="3" t="n"/>
     </row>
-    <row r="21" ht="24.75" customHeight="1">
-      <c r="A21" s="74" t="n"/>
+    <row r="21" ht="24.75" customHeight="1" s="60">
+      <c r="A21" s="77" t="n"/>
       <c r="B21" s="3" t="n"/>
       <c r="C21" s="3" t="n"/>
       <c r="D21" s="3" t="n"/>
       <c r="E21" s="3" t="n"/>
     </row>
-    <row r="22" ht="24.75" customHeight="1">
-      <c r="A22" s="74" t="n"/>
+    <row r="22" ht="24.75" customHeight="1" s="60">
+      <c r="A22" s="77" t="n"/>
       <c r="B22" s="3" t="n"/>
       <c r="C22" s="3" t="n"/>
       <c r="D22" s="3" t="n"/>
       <c r="E22" s="3" t="n"/>
     </row>
-    <row r="23" ht="24.75" customHeight="1">
-      <c r="A23" s="74" t="n"/>
+    <row r="23" ht="24.75" customHeight="1" s="60">
+      <c r="A23" s="77" t="n"/>
       <c r="B23" s="3" t="n"/>
       <c r="C23" s="3" t="n"/>
       <c r="D23" s="3" t="n"/>
       <c r="E23" s="3" t="n"/>
     </row>
-    <row r="24" ht="24.75" customHeight="1">
-      <c r="A24" s="74" t="n"/>
+    <row r="24" ht="24.75" customHeight="1" s="60">
+      <c r="A24" s="77" t="n"/>
       <c r="B24" s="3" t="n"/>
       <c r="C24" s="3" t="n"/>
       <c r="D24" s="3" t="n"/>
       <c r="E24" s="3" t="n"/>
     </row>
-    <row r="25" ht="24.75" customHeight="1">
-      <c r="A25" s="74" t="n"/>
+    <row r="25" ht="24.75" customHeight="1" s="60">
+      <c r="A25" s="77" t="n"/>
       <c r="B25" s="3" t="n"/>
       <c r="C25" s="3" t="n"/>
       <c r="D25" s="3" t="n"/>
       <c r="E25" s="3" t="n"/>
     </row>
-    <row r="26" ht="24.75" customHeight="1">
-      <c r="A26" s="74" t="n"/>
+    <row r="26" ht="24.75" customHeight="1" s="60">
+      <c r="A26" s="77" t="n"/>
       <c r="B26" s="3" t="n"/>
       <c r="C26" s="3" t="n"/>
       <c r="D26" s="3" t="n"/>
       <c r="E26" s="3" t="n"/>
     </row>
-    <row r="27" ht="24.75" customHeight="1">
-      <c r="A27" s="74" t="n"/>
+    <row r="27" ht="24.75" customHeight="1" s="60">
+      <c r="A27" s="77" t="n"/>
       <c r="B27" s="3" t="n"/>
       <c r="C27" s="3" t="n"/>
       <c r="D27" s="3" t="n"/>
       <c r="E27" s="3" t="n"/>
     </row>
-    <row r="28" ht="24.75" customHeight="1">
-      <c r="A28" s="74" t="n"/>
+    <row r="28" ht="24.75" customHeight="1" s="60">
+      <c r="A28" s="77" t="n"/>
       <c r="B28" s="3" t="n"/>
       <c r="C28" s="3" t="n"/>
       <c r="D28" s="3" t="n"/>
       <c r="E28" s="3" t="n"/>
     </row>
-    <row r="29" ht="24.75" customHeight="1">
-      <c r="A29" s="74" t="n"/>
+    <row r="29" ht="24.75" customHeight="1" s="60">
+      <c r="A29" s="77" t="n"/>
       <c r="B29" s="3" t="n"/>
       <c r="C29" s="3" t="n"/>
       <c r="D29" s="3" t="n"/>
       <c r="E29" s="3" t="n"/>
     </row>
-    <row r="30" ht="24.75" customHeight="1">
-      <c r="A30" s="74" t="n"/>
+    <row r="30" ht="24.75" customHeight="1" s="60">
+      <c r="A30" s="77" t="n"/>
       <c r="B30" s="3" t="n"/>
       <c r="C30" s="3" t="n"/>
       <c r="D30" s="3" t="n"/>
@@ -3542,30 +3546,30 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K78"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.875" defaultRowHeight="68.09999999999999" customHeight="1"/>
+  <dimension ref="A1:K76"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="68" customHeight="1"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="28.625" customWidth="1" min="3" max="3"/>
-    <col width="24.625" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="27" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="70.375" bestFit="1" customWidth="1" style="10" min="7" max="7"/>
-    <col width="12" bestFit="1" customWidth="1" min="8" max="8"/>
-    <col width="12.875" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="10.375" bestFit="1" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" style="60" min="1" max="1"/>
+    <col width="20" customWidth="1" style="60" min="2" max="2"/>
+    <col width="28.6640625" customWidth="1" style="60" min="3" max="3"/>
+    <col width="24.6640625" bestFit="1" customWidth="1" style="60" min="4" max="4"/>
+    <col width="27" bestFit="1" customWidth="1" style="60" min="5" max="5"/>
+    <col width="13" customWidth="1" style="60" min="6" max="6"/>
+    <col width="70.33203125" bestFit="1" customWidth="1" style="61" min="7" max="7"/>
+    <col width="12" bestFit="1" customWidth="1" style="60" min="8" max="8"/>
+    <col width="12.83203125" customWidth="1" style="60" min="9" max="9"/>
+    <col width="22" customWidth="1" style="60" min="10" max="10"/>
+    <col width="10.33203125" bestFit="1" customWidth="1" style="60" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="60" customHeight="1">
-      <c r="A1" s="58" t="inlineStr">
+    <row r="1" ht="60" customHeight="1" s="60">
+      <c r="A1" s="59" t="inlineStr">
         <is>
           <t>[제주_스마트도시사업] AI주차민원솔루션 기능구조도</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="12.95" customHeight="1" thickBot="1">
+    <row r="2" ht="13" customHeight="1" s="60" thickBot="1">
       <c r="A2" s="12" t="n"/>
       <c r="B2" s="12" t="n"/>
       <c r="C2" s="12" t="n"/>
@@ -3577,7 +3581,7 @@
       <c r="J2" s="12" t="n"/>
       <c r="K2" s="12" t="n"/>
     </row>
-    <row r="3" ht="32.1" customHeight="1" thickBot="1">
+    <row r="3" ht="32" customHeight="1" s="60" thickBot="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
           <t>요구사항ID</t>
@@ -3634,7 +3638,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="32.1" customHeight="1">
+    <row r="4" ht="32" customHeight="1" s="60">
       <c r="A4" s="23" t="inlineStr">
         <is>
           <t>REQ-SFR-003-08</t>
@@ -3687,7 +3691,7 @@
       </c>
       <c r="K4" s="24" t="n"/>
     </row>
-    <row r="5" ht="32.1" customHeight="1">
+    <row r="5" ht="32" customHeight="1" s="60">
       <c r="A5" s="27" t="inlineStr">
         <is>
           <t>REQ-SFR-005-07</t>
@@ -3740,7 +3744,7 @@
       </c>
       <c r="K5" s="28" t="n"/>
     </row>
-    <row r="6" ht="32.1" customHeight="1">
+    <row r="6" ht="32" customHeight="1" s="60">
       <c r="A6" s="23" t="inlineStr">
         <is>
           <t>REQ-SFR-003-07</t>
@@ -3773,7 +3777,7 @@
       </c>
       <c r="G6" s="17" t="inlineStr">
         <is>
-          <t>이제/주간/월간 탭 및 상세 필터(날짜 범위) 설정 기능</t>
+          <t>어제/주간/월간 탭 및 상세 필터(날짜 범위) 설정 기능</t>
         </is>
       </c>
       <c r="H6" s="16" t="inlineStr">
@@ -3793,7 +3797,7 @@
       </c>
       <c r="K6" s="24" t="n"/>
     </row>
-    <row r="7" ht="32.1" customHeight="1">
+    <row r="7" ht="32" customHeight="1" s="60">
       <c r="A7" s="25" t="inlineStr">
         <is>
           <t>REQ-SFR-003-07</t>
@@ -3826,7 +3830,7 @@
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>총 민원 건수·공영주차장 현황(개소)·위험단계알림 건수 카드 (단속 건수는 월 1회 갱신으로 제외)</t>
+          <t>총 민원 건수·공영주차장 현황(개소)·위험단계알림 건수 카드</t>
         </is>
       </c>
       <c r="H7" s="14" t="inlineStr">
@@ -3846,7 +3850,7 @@
       </c>
       <c r="K7" s="26" t="n"/>
     </row>
-    <row r="8" ht="32.1" customHeight="1">
+    <row r="8" ht="32" customHeight="1" s="60">
       <c r="A8" s="25" t="inlineStr">
         <is>
           <t>REQ-SFR-003-01</t>
@@ -3879,7 +3883,7 @@
       </c>
       <c r="G8" s="15" t="inlineStr">
         <is>
-          <t>시간대별(00~22시) 민원 유형 라인 차트 — 어제/주간/월간 조회 단위 모두 시간대별 집계, 단위에 따라 집계 규모 변경</t>
+          <t>시간대별 민원 유형 라인 차트 — 어제/주간/월간 조회 단위 모두 시간대별 집계, 단위에 따라 집계 규모 변경</t>
         </is>
       </c>
       <c r="H8" s="14" t="inlineStr">
@@ -3899,7 +3903,7 @@
       </c>
       <c r="K8" s="26" t="n"/>
     </row>
-    <row r="9" ht="32.1" customHeight="1">
+    <row r="9" ht="32" customHeight="1" s="60">
       <c r="A9" s="25" t="inlineStr">
         <is>
           <t>REQ-SFR-003-02</t>
@@ -3917,12 +3921,12 @@
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>민원 집중구역 순위</t>
+          <t>불법주차 집중구역 순위</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>Top5 목록 + GIS 보기</t>
+          <t>Top5 목록 + 자세히 보기</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
@@ -3952,7 +3956,7 @@
       </c>
       <c r="K9" s="26" t="n"/>
     </row>
-    <row r="10" ht="32.1" customHeight="1">
+    <row r="10" ht="32" customHeight="1" s="60">
       <c r="A10" s="25" t="inlineStr">
         <is>
           <t>REQ-SFR-003-03</t>
@@ -3985,7 +3989,7 @@
       </c>
       <c r="G10" s="15" t="inlineStr">
         <is>
-          <t>읍·면·동 Top5 민원 건수 카드, 전일 대비 증감률·순위 변동·유형별 건수 및 스택바 표시. 전체 보기 링크</t>
+          <t>읍·면·동 Top5 민원 건수 카드, 전일 대비 증감률 · 순위 변동 · 호버 시 유형별 건수 및 스택바 표시. 전체 보기 링크</t>
         </is>
       </c>
       <c r="H10" s="14" t="inlineStr">
@@ -4005,7 +4009,7 @@
       </c>
       <c r="K10" s="26" t="n"/>
     </row>
-    <row r="11" ht="32.1" customHeight="1">
+    <row r="11" ht="32" customHeight="1" s="60">
       <c r="A11" s="25" t="inlineStr">
         <is>
           <t>REQ-SFR-003-10</t>
@@ -4023,12 +4027,12 @@
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>최근 분석 요약</t>
+          <t>최근 정책효과 시뮬레이션 목록</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>분석 상태 목록 위젯</t>
+          <t>분석 이력 목록</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
@@ -4038,7 +4042,7 @@
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>최근 정책 효과 시뮬레이션 목록 표시. 목록이 비면 빈 상태 안내 문구 표시. 전체 → 정책 효과 시뮬레이션 이동</t>
+          <t>최근 정책 효과 시뮬레이션 목록 표시.  전체 → 정책 효과 시뮬레이션 이동</t>
         </is>
       </c>
       <c r="H11" s="14" t="inlineStr">
@@ -4058,7 +4062,7 @@
       </c>
       <c r="K11" s="26" t="n"/>
     </row>
-    <row r="12" ht="32.1" customHeight="1">
+    <row r="12" ht="32" customHeight="1" s="60">
       <c r="A12" s="25" t="inlineStr">
         <is>
           <t>REQ-SFR-005-05</t>
@@ -4076,12 +4080,12 @@
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>최근 보고서 요약</t>
+          <t>최근 보고서 목록</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>보고서 목록 위젯</t>
+          <t xml:space="preserve">보고서 목록 </t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
@@ -4091,7 +4095,7 @@
       </c>
       <c r="G12" s="15" t="inlineStr">
         <is>
-          <t>최근 생성 보고서 목록(제목·일시). 항목 클릭 시 보고서 목록의 해당 행으로 이동·강조. 빈 상태 안내 포함</t>
+          <t>최근 생성 보고서 목록(제목·일시). 항목 클릭 시 보고서 목록의 해당 행으로 이동</t>
         </is>
       </c>
       <c r="H12" s="14" t="inlineStr">
@@ -4111,7 +4115,7 @@
       </c>
       <c r="K12" s="26" t="n"/>
     </row>
-    <row r="13" ht="32.1" customHeight="1">
+    <row r="13" ht="32" customHeight="1" s="60">
       <c r="A13" s="27" t="inlineStr">
         <is>
           <t>REQ-SFR-005-07</t>
@@ -4129,7 +4133,7 @@
       </c>
       <c r="D13" s="18" t="inlineStr">
         <is>
-          <t>AI 어시스턴트 패널</t>
+          <t>AI 어시스턴트 패널, 최근 질문 목록</t>
         </is>
       </c>
       <c r="E13" s="18" t="inlineStr">
@@ -4144,7 +4148,7 @@
       </c>
       <c r="G13" s="19" t="inlineStr">
         <is>
-          <t>AI 어시스턴트 빠른 질문 입력창 및 추천 질문 3개 표시. 대화 열기 버튼 → AI 어시스턴트 화면 이동</t>
+          <t>AI 어시스턴트 빠른 질문 입력창 및 최근질문 3개 표시. 대화 열기 버튼 → AI 어시스턴트 화면 이동</t>
         </is>
       </c>
       <c r="H13" s="18" t="inlineStr">
@@ -4164,7 +4168,7 @@
       </c>
       <c r="K13" s="28" t="n"/>
     </row>
-    <row r="14" ht="32.1" customHeight="1">
+    <row r="14" ht="32" customHeight="1" s="60">
       <c r="A14" s="23" t="inlineStr">
         <is>
           <t>REQ-SFR-003-03</t>
@@ -4217,7 +4221,7 @@
       </c>
       <c r="K14" s="24" t="n"/>
     </row>
-    <row r="15" ht="32.1" customHeight="1">
+    <row r="15" ht="32" customHeight="1" s="60">
       <c r="A15" s="29" t="inlineStr">
         <is>
           <t>REQ-SFR-003-07</t>
@@ -4270,7 +4274,7 @@
       </c>
       <c r="K15" s="30" t="n"/>
     </row>
-    <row r="16" ht="32.1" customHeight="1">
+    <row r="16" ht="32" customHeight="1" s="60">
       <c r="A16" s="25" t="inlineStr">
         <is>
           <t>REQ-SFR-003-09</t>
@@ -4293,7 +4297,7 @@
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>민원 히트맵 레이어</t>
+          <t>민원 분석 레이어</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
@@ -4303,7 +4307,7 @@
       </c>
       <c r="G16" s="15" t="inlineStr">
         <is>
-          <t>민원 히트맵 표시, 히트맵 중심점 동단위 건수 표기.</t>
+          <t>분석레이어(민원다발지역/집중단속지역/수요부족지역 선택→지도 시각화, 읍면동별 순위 표시). 히트맵 표현 시 민원 건수·단속 건수·부족률 기반 밀도 히트맵 표출</t>
         </is>
       </c>
       <c r="H16" s="14" t="inlineStr">
@@ -4323,7 +4327,7 @@
       </c>
       <c r="K16" s="26" t="n"/>
     </row>
-    <row r="17" ht="32.1" customHeight="1">
+    <row r="17" ht="32" customHeight="1" s="60">
       <c r="A17" s="25" t="inlineStr">
         <is>
           <t>REQ-SFR-003-09</t>
@@ -4356,7 +4360,7 @@
       </c>
       <c r="G17" s="15" t="inlineStr">
         <is>
-          <t>지도 레이어 패널 — 민원 다발/단속 집중/수요 부족(택1 라디오) + 공영주차장·행정동 경계 토글. 레이어 선택에 따라 우측 순위 카드 연동 전환</t>
+          <t>지도 레이어 패널 — 민원 다발/단속 집중/수요 부족(택1 라디오) + 공영주차장·행정동 경계 토글. 레이어 선택에 따라 우측 순위 패널 전환. 각 분석 레이어는 읍면동(폴리곤) ↔ 히트맵(밀도) 표현 전환 지원</t>
         </is>
       </c>
       <c r="H17" s="14" t="inlineStr">
@@ -4376,7 +4380,7 @@
       </c>
       <c r="K17" s="26" t="n"/>
     </row>
-    <row r="18" ht="32.1" customHeight="1">
+    <row r="18" ht="32" customHeight="1" s="60">
       <c r="A18" s="25" t="inlineStr">
         <is>
           <t>REQ-SFR-003-09</t>
@@ -4409,7 +4413,7 @@
       </c>
       <c r="G18" s="15" t="inlineStr">
         <is>
-          <t>히트맵 색상 범례 표시</t>
+          <t>색상 범례 표시 — 등급(심각·경고·주의) 범례, 히트맵 선택 시 그라데이션(낮음~높음) 범례로 전환</t>
         </is>
       </c>
       <c r="H18" s="14" t="inlineStr">
@@ -4429,7 +4433,7 @@
       </c>
       <c r="K18" s="26" t="n"/>
     </row>
-    <row r="19" ht="32.1" customHeight="1">
+    <row r="19" ht="32" customHeight="1" s="60">
       <c r="A19" s="25" t="inlineStr">
         <is>
           <t>REQ-SFR-003-01</t>
@@ -4447,7 +4451,7 @@
       </c>
       <c r="D19" s="14" t="inlineStr">
         <is>
-          <t>지역별 민원 현황</t>
+          <t>민원/단속/수요부족 순위</t>
         </is>
       </c>
       <c r="E19" s="14" t="inlineStr">
@@ -4482,7 +4486,7 @@
       </c>
       <c r="K19" s="26" t="n"/>
     </row>
-    <row r="20" ht="32.1" customHeight="1">
+    <row r="20" ht="32" customHeight="1" s="60">
       <c r="A20" s="27" t="inlineStr">
         <is>
           <t>REQ-SFR-003-02</t>
@@ -4535,7 +4539,7 @@
       </c>
       <c r="K20" s="28" t="n"/>
     </row>
-    <row r="21" ht="32.1" customHeight="1">
+    <row r="21" ht="32" customHeight="1" s="60">
       <c r="A21" s="27" t="inlineStr">
         <is>
           <t>REQ-SFR-003-10</t>
@@ -4586,9 +4590,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="K21" s="28" t="inlineStr"/>
-    </row>
-    <row r="22" ht="32.1" customHeight="1">
+      <c r="K21" s="28" t="n"/>
+    </row>
+    <row r="22" ht="32" customHeight="1" s="60">
       <c r="A22" s="23" t="inlineStr">
         <is>
           <t>REQ-SFR-003-02</t>
@@ -4621,7 +4625,7 @@
       </c>
       <c r="G22" s="17" t="inlineStr">
         <is>
-          <t>제주 전역 GIS 지도에 불법 주차 집중 구역 순위 마커(Top7) 표시. 목록 행 클릭 시 지도 확대 이동 및 팝업</t>
+          <t>제주 전역 GIS 지도에 불법 주차 집중 구역 순위 마커 표시. 목록 행 클릭 시 지도 확대 이동 및 팝업 표시</t>
         </is>
       </c>
       <c r="H22" s="16" t="inlineStr">
@@ -4641,7 +4645,7 @@
       </c>
       <c r="K22" s="24" t="n"/>
     </row>
-    <row r="23" ht="32.1" customHeight="1">
+    <row r="23" ht="32" customHeight="1" s="60">
       <c r="A23" s="25" t="inlineStr">
         <is>
           <t>REQ-SFR-003-02</t>
@@ -4664,7 +4668,7 @@
       </c>
       <c r="E23" s="14" t="inlineStr">
         <is>
-          <t>분석 결과 요약 패널</t>
+          <t>불법주차 집중구역 순위</t>
         </is>
       </c>
       <c r="F23" s="14" t="inlineStr">
@@ -4674,7 +4678,7 @@
       </c>
       <c r="G23" s="15" t="inlineStr">
         <is>
-          <t>총 분석 격자 수·단계별(심각/경고/주의/양호) 격자 수 요약 패널 표시</t>
+          <t>종합점수(민원 건수 60% + 단속 40%) 기준 우선순위 목록</t>
         </is>
       </c>
       <c r="H23" s="14" t="inlineStr">
@@ -4694,68 +4698,68 @@
       </c>
       <c r="K23" s="26" t="n"/>
     </row>
-    <row r="24" ht="32.1" customHeight="1">
-      <c r="A24" s="25" t="inlineStr">
+    <row r="24" ht="32" customHeight="1" s="60">
+      <c r="A24" s="27" t="inlineStr">
         <is>
           <t>REQ-SFR-003-02</t>
         </is>
       </c>
-      <c r="B24" s="14" t="inlineStr">
+      <c r="B24" s="18" t="inlineStr">
         <is>
           <t>FN-PAR-03-01-03</t>
         </is>
       </c>
-      <c r="C24" s="32" t="inlineStr">
+      <c r="C24" s="34" t="inlineStr">
         <is>
           <t>불법 주차 집중 구역 분석</t>
         </is>
       </c>
-      <c r="D24" s="32" t="inlineStr">
+      <c r="D24" s="34" t="inlineStr">
         <is>
           <t>집중구역 분석 GIS</t>
         </is>
       </c>
-      <c r="E24" s="14" t="inlineStr">
-        <is>
-          <t>불법주차 집중구역 순위</t>
-        </is>
-      </c>
-      <c r="F24" s="14" t="inlineStr">
+      <c r="E24" s="18" t="inlineStr">
+        <is>
+          <t>분석 설정 패널</t>
+        </is>
+      </c>
+      <c r="F24" s="18" t="inlineStr">
         <is>
           <t>UI-PAR-003-01</t>
         </is>
       </c>
-      <c r="G24" s="15" t="inlineStr">
-        <is>
-          <t>종합점수(민원 건수 60% + 단속 40%) 기준 Top7 목록 — 등급은 절대 점수(심각 80점 이상/경고 60~79/주의 40~59)</t>
-        </is>
-      </c>
-      <c r="H24" s="14" t="inlineStr">
+      <c r="G24" s="19" t="inlineStr">
+        <is>
+          <t>분석 지역·분석 기간(최근1/3/6개월, 월 단위 직접 설정) 조건 입력 후 분석 실행 — 분석 최소 단위는 월</t>
+        </is>
+      </c>
+      <c r="H24" s="18" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I24" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J24" s="14" t="inlineStr">
+      <c r="I24" s="39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J24" s="18" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K24" s="26" t="n"/>
-    </row>
-    <row r="25" ht="32.1" customHeight="1">
+      <c r="K24" s="28" t="n"/>
+    </row>
+    <row r="25" ht="32" customHeight="1" s="60">
       <c r="A25" s="27" t="inlineStr">
         <is>
-          <t>REQ-SFR-003-02</t>
+          <t>REQ-SFR-003-10</t>
         </is>
       </c>
       <c r="B25" s="18" t="inlineStr">
         <is>
-          <t>FN-PAR-03-01-04</t>
+          <t>FN-PAR-03-01-05</t>
         </is>
       </c>
       <c r="C25" s="34" t="inlineStr">
@@ -4765,12 +4769,12 @@
       </c>
       <c r="D25" s="34" t="inlineStr">
         <is>
-          <t>집중구역 분석 GIS</t>
+          <t>내보내기</t>
         </is>
       </c>
       <c r="E25" s="18" t="inlineStr">
         <is>
-          <t>분석 설정 패널</t>
+          <t>PDF/DOCX 내보내기</t>
         </is>
       </c>
       <c r="F25" s="18" t="inlineStr">
@@ -4780,7 +4784,7 @@
       </c>
       <c r="G25" s="19" t="inlineStr">
         <is>
-          <t>분석 지역·분석 기간(최근1/3/6개월, 월 단위 직접 설정) 조건 입력 후 분석 실행 — 분석 최소 단위는 월</t>
+          <t>분석 결과를 PDF/DOCX 보고서로 내보내기 — 내보낸 보고서는 보고서 목록의 직접 생성 보고서 목록에 표시</t>
         </is>
       </c>
       <c r="H25" s="18" t="inlineStr">
@@ -4800,1528 +4804,1524 @@
       </c>
       <c r="K25" s="28" t="n"/>
     </row>
-    <row r="26" ht="32.1" customHeight="1">
-      <c r="A26" s="27" t="inlineStr">
+    <row r="26" ht="32" customHeight="1" s="60">
+      <c r="A26" s="23" t="inlineStr">
+        <is>
+          <t>REQ-SFR-003-05</t>
+        </is>
+      </c>
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>FN-PAR-03-02-01</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="inlineStr">
+        <is>
+          <t>정책 효과 시뮬레이션</t>
+        </is>
+      </c>
+      <c r="D26" s="16" t="inlineStr">
+        <is>
+          <t>정책 변수 설정</t>
+        </is>
+      </c>
+      <c r="E26" s="16" t="inlineStr">
+        <is>
+          <t>정책 유형 탭 선택</t>
+        </is>
+      </c>
+      <c r="F26" s="16" t="inlineStr">
+        <is>
+          <t>UI-PAR-003-02</t>
+        </is>
+      </c>
+      <c r="G26" s="17" t="inlineStr">
+        <is>
+          <t>정책 유형 탭 전환: 주차장 확충 / 이면도로 정비 / 요금제 적용 3종 탭 선택</t>
+        </is>
+      </c>
+      <c r="H26" s="16" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I26" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J26" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K26" s="24" t="n"/>
+    </row>
+    <row r="27" ht="32" customHeight="1" s="60">
+      <c r="A27" s="25" t="inlineStr">
+        <is>
+          <t>REQ-SFR-003-05</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>FN-PAR-03-02-02</t>
+        </is>
+      </c>
+      <c r="C27" s="32" t="inlineStr">
+        <is>
+          <t>정책 효과 시뮬레이션</t>
+        </is>
+      </c>
+      <c r="D27" s="32" t="inlineStr">
+        <is>
+          <t>정책 변수 설정</t>
+        </is>
+      </c>
+      <c r="E27" s="14" t="inlineStr">
+        <is>
+          <t>주차장 확충 파라미터</t>
+        </is>
+      </c>
+      <c r="F27" s="14" t="inlineStr">
+        <is>
+          <t>UI-PAR-003-02</t>
+        </is>
+      </c>
+      <c r="G27" s="15" t="inlineStr">
+        <is>
+          <t>[주차장 확충] 대상 지역·확충 방식(공한지 조성/복층화/신규 조성)·주차면 증설 수 입력 후 시뮬레이션 실행</t>
+        </is>
+      </c>
+      <c r="H27" s="14" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I27" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J27" s="14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K27" s="26" t="n"/>
+    </row>
+    <row r="28" ht="32" customHeight="1" s="60">
+      <c r="A28" s="25" t="inlineStr">
+        <is>
+          <t>REQ-SFR-003-05</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>FN-PAR-03-02-03</t>
+        </is>
+      </c>
+      <c r="C28" s="32" t="inlineStr">
+        <is>
+          <t>정책 효과 시뮬레이션</t>
+        </is>
+      </c>
+      <c r="D28" s="32" t="inlineStr">
+        <is>
+          <t>정책 변수 설정</t>
+        </is>
+      </c>
+      <c r="E28" s="14" t="inlineStr">
+        <is>
+          <t>이면도로 정비 파라미터</t>
+        </is>
+      </c>
+      <c r="F28" s="14" t="inlineStr">
+        <is>
+          <t>UI-PAR-003-02-1</t>
+        </is>
+      </c>
+      <c r="G28" s="15" t="inlineStr">
+        <is>
+          <t>[이면도로 정비] 대상 지역·정비 방식(상업지역형(주차환경개선지구)/주거지역형(주민참여형))·정비 구간 연장(m) 입력</t>
+        </is>
+      </c>
+      <c r="H28" s="14" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I28" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J28" s="14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K28" s="26" t="n"/>
+    </row>
+    <row r="29" ht="32" customHeight="1" s="60">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>REQ-SFR-003-05</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>FN-PAR-03-02-04</t>
+        </is>
+      </c>
+      <c r="C29" s="32" t="inlineStr">
+        <is>
+          <t>정책 효과 시뮬레이션</t>
+        </is>
+      </c>
+      <c r="D29" s="32" t="inlineStr">
+        <is>
+          <t>정책 변수 설정</t>
+        </is>
+      </c>
+      <c r="E29" s="14" t="inlineStr">
+        <is>
+          <t>요금제 적용 파라미터</t>
+        </is>
+      </c>
+      <c r="F29" s="14" t="inlineStr">
+        <is>
+          <t>UI-PAR-003-02-1</t>
+        </is>
+      </c>
+      <c r="G29" s="15" t="inlineStr">
+        <is>
+          <t>[요금제 적용] 대상 지역·적용 방식(요금 인상/무료→유료 전환)·적용 급지(전체/1급지(동)/2급지(읍·면), 제주 전체·시 전체 선택 시에만)·인상률(+10/20/30%, 요금 인상 시)</t>
+        </is>
+      </c>
+      <c r="H29" s="14" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I29" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J29" s="14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K29" s="26" t="inlineStr">
+        <is>
+          <t>설계감리 시정 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="32" customHeight="1" s="60" thickBot="1">
+      <c r="A30" s="25" t="inlineStr">
         <is>
           <t>REQ-SFR-003-10</t>
         </is>
       </c>
-      <c r="B26" s="18" t="inlineStr">
-        <is>
-          <t>FN-PAR-03-01-05</t>
-        </is>
-      </c>
-      <c r="C26" s="34" t="inlineStr">
-        <is>
-          <t>불법 주차 집중 구역 분석</t>
-        </is>
-      </c>
-      <c r="D26" s="34" t="inlineStr">
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>FN-PAR-03-02-05</t>
+        </is>
+      </c>
+      <c r="C30" s="32" t="inlineStr">
+        <is>
+          <t>정책 효과 시뮬레이션</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t>효과 예측 결과</t>
+        </is>
+      </c>
+      <c r="E30" s="14" t="inlineStr">
+        <is>
+          <t>효과 예측 KPI 카드</t>
+        </is>
+      </c>
+      <c r="F30" s="14" t="inlineStr">
+        <is>
+          <t>UI-PAR-003-02</t>
+        </is>
+      </c>
+      <c r="G30" s="15" t="inlineStr">
+        <is>
+          <t>효과 예측 KPI: 민원 감소 예측·혼잡도 개선(혼잡 지수 = (정상 이용+불법주차)÷공급 면수). 분석 근거 ⓘ 팝오버(가정값 기반 고지 포함)</t>
+        </is>
+      </c>
+      <c r="H30" s="14" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I30" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J30" s="14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K30" s="26" t="n"/>
+    </row>
+    <row r="31" ht="32" customHeight="1" s="60">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>REQ-SFR-003-12</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>FN-PAR-03-02-06</t>
+        </is>
+      </c>
+      <c r="C31" s="32" t="inlineStr">
+        <is>
+          <t>정책 효과 시뮬레이션</t>
+        </is>
+      </c>
+      <c r="D31" s="14" t="inlineStr">
+        <is>
+          <t>시나리오 비교 테이블</t>
+        </is>
+      </c>
+      <c r="E31" s="14" t="inlineStr">
+        <is>
+          <t>비교 결과 PDF 다운로드</t>
+        </is>
+      </c>
+      <c r="F31" s="14" t="inlineStr">
+        <is>
+          <t>UI-PAR-003-02</t>
+        </is>
+      </c>
+      <c r="G31" s="15" t="inlineStr">
+        <is>
+          <t>시나리오 비교 테이블 — 정책 유형 필터 칩(건수 표시), 체크박스 선택 내보내기(PDF/DOCX, 비교 차트 포함), 행 삭제(확인 모달)</t>
+        </is>
+      </c>
+      <c r="H31" s="14" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I31" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J31" s="14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K31" s="26" t="inlineStr">
+        <is>
+          <t>설계감리 시정 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="32" customHeight="1" s="60">
+      <c r="A32" s="23" t="inlineStr">
+        <is>
+          <t>REQ-SFR-003-04</t>
+        </is>
+      </c>
+      <c r="B32" s="16" t="inlineStr">
+        <is>
+          <t>FN-PAR-03-03-01</t>
+        </is>
+      </c>
+      <c r="C32" s="16" t="inlineStr">
+        <is>
+          <t>생활권 시뮬레이션</t>
+        </is>
+      </c>
+      <c r="D32" s="16" t="inlineStr">
+        <is>
+          <t>생활권 분석 설정</t>
+        </is>
+      </c>
+      <c r="E32" s="16" t="inlineStr">
+        <is>
+          <t>분석 조건 설정 패널</t>
+        </is>
+      </c>
+      <c r="F32" s="16" t="inlineStr">
+        <is>
+          <t>UI-PAR-003-03</t>
+        </is>
+      </c>
+      <c r="G32" s="17" t="inlineStr">
+        <is>
+          <t>분석 내용 선택·분석 지역·분석 기간(최근1/3/6개월·직접 설정·날짜 범위)·격자 크기(1km/500m/250m/100m) 설정 후 생활권 분석 실행</t>
+        </is>
+      </c>
+      <c r="H32" s="16" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I32" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J32" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K32" s="24" t="n"/>
+    </row>
+    <row r="33" ht="32" customHeight="1" s="60">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>REQ-SFR-003-09</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>FN-PAR-03-03-02</t>
+        </is>
+      </c>
+      <c r="C33" s="32" t="inlineStr">
+        <is>
+          <t>생활권 시뮬레이션</t>
+        </is>
+      </c>
+      <c r="D33" s="14" t="inlineStr">
+        <is>
+          <t>격자 GIS 지도</t>
+        </is>
+      </c>
+      <c r="E33" s="14" t="inlineStr">
+        <is>
+          <t>격자 히트맵 시각화</t>
+        </is>
+      </c>
+      <c r="F33" s="14" t="inlineStr">
+        <is>
+          <t>UI-PAR-003-03</t>
+        </is>
+      </c>
+      <c r="G33" s="15" t="inlineStr">
+        <is>
+          <t>격자(100m~1km) 기반 GIS 히트맵 — 5단계 색상(심각/경고/주의/보통/낮음). 민원·수급은 백분위, 혼잡도는 절대 기준(지수 1.0=100점)</t>
+        </is>
+      </c>
+      <c r="H33" s="14" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I33" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J33" s="14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K33" s="26" t="n"/>
+    </row>
+    <row r="34" ht="32" customHeight="1" s="60">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>REQ-SFR-003-04</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>FN-PAR-03-03-03</t>
+        </is>
+      </c>
+      <c r="C34" s="32" t="inlineStr">
+        <is>
+          <t>생활권 시뮬레이션</t>
+        </is>
+      </c>
+      <c r="D34" s="32" t="inlineStr">
+        <is>
+          <t>격자 GIS 지도</t>
+        </is>
+      </c>
+      <c r="E34" s="14" t="inlineStr">
+        <is>
+          <t>격자 팝업</t>
+        </is>
+      </c>
+      <c r="F34" s="14" t="inlineStr">
+        <is>
+          <t>UI-PAR-003-03</t>
+        </is>
+      </c>
+      <c r="G34" s="15" t="inlineStr">
+        <is>
+          <t>선택 격자 클릭 시 팝업: 위치명·총 건수·기간· 유형별 건수 상세 표시</t>
+        </is>
+      </c>
+      <c r="H34" s="14" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I34" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J34" s="14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K34" s="26" t="n"/>
+    </row>
+    <row r="35" ht="32" customHeight="1" s="60">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>REQ-SFR-003-04</t>
+        </is>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>FN-PAR-03-03-04</t>
+        </is>
+      </c>
+      <c r="C35" s="32" t="inlineStr">
+        <is>
+          <t>생활권 시뮬레이션</t>
+        </is>
+      </c>
+      <c r="D35" s="14" t="inlineStr">
+        <is>
+          <t>분석 결과 요약</t>
+        </is>
+      </c>
+      <c r="E35" s="14" t="inlineStr">
+        <is>
+          <t>격자 기반 분석 요약 패널</t>
+        </is>
+      </c>
+      <c r="F35" s="14" t="inlineStr">
+        <is>
+          <t>UI-PAR-003-03</t>
+        </is>
+      </c>
+      <c r="G35" s="15" t="inlineStr">
+        <is>
+          <t>총 분석 격자 수 + 5단계 격자 수 요약, 격자 크기 칩·등급 산정 기준 ⓘ 팝오버</t>
+        </is>
+      </c>
+      <c r="H35" s="14" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I35" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J35" s="14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K35" s="26" t="inlineStr">
+        <is>
+          <t>설계감리 시정 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="32" customHeight="1" s="60">
+      <c r="A36" s="27" t="inlineStr">
+        <is>
+          <t>REQ-SFR-003-04</t>
+        </is>
+      </c>
+      <c r="B36" s="18" t="inlineStr">
+        <is>
+          <t>FN-PAR-03-03-05</t>
+        </is>
+      </c>
+      <c r="C36" s="34" t="inlineStr">
+        <is>
+          <t>생활권 시뮬레이션</t>
+        </is>
+      </c>
+      <c r="D36" s="18" t="inlineStr">
+        <is>
+          <t>민원 집중구역 목록</t>
+        </is>
+      </c>
+      <c r="E36" s="18" t="inlineStr">
+        <is>
+          <t>격자 기반 집중구역 Top 목록</t>
+        </is>
+      </c>
+      <c r="F36" s="18" t="inlineStr">
+        <is>
+          <t>UI-PAR-003-03</t>
+        </is>
+      </c>
+      <c r="G36" s="19" t="inlineStr">
+        <is>
+          <t>격자 분석 집중 구역 Top8(심각·경고·주의) 목록 — 동 + 격자 중심 POI 명칭으로 표시. 행 클릭 시 지도 이동·팝업. 혼잡도 모드는 혼잡 점수 안내 ⓘ 제공</t>
+        </is>
+      </c>
+      <c r="H36" s="18" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I36" s="39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J36" s="18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K36" s="28" t="n"/>
+    </row>
+    <row r="37" ht="32" customHeight="1" s="60">
+      <c r="A37" s="27" t="inlineStr">
+        <is>
+          <t>REQ-SFR-003-10</t>
+        </is>
+      </c>
+      <c r="B37" s="18" t="inlineStr">
+        <is>
+          <t>FN-PAR-03-03-06</t>
+        </is>
+      </c>
+      <c r="C37" s="34" t="inlineStr">
+        <is>
+          <t>생활권 시뮬레이션</t>
+        </is>
+      </c>
+      <c r="D37" s="18" t="inlineStr">
         <is>
           <t>내보내기</t>
         </is>
       </c>
-      <c r="E26" s="18" t="inlineStr">
+      <c r="E37" s="18" t="inlineStr">
         <is>
           <t>PDF/DOCX 내보내기</t>
         </is>
       </c>
-      <c r="F26" s="18" t="inlineStr">
-        <is>
-          <t>UI-PAR-003-01</t>
-        </is>
-      </c>
-      <c r="G26" s="19" t="inlineStr">
+      <c r="F37" s="18" t="inlineStr">
+        <is>
+          <t>UI-PAR-003-03</t>
+        </is>
+      </c>
+      <c r="G37" s="19" t="inlineStr">
         <is>
           <t>분석 결과를 PDF/DOCX 보고서로 내보내기 — 내보낸 보고서는 보고서 목록의 직접 생성 보고서 목록에 표시</t>
         </is>
       </c>
-      <c r="H26" s="18" t="inlineStr">
+      <c r="H37" s="18" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I26" s="39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J26" s="18" t="inlineStr">
+      <c r="I37" s="39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J37" s="18" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K26" s="28" t="inlineStr"/>
-    </row>
-    <row r="27" ht="32.1" customHeight="1">
-      <c r="A27" s="23" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-05</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>FN-PAR-03-02-01</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>정책 효과 시뮬레이션</t>
-        </is>
-      </c>
-      <c r="D27" s="16" t="inlineStr">
-        <is>
-          <t>정책 변수 설정</t>
-        </is>
-      </c>
-      <c r="E27" s="16" t="inlineStr">
-        <is>
-          <t>정책 유형 탭 선택</t>
-        </is>
-      </c>
-      <c r="F27" s="16" t="inlineStr">
-        <is>
-          <t>UI-PAR-003-02</t>
-        </is>
-      </c>
-      <c r="G27" s="17" t="inlineStr">
-        <is>
-          <t>정책 유형 탭 전환: 주차장 확충 / 이면도로 정비 / 요금제 적용 3종 탭 선택</t>
-        </is>
-      </c>
-      <c r="H27" s="16" t="inlineStr">
+      <c r="K37" s="28" t="n"/>
+    </row>
+    <row r="38" ht="32" customHeight="1" s="60">
+      <c r="A38" s="23" t="inlineStr">
+        <is>
+          <t>REQ-SFR-003-06</t>
+        </is>
+      </c>
+      <c r="B38" s="16" t="inlineStr">
+        <is>
+          <t>FN-PAR-03-04-01</t>
+        </is>
+      </c>
+      <c r="C38" s="16" t="inlineStr">
+        <is>
+          <t>구역추천</t>
+        </is>
+      </c>
+      <c r="D38" s="16" t="inlineStr">
+        <is>
+          <t>구역 추천 설정</t>
+        </is>
+      </c>
+      <c r="E38" s="16" t="inlineStr">
+        <is>
+          <t>추천 조건 설정 패널</t>
+        </is>
+      </c>
+      <c r="F38" s="16" t="inlineStr">
+        <is>
+          <t>UI-PAR-003-04</t>
+        </is>
+      </c>
+      <c r="G38" s="17" t="inlineStr">
+        <is>
+          <t>분석 내용(요금제 적용/공유주차제 적용)·분석 지역·분석 기간(월 단위) 설정 후 구역 추천 실행</t>
+        </is>
+      </c>
+      <c r="H38" s="16" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I27" s="37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J27" s="16" t="inlineStr">
+      <c r="I38" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J38" s="16" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K27" s="24" t="n"/>
-    </row>
-    <row r="28" ht="32.1" customHeight="1">
-      <c r="A28" s="25" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-05</t>
-        </is>
-      </c>
-      <c r="B28" s="14" t="inlineStr">
-        <is>
-          <t>FN-PAR-03-02-02</t>
-        </is>
-      </c>
-      <c r="C28" s="32" t="inlineStr">
-        <is>
-          <t>정책 효과 시뮬레이션</t>
-        </is>
-      </c>
-      <c r="D28" s="32" t="inlineStr">
-        <is>
-          <t>정책 변수 설정</t>
-        </is>
-      </c>
-      <c r="E28" s="14" t="inlineStr">
-        <is>
-          <t>주차장 확충 파라미터</t>
-        </is>
-      </c>
-      <c r="F28" s="14" t="inlineStr">
-        <is>
-          <t>UI-PAR-003-02</t>
-        </is>
-      </c>
-      <c r="G28" s="15" t="inlineStr">
-        <is>
-          <t>[주차장 확충] 대상 지역·확충 방식(공한지 조성/복층화/신규 조성)·주차면 증설 수 입력 후 시뮬레이션 실행</t>
-        </is>
-      </c>
-      <c r="H28" s="14" t="inlineStr">
+      <c r="K38" s="24" t="n"/>
+    </row>
+    <row r="39" ht="32" customHeight="1" s="60">
+      <c r="A39" s="25" t="inlineStr">
+        <is>
+          <t>REQ-SFR-003-06</t>
+        </is>
+      </c>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>FN-PAR-03-04-02</t>
+        </is>
+      </c>
+      <c r="C39" s="32" t="inlineStr">
+        <is>
+          <t>구역추천</t>
+        </is>
+      </c>
+      <c r="D39" s="14" t="inlineStr">
+        <is>
+          <t>구역 추천 GIS</t>
+        </is>
+      </c>
+      <c r="E39" s="14" t="inlineStr">
+        <is>
+          <t>GIS 지도 + 순위 마커</t>
+        </is>
+      </c>
+      <c r="F39" s="14" t="inlineStr">
+        <is>
+          <t>UI-PAR-003-04</t>
+        </is>
+      </c>
+      <c r="G39" s="15" t="inlineStr">
+        <is>
+          <t>GIS 지도에 추천 구역 순위 핀 마커 표시 — 핀 클릭 시 상세 팝업</t>
+        </is>
+      </c>
+      <c r="H39" s="14" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I28" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J28" s="14" t="inlineStr">
+      <c r="I39" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J39" s="14" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K28" s="26" t="n"/>
-    </row>
-    <row r="29" ht="32.1" customHeight="1">
-      <c r="A29" s="25" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-05</t>
-        </is>
-      </c>
-      <c r="B29" s="14" t="inlineStr">
-        <is>
-          <t>FN-PAR-03-02-03</t>
-        </is>
-      </c>
-      <c r="C29" s="32" t="inlineStr">
-        <is>
-          <t>정책 효과 시뮬레이션</t>
-        </is>
-      </c>
-      <c r="D29" s="32" t="inlineStr">
-        <is>
-          <t>정책 변수 설정</t>
-        </is>
-      </c>
-      <c r="E29" s="14" t="inlineStr">
-        <is>
-          <t>이면도로 정비 파라미터</t>
-        </is>
-      </c>
-      <c r="F29" s="14" t="inlineStr">
-        <is>
-          <t>UI-PAR-003-02-1</t>
-        </is>
-      </c>
-      <c r="G29" s="15" t="inlineStr">
-        <is>
-          <t>[이면도로 정비] 대상 지역·정비 방식(상업지역형(주차환경개선지구)/주거지역형(주민참여형))·정비 구간 연장(m) 입력</t>
-        </is>
-      </c>
-      <c r="H29" s="14" t="inlineStr">
+      <c r="K39" s="26" t="n"/>
+    </row>
+    <row r="40" ht="32" customHeight="1" s="60">
+      <c r="A40" s="50" t="inlineStr">
+        <is>
+          <t>REQ-SFR-003-06</t>
+        </is>
+      </c>
+      <c r="B40" s="51" t="inlineStr">
+        <is>
+          <t>FN-PAR-03-04-03</t>
+        </is>
+      </c>
+      <c r="C40" s="52" t="inlineStr">
+        <is>
+          <t>구역추천</t>
+        </is>
+      </c>
+      <c r="D40" s="51" t="inlineStr">
+        <is>
+          <t>요금제 적용 추천 구역 순위</t>
+        </is>
+      </c>
+      <c r="E40" s="51" t="inlineStr">
+        <is>
+          <t>구역 추천 결과 목록</t>
+        </is>
+      </c>
+      <c r="F40" s="51" t="inlineStr">
+        <is>
+          <t>UI-PAR-003-04</t>
+        </is>
+      </c>
+      <c r="G40" s="53" t="inlineStr">
+        <is>
+          <t>민원 증가 추세를 분석하여 요금제·공유주차제 적용 추천 구역 순위 표시 — 산정 기준 ⓘ 팝오버 제공, 목록과 지도 연동</t>
+        </is>
+      </c>
+      <c r="H40" s="51" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I29" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J29" s="14" t="inlineStr">
+      <c r="I40" s="54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J40" s="51" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K29" s="26" t="n"/>
-    </row>
-    <row r="30" ht="32.1" customHeight="1">
-      <c r="A30" s="25" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-05</t>
-        </is>
-      </c>
-      <c r="B30" s="14" t="inlineStr">
-        <is>
-          <t>FN-PAR-03-02-04</t>
-        </is>
-      </c>
-      <c r="C30" s="32" t="inlineStr">
-        <is>
-          <t>정책 효과 시뮬레이션</t>
-        </is>
-      </c>
-      <c r="D30" s="32" t="inlineStr">
-        <is>
-          <t>정책 변수 설정</t>
-        </is>
-      </c>
-      <c r="E30" s="14" t="inlineStr">
-        <is>
-          <t>요금제 적용 파라미터</t>
-        </is>
-      </c>
-      <c r="F30" s="14" t="inlineStr">
-        <is>
-          <t>UI-PAR-003-02-1</t>
-        </is>
-      </c>
-      <c r="G30" s="15" t="inlineStr">
-        <is>
-          <t>[요금제 적용] 대상 지역·적용 방식(요금 인상/무료→유료 전환)·적용 급지(전체/1급지(동)/2급지(읍·면), 제주 전체·시 전체 선택 시에만)·인상률(+10/20/30%, 요금 인상 시)</t>
-        </is>
-      </c>
-      <c r="H30" s="14" t="inlineStr">
+      <c r="K40" s="55" t="n"/>
+    </row>
+    <row r="41" ht="32" customHeight="1" s="60">
+      <c r="A41" s="50" t="inlineStr">
+        <is>
+          <t>REQ-SFR-003-10</t>
+        </is>
+      </c>
+      <c r="B41" s="51" t="inlineStr">
+        <is>
+          <t>FN-PAR-03-04-04</t>
+        </is>
+      </c>
+      <c r="C41" s="52" t="inlineStr">
+        <is>
+          <t>구역추천</t>
+        </is>
+      </c>
+      <c r="D41" s="51" t="inlineStr">
+        <is>
+          <t>내보내기</t>
+        </is>
+      </c>
+      <c r="E41" s="51" t="inlineStr">
+        <is>
+          <t>PDF/DOCX 내보내기</t>
+        </is>
+      </c>
+      <c r="F41" s="51" t="inlineStr">
+        <is>
+          <t>UI-PAR-003-04</t>
+        </is>
+      </c>
+      <c r="G41" s="53" t="inlineStr">
+        <is>
+          <t>분석 결과를 PDF/DOCX 보고서로 내보내기 — 내보낸 보고서는 보고서 목록의 직접 생성 보고서 목록에 표시</t>
+        </is>
+      </c>
+      <c r="H41" s="51" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I30" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J30" s="14" t="inlineStr">
+      <c r="I41" s="54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J41" s="51" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K30" s="26" t="inlineStr">
+      <c r="K41" s="55" t="n"/>
+    </row>
+    <row r="42" ht="32" customHeight="1" s="60" thickBot="1">
+      <c r="A42" s="23" t="inlineStr">
+        <is>
+          <t>REQ-SFR-005-04</t>
+        </is>
+      </c>
+      <c r="B42" s="16" t="inlineStr">
+        <is>
+          <t>FN-PAR-03-05-01</t>
+        </is>
+      </c>
+      <c r="C42" s="16" t="inlineStr">
+        <is>
+          <t>투자우선순위 보드</t>
+        </is>
+      </c>
+      <c r="D42" s="16" t="inlineStr">
+        <is>
+          <t>KPI 요약</t>
+        </is>
+      </c>
+      <c r="E42" s="16" t="inlineStr">
+        <is>
+          <t>KPI 카드</t>
+        </is>
+      </c>
+      <c r="F42" s="16" t="inlineStr">
+        <is>
+          <t>UI-PAR-003-05</t>
+        </is>
+      </c>
+      <c r="G42" s="17" t="inlineStr">
+        <is>
+          <t>분석 대상 주차장 수·높음 우선순위 개소·최근 3개월 사고 건수 KPI 카드 표시</t>
+        </is>
+      </c>
+      <c r="H42" s="16" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I42" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J42" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K42" s="24" t="inlineStr">
         <is>
           <t>설계감리 시정 완료</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="32.1" customHeight="1" thickBot="1">
-      <c r="A31" s="25" t="inlineStr">
+    <row r="43" ht="32" customHeight="1" s="60">
+      <c r="A43" s="25" t="inlineStr">
+        <is>
+          <t>REQ-SFR-005-04</t>
+        </is>
+      </c>
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t>FN-PAR-03-05-02</t>
+        </is>
+      </c>
+      <c r="C43" s="31" t="inlineStr">
+        <is>
+          <t>투자우선순위 보드</t>
+        </is>
+      </c>
+      <c r="D43" s="14" t="inlineStr">
+        <is>
+          <t>투자우선순위 GIS</t>
+        </is>
+      </c>
+      <c r="E43" s="14" t="inlineStr">
+        <is>
+          <t>GIS 지도 + 우선순위 마커</t>
+        </is>
+      </c>
+      <c r="F43" s="14" t="inlineStr">
+        <is>
+          <t>UI-PAR-003-05</t>
+        </is>
+      </c>
+      <c r="G43" s="15" t="inlineStr">
+        <is>
+          <t>제주 전역 GIS 지도에 우선순위 공영주차장 마커 표시(높음, 중간만 표시). 선택 시 주차장 상세 팝업(위치·총 면수·준공연도·경과연수)</t>
+        </is>
+      </c>
+      <c r="H43" s="14" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I43" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J43" s="14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K43" s="26" t="inlineStr">
+        <is>
+          <t>설계감리 시정 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="32" customHeight="1" s="60">
+      <c r="A44" s="25" t="inlineStr">
+        <is>
+          <t>REQ-SFR-005-04</t>
+        </is>
+      </c>
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>FN-PAR-03-05-03</t>
+        </is>
+      </c>
+      <c r="C44" s="31" t="inlineStr">
+        <is>
+          <t>투자우선순위 보드</t>
+        </is>
+      </c>
+      <c r="D44" s="31" t="inlineStr">
+        <is>
+          <t>투자우선순위 GIS</t>
+        </is>
+      </c>
+      <c r="E44" s="14" t="inlineStr">
+        <is>
+          <t>주차장 상세 팝업</t>
+        </is>
+      </c>
+      <c r="F44" s="14" t="inlineStr">
+        <is>
+          <t>UI-PAR-003-05</t>
+        </is>
+      </c>
+      <c r="G44" s="15" t="inlineStr">
+        <is>
+          <t>선택 주차장 팝업: 주차장명·주소·총 면수·준공연도·경과연수 및 안전위험도·민원 빈도·이용 패턴·단속 건수 4개 지표 게이지 표시</t>
+        </is>
+      </c>
+      <c r="H44" s="14" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I44" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J44" s="14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K44" s="26" t="inlineStr">
+        <is>
+          <t>설계감리 시정 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="32" customHeight="1" s="60">
+      <c r="A45" s="27" t="inlineStr">
+        <is>
+          <t>REQ-SFR-005-04</t>
+        </is>
+      </c>
+      <c r="B45" s="18" t="inlineStr">
+        <is>
+          <t>FN-PAR-03-05-04</t>
+        </is>
+      </c>
+      <c r="C45" s="33" t="inlineStr">
+        <is>
+          <t>투자우선순위 보드</t>
+        </is>
+      </c>
+      <c r="D45" s="18" t="inlineStr">
+        <is>
+          <t>투자·보강 우선순위 목록</t>
+        </is>
+      </c>
+      <c r="E45" s="18" t="inlineStr">
+        <is>
+          <t>종합점수 기반 순위 Top 목록</t>
+        </is>
+      </c>
+      <c r="F45" s="18" t="inlineStr">
+        <is>
+          <t>UI-PAR-003-05</t>
+        </is>
+      </c>
+      <c r="G45" s="19" t="inlineStr">
+        <is>
+          <t>종합점수(안전위험도 25%·민원 빈도 25%·이용 패턴 20%·단속 건수 25% — 설정에서 가중치 변경 가능) 기준 우선순위 목록 — 행 클릭 시 지도 확대 이동·팝업, 등급(높음/중간/낮음) 점 표시</t>
+        </is>
+      </c>
+      <c r="H45" s="18" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I45" s="39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J45" s="18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K45" s="28" t="inlineStr">
+        <is>
+          <t>설계감리 시정 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="32" customHeight="1" s="60">
+      <c r="A46" s="27" t="inlineStr">
         <is>
           <t>REQ-SFR-003-10</t>
         </is>
       </c>
-      <c r="B31" s="14" t="inlineStr">
-        <is>
-          <t>FN-PAR-03-02-05</t>
-        </is>
-      </c>
-      <c r="C31" s="32" t="inlineStr">
-        <is>
-          <t>정책 효과 시뮬레이션</t>
-        </is>
-      </c>
-      <c r="D31" s="14" t="inlineStr">
-        <is>
-          <t>효과 예측 결과</t>
-        </is>
-      </c>
-      <c r="E31" s="14" t="inlineStr">
-        <is>
-          <t>효과 예측 KPI 카드</t>
-        </is>
-      </c>
-      <c r="F31" s="14" t="inlineStr">
-        <is>
-          <t>UI-PAR-003-02</t>
-        </is>
-      </c>
-      <c r="G31" s="15" t="inlineStr">
-        <is>
-          <t>효과 예측 KPI: 민원 감소 예측·혼잡도 개선(혼잡 지수 = (정상 이용+불법주차)÷공급 면수). 분석 근거 ⓘ 팝오버(가정값 기반 고지 포함)</t>
-        </is>
-      </c>
-      <c r="H31" s="14" t="inlineStr">
+      <c r="B46" s="18" t="inlineStr">
+        <is>
+          <t>FN-PAR-03-05-05</t>
+        </is>
+      </c>
+      <c r="C46" s="33" t="inlineStr">
+        <is>
+          <t>투자우선순위 보드</t>
+        </is>
+      </c>
+      <c r="D46" s="18" t="inlineStr">
+        <is>
+          <t>내보내기</t>
+        </is>
+      </c>
+      <c r="E46" s="18" t="inlineStr">
+        <is>
+          <t>PDF/DOCX 내보내기</t>
+        </is>
+      </c>
+      <c r="F46" s="18" t="inlineStr">
+        <is>
+          <t>UI-PAR-003-05</t>
+        </is>
+      </c>
+      <c r="G46" s="19" t="inlineStr">
+        <is>
+          <t>분석 결과를 PDF/DOCX 보고서로 내보내기 — 내보낸 보고서는 보고서 목록의 직접 생성 보고서 목록에 표시</t>
+        </is>
+      </c>
+      <c r="H46" s="18" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I31" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J31" s="14" t="inlineStr">
+      <c r="I46" s="39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J46" s="18" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K31" s="26" t="n"/>
-    </row>
-    <row r="32" ht="32.1" customHeight="1">
-      <c r="A32" s="25" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-12</t>
-        </is>
-      </c>
-      <c r="B32" s="14" t="inlineStr">
-        <is>
-          <t>FN-PAR-03-02-06</t>
-        </is>
-      </c>
-      <c r="C32" s="32" t="inlineStr">
-        <is>
-          <t>정책 효과 시뮬레이션</t>
-        </is>
-      </c>
-      <c r="D32" s="14" t="inlineStr">
-        <is>
-          <t>시나리오 비교 테이블</t>
-        </is>
-      </c>
-      <c r="E32" s="14" t="inlineStr">
-        <is>
-          <t>비교 결과 PDF 다운로드</t>
-        </is>
-      </c>
-      <c r="F32" s="14" t="inlineStr">
-        <is>
-          <t>UI-PAR-003-02</t>
-        </is>
-      </c>
-      <c r="G32" s="15" t="inlineStr">
-        <is>
-          <t>시나리오 비교 테이블 — 정책 유형 필터 칩(건수 병기), 체크박스 선택 내보내기(PDF/DOCX, 비교 차트 포함), 행 삭제(확인 모달)</t>
-        </is>
-      </c>
-      <c r="H32" s="14" t="inlineStr">
+      <c r="K46" s="28" t="n"/>
+    </row>
+    <row r="47" ht="32" customHeight="1" s="60">
+      <c r="A47" s="29" t="inlineStr">
+        <is>
+          <t>REQ-SFR-005-05</t>
+        </is>
+      </c>
+      <c r="B47" s="20" t="inlineStr">
+        <is>
+          <t>FN-PAR-04-01-01</t>
+        </is>
+      </c>
+      <c r="C47" s="20" t="inlineStr">
+        <is>
+          <t>보고서 목록</t>
+        </is>
+      </c>
+      <c r="D47" s="20" t="inlineStr">
+        <is>
+          <t>자동 생성 보고서 목록</t>
+        </is>
+      </c>
+      <c r="E47" s="20" t="inlineStr">
+        <is>
+          <t>자동 생성 보고서 목록</t>
+        </is>
+      </c>
+      <c r="F47" s="20" t="inlineStr">
+        <is>
+          <t>UI-PAR-004-01</t>
+        </is>
+      </c>
+      <c r="G47" s="21" t="inlineStr">
+        <is>
+          <t>자동 생성된 보고서 목록 조회.</t>
+        </is>
+      </c>
+      <c r="H47" s="20" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I32" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J32" s="14" t="inlineStr">
+      <c r="I47" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J47" s="20" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K32" s="26" t="inlineStr">
+      <c r="K47" s="30" t="n"/>
+    </row>
+    <row r="48" ht="32" customHeight="1" s="60">
+      <c r="A48" s="25" t="inlineStr">
+        <is>
+          <t>REQ-SFR-003-11</t>
+        </is>
+      </c>
+      <c r="B48" s="14" t="inlineStr">
+        <is>
+          <t>FN-PAR-04-01-02</t>
+        </is>
+      </c>
+      <c r="C48" s="31" t="inlineStr">
+        <is>
+          <t>보고서 목록</t>
+        </is>
+      </c>
+      <c r="D48" s="14" t="inlineStr">
+        <is>
+          <t>직접 생성 보고서 목록</t>
+        </is>
+      </c>
+      <c r="E48" s="14" t="inlineStr">
+        <is>
+          <t>직접 생성 보고서 목록</t>
+        </is>
+      </c>
+      <c r="F48" s="14" t="inlineStr">
+        <is>
+          <t>UI-PAR-004-01</t>
+        </is>
+      </c>
+      <c r="G48" s="15" t="inlineStr">
+        <is>
+          <t>직접 생성 보고서 목록 — 보고서명 검색·출처·생성일 필터, 행 삭제(확인 모달)</t>
+        </is>
+      </c>
+      <c r="H48" s="14" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I48" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J48" s="14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K48" s="26" t="inlineStr">
         <is>
           <t>설계감리 시정 완료</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="32.1" customHeight="1">
-      <c r="A33" s="23" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-04</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="inlineStr">
-        <is>
-          <t>FN-PAR-03-03-01</t>
-        </is>
-      </c>
-      <c r="C33" s="16" t="inlineStr">
-        <is>
-          <t>생활권 시뮬레이션</t>
-        </is>
-      </c>
-      <c r="D33" s="16" t="inlineStr">
-        <is>
-          <t>생활권 분석 설정</t>
-        </is>
-      </c>
-      <c r="E33" s="16" t="inlineStr">
-        <is>
-          <t>분석 조건 설정 패널</t>
-        </is>
-      </c>
-      <c r="F33" s="16" t="inlineStr">
-        <is>
-          <t>UI-PAR-003-03</t>
-        </is>
-      </c>
-      <c r="G33" s="17" t="inlineStr">
-        <is>
-          <t>분석 내용 선택·분석 지역·분석 기간(최근1/3/6개월·직접 설정·날짜 범위)·격자 크기(1km/500m/250m/100m) 설정 후 생활권 분석 실행</t>
-        </is>
-      </c>
-      <c r="H33" s="16" t="inlineStr">
+    <row r="49" ht="32" customHeight="1" s="60">
+      <c r="A49" s="25" t="inlineStr">
+        <is>
+          <t>REQ-SFR-005-05</t>
+        </is>
+      </c>
+      <c r="B49" s="14" t="inlineStr">
+        <is>
+          <t>FN-PAR-04-02-01</t>
+        </is>
+      </c>
+      <c r="C49" s="14" t="inlineStr">
+        <is>
+          <t>보고서 관리</t>
+        </is>
+      </c>
+      <c r="D49" s="14" t="inlineStr">
+        <is>
+          <t>자동 생성 설정 목록</t>
+        </is>
+      </c>
+      <c r="E49" s="14" t="inlineStr">
+        <is>
+          <t>자동 생성 설정 목록</t>
+        </is>
+      </c>
+      <c r="F49" s="14" t="inlineStr">
+        <is>
+          <t>UI-PAR-004-02</t>
+        </is>
+      </c>
+      <c r="G49" s="15" t="inlineStr">
+        <is>
+          <t>보고서 자동 생성 설정에서 확인된 목록 조회, 수정 버튼 클릭시 배포부서/배포주기/배포일자 수정</t>
+        </is>
+      </c>
+      <c r="H49" s="14" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I33" s="37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J33" s="16" t="inlineStr">
+      <c r="I49" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J49" s="14" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K33" s="24" t="n"/>
-    </row>
-    <row r="34" ht="32.1" customHeight="1">
-      <c r="A34" s="25" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-09</t>
-        </is>
-      </c>
-      <c r="B34" s="14" t="inlineStr">
-        <is>
-          <t>FN-PAR-03-03-02</t>
-        </is>
-      </c>
-      <c r="C34" s="32" t="inlineStr">
-        <is>
-          <t>생활권 시뮬레이션</t>
-        </is>
-      </c>
-      <c r="D34" s="14" t="inlineStr">
-        <is>
-          <t>격자 GIS 지도</t>
-        </is>
-      </c>
-      <c r="E34" s="14" t="inlineStr">
-        <is>
-          <t>격자 히트맵 시각화</t>
-        </is>
-      </c>
-      <c r="F34" s="14" t="inlineStr">
-        <is>
-          <t>UI-PAR-003-03</t>
-        </is>
-      </c>
-      <c r="G34" s="15" t="inlineStr">
-        <is>
-          <t>격자(100m~1km) 기반 GIS 히트맵 — 5단계 색상(심각/경고/주의/보통/낮음). 민원·수급은 백분위, 혼잡도는 절대 기준(지수 1.0=100점)</t>
-        </is>
-      </c>
-      <c r="H34" s="14" t="inlineStr">
+      <c r="K49" s="26" t="n"/>
+    </row>
+    <row r="50" ht="32" customHeight="1" s="60">
+      <c r="A50" s="27" t="inlineStr">
+        <is>
+          <t>REQ-SFR-005-06</t>
+        </is>
+      </c>
+      <c r="B50" s="18" t="inlineStr">
+        <is>
+          <t>FN-PAR-04-02-02</t>
+        </is>
+      </c>
+      <c r="C50" s="33" t="inlineStr">
+        <is>
+          <t>보고서 관리</t>
+        </is>
+      </c>
+      <c r="D50" s="18" t="inlineStr">
+        <is>
+          <t>보고서 자동 생성 설정</t>
+        </is>
+      </c>
+      <c r="E50" s="18" t="inlineStr">
+        <is>
+          <t>배포 부서·배포 주기·배포 일자 설정</t>
+        </is>
+      </c>
+      <c r="F50" s="18" t="inlineStr">
+        <is>
+          <t>UI-PAR-004-02</t>
+        </is>
+      </c>
+      <c r="G50" s="19" t="inlineStr">
+        <is>
+          <t>배포 부서, 배포 주기, 배포 일자, 보고서 자동생성버튼</t>
+        </is>
+      </c>
+      <c r="H50" s="18" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I34" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J34" s="14" t="inlineStr">
+      <c r="I50" s="39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J50" s="18" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K34" s="26" t="n"/>
-    </row>
-    <row r="35" ht="32.1" customHeight="1">
-      <c r="A35" s="25" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-04</t>
-        </is>
-      </c>
-      <c r="B35" s="14" t="inlineStr">
-        <is>
-          <t>FN-PAR-03-03-03</t>
-        </is>
-      </c>
-      <c r="C35" s="32" t="inlineStr">
-        <is>
-          <t>생활권 시뮬레이션</t>
-        </is>
-      </c>
-      <c r="D35" s="32" t="inlineStr">
-        <is>
-          <t>격자 GIS 지도</t>
-        </is>
-      </c>
-      <c r="E35" s="14" t="inlineStr">
-        <is>
-          <t>격자 팝업</t>
-        </is>
-      </c>
-      <c r="F35" s="14" t="inlineStr">
-        <is>
-          <t>UI-PAR-003-03</t>
-        </is>
-      </c>
-      <c r="G35" s="15" t="inlineStr">
-        <is>
-          <t>선택 격자 클릭 시 팝업: 위치명·총 건수·기간· 유형별 건수 상세 표시</t>
-        </is>
-      </c>
-      <c r="H35" s="14" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I35" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J35" s="14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K35" s="26" t="n"/>
-    </row>
-    <row r="36" ht="32.1" customHeight="1">
-      <c r="A36" s="25" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-04</t>
-        </is>
-      </c>
-      <c r="B36" s="14" t="inlineStr">
-        <is>
-          <t>FN-PAR-03-03-04</t>
-        </is>
-      </c>
-      <c r="C36" s="32" t="inlineStr">
-        <is>
-          <t>생활권 시뮬레이션</t>
-        </is>
-      </c>
-      <c r="D36" s="14" t="inlineStr">
-        <is>
-          <t>분석 결과 요약</t>
-        </is>
-      </c>
-      <c r="E36" s="14" t="inlineStr">
-        <is>
-          <t>격자 기반 분석 요약 패널</t>
-        </is>
-      </c>
-      <c r="F36" s="14" t="inlineStr">
-        <is>
-          <t>UI-PAR-003-03</t>
-        </is>
-      </c>
-      <c r="G36" s="15" t="inlineStr">
-        <is>
-          <t>총 분석 격자 수 + 5단계 격자 수 요약, 격자 크기 칩·등급 산정 기준 ⓘ 팝오버</t>
-        </is>
-      </c>
-      <c r="H36" s="14" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I36" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J36" s="14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K36" s="26" t="inlineStr">
-        <is>
-          <t>설계감리 시정 완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="32.1" customHeight="1">
-      <c r="A37" s="27" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-04</t>
-        </is>
-      </c>
-      <c r="B37" s="18" t="inlineStr">
-        <is>
-          <t>FN-PAR-03-03-05</t>
-        </is>
-      </c>
-      <c r="C37" s="34" t="inlineStr">
-        <is>
-          <t>생활권 시뮬레이션</t>
-        </is>
-      </c>
-      <c r="D37" s="18" t="inlineStr">
-        <is>
-          <t>민원 집중구역 목록</t>
-        </is>
-      </c>
-      <c r="E37" s="18" t="inlineStr">
-        <is>
-          <t>격자 기반 집중구역 Top 목록</t>
-        </is>
-      </c>
-      <c r="F37" s="18" t="inlineStr">
-        <is>
-          <t>UI-PAR-003-03</t>
-        </is>
-      </c>
-      <c r="G37" s="19" t="inlineStr">
-        <is>
-          <t>격자 분석 집중 구역 Top8(심각·경고·주의) 목록 — 동 + 격자 중심 POI 명칭으로 표시. 행 클릭 시 지도 이동·팝업. 혼잡도 모드는 혼잡 점수 안내 ⓘ 제공</t>
-        </is>
-      </c>
-      <c r="H37" s="18" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I37" s="39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J37" s="18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K37" s="28" t="n"/>
-    </row>
-    <row r="38" ht="32.1" customHeight="1">
-      <c r="A38" s="27" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-10</t>
-        </is>
-      </c>
-      <c r="B38" s="18" t="inlineStr">
-        <is>
-          <t>FN-PAR-03-03-06</t>
-        </is>
-      </c>
-      <c r="C38" s="34" t="inlineStr">
-        <is>
-          <t>생활권 시뮬레이션</t>
-        </is>
-      </c>
-      <c r="D38" s="18" t="inlineStr">
-        <is>
-          <t>내보내기</t>
-        </is>
-      </c>
-      <c r="E38" s="18" t="inlineStr">
-        <is>
-          <t>PDF/DOCX 내보내기</t>
-        </is>
-      </c>
-      <c r="F38" s="18" t="inlineStr">
-        <is>
-          <t>UI-PAR-003-03</t>
-        </is>
-      </c>
-      <c r="G38" s="19" t="inlineStr">
-        <is>
-          <t>분석 결과를 PDF/DOCX 보고서로 내보내기 — 내보낸 보고서는 보고서 목록의 직접 생성 보고서 목록에 표시</t>
-        </is>
-      </c>
-      <c r="H38" s="18" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I38" s="39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J38" s="18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K38" s="28" t="inlineStr"/>
-    </row>
-    <row r="39" ht="32.1" customHeight="1">
-      <c r="A39" s="23" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-06</t>
-        </is>
-      </c>
-      <c r="B39" s="16" t="inlineStr">
-        <is>
-          <t>FN-PAR-03-04-01</t>
-        </is>
-      </c>
-      <c r="C39" s="16" t="inlineStr">
-        <is>
-          <t>구역추천</t>
-        </is>
-      </c>
-      <c r="D39" s="16" t="inlineStr">
-        <is>
-          <t>구역 추천 설정</t>
-        </is>
-      </c>
-      <c r="E39" s="16" t="inlineStr">
-        <is>
-          <t>추천 조건 설정 패널</t>
-        </is>
-      </c>
-      <c r="F39" s="16" t="inlineStr">
-        <is>
-          <t>UI-PAR-003-04</t>
-        </is>
-      </c>
-      <c r="G39" s="17" t="inlineStr">
-        <is>
-          <t>분석 내용(요금제 적용/공유주차제 적용)·분석 지역·분석 기간(월 단위) 설정 후 구역 추천 실행</t>
-        </is>
-      </c>
-      <c r="H39" s="16" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I39" s="37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J39" s="16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K39" s="24" t="n"/>
-    </row>
-    <row r="40" ht="32.1" customHeight="1" thickBot="1">
-      <c r="A40" s="25" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-06</t>
-        </is>
-      </c>
-      <c r="B40" s="14" t="inlineStr">
-        <is>
-          <t>FN-PAR-03-04-02</t>
-        </is>
-      </c>
-      <c r="C40" s="32" t="inlineStr">
-        <is>
-          <t>구역추천</t>
-        </is>
-      </c>
-      <c r="D40" s="14" t="inlineStr">
-        <is>
-          <t>구역 추천 GIS</t>
-        </is>
-      </c>
-      <c r="E40" s="14" t="inlineStr">
-        <is>
-          <t>GIS 지도 + 순위 마커</t>
-        </is>
-      </c>
-      <c r="F40" s="14" t="inlineStr">
-        <is>
-          <t>UI-PAR-003-04</t>
-        </is>
-      </c>
-      <c r="G40" s="15" t="inlineStr">
-        <is>
-          <t>제주 전역 GIS 지도에 추천 구역 순위 핀 마커 표시 — 우선순위(높음/중간/낮음) 범례 색상, 핀 클릭 시 상세 팝업</t>
-        </is>
-      </c>
-      <c r="H40" s="14" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I40" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J40" s="14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K40" s="26" t="n"/>
-    </row>
-    <row r="41" ht="32.1" customHeight="1">
-      <c r="A41" s="25" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-06</t>
-        </is>
-      </c>
-      <c r="B41" s="14" t="inlineStr">
-        <is>
-          <t>FN-PAR-03-04-03</t>
-        </is>
-      </c>
-      <c r="C41" s="32" t="inlineStr">
-        <is>
-          <t>구역추천</t>
-        </is>
-      </c>
-      <c r="D41" s="14" t="inlineStr">
-        <is>
-          <t>분석 결과 요약</t>
-        </is>
-      </c>
-      <c r="E41" s="14" t="inlineStr">
-        <is>
-          <t>격자 기반 분석 요약 패널</t>
-        </is>
-      </c>
-      <c r="F41" s="14" t="inlineStr">
-        <is>
-          <t>UI-PAR-003-04</t>
-        </is>
-      </c>
-      <c r="G41" s="15" t="inlineStr">
-        <is>
-          <t>총 분석 격자 수·단계별(심각/경고/주의/양호) 격자 수 요약 패널</t>
-        </is>
-      </c>
-      <c r="H41" s="14" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I41" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J41" s="14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K41" s="26" t="n"/>
-    </row>
-    <row r="42" ht="32.1" customHeight="1">
-      <c r="A42" s="50" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-06</t>
-        </is>
-      </c>
-      <c r="B42" s="51" t="inlineStr">
-        <is>
-          <t>FN-PAR-03-04-04</t>
-        </is>
-      </c>
-      <c r="C42" s="52" t="inlineStr">
-        <is>
-          <t>구역추천</t>
-        </is>
-      </c>
-      <c r="D42" s="51" t="inlineStr">
-        <is>
-          <t>요금제 적용 추천 구역 순위</t>
-        </is>
-      </c>
-      <c r="E42" s="51" t="inlineStr">
-        <is>
-          <t>구역 추천 결과 Top 목록</t>
-        </is>
-      </c>
-      <c r="F42" s="51" t="inlineStr">
-        <is>
-          <t>UI-PAR-003-04</t>
-        </is>
-      </c>
-      <c r="G42" s="53" t="inlineStr">
-        <is>
-          <t>민원 증가 추세를 분석하여 요금제·공유주차제 적용 추천 구역 순위 표시 — 산정 기준 ⓘ 팝오버 제공, 목록과 지도 연동</t>
-        </is>
-      </c>
-      <c r="H42" s="51" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I42" s="54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J42" s="51" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K42" s="55" t="n"/>
-    </row>
-    <row r="43" ht="32.1" customHeight="1">
-      <c r="A43" s="50" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-10</t>
-        </is>
-      </c>
-      <c r="B43" s="51" t="inlineStr">
-        <is>
-          <t>FN-PAR-03-04-05</t>
-        </is>
-      </c>
-      <c r="C43" s="52" t="inlineStr">
-        <is>
-          <t>구역추천</t>
-        </is>
-      </c>
-      <c r="D43" s="51" t="inlineStr">
-        <is>
-          <t>내보내기</t>
-        </is>
-      </c>
-      <c r="E43" s="51" t="inlineStr">
-        <is>
-          <t>PDF/DOCX 내보내기</t>
-        </is>
-      </c>
-      <c r="F43" s="51" t="inlineStr">
-        <is>
-          <t>UI-PAR-003-04</t>
-        </is>
-      </c>
-      <c r="G43" s="53" t="inlineStr">
-        <is>
-          <t>분석 결과를 PDF/DOCX 보고서로 내보내기 — 내보낸 보고서는 보고서 목록의 직접 생성 보고서 목록에 표시</t>
-        </is>
-      </c>
-      <c r="H43" s="51" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I43" s="54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J43" s="51" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K43" s="55" t="inlineStr"/>
-    </row>
-    <row r="44" ht="32.1" customHeight="1" thickBot="1">
-      <c r="A44" s="23" t="inlineStr">
-        <is>
-          <t>REQ-SFR-005-04</t>
-        </is>
-      </c>
-      <c r="B44" s="16" t="inlineStr">
-        <is>
-          <t>FN-PAR-03-05-01</t>
-        </is>
-      </c>
-      <c r="C44" s="16" t="inlineStr">
-        <is>
-          <t>투자우선순위 보드</t>
-        </is>
-      </c>
-      <c r="D44" s="16" t="inlineStr">
-        <is>
-          <t>KPI 요약</t>
-        </is>
-      </c>
-      <c r="E44" s="16" t="inlineStr">
-        <is>
-          <t>KPI 카드</t>
-        </is>
-      </c>
-      <c r="F44" s="16" t="inlineStr">
-        <is>
-          <t>UI-PAR-003-05</t>
-        </is>
-      </c>
-      <c r="G44" s="17" t="inlineStr">
-        <is>
-          <t>분석 대상 주차장 수·높음 우선순위 개소·최근 3개월 사고 건수 KPI 카드 표시</t>
-        </is>
-      </c>
-      <c r="H44" s="16" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I44" s="37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J44" s="16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K44" s="24" t="inlineStr">
-        <is>
-          <t>설계감리 시정 완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="32.1" customHeight="1">
-      <c r="A45" s="25" t="inlineStr">
-        <is>
-          <t>REQ-SFR-005-04</t>
-        </is>
-      </c>
-      <c r="B45" s="14" t="inlineStr">
-        <is>
-          <t>FN-PAR-03-05-02</t>
-        </is>
-      </c>
-      <c r="C45" s="31" t="inlineStr">
-        <is>
-          <t>투자우선순위 보드</t>
-        </is>
-      </c>
-      <c r="D45" s="14" t="inlineStr">
-        <is>
-          <t>투자우선순위 GIS</t>
-        </is>
-      </c>
-      <c r="E45" s="14" t="inlineStr">
-        <is>
-          <t>GIS 지도 + 우선순위 마커</t>
-        </is>
-      </c>
-      <c r="F45" s="14" t="inlineStr">
-        <is>
-          <t>UI-PAR-003-05</t>
-        </is>
-      </c>
-      <c r="G45" s="15" t="inlineStr">
-        <is>
-          <t>제주 전역 GIS 지도에 공영주차장 위치별 우선순위(높음/중간/낮음) 색상 마커 표시. 선택 시 주차장 상세 팝업(위치·총 면수·준공연도·경과연수)</t>
-        </is>
-      </c>
-      <c r="H45" s="14" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I45" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J45" s="14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K45" s="26" t="inlineStr">
-        <is>
-          <t>설계감리 시정 완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="32.1" customHeight="1">
-      <c r="A46" s="25" t="inlineStr">
-        <is>
-          <t>REQ-SFR-005-04</t>
-        </is>
-      </c>
-      <c r="B46" s="14" t="inlineStr">
-        <is>
-          <t>FN-PAR-03-05-03</t>
-        </is>
-      </c>
-      <c r="C46" s="31" t="inlineStr">
-        <is>
-          <t>투자우선순위 보드</t>
-        </is>
-      </c>
-      <c r="D46" s="31" t="inlineStr">
-        <is>
-          <t>투자우선순위 GIS</t>
-        </is>
-      </c>
-      <c r="E46" s="14" t="inlineStr">
-        <is>
-          <t>주차장 상세 팝업</t>
-        </is>
-      </c>
-      <c r="F46" s="14" t="inlineStr">
-        <is>
-          <t>UI-PAR-003-05</t>
-        </is>
-      </c>
-      <c r="G46" s="15" t="inlineStr">
-        <is>
-          <t>선택 주차장 팝업: 주차장명·주소·총 면수·준공연도·경과연수 및 안전위험도·민원 빈도·이용 패턴·단속 건수 4개 지표 게이지 표시</t>
-        </is>
-      </c>
-      <c r="H46" s="14" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I46" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J46" s="14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K46" s="26" t="inlineStr">
-        <is>
-          <t>설계감리 시정 완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="32.1" customHeight="1">
-      <c r="A47" s="27" t="inlineStr">
-        <is>
-          <t>REQ-SFR-005-04</t>
-        </is>
-      </c>
-      <c r="B47" s="18" t="inlineStr">
-        <is>
-          <t>FN-PAR-03-05-04</t>
-        </is>
-      </c>
-      <c r="C47" s="33" t="inlineStr">
-        <is>
-          <t>투자우선순위 보드</t>
-        </is>
-      </c>
-      <c r="D47" s="18" t="inlineStr">
-        <is>
-          <t>투자·보강 우선순위 목록</t>
-        </is>
-      </c>
-      <c r="E47" s="18" t="inlineStr">
-        <is>
-          <t>종합점수 기반 순위 Top 목록</t>
-        </is>
-      </c>
-      <c r="F47" s="18" t="inlineStr">
-        <is>
-          <t>UI-PAR-003-05</t>
-        </is>
-      </c>
-      <c r="G47" s="19" t="inlineStr">
-        <is>
-          <t>종합점수(안전위험도 25%·민원 빈도 25%·이용 패턴 20%·단속 건수 25% — 설정에서 가중치 변경 가능) 기준 우선순위 목록 — 행 클릭 시 지도 확대 이동·팝업, 등급(높음/중간/낮음) 점 표시</t>
-        </is>
-      </c>
-      <c r="H47" s="18" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I47" s="39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J47" s="18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K47" s="28" t="inlineStr">
-        <is>
-          <t>설계감리 시정 완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="32.1" customHeight="1">
-      <c r="A48" s="27" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-10</t>
-        </is>
-      </c>
-      <c r="B48" s="18" t="inlineStr">
-        <is>
-          <t>FN-PAR-03-05-05</t>
-        </is>
-      </c>
-      <c r="C48" s="33" t="inlineStr">
-        <is>
-          <t>투자우선순위 보드</t>
-        </is>
-      </c>
-      <c r="D48" s="18" t="inlineStr">
-        <is>
-          <t>내보내기</t>
-        </is>
-      </c>
-      <c r="E48" s="18" t="inlineStr">
-        <is>
-          <t>PDF/DOCX 내보내기</t>
-        </is>
-      </c>
-      <c r="F48" s="18" t="inlineStr">
-        <is>
-          <t>UI-PAR-003-05</t>
-        </is>
-      </c>
-      <c r="G48" s="19" t="inlineStr">
-        <is>
-          <t>분석 결과를 PDF/DOCX 보고서로 내보내기 — 내보낸 보고서는 보고서 목록의 직접 생성 보고서 목록에 표시</t>
-        </is>
-      </c>
-      <c r="H48" s="18" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I48" s="39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J48" s="18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K48" s="28" t="inlineStr"/>
-    </row>
-    <row r="49" ht="32.1" customHeight="1">
-      <c r="A49" s="29" t="inlineStr">
-        <is>
-          <t>REQ-SFR-005-05</t>
-        </is>
-      </c>
-      <c r="B49" s="20" t="inlineStr">
-        <is>
-          <t>FN-PAR-04-01-01</t>
-        </is>
-      </c>
-      <c r="C49" s="20" t="inlineStr">
-        <is>
-          <t>보고서 목록</t>
-        </is>
-      </c>
-      <c r="D49" s="20" t="inlineStr">
-        <is>
-          <t>자동 생성 보고서 목록</t>
-        </is>
-      </c>
-      <c r="E49" s="20" t="inlineStr">
-        <is>
-          <t>자동 생성 보고서 목록</t>
-        </is>
-      </c>
-      <c r="F49" s="20" t="inlineStr">
-        <is>
-          <t>UI-PAR-004-01</t>
-        </is>
-      </c>
-      <c r="G49" s="21" t="inlineStr">
-        <is>
-          <t>자동 생성된 보고서 목록 조회.</t>
-        </is>
-      </c>
-      <c r="H49" s="20" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I49" s="56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J49" s="20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K49" s="30" t="n"/>
-    </row>
-    <row r="50" ht="32.1" customHeight="1">
-      <c r="A50" s="25" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-11</t>
-        </is>
-      </c>
-      <c r="B50" s="14" t="inlineStr">
-        <is>
-          <t>FN-PAR-04-01-02</t>
-        </is>
-      </c>
-      <c r="C50" s="31" t="inlineStr">
-        <is>
-          <t>보고서 목록</t>
-        </is>
-      </c>
-      <c r="D50" s="14" t="inlineStr">
-        <is>
-          <t>직접 생성 보고서 목록</t>
-        </is>
-      </c>
-      <c r="E50" s="14" t="inlineStr">
-        <is>
-          <t>직접 생성 보고서 목록</t>
-        </is>
-      </c>
-      <c r="F50" s="14" t="inlineStr">
-        <is>
-          <t>UI-PAR-004-01</t>
-        </is>
-      </c>
-      <c r="G50" s="15" t="inlineStr">
-        <is>
-          <t>직접 생성 보고서 목록 — 보고서명 검색·출처·생성일 필터, 행 삭제(확인 모달)</t>
-        </is>
-      </c>
-      <c r="H50" s="14" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I50" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J50" s="14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K50" s="26" t="inlineStr">
-        <is>
-          <t>설계감리 시정 완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="32.1" customHeight="1">
-      <c r="A51" s="25" t="inlineStr">
-        <is>
-          <t>REQ-SFR-005-05</t>
-        </is>
-      </c>
-      <c r="B51" s="14" t="inlineStr">
-        <is>
-          <t>FN-PAR-04-02-01</t>
-        </is>
-      </c>
-      <c r="C51" s="14" t="inlineStr">
-        <is>
-          <t>보고서 관리</t>
-        </is>
-      </c>
-      <c r="D51" s="14" t="inlineStr">
-        <is>
-          <t>자동 생성 설정 목록</t>
-        </is>
-      </c>
-      <c r="E51" s="14" t="inlineStr">
-        <is>
-          <t>자동 생성 설정 목록</t>
-        </is>
-      </c>
-      <c r="F51" s="14" t="inlineStr">
-        <is>
-          <t>UI-PAR-004-02</t>
-        </is>
-      </c>
-      <c r="G51" s="15" t="inlineStr">
-        <is>
-          <t>보고서 자동 생성 설정에서 확인된 목록 조회, 수정 버튼 클릭시 배포부서/배포주기/배포일자 수정</t>
-        </is>
-      </c>
-      <c r="H51" s="14" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I51" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J51" s="14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K51" s="26" t="n"/>
-    </row>
-    <row r="52" ht="32.1" customHeight="1">
-      <c r="A52" s="27" t="inlineStr">
-        <is>
-          <t>REQ-SFR-005-06</t>
-        </is>
-      </c>
-      <c r="B52" s="18" t="inlineStr">
-        <is>
-          <t>FN-PAR-04-02-02</t>
-        </is>
-      </c>
-      <c r="C52" s="33" t="inlineStr">
-        <is>
-          <t>보고서 관리</t>
-        </is>
-      </c>
-      <c r="D52" s="18" t="inlineStr">
-        <is>
-          <t>보고서 자동 생성 설정</t>
-        </is>
-      </c>
-      <c r="E52" s="18" t="inlineStr">
-        <is>
-          <t>배포 부서·배포 주기·배포 일자 설정</t>
-        </is>
-      </c>
-      <c r="F52" s="18" t="inlineStr">
-        <is>
-          <t>UI-PAR-004-02</t>
-        </is>
-      </c>
-      <c r="G52" s="19" t="inlineStr">
-        <is>
-          <t>배포 부서, 배포 주기, 배포 일자, 보고서 자동생성버튼</t>
-        </is>
-      </c>
-      <c r="H52" s="18" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I52" s="39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J52" s="18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K52" s="28" t="inlineStr">
+      <c r="K50" s="28" t="inlineStr">
         <is>
           <t>REQ-SFR-005-05 
 설계감리 시정 완료</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="32.1" customHeight="1">
-      <c r="A53" s="29" t="inlineStr">
+    <row r="51" ht="32" customHeight="1" s="60">
+      <c r="A51" s="29" t="inlineStr">
         <is>
           <t>REQ-SFR-003-08</t>
         </is>
       </c>
-      <c r="B53" s="20" t="inlineStr">
+      <c r="B51" s="20" t="inlineStr">
         <is>
           <t>FN-PAR-04-03-01</t>
         </is>
       </c>
-      <c r="C53" s="20" t="inlineStr">
+      <c r="C51" s="20" t="inlineStr">
         <is>
           <t>위험단계 알림 조회</t>
         </is>
       </c>
-      <c r="D53" s="20" t="inlineStr">
+      <c r="D51" s="20" t="inlineStr">
         <is>
           <t>조회 단위 필터</t>
         </is>
       </c>
-      <c r="E53" s="20" t="inlineStr">
+      <c r="E51" s="20" t="inlineStr">
         <is>
           <t>기간 탭 및 상세 필터</t>
         </is>
       </c>
-      <c r="F53" s="20" t="inlineStr">
+      <c r="F51" s="20" t="inlineStr">
         <is>
           <t>UI-PAR-004-03</t>
         </is>
       </c>
-      <c r="G53" s="21" t="inlineStr">
+      <c r="G51" s="21" t="inlineStr">
         <is>
           <t>단계(전체/심각/경고/주의), 지역,기간 선택</t>
         </is>
       </c>
-      <c r="H53" s="20" t="inlineStr">
+      <c r="H51" s="20" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I53" s="56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J53" s="20" t="inlineStr">
+      <c r="I51" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J51" s="20" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K53" s="30" t="n"/>
-    </row>
-    <row r="54" ht="32.1" customHeight="1">
+      <c r="K51" s="30" t="n"/>
+    </row>
+    <row r="52" ht="32" customHeight="1" s="60">
+      <c r="A52" s="25" t="inlineStr">
+        <is>
+          <t>REQ-SFR-003-08</t>
+        </is>
+      </c>
+      <c r="B52" s="14" t="inlineStr">
+        <is>
+          <t>FN-PAR-04-03-02</t>
+        </is>
+      </c>
+      <c r="C52" s="32" t="inlineStr">
+        <is>
+          <t>위험단계 알림 조회</t>
+        </is>
+      </c>
+      <c r="D52" s="14" t="inlineStr">
+        <is>
+          <t>KPI 요약</t>
+        </is>
+      </c>
+      <c r="E52" s="14" t="inlineStr">
+        <is>
+          <t>KPI 카드</t>
+        </is>
+      </c>
+      <c r="F52" s="14" t="inlineStr">
+        <is>
+          <t>UI-PAR-004-03</t>
+        </is>
+      </c>
+      <c r="G52" s="15" t="inlineStr">
+        <is>
+          <t>KPI 카드(조회 알림 건수/위험 알림 건수/누적 민원 수) 표시</t>
+        </is>
+      </c>
+      <c r="H52" s="14" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I52" s="14" t="n"/>
+      <c r="J52" s="14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K52" s="26" t="n"/>
+    </row>
+    <row r="53" ht="32" customHeight="1" s="60">
+      <c r="A53" s="25" t="inlineStr">
+        <is>
+          <t>REQ-SFR-003-08</t>
+        </is>
+      </c>
+      <c r="B53" s="14" t="inlineStr">
+        <is>
+          <t>FN-PAR-04-03-03</t>
+        </is>
+      </c>
+      <c r="C53" s="32" t="inlineStr">
+        <is>
+          <t>위험단계 알림 조회</t>
+        </is>
+      </c>
+      <c r="D53" s="14" t="inlineStr">
+        <is>
+          <t>알림 이력 조회</t>
+        </is>
+      </c>
+      <c r="E53" s="14" t="inlineStr">
+        <is>
+          <t>알림 이력 테이블</t>
+        </is>
+      </c>
+      <c r="F53" s="14" t="inlineStr">
+        <is>
+          <t>UI-PAR-004-03</t>
+        </is>
+      </c>
+      <c r="G53" s="15" t="inlineStr">
+        <is>
+          <t>발송된 위험단계 알림 이력 테이블 — 단계(심각/경고/주의 배지)·지역·내용·일시·민원 수</t>
+        </is>
+      </c>
+      <c r="H53" s="14" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I53" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J53" s="14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K53" s="26" t="n"/>
+    </row>
+    <row r="54" ht="54" customHeight="1" s="60">
       <c r="A54" s="25" t="inlineStr">
         <is>
           <t>REQ-SFR-003-08</t>
@@ -6329,32 +6329,32 @@
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>FN-PAR-04-03-02</t>
-        </is>
-      </c>
-      <c r="C54" s="32" t="inlineStr">
-        <is>
-          <t>위험단계 알림 조회</t>
+          <t>FN-PAR-04-04-01</t>
+        </is>
+      </c>
+      <c r="C54" s="14" t="inlineStr">
+        <is>
+          <t>위험단계 알림 관리</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr">
         <is>
-          <t>KPI 요약</t>
+          <t>알림 기준 설정</t>
         </is>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t>KPI 카드</t>
+          <t>단계별 임계값 설정</t>
         </is>
       </c>
       <c r="F54" s="14" t="inlineStr">
         <is>
-          <t>UI-PAR-004-03</t>
+          <t>UI-PAR-004-04</t>
         </is>
       </c>
       <c r="G54" s="15" t="inlineStr">
         <is>
-          <t>KPI 카드(조회 알림 건수/위험 알림 건수/누적 민원 수) 표시</t>
+          <t>민원 증가율 기준 단계별 알림 기준 카드 — 심각 30%/경고 20%/주의 10% 이상 + 최소 건수 10건 표시. 설정 버튼 → 알림 기준 설정 팝업에서 단계별 증가율(%)·최소 건수 입력 후 저장(서비스 공통 반영, 다음날부터 적용, 민원 건수가 최소 건수 미만이면 알림 미발생)</t>
         </is>
       </c>
       <c r="H54" s="14" t="inlineStr">
@@ -6362,7 +6362,11 @@
           <t>신규</t>
         </is>
       </c>
-      <c r="I54" s="14" t="n"/>
+      <c r="I54" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="J54" s="14" t="inlineStr">
         <is>
           <t>O</t>
@@ -6370,1317 +6374,1211 @@
       </c>
       <c r="K54" s="26" t="n"/>
     </row>
-    <row r="55" ht="32.1" customHeight="1">
-      <c r="A55" s="25" t="inlineStr">
+    <row r="55" ht="32" customHeight="1" s="60">
+      <c r="A55" s="27" t="inlineStr">
         <is>
           <t>REQ-SFR-003-08</t>
         </is>
       </c>
-      <c r="B55" s="14" t="inlineStr">
-        <is>
-          <t>FN-PAR-04-03-03</t>
-        </is>
-      </c>
-      <c r="C55" s="32" t="inlineStr">
-        <is>
-          <t>위험단계 알림 조회</t>
-        </is>
-      </c>
-      <c r="D55" s="14" t="inlineStr">
-        <is>
-          <t>알림 이력 조회</t>
-        </is>
-      </c>
-      <c r="E55" s="14" t="inlineStr">
-        <is>
-          <t>알림 이력 테이블</t>
-        </is>
-      </c>
-      <c r="F55" s="14" t="inlineStr">
-        <is>
-          <t>UI-PAR-004-03</t>
-        </is>
-      </c>
-      <c r="G55" s="15" t="inlineStr">
-        <is>
-          <t>발송된 위험단계 알림 이력 테이블 — 단계(심각/경고/주의 배지)·지역·내용·일시·민원 수</t>
-        </is>
-      </c>
-      <c r="H55" s="14" t="inlineStr">
+      <c r="B55" s="18" t="inlineStr">
+        <is>
+          <t>FN-PAR-04-04-02</t>
+        </is>
+      </c>
+      <c r="C55" s="34" t="inlineStr">
+        <is>
+          <t>위험단계 알림 관리</t>
+        </is>
+      </c>
+      <c r="D55" s="18" t="inlineStr">
+        <is>
+          <t>수신자 관리</t>
+        </is>
+      </c>
+      <c r="E55" s="18" t="inlineStr">
+        <is>
+          <t>수신자 목록</t>
+        </is>
+      </c>
+      <c r="F55" s="18" t="inlineStr">
+        <is>
+          <t>UI-PAR-004-04</t>
+        </is>
+      </c>
+      <c r="G55" s="19" t="inlineStr">
+        <is>
+          <t>수신자 목록 및 추가 팝업 — 기본 정보는 로그인 사용자 자동 입력(사용자 목록 불러오기 전환 가능), 지역 다중 추가(+버튼·칩), 알림 단계 누적 선택. 삭제 시 확인 모달</t>
+        </is>
+      </c>
+      <c r="H55" s="18" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I55" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J55" s="14" t="inlineStr">
+      <c r="I55" s="39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J55" s="18" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K55" s="26" t="n"/>
-    </row>
-    <row r="56" ht="32.1" customHeight="1">
-      <c r="A56" s="25" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-08</t>
-        </is>
-      </c>
-      <c r="B56" s="14" t="inlineStr">
-        <is>
-          <t>FN-PAR-04-04-01</t>
-        </is>
-      </c>
-      <c r="C56" s="14" t="inlineStr">
-        <is>
-          <t>위험단계 알림 관리</t>
-        </is>
-      </c>
-      <c r="D56" s="14" t="inlineStr">
-        <is>
-          <t>알림 기준 설정</t>
-        </is>
-      </c>
-      <c r="E56" s="14" t="inlineStr">
-        <is>
-          <t>단계별 임계값 설정</t>
-        </is>
-      </c>
-      <c r="F56" s="14" t="inlineStr">
-        <is>
-          <t>UI-PAR-004-04</t>
-        </is>
-      </c>
-      <c r="G56" s="15" t="inlineStr">
-        <is>
-          <t>민원 증가율 기준 단계별 알림 기준 카드 — 심각 30%/경고 20%/주의 10% 이상 + 최소 건수 10건 표시. 설정 버튼 → 알림 기준 설정 팝업에서 단계별 증가율(%)·최소 건수 입력 후 저장(서비스 공통 반영, 다음날부터 적용, 민원 건수가 최소 건수 미만이면 알림 미발생)</t>
-        </is>
-      </c>
-      <c r="H56" s="14" t="inlineStr">
+      <c r="K55" s="28" t="n"/>
+    </row>
+    <row r="56" ht="32" customHeight="1" s="60">
+      <c r="A56" s="23" t="inlineStr">
+        <is>
+          <t>REQ-SFR-005-07</t>
+        </is>
+      </c>
+      <c r="B56" s="16" t="inlineStr">
+        <is>
+          <t>FN-PAR-05-01-01</t>
+        </is>
+      </c>
+      <c r="C56" s="16" t="inlineStr">
+        <is>
+          <t>AI 어시스턴트</t>
+        </is>
+      </c>
+      <c r="D56" s="16" t="inlineStr">
+        <is>
+          <t>AI 채팅</t>
+        </is>
+      </c>
+      <c r="E56" s="16" t="inlineStr">
+        <is>
+          <t>질문·답변 인터페이스</t>
+        </is>
+      </c>
+      <c r="F56" s="16" t="inlineStr">
+        <is>
+          <t>UI-PAR-005-01</t>
+        </is>
+      </c>
+      <c r="G56" s="17" t="inlineStr">
+        <is>
+          <t>sLLM 기반 대화형 인터페이스. 인사말 그리팅 표시. 자연어 질의응답·파일 첨부 지원. 행정 정보 검색·민원 분석 요청 처리</t>
+        </is>
+      </c>
+      <c r="H56" s="16" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I56" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J56" s="14" t="inlineStr">
+      <c r="I56" s="16" t="inlineStr">
+        <is>
+          <t>sLLM(EXAONE)</t>
+        </is>
+      </c>
+      <c r="J56" s="16" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K56" s="26" t="n"/>
-    </row>
-    <row r="57" ht="32.1" customHeight="1">
-      <c r="A57" s="27" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-08</t>
-        </is>
-      </c>
-      <c r="B57" s="18" t="inlineStr">
-        <is>
-          <t>FN-PAR-04-04-02</t>
-        </is>
-      </c>
-      <c r="C57" s="34" t="inlineStr">
-        <is>
-          <t>위험단계 알림 관리</t>
-        </is>
-      </c>
-      <c r="D57" s="18" t="inlineStr">
-        <is>
-          <t>수신자 관리</t>
-        </is>
-      </c>
-      <c r="E57" s="18" t="inlineStr">
-        <is>
-          <t>수신자 목록</t>
-        </is>
-      </c>
-      <c r="F57" s="18" t="inlineStr">
-        <is>
-          <t>UI-PAR-004-04</t>
-        </is>
-      </c>
-      <c r="G57" s="19" t="inlineStr">
-        <is>
-          <t>수신자 목록 및 추가 팝업 — 기본 정보는 로그인 사용자 자동 입력(사용자 목록 불러오기 전환 가능), 지역 다중 추가(+버튼·칩), 알림 단계 누적 선택. 삭제 시 확인 모달</t>
-        </is>
-      </c>
-      <c r="H57" s="18" t="inlineStr">
+      <c r="K56" s="24" t="n"/>
+    </row>
+    <row r="57" ht="32" customHeight="1" s="60">
+      <c r="A57" s="25" t="inlineStr">
+        <is>
+          <t>REQ-SFR-005-08</t>
+        </is>
+      </c>
+      <c r="B57" s="14" t="inlineStr">
+        <is>
+          <t>FN-PAR-05-01-02</t>
+        </is>
+      </c>
+      <c r="C57" s="32" t="inlineStr">
+        <is>
+          <t>AI 어시스턴트</t>
+        </is>
+      </c>
+      <c r="D57" s="32" t="inlineStr">
+        <is>
+          <t>AI 채팅</t>
+        </is>
+      </c>
+      <c r="E57" s="14" t="inlineStr">
+        <is>
+          <t>조례 검색·RAG 연계 답변</t>
+        </is>
+      </c>
+      <c r="F57" s="14" t="inlineStr">
+        <is>
+          <t>UI-PAR-005-01</t>
+        </is>
+      </c>
+      <c r="G57" s="15" t="inlineStr">
+        <is>
+          <t>민원 관련 행정 정보(조례 등) RAG 기반 검색 및 답변 생성. 조례명·원문 보기 링크 카드 형태 응답</t>
+        </is>
+      </c>
+      <c r="H57" s="14" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I57" s="39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J57" s="18" t="inlineStr">
+      <c r="I57" s="14" t="inlineStr">
+        <is>
+          <t>RAG·Vector DB</t>
+        </is>
+      </c>
+      <c r="J57" s="14" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K57" s="28" t="n"/>
-    </row>
-    <row r="58" ht="32.1" customHeight="1">
-      <c r="A58" s="23" t="inlineStr">
+      <c r="K57" s="26" t="n"/>
+    </row>
+    <row r="58" ht="32" customHeight="1" s="60">
+      <c r="A58" s="41" t="inlineStr">
+        <is>
+          <t>REQ-SFR-005-09</t>
+        </is>
+      </c>
+      <c r="B58" s="42" t="inlineStr">
+        <is>
+          <t>FN-PAR-05-05</t>
+        </is>
+      </c>
+      <c r="C58" s="57" t="inlineStr">
+        <is>
+          <t>AI 어시스턴트</t>
+        </is>
+      </c>
+      <c r="D58" s="32" t="inlineStr">
+        <is>
+          <t>AI 채팅</t>
+        </is>
+      </c>
+      <c r="E58" s="42" t="inlineStr">
+        <is>
+          <t>대량 민원 자동 요약</t>
+        </is>
+      </c>
+      <c r="F58" s="42" t="inlineStr">
+        <is>
+          <t>UI-PAR-005-02</t>
+        </is>
+      </c>
+      <c r="G58" s="43" t="inlineStr">
+        <is>
+          <t>대량 민원 내용을 sLLM으로 자동 요약하여 보고용 리포트 생성. AI 응답 하단 리포트 생성 버튼 제공</t>
+        </is>
+      </c>
+      <c r="H58" s="42" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I58" s="42" t="inlineStr">
+        <is>
+          <t>sLLM(EXAONE)</t>
+        </is>
+      </c>
+      <c r="J58" s="42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K58" s="44" t="n"/>
+    </row>
+    <row r="59" ht="32" customHeight="1" s="60">
+      <c r="A59" s="41" t="inlineStr">
+        <is>
+          <t>REQ-SFR-005-05</t>
+        </is>
+      </c>
+      <c r="B59" s="42" t="inlineStr">
+        <is>
+          <t>FN-PAR-05-06</t>
+        </is>
+      </c>
+      <c r="C59" s="57" t="inlineStr">
+        <is>
+          <t>AI 어시스턴트</t>
+        </is>
+      </c>
+      <c r="D59" s="32" t="inlineStr">
+        <is>
+          <t>AI 채팅</t>
+        </is>
+      </c>
+      <c r="E59" s="42" t="inlineStr">
+        <is>
+          <t>리포트 미리보기·다운로드</t>
+        </is>
+      </c>
+      <c r="F59" s="42" t="inlineStr">
+        <is>
+          <t>UI-PAR-005-03</t>
+        </is>
+      </c>
+      <c r="G59" s="43" t="inlineStr">
+        <is>
+          <t>AI 생성 민원 요약 보고서 미리보기 및 다운로드(PDF/DOCX)</t>
+        </is>
+      </c>
+      <c r="H59" s="42" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I59" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J59" s="42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K59" s="44" t="n"/>
+    </row>
+    <row r="60" ht="31" customHeight="1" s="60">
+      <c r="A60" s="41" t="inlineStr">
+        <is>
+          <t>REQ-SFR-005-01</t>
+        </is>
+      </c>
+      <c r="B60" s="42" t="inlineStr">
+        <is>
+          <t>FN-PAR-05-07</t>
+        </is>
+      </c>
+      <c r="C60" s="57" t="inlineStr">
+        <is>
+          <t>AI 어시스턴트</t>
+        </is>
+      </c>
+      <c r="D60" s="32" t="inlineStr">
+        <is>
+          <t>AI 채팅</t>
+        </is>
+      </c>
+      <c r="E60" s="42" t="inlineStr">
+        <is>
+          <t>융합 데이터 통합 분석 답변</t>
+        </is>
+      </c>
+      <c r="F60" s="42" t="inlineStr">
+        <is>
+          <t>UI-PAR-005-04</t>
+        </is>
+      </c>
+      <c r="G60" s="43" t="inlineStr">
+        <is>
+          <t>민원 데이터와 감시(화재·안전) 데이터를 결합해야 답이 나오는 질문에 AI 에이전트를 호출, 융합 데이터에서 종합 인사이트를 도출하여 AI 어시스턴트 답변으로 표시. 리포트 생성 버튼 제공</t>
+        </is>
+      </c>
+      <c r="H60" s="42" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I60" s="42" t="inlineStr">
+        <is>
+          <t>AI 에이전트</t>
+        </is>
+      </c>
+      <c r="J60" s="42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K60" s="44" t="n"/>
+    </row>
+    <row r="61" ht="31" customHeight="1" s="60">
+      <c r="A61" s="25" t="inlineStr">
         <is>
           <t>REQ-SFR-005-07</t>
         </is>
       </c>
-      <c r="B58" s="16" t="inlineStr">
-        <is>
-          <t>FN-PAR-05-01-01</t>
-        </is>
-      </c>
-      <c r="C58" s="16" t="inlineStr">
+      <c r="B61" s="14" t="inlineStr">
+        <is>
+          <t>FN-PAR-05-02</t>
+        </is>
+      </c>
+      <c r="C61" s="32" t="inlineStr">
         <is>
           <t>AI 어시스턴트</t>
         </is>
       </c>
-      <c r="D58" s="16" t="inlineStr">
-        <is>
-          <t>AI 채팅</t>
-        </is>
-      </c>
-      <c r="E58" s="16" t="inlineStr">
-        <is>
-          <t>질문·답변 인터페이스</t>
-        </is>
-      </c>
-      <c r="F58" s="16" t="inlineStr">
+      <c r="D61" s="14" t="inlineStr">
+        <is>
+          <t>최근 대화</t>
+        </is>
+      </c>
+      <c r="E61" s="14" t="inlineStr">
+        <is>
+          <t>대화 이력 목록</t>
+        </is>
+      </c>
+      <c r="F61" s="14" t="inlineStr">
         <is>
           <t>UI-PAR-005-01</t>
         </is>
       </c>
-      <c r="G58" s="17" t="inlineStr">
-        <is>
-          <t>sLLM 기반 대화형 인터페이스. 인사말 그리팅 표시. 자연어 질의응답·파일 첨부 지원. 행정 정보 검색·민원 분석 요청 처리</t>
-        </is>
-      </c>
-      <c r="H58" s="16" t="inlineStr">
+      <c r="G61" s="15" t="inlineStr">
+        <is>
+          <t>최근 대화 목록(제목·일시) — 항목 클릭 시 대화 재개, 새 대화 버튼, 행별 X 삭제(확인 모달)</t>
+        </is>
+      </c>
+      <c r="H61" s="14" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I58" s="16" t="inlineStr">
-        <is>
-          <t>sLLM(EXAONE)</t>
-        </is>
-      </c>
-      <c r="J58" s="16" t="inlineStr">
+      <c r="I61" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J61" s="14" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K58" s="24" t="n"/>
-    </row>
-    <row r="59" ht="32.1" customHeight="1">
-      <c r="A59" s="25" t="inlineStr">
-        <is>
-          <t>REQ-SFR-005-08</t>
-        </is>
-      </c>
-      <c r="B59" s="14" t="inlineStr">
-        <is>
-          <t>FN-PAR-05-01-02</t>
-        </is>
-      </c>
-      <c r="C59" s="32" t="inlineStr">
+      <c r="K61" s="26" t="n"/>
+    </row>
+    <row r="62" ht="31" customHeight="1" s="60">
+      <c r="A62" s="25" t="inlineStr">
+        <is>
+          <t>REQ-SFR-005-09</t>
+        </is>
+      </c>
+      <c r="B62" s="14" t="inlineStr">
+        <is>
+          <t>FN-PAR-05-03</t>
+        </is>
+      </c>
+      <c r="C62" s="32" t="inlineStr">
         <is>
           <t>AI 어시스턴트</t>
         </is>
       </c>
-      <c r="D59" s="32" t="inlineStr">
-        <is>
-          <t>AI 채팅</t>
-        </is>
-      </c>
-      <c r="E59" s="14" t="inlineStr">
-        <is>
-          <t>조례 검색·RAG 연계 답변</t>
-        </is>
-      </c>
-      <c r="F59" s="14" t="inlineStr">
+      <c r="D62" s="14" t="inlineStr">
+        <is>
+          <t>최근 리포트</t>
+        </is>
+      </c>
+      <c r="E62" s="14" t="inlineStr">
+        <is>
+          <t>리포트 목록 및 다운로드</t>
+        </is>
+      </c>
+      <c r="F62" s="14" t="inlineStr">
         <is>
           <t>UI-PAR-005-01</t>
         </is>
       </c>
-      <c r="G59" s="15" t="inlineStr">
-        <is>
-          <t>민원 관련 행정 정보(조례 등) RAG 기반 검색 및 답변 생성. 조례명·원문 보기 링크 카드 형태 응답</t>
-        </is>
-      </c>
-      <c r="H59" s="14" t="inlineStr">
+      <c r="G62" s="15" t="inlineStr">
+        <is>
+          <t>AI 생성 민원 요약 리포트 목록(제목·날짜) 조회 및 개별 다운로드(↓) 기능</t>
+        </is>
+      </c>
+      <c r="H62" s="14" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I59" s="14" t="inlineStr">
-        <is>
-          <t>RAG·Vector DB</t>
-        </is>
-      </c>
-      <c r="J59" s="14" t="inlineStr">
+      <c r="I62" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J62" s="14" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K59" s="26" t="n"/>
-    </row>
-    <row r="60" ht="32.1" customHeight="1">
-      <c r="A60" s="41" t="inlineStr">
-        <is>
-          <t>REQ-SFR-005-09</t>
-        </is>
-      </c>
-      <c r="B60" s="42" t="inlineStr">
-        <is>
-          <t>FN-PAR-05-05</t>
-        </is>
-      </c>
-      <c r="C60" s="57" t="inlineStr">
+      <c r="K62" s="26" t="n"/>
+    </row>
+    <row r="63" ht="31" customHeight="1" s="60">
+      <c r="A63" s="50" t="inlineStr">
+        <is>
+          <t>REQ-SFR-005-07</t>
+        </is>
+      </c>
+      <c r="B63" s="51" t="inlineStr">
+        <is>
+          <t>FN-PAR-05-04</t>
+        </is>
+      </c>
+      <c r="C63" s="52" t="inlineStr">
         <is>
           <t>AI 어시스턴트</t>
         </is>
       </c>
-      <c r="D60" s="32" t="inlineStr">
-        <is>
-          <t>AI 채팅</t>
-        </is>
-      </c>
-      <c r="E60" s="42" t="inlineStr">
-        <is>
-          <t>대량 민원 자동 요약</t>
-        </is>
-      </c>
-      <c r="F60" s="42" t="inlineStr">
-        <is>
-          <t>UI-PAR-005-02</t>
-        </is>
-      </c>
-      <c r="G60" s="43" t="inlineStr">
-        <is>
-          <t>대량 민원 내용을 sLLM으로 자동 요약하여 보고용 리포트 생성. AI 응답 하단 리포트 생성 버튼 제공</t>
-        </is>
-      </c>
-      <c r="H60" s="42" t="inlineStr">
+      <c r="D63" s="51" t="inlineStr">
+        <is>
+          <t>자주 하는 질문(FAQ)</t>
+        </is>
+      </c>
+      <c r="E63" s="51" t="inlineStr">
+        <is>
+          <t>FAQ 목록</t>
+        </is>
+      </c>
+      <c r="F63" s="14" t="inlineStr">
+        <is>
+          <t>UI-PAR-005-01</t>
+        </is>
+      </c>
+      <c r="G63" s="53" t="inlineStr">
+        <is>
+          <t>이번 달 민원 현황 요약·불법주차 단속 관련 행정 절차·공유주차제 도입 요건 등 자주 사용 질문 목록. 클릭 시 입력창 자동 입력</t>
+        </is>
+      </c>
+      <c r="H63" s="51" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I60" s="42" t="inlineStr">
-        <is>
-          <t>sLLM(EXAONE)</t>
-        </is>
-      </c>
-      <c r="J60" s="42" t="inlineStr">
+      <c r="I63" s="54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J63" s="51" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K60" s="44" t="n"/>
-    </row>
-    <row r="61" ht="32.1" customHeight="1">
-      <c r="A61" s="41" t="inlineStr">
-        <is>
-          <t>REQ-SFR-005-05</t>
-        </is>
-      </c>
-      <c r="B61" s="42" t="inlineStr">
-        <is>
-          <t>FN-PAR-05-06</t>
-        </is>
-      </c>
-      <c r="C61" s="57" t="inlineStr">
-        <is>
-          <t>AI 어시스턴트</t>
-        </is>
-      </c>
-      <c r="D61" s="32" t="inlineStr">
-        <is>
-          <t>AI 채팅</t>
-        </is>
-      </c>
-      <c r="E61" s="42" t="inlineStr">
-        <is>
-          <t>리포트 미리보기·다운로드</t>
-        </is>
-      </c>
-      <c r="F61" s="42" t="inlineStr">
-        <is>
-          <t>UI-PAR-005-03</t>
-        </is>
-      </c>
-      <c r="G61" s="43" t="inlineStr">
-        <is>
-          <t>AI 생성 민원 요약 보고서 미리보기 및 다운로드(PDF/DOCX)</t>
-        </is>
-      </c>
-      <c r="H61" s="42" t="inlineStr">
+      <c r="K63" s="55" t="n"/>
+    </row>
+    <row r="64" ht="31" customHeight="1" s="60">
+      <c r="A64" s="41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B64" s="42" t="inlineStr">
+        <is>
+          <t>FN-PAR-06-01</t>
+        </is>
+      </c>
+      <c r="C64" s="32" t="inlineStr">
+        <is>
+          <t>설정</t>
+        </is>
+      </c>
+      <c r="D64" s="42" t="inlineStr">
+        <is>
+          <t>메뉴 권한 관리</t>
+        </is>
+      </c>
+      <c r="E64" s="42" t="inlineStr">
+        <is>
+          <t>메뉴별 권한 그룹 지정</t>
+        </is>
+      </c>
+      <c r="F64" s="42" t="inlineStr">
+        <is>
+          <t>UI-PAR-006-01</t>
+        </is>
+      </c>
+      <c r="G64" s="43" t="inlineStr">
+        <is>
+          <t>메뉴별 권한 그룹 지정 — 시스템 관리자 항상 허용(해제 불가), 일반 사용자는 관리 메뉴 부여 불가, 서비스 관리자 해제 시 일반 사용자 동시 해제</t>
+        </is>
+      </c>
+      <c r="H64" s="42" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I61" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J61" s="42" t="inlineStr">
+      <c r="I64" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J64" s="42" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K61" s="44" t="n"/>
-    </row>
-    <row r="62" ht="30.95" customHeight="1">
-      <c r="A62" s="41" t="inlineStr">
+      <c r="K64" s="44" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="31" customHeight="1" s="60">
+      <c r="A65" s="41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B65" s="42" t="inlineStr">
+        <is>
+          <t>FN-PAR-06-02</t>
+        </is>
+      </c>
+      <c r="C65" s="31" t="inlineStr">
+        <is>
+          <t>설정</t>
+        </is>
+      </c>
+      <c r="D65" s="42" t="inlineStr">
+        <is>
+          <t>메뉴 권한 관리</t>
+        </is>
+      </c>
+      <c r="E65" s="42" t="inlineStr">
+        <is>
+          <t>권한 저장</t>
+        </is>
+      </c>
+      <c r="F65" s="42" t="inlineStr">
+        <is>
+          <t>UI-PAR-006-01</t>
+        </is>
+      </c>
+      <c r="G65" s="43" t="inlineStr">
+        <is>
+          <t>메뉴별 권한 설정 저장(메뉴 단위 저장)</t>
+        </is>
+      </c>
+      <c r="H65" s="42" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I65" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J65" s="42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K65" s="44" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="45" customHeight="1" s="60">
+      <c r="A66" s="41" t="inlineStr">
+        <is>
+          <t>REQ-SFR-005-10</t>
+        </is>
+      </c>
+      <c r="B66" s="42" t="inlineStr">
+        <is>
+          <t>FN-PAR-06-03</t>
+        </is>
+      </c>
+      <c r="C66" s="31" t="inlineStr">
+        <is>
+          <t>설정</t>
+        </is>
+      </c>
+      <c r="D66" s="42" t="inlineStr">
+        <is>
+          <t>분석 지표 가중치 설정</t>
+        </is>
+      </c>
+      <c r="E66" s="42" t="inlineStr">
+        <is>
+          <t>종합점수 가중치</t>
+        </is>
+      </c>
+      <c r="F66" s="42" t="inlineStr">
+        <is>
+          <t>UI-PAR-006-02</t>
+        </is>
+      </c>
+      <c r="G66" s="43" t="inlineStr">
+        <is>
+          <t>집중구역 분석/구역 추천/투자·보강 우선순위 3개 모델의 가중치 조정(합 100% 검증)</t>
+        </is>
+      </c>
+      <c r="H66" s="42" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I66" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J66" s="42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K66" s="44" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="30" customHeight="1" s="60">
+      <c r="A67" s="41" t="inlineStr">
+        <is>
+          <t>REQ-SFR-005-10</t>
+        </is>
+      </c>
+      <c r="B67" s="42" t="inlineStr">
+        <is>
+          <t>FN-PAR-06-04</t>
+        </is>
+      </c>
+      <c r="C67" s="31" t="inlineStr">
+        <is>
+          <t>설정</t>
+        </is>
+      </c>
+      <c r="D67" s="42" t="inlineStr">
+        <is>
+          <t>분석 지표 가중치 설정</t>
+        </is>
+      </c>
+      <c r="E67" s="42" t="inlineStr">
+        <is>
+          <t>설정 변경 이력</t>
+        </is>
+      </c>
+      <c r="F67" s="42" t="inlineStr">
+        <is>
+          <t>UI-PAR-006-02</t>
+        </is>
+      </c>
+      <c r="G67" s="43" t="inlineStr">
+        <is>
+          <t>변경일시, 변경자, 변경 항목, 변경 내용에 대한 목록 조회</t>
+        </is>
+      </c>
+      <c r="H67" s="42" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I67" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J67" s="42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K67" s="44" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="30" customHeight="1" s="60">
+      <c r="A68" s="41" t="inlineStr">
+        <is>
+          <t>REQ-SFR-005-10</t>
+        </is>
+      </c>
+      <c r="B68" s="42" t="inlineStr">
+        <is>
+          <t>FN-PAR-06-05</t>
+        </is>
+      </c>
+      <c r="C68" s="31" t="inlineStr">
+        <is>
+          <t>설정</t>
+        </is>
+      </c>
+      <c r="D68" s="42" t="inlineStr">
+        <is>
+          <t>분석 지표 가중치 설정</t>
+        </is>
+      </c>
+      <c r="E68" s="42" t="inlineStr">
+        <is>
+          <t>기본값 초기화</t>
+        </is>
+      </c>
+      <c r="F68" s="42" t="inlineStr">
+        <is>
+          <t>UI-PAR-006-02</t>
+        </is>
+      </c>
+      <c r="G68" s="43" t="inlineStr">
+        <is>
+          <t>기존 종합점수 가중치로 초기화</t>
+        </is>
+      </c>
+      <c r="H68" s="42" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I68" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J68" s="42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K68" s="44" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="30" customHeight="1" s="60">
+      <c r="A69" s="48" t="inlineStr">
+        <is>
+          <t>REQ-SFR-005-10</t>
+        </is>
+      </c>
+      <c r="B69" s="46" t="inlineStr">
+        <is>
+          <t>FN-PAR-06-06</t>
+        </is>
+      </c>
+      <c r="C69" s="33" t="inlineStr">
+        <is>
+          <t>설정</t>
+        </is>
+      </c>
+      <c r="D69" s="46" t="inlineStr">
+        <is>
+          <t>분석 지표 가중치 설정</t>
+        </is>
+      </c>
+      <c r="E69" s="46" t="inlineStr">
+        <is>
+          <t>설정 저장</t>
+        </is>
+      </c>
+      <c r="F69" s="46" t="inlineStr">
+        <is>
+          <t>UI-PAR-006-02</t>
+        </is>
+      </c>
+      <c r="G69" s="47" t="inlineStr">
+        <is>
+          <t>변경한 가중치 설정 저장 버튼</t>
+        </is>
+      </c>
+      <c r="H69" s="46" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I69" s="46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J69" s="46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K69" s="49" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="31" customHeight="1" s="60" thickBot="1">
+      <c r="A70" s="48" t="inlineStr">
+        <is>
+          <t>REQ-SFR-003-07</t>
+        </is>
+      </c>
+      <c r="B70" s="46" t="inlineStr">
+        <is>
+          <t>FN-PAR-C01-04</t>
+        </is>
+      </c>
+      <c r="C70" s="58" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="D70" s="46" t="inlineStr">
+        <is>
+          <t>데이터 기준일 안내</t>
+        </is>
+      </c>
+      <c r="E70" s="46" t="inlineStr">
+        <is>
+          <t>데이터 기준일 팝오버</t>
+        </is>
+      </c>
+      <c r="F70" s="46" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="G70" s="47" t="inlineStr">
+        <is>
+          <t>헤더 '최근 갱신' 문구의 ⓘ 호버 시 데이터별 기준일·갱신 주기 팝오버 표시(민원 3종·단속·공영주차장)</t>
+        </is>
+      </c>
+      <c r="H70" s="46" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I70" s="46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J70" s="46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K70" s="49" t="inlineStr">
+        <is>
+          <t>대시보드·민원현황</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="30" customHeight="1" s="60">
+      <c r="A71" s="48" t="inlineStr">
+        <is>
+          <t>REQ-SFR-003-10</t>
+        </is>
+      </c>
+      <c r="B71" s="46" t="inlineStr">
+        <is>
+          <t>FN-PAR-C01-05</t>
+        </is>
+      </c>
+      <c r="C71" s="58" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="D71" s="46" t="inlineStr">
+        <is>
+          <t>삭제 확인</t>
+        </is>
+      </c>
+      <c r="E71" s="46" t="inlineStr">
+        <is>
+          <t>삭제 확인 모달</t>
+        </is>
+      </c>
+      <c r="F71" s="46" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="G71" s="47" t="inlineStr">
+        <is>
+          <t>모든 삭제 동작(시나리오·보고서·자동 생성 설정·수신자·최근 대화)에 확인 모달 적용 — '삭제하면 되돌릴 수 없습니다' 경고 및 취소/삭제 버튼</t>
+        </is>
+      </c>
+      <c r="H71" s="46" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I71" s="46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J71" s="46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K71" s="49" t="n"/>
+    </row>
+    <row r="72" ht="45" customHeight="1" s="60">
+      <c r="A72" s="29" t="inlineStr">
+        <is>
+          <t>REQ-SFR-003-14</t>
+        </is>
+      </c>
+      <c r="B72" s="20" t="inlineStr">
+        <is>
+          <t>FN-PAR-SYS-01</t>
+        </is>
+      </c>
+      <c r="C72" s="20" t="n"/>
+      <c r="D72" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E72" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F72" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G72" s="45" t="inlineStr">
+        <is>
+          <t>분석 모델 재학습은 AI 어시스턴트(sLLM+RAG) 학습으로 대체 수행. 신규 민원 유형·정책 변화·도시 환경 변화 발생 시 조례·정책문서 재색인(Vector DB 갱신), 첨부문서 학습, 대화 이력·FAQ 축적을 통해 지속 고도화. 모델 개선 프로세스는 AI 어시스턴트 운영 절차에 포함</t>
+        </is>
+      </c>
+      <c r="H72" s="20" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I72" s="20" t="inlineStr">
+        <is>
+          <t>sLLM(EXAONE)·RAG·Vector DB</t>
+        </is>
+      </c>
+      <c r="J72" s="20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K72" s="30" t="inlineStr">
+        <is>
+          <t>비화면</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="30" customHeight="1" s="60">
+      <c r="A73" s="25" t="inlineStr">
+        <is>
+          <t>REQ-SFR-005-02</t>
+        </is>
+      </c>
+      <c r="B73" s="14" t="inlineStr">
+        <is>
+          <t>FN-PAR-SYS-02</t>
+        </is>
+      </c>
+      <c r="C73" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D73" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E73" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F73" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G73" s="35" t="inlineStr">
+        <is>
+          <t>D-hub에 적제된 통합데이터 활용하여 민원 3종 이상·정책행정문서 12종 이상 데이터의 수집→정제→구조화→적용 전 과정 관리. 데이터 유형별 적용 목적·활용 시나리오 관리</t>
+        </is>
+      </c>
+      <c r="H73" s="14" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I73" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J73" s="14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K73" s="26" t="inlineStr">
+        <is>
+          <t>비화면</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="30" customHeight="1" s="60">
+      <c r="A74" s="25" t="inlineStr">
+        <is>
+          <t>REQ-SFR-005-03</t>
+        </is>
+      </c>
+      <c r="B74" s="14" t="inlineStr">
+        <is>
+          <t>FN-PAR-SYS-03</t>
+        </is>
+      </c>
+      <c r="C74" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D74" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E74" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F74" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G74" s="35" t="inlineStr">
+        <is>
+          <t>비정형 문서·스캔 문서·이미지 기반 행정자료를 AI RPA로 자동 수집하고 AI OCR로 텍스트 추출·정형화·구조화 적재</t>
+        </is>
+      </c>
+      <c r="H74" s="14" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I74" s="14" t="inlineStr">
+        <is>
+          <t>AI RPA·AI OCR</t>
+        </is>
+      </c>
+      <c r="J74" s="14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K74" s="26" t="inlineStr">
+        <is>
+          <t>비화면</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="30" customHeight="1" s="60">
+      <c r="A75" s="25" t="inlineStr">
         <is>
           <t>REQ-SFR-005-01</t>
         </is>
       </c>
-      <c r="B62" s="42" t="inlineStr">
-        <is>
-          <t>FN-PAR-05-07</t>
-        </is>
-      </c>
-      <c r="C62" s="57" t="inlineStr">
-        <is>
-          <t>AI 어시스턴트</t>
-        </is>
-      </c>
-      <c r="D62" s="32" t="inlineStr">
-        <is>
-          <t>AI 채팅</t>
-        </is>
-      </c>
-      <c r="E62" s="42" t="inlineStr">
-        <is>
-          <t>융합 데이터 통합 분석 답변</t>
-        </is>
-      </c>
-      <c r="F62" s="42" t="inlineStr">
-        <is>
-          <t>UI-PAR-005-04</t>
-        </is>
-      </c>
-      <c r="G62" s="43" t="inlineStr">
-        <is>
-          <t>민원 데이터와 감시(화재·안전) 데이터를 결합해야 답이 나오는 질문에 AI 에이전트를 호출, 융합 데이터에서 종합 인사이트를 도출하여 AI 어시스턴트 답변으로 표시. 리포트 생성 버튼 제공</t>
-        </is>
-      </c>
-      <c r="H62" s="42" t="inlineStr">
+      <c r="B75" s="14" t="inlineStr">
+        <is>
+          <t>FN-PAR-SYS-04</t>
+        </is>
+      </c>
+      <c r="C75" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D75" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E75" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F75" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G75" s="35" t="inlineStr">
+        <is>
+          <t>민원 분석 대응 솔루션과 실시간 공영주차장 감시 대응 솔루션의 수집·분석 데이터를 결합·융합하여 상관관계 분석 및 종합 인사이트 도출. 대시보드·보고서로 반영</t>
+        </is>
+      </c>
+      <c r="H75" s="14" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I62" s="42" t="inlineStr">
-        <is>
-          <t>AI 에이전트</t>
-        </is>
-      </c>
-      <c r="J62" s="42" t="inlineStr">
+      <c r="I75" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J75" s="14" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K62" s="44" t="n"/>
-    </row>
-    <row r="63" ht="30.95" customHeight="1">
-      <c r="A63" s="25" t="inlineStr">
-        <is>
-          <t>REQ-SFR-005-07</t>
-        </is>
-      </c>
-      <c r="B63" s="14" t="inlineStr">
-        <is>
-          <t>FN-PAR-05-02</t>
-        </is>
-      </c>
-      <c r="C63" s="32" t="inlineStr">
-        <is>
-          <t>AI 어시스턴트</t>
-        </is>
-      </c>
-      <c r="D63" s="14" t="inlineStr">
-        <is>
-          <t>최근 대화</t>
-        </is>
-      </c>
-      <c r="E63" s="14" t="inlineStr">
-        <is>
-          <t>대화 이력 목록</t>
-        </is>
-      </c>
-      <c r="F63" s="14" t="inlineStr">
-        <is>
-          <t>UI-PAR-005-01</t>
-        </is>
-      </c>
-      <c r="G63" s="15" t="inlineStr">
-        <is>
-          <t>최근 대화 목록(제목·일시) — 항목 클릭 시 대화 재개, 새 대화 버튼, 행별 X 삭제(확인 모달)</t>
-        </is>
-      </c>
-      <c r="H63" s="14" t="inlineStr">
+      <c r="K75" s="26" t="inlineStr">
+        <is>
+          <t>비화면</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="30" customHeight="1" s="60">
+      <c r="A76" s="27" t="inlineStr">
+        <is>
+          <t>REQ-SFR-005-10</t>
+        </is>
+      </c>
+      <c r="B76" s="18" t="inlineStr">
+        <is>
+          <t>FN-PAR-SYS-05</t>
+        </is>
+      </c>
+      <c r="C76" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D76" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E76" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F76" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G76" s="36" t="inlineStr">
+        <is>
+          <t>타 지자체 확산 적용을 위해 데이터 구조·분석 지표·가중치·기능 구성을 지역 여건에 맞게 설정·조정. 오픈 소스 활용. 공통코드 및 지표 가중치 관리</t>
+        </is>
+      </c>
+      <c r="H76" s="18" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I63" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J63" s="14" t="inlineStr">
+      <c r="I76" s="39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J76" s="18" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K63" s="26" t="n"/>
-    </row>
-    <row r="64" ht="30.95" customHeight="1">
-      <c r="A64" s="25" t="inlineStr">
-        <is>
-          <t>REQ-SFR-005-09</t>
-        </is>
-      </c>
-      <c r="B64" s="14" t="inlineStr">
-        <is>
-          <t>FN-PAR-05-03</t>
-        </is>
-      </c>
-      <c r="C64" s="32" t="inlineStr">
-        <is>
-          <t>AI 어시스턴트</t>
-        </is>
-      </c>
-      <c r="D64" s="14" t="inlineStr">
-        <is>
-          <t>최근 리포트</t>
-        </is>
-      </c>
-      <c r="E64" s="14" t="inlineStr">
-        <is>
-          <t>리포트 목록 및 다운로드</t>
-        </is>
-      </c>
-      <c r="F64" s="14" t="inlineStr">
-        <is>
-          <t>UI-PAR-005-01</t>
-        </is>
-      </c>
-      <c r="G64" s="15" t="inlineStr">
-        <is>
-          <t>AI 생성 민원 요약 리포트 목록(제목·날짜) 조회 및 개별 다운로드(↓) 기능</t>
-        </is>
-      </c>
-      <c r="H64" s="14" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I64" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J64" s="14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K64" s="26" t="n"/>
-    </row>
-    <row r="65" ht="30.95" customHeight="1">
-      <c r="A65" s="50" t="inlineStr">
-        <is>
-          <t>REQ-SFR-005-07</t>
-        </is>
-      </c>
-      <c r="B65" s="51" t="inlineStr">
-        <is>
-          <t>FN-PAR-05-04</t>
-        </is>
-      </c>
-      <c r="C65" s="52" t="inlineStr">
-        <is>
-          <t>AI 어시스턴트</t>
-        </is>
-      </c>
-      <c r="D65" s="51" t="inlineStr">
-        <is>
-          <t>자주 하는 질문(FAQ)</t>
-        </is>
-      </c>
-      <c r="E65" s="51" t="inlineStr">
-        <is>
-          <t>FAQ 목록</t>
-        </is>
-      </c>
-      <c r="F65" s="14" t="inlineStr">
-        <is>
-          <t>UI-PAR-005-01</t>
-        </is>
-      </c>
-      <c r="G65" s="53" t="inlineStr">
-        <is>
-          <t>이번 달 민원 현황 요약·불법주차 단속 관련 행정 절차·공유주차제 도입 요건 등 자주 사용 질문 목록. 클릭 시 입력창 자동 입력</t>
-        </is>
-      </c>
-      <c r="H65" s="51" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I65" s="54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J65" s="51" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K65" s="55" t="n"/>
-    </row>
-    <row r="66" ht="30.95" customHeight="1">
-      <c r="A66" s="41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B66" s="42" t="inlineStr">
-        <is>
-          <t>FN-PAR-06-01</t>
-        </is>
-      </c>
-      <c r="C66" s="32" t="inlineStr">
-        <is>
-          <t>설정</t>
-        </is>
-      </c>
-      <c r="D66" s="42" t="inlineStr">
-        <is>
-          <t>메뉴 권한 관리</t>
-        </is>
-      </c>
-      <c r="E66" s="42" t="inlineStr">
-        <is>
-          <t>메뉴별 권한 그룹 지정</t>
-        </is>
-      </c>
-      <c r="F66" s="42" t="inlineStr">
-        <is>
-          <t>UI-PAR-006-01</t>
-        </is>
-      </c>
-      <c r="G66" s="43" t="inlineStr">
-        <is>
-          <t>메뉴별 권한 그룹 지정 — 시스템 관리자 항상 허용(해제 불가), 일반 사용자는 관리 메뉴 부여 불가, 서비스 관리자 해제 시 일반 사용자 동시 해제</t>
-        </is>
-      </c>
-      <c r="H66" s="42" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I66" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J66" s="42" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K66" s="44" t="inlineStr">
-        <is>
-          <t>관리자</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="30.95" customHeight="1">
-      <c r="A67" s="41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B67" s="42" t="inlineStr">
-        <is>
-          <t>FN-PAR-06-02</t>
-        </is>
-      </c>
-      <c r="C67" s="31" t="inlineStr">
-        <is>
-          <t>설정</t>
-        </is>
-      </c>
-      <c r="D67" s="42" t="inlineStr">
-        <is>
-          <t>메뉴 권한 관리</t>
-        </is>
-      </c>
-      <c r="E67" s="42" t="inlineStr">
-        <is>
-          <t>권한 저장</t>
-        </is>
-      </c>
-      <c r="F67" s="42" t="inlineStr">
-        <is>
-          <t>UI-PAR-006-01</t>
-        </is>
-      </c>
-      <c r="G67" s="43" t="inlineStr">
-        <is>
-          <t>메뉴별 권한 설정 저장(메뉴 단위 저장)</t>
-        </is>
-      </c>
-      <c r="H67" s="42" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I67" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J67" s="42" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K67" s="44" t="inlineStr">
-        <is>
-          <t>관리자</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="45" customHeight="1">
-      <c r="A68" s="41" t="inlineStr">
-        <is>
-          <t>REQ-SFR-005-10</t>
-        </is>
-      </c>
-      <c r="B68" s="42" t="inlineStr">
-        <is>
-          <t>FN-PAR-06-03</t>
-        </is>
-      </c>
-      <c r="C68" s="31" t="inlineStr">
-        <is>
-          <t>설정</t>
-        </is>
-      </c>
-      <c r="D68" s="42" t="inlineStr">
-        <is>
-          <t>분석 지표 가중치 설정</t>
-        </is>
-      </c>
-      <c r="E68" s="42" t="inlineStr">
-        <is>
-          <t>종합점수 가중치</t>
-        </is>
-      </c>
-      <c r="F68" s="42" t="inlineStr">
-        <is>
-          <t>UI-PAR-006-02</t>
-        </is>
-      </c>
-      <c r="G68" s="43" t="inlineStr">
-        <is>
-          <t>집중구역 분석/구역 추천/투자·보강 우선순위 3개 모델의 가중치 조정(합 100% 검증)</t>
-        </is>
-      </c>
-      <c r="H68" s="42" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I68" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J68" s="42" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K68" s="44" t="inlineStr">
-        <is>
-          <t>관리자</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="30" customHeight="1">
-      <c r="A69" s="41" t="inlineStr">
-        <is>
-          <t>REQ-SFR-005-10</t>
-        </is>
-      </c>
-      <c r="B69" s="42" t="inlineStr">
-        <is>
-          <t>FN-PAR-06-04</t>
-        </is>
-      </c>
-      <c r="C69" s="31" t="inlineStr">
-        <is>
-          <t>설정</t>
-        </is>
-      </c>
-      <c r="D69" s="42" t="inlineStr">
-        <is>
-          <t>분석 지표 가중치 설정</t>
-        </is>
-      </c>
-      <c r="E69" s="42" t="inlineStr">
-        <is>
-          <t>설정 변경 이력</t>
-        </is>
-      </c>
-      <c r="F69" s="42" t="inlineStr">
-        <is>
-          <t>UI-PAR-006-02</t>
-        </is>
-      </c>
-      <c r="G69" s="43" t="inlineStr">
-        <is>
-          <t>변경일시, 변경자, 변경 항목, 변경 내용에 대한 목록 조회</t>
-        </is>
-      </c>
-      <c r="H69" s="42" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I69" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J69" s="42" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K69" s="44" t="inlineStr">
-        <is>
-          <t>관리자</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="30" customHeight="1">
-      <c r="A70" s="41" t="inlineStr">
-        <is>
-          <t>REQ-SFR-005-10</t>
-        </is>
-      </c>
-      <c r="B70" s="42" t="inlineStr">
-        <is>
-          <t>FN-PAR-06-05</t>
-        </is>
-      </c>
-      <c r="C70" s="31" t="inlineStr">
-        <is>
-          <t>설정</t>
-        </is>
-      </c>
-      <c r="D70" s="42" t="inlineStr">
-        <is>
-          <t>분석 지표 가중치 설정</t>
-        </is>
-      </c>
-      <c r="E70" s="42" t="inlineStr">
-        <is>
-          <t>기본값 초기화</t>
-        </is>
-      </c>
-      <c r="F70" s="42" t="inlineStr">
-        <is>
-          <t>UI-PAR-006-02</t>
-        </is>
-      </c>
-      <c r="G70" s="43" t="inlineStr">
-        <is>
-          <t>기존 종합점수 가중치로 초기화</t>
-        </is>
-      </c>
-      <c r="H70" s="42" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I70" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J70" s="42" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K70" s="44" t="inlineStr">
-        <is>
-          <t>관리자</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="30" customHeight="1">
-      <c r="A71" s="48" t="inlineStr">
-        <is>
-          <t>REQ-SFR-005-10</t>
-        </is>
-      </c>
-      <c r="B71" s="46" t="inlineStr">
-        <is>
-          <t>FN-PAR-06-06</t>
-        </is>
-      </c>
-      <c r="C71" s="33" t="inlineStr">
-        <is>
-          <t>설정</t>
-        </is>
-      </c>
-      <c r="D71" s="46" t="inlineStr">
-        <is>
-          <t>분석 지표 가중치 설정</t>
-        </is>
-      </c>
-      <c r="E71" s="46" t="inlineStr">
-        <is>
-          <t>설정 저장</t>
-        </is>
-      </c>
-      <c r="F71" s="46" t="inlineStr">
-        <is>
-          <t>UI-PAR-006-02</t>
-        </is>
-      </c>
-      <c r="G71" s="47" t="inlineStr">
-        <is>
-          <t>변경한 가중치 설정 저장 버튼</t>
-        </is>
-      </c>
-      <c r="H71" s="46" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I71" s="46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J71" s="46" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K71" s="49" t="inlineStr">
-        <is>
-          <t>관리자</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="30.95" customHeight="1" thickBot="1">
-      <c r="A72" s="48" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-07</t>
-        </is>
-      </c>
-      <c r="B72" s="46" t="inlineStr">
-        <is>
-          <t>FN-PAR-C01-04</t>
-        </is>
-      </c>
-      <c r="C72" s="75" t="inlineStr">
-        <is>
-          <t>공통</t>
-        </is>
-      </c>
-      <c r="D72" s="46" t="inlineStr">
-        <is>
-          <t>데이터 기준일 안내</t>
-        </is>
-      </c>
-      <c r="E72" s="46" t="inlineStr">
-        <is>
-          <t>데이터 기준일 팝오버</t>
-        </is>
-      </c>
-      <c r="F72" s="46" t="inlineStr">
-        <is>
-          <t>공통</t>
-        </is>
-      </c>
-      <c r="G72" s="47" t="inlineStr">
-        <is>
-          <t>헤더 '최근 갱신' 문구의 ⓘ 호버 시 데이터별 기준일·갱신 주기 팝오버 표시(민원 3종·단속·공영주차장)</t>
-        </is>
-      </c>
-      <c r="H72" s="46" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I72" s="46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J72" s="46" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K72" s="49" t="inlineStr">
-        <is>
-          <t>대시보드·민원현황</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="48" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-10</t>
-        </is>
-      </c>
-      <c r="B73" s="46" t="inlineStr">
-        <is>
-          <t>FN-PAR-C01-05</t>
-        </is>
-      </c>
-      <c r="C73" s="75" t="inlineStr">
-        <is>
-          <t>공통</t>
-        </is>
-      </c>
-      <c r="D73" s="46" t="inlineStr">
-        <is>
-          <t>삭제 확인</t>
-        </is>
-      </c>
-      <c r="E73" s="46" t="inlineStr">
-        <is>
-          <t>삭제 확인 모달</t>
-        </is>
-      </c>
-      <c r="F73" s="46" t="inlineStr">
-        <is>
-          <t>공통</t>
-        </is>
-      </c>
-      <c r="G73" s="47" t="inlineStr">
-        <is>
-          <t>모든 삭제 동작(시나리오·보고서·자동 생성 설정·수신자·최근 대화)에 확인 모달 적용 — '삭제하면 되돌릴 수 없습니다' 경고 및 취소/삭제 버튼</t>
-        </is>
-      </c>
-      <c r="H73" s="46" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I73" s="46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J73" s="46" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K73" s="49" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="29" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-14</t>
-        </is>
-      </c>
-      <c r="B74" s="20" t="inlineStr">
-        <is>
-          <t>FN-PAR-SYS-01</t>
-        </is>
-      </c>
-      <c r="C74" s="20" t="n"/>
-      <c r="D74" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E74" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F74" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G74" s="45" t="inlineStr">
-        <is>
-          <t>분석 모델 재학습은 AI 어시스턴트(sLLM+RAG) 학습으로 대체 수행. 신규 민원 유형·정책 변화·도시 환경 변화 발생 시 조례·정책문서 재색인(Vector DB 갱신), 첨부문서 학습, 대화 이력·FAQ 축적을 통해 지속 고도화. 모델 개선 프로세스는 AI 어시스턴트 운영 절차에 포함</t>
-        </is>
-      </c>
-      <c r="H74" s="20" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I74" s="20" t="inlineStr">
-        <is>
-          <t>sLLM(EXAONE)·RAG·Vector DB</t>
-        </is>
-      </c>
-      <c r="J74" s="20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K74" s="30" t="inlineStr">
-        <is>
-          <t>비화면</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="25" t="inlineStr">
-        <is>
-          <t>REQ-SFR-005-02</t>
-        </is>
-      </c>
-      <c r="B75" s="14" t="inlineStr">
-        <is>
-          <t>FN-PAR-SYS-02</t>
-        </is>
-      </c>
-      <c r="C75" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D75" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E75" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F75" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G75" s="35" t="inlineStr">
-        <is>
-          <t>D-hub에 적제된 통합데이터 활용하여 민원 3종 이상·정책행정문서 12종 이상 데이터의 수집→정제→구조화→적용 전 과정 관리. 데이터 유형별 적용 목적·활용 시나리오 관리</t>
-        </is>
-      </c>
-      <c r="H75" s="14" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I75" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J75" s="14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K75" s="26" t="inlineStr">
-        <is>
-          <t>비화면</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="25" t="inlineStr">
-        <is>
-          <t>REQ-SFR-005-03</t>
-        </is>
-      </c>
-      <c r="B76" s="14" t="inlineStr">
-        <is>
-          <t>FN-PAR-SYS-03</t>
-        </is>
-      </c>
-      <c r="C76" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D76" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E76" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F76" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G76" s="35" t="inlineStr">
-        <is>
-          <t>비정형 문서·스캔 문서·이미지 기반 행정자료를 AI RPA로 자동 수집하고 AI OCR로 텍스트 추출·정형화·구조화 적재</t>
-        </is>
-      </c>
-      <c r="H76" s="14" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I76" s="14" t="inlineStr">
-        <is>
-          <t>AI RPA·AI OCR</t>
-        </is>
-      </c>
-      <c r="J76" s="14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K76" s="26" t="inlineStr">
-        <is>
-          <t>비화면</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="25" t="inlineStr">
-        <is>
-          <t>REQ-SFR-005-01</t>
-        </is>
-      </c>
-      <c r="B77" s="14" t="inlineStr">
-        <is>
-          <t>FN-PAR-SYS-04</t>
-        </is>
-      </c>
-      <c r="C77" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D77" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E77" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F77" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G77" s="35" t="inlineStr">
-        <is>
-          <t>민원 분석 대응 솔루션과 실시간 공영주차장 감시 대응 솔루션의 수집·분석 데이터를 결합·융합하여 상관관계 분석 및 종합 인사이트 도출. 대시보드·보고서로 반영</t>
-        </is>
-      </c>
-      <c r="H77" s="14" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I77" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J77" s="14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K77" s="26" t="inlineStr">
-        <is>
-          <t>비화면</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="27" t="inlineStr">
-        <is>
-          <t>REQ-SFR-005-10</t>
-        </is>
-      </c>
-      <c r="B78" s="18" t="inlineStr">
-        <is>
-          <t>FN-PAR-SYS-05</t>
-        </is>
-      </c>
-      <c r="C78" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D78" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E78" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F78" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G78" s="36" t="inlineStr">
-        <is>
-          <t>타 지자체 확산 적용을 위해 데이터 구조·분석 지표·가중치·기능 구성을 지역 여건에 맞게 설정·조정. 오픈 소스 활용. 공통코드 및 지표 가중치 관리</t>
-        </is>
-      </c>
-      <c r="H78" s="18" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I78" s="39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J78" s="18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K78" s="28" t="inlineStr">
+      <c r="K76" s="28" t="inlineStr">
         <is>
           <t>비화면</t>
         </is>

--- a/Audit/JJ_PD_IP_A02_기능구조도_v1.5_이노팸.xlsx
+++ b/Audit/JJ_PD_IP_A02_기능구조도_v1.5_이노팸.xlsx
@@ -4307,7 +4307,7 @@
       </c>
       <c r="G16" s="15" t="inlineStr">
         <is>
-          <t>분석레이어(민원다발지역/집중단속지역/수요부족지역 선택→지도 시각화, 읍면동별 순위 표시). 히트맵 표현 시 민원 건수·단속 건수·부족률 기반 밀도 히트맵 표출</t>
+          <t>분석레이어(민원다발지역/집중단속지역/수요부족지역 선택→지도 시각화, 읍면동별 순위 표시). 민원 다발·단속 집중 레이어는 히트맵 표현 시 민원 건수·단속 건수 기반 밀도 히트맵 표출</t>
         </is>
       </c>
       <c r="H16" s="14" t="inlineStr">
@@ -4360,7 +4360,7 @@
       </c>
       <c r="G17" s="15" t="inlineStr">
         <is>
-          <t>지도 레이어 패널 — 민원 다발/단속 집중/수요 부족(택1 라디오) + 공영주차장·행정동 경계 토글. 레이어 선택에 따라 우측 순위 패널 전환. 각 분석 레이어는 읍면동(폴리곤) ↔ 히트맵(밀도) 표현 전환 지원</t>
+          <t>지도 레이어 패널 — 민원 다발/단속 집중/수요 부족(택1 라디오) + 공영주차장·행정동 경계 토글. 레이어 선택에 따라 우측 순위 패널 전환. 민원 다발·단속 집중 레이어는 읍면동(폴리곤) ↔ 히트맵(밀도) 표현 전환 지원(수요 부족 지역 제외)</t>
         </is>
       </c>
       <c r="H17" s="14" t="inlineStr">

--- a/Audit/JJ_PD_IP_A02_기능구조도_v1.5_이노팸.xlsx
+++ b/Audit/JJ_PD_IP_A02_기능구조도_v1.5_이노팸.xlsx
@@ -4307,7 +4307,7 @@
       </c>
       <c r="G16" s="15" t="inlineStr">
         <is>
-          <t>분석레이어(민원다발지역/집중단속지역/수요부족지역 선택→지도 시각화, 읍면동별 순위 표시). 민원 다발·단속 집중 레이어는 히트맵 표현 시 민원 건수·단속 건수 기반 밀도 히트맵 표출</t>
+          <t>분석레이어(민원다발지역/집중단속지역/수요부족지역 중 하나 선택 → 지도 데이터 시각화). 민원 다발·단속 집중 레이어는 히트맵 표현 시 민원 건수·단속 건수 기반 밀도 히트맵 표출</t>
         </is>
       </c>
       <c r="H16" s="14" t="inlineStr">

--- a/Audit/JJ_PD_IP_A02_기능구조도_v1.5_이노팸.xlsx
+++ b/Audit/JJ_PD_IP_A02_기능구조도_v1.5_이노팸.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-50580" yWindow="2360" windowWidth="45860" windowHeight="23080" tabRatio="710" firstSheet="2" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" tabRatio="710" firstSheet="2" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="표지" sheetId="1" state="visible" r:id="rId1"/>
@@ -49,36 +49,36 @@
     <definedName name="_SX25">[1]COST!#REF!</definedName>
     <definedName name="_Table1_In1" hidden="1">#REF!</definedName>
     <definedName name="_Table1_Out" hidden="1">#REF!</definedName>
-    <definedName name="_wo1">'[3]예정(3)'!#REF!</definedName>
-    <definedName name="\0">'[4]9GNG운반'!#REF!</definedName>
-    <definedName name="\A">'[4]9GNG운반'!#REF!</definedName>
-    <definedName name="\B">'[4]9GNG운반'!#REF!</definedName>
-    <definedName name="\I">'[4]9GNG운반'!#REF!</definedName>
-    <definedName name="\O">'[4]9GNG운반'!#REF!</definedName>
-    <definedName name="\P">'[4]9GNG운반'!#REF!</definedName>
-    <definedName name="\Q">'[4]9GNG운반'!#REF!</definedName>
+    <definedName name="_wo1">'[2]예정(3)'!#REF!</definedName>
+    <definedName name="\0">'[3]9GNG운반'!#REF!</definedName>
+    <definedName name="\A">'[3]9GNG운반'!#REF!</definedName>
+    <definedName name="\B">'[3]9GNG운반'!#REF!</definedName>
+    <definedName name="\I">'[3]9GNG운반'!#REF!</definedName>
+    <definedName name="\O">'[3]9GNG운반'!#REF!</definedName>
+    <definedName name="\P">'[3]9GNG운반'!#REF!</definedName>
+    <definedName name="\Q">'[3]9GNG운반'!#REF!</definedName>
     <definedName name="ㄱ" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
     <definedName name="ㄱㄱㄷㄱ">#REF!</definedName>
     <definedName name="ㄱㅎㄷㄱㅎ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="가" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="개정이력">[6]단계별측정!#REF!</definedName>
+    <definedName name="개정이력">[4]단계별측정!#REF!</definedName>
     <definedName name="계획표">#REF!</definedName>
     <definedName name="공사설명서" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="과업">[7]COST!#REF!</definedName>
+    <definedName name="과업">[5]COST!#REF!</definedName>
     <definedName name="과업대비표1">#REF!</definedName>
     <definedName name="국소수_서울">#REF!</definedName>
     <definedName name="기존프로그램">#REF!</definedName>
     <definedName name="기준용어">#REF!</definedName>
     <definedName name="ㄴ" hidden="1">#REF!</definedName>
-    <definedName name="ㄴㄴ">[9]단계별측정!#REF!</definedName>
+    <definedName name="ㄴㄴ">[6]단계별측정!#REF!</definedName>
     <definedName name="ㄴㄴㄱ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="ㄴㄹ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="ㄴ아러" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="나" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="납기1">[11]IN!$B$5</definedName>
-    <definedName name="납기2">[13]IN!$B$5</definedName>
-    <definedName name="납기3">[11]IN!$D$5</definedName>
-    <definedName name="납기4">[13]IN!$D$5</definedName>
+    <definedName name="납기1">[7]IN!$B$5</definedName>
+    <definedName name="납기2">[8]IN!$B$5</definedName>
+    <definedName name="납기3">[7]IN!$D$5</definedName>
+    <definedName name="납기4">[8]IN!$D$5</definedName>
     <definedName name="ㄷ가" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="ㄷㄷㄷ">#REF!</definedName>
     <definedName name="다" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
@@ -128,7 +128,7 @@
     <definedName name="아ㅣㅈ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="아ㅣㅈㅂ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="알람관리">#REF!</definedName>
-    <definedName name="이력">[6]검토측정!#REF!</definedName>
+    <definedName name="이력">[4]검토측정!#REF!</definedName>
     <definedName name="이름" hidden="1">#REF!</definedName>
     <definedName name="이름1">#REF!</definedName>
     <definedName name="일반현황__2_">#REF!</definedName>
@@ -140,8 +140,8 @@
     <definedName name="자" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="자ㅓㄷ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="재료집계3">#REF!</definedName>
-    <definedName name="전기출력2">[14]ELEC!$B$3:$M$3,[14]ELEC!$B$4:$M$4,[14]ELEC!$B$5:$M$5,[14]ELEC!$B$7:$M$7</definedName>
-    <definedName name="전기출력3">[14]ELEC!$B$3:$M$3,[14]ELEC!$B$6:$M$6,[14]ELEC!$B$8:$M$8</definedName>
+    <definedName name="전기출력2">[9]ELEC!$B$3:$M$3,[9]ELEC!$B$4:$M$4,[9]ELEC!$B$5:$M$5,[9]ELEC!$B$7:$M$7</definedName>
+    <definedName name="전기출력3">[9]ELEC!$B$3:$M$3,[9]ELEC!$B$6:$M$6,[9]ELEC!$B$8:$M$8</definedName>
     <definedName name="정" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="제주추가종합수정안" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
     <definedName name="중계기현황">#REF!</definedName>
@@ -153,7 +153,7 @@
     <definedName name="충남신설">#REF!</definedName>
     <definedName name="충북신설">#REF!</definedName>
     <definedName name="ㅋ">#REF!</definedName>
-    <definedName name="ㅋㅋ">[9]단계별측정!#REF!</definedName>
+    <definedName name="ㅋㅋ">[6]단계별측정!#REF!</definedName>
     <definedName name="ㅋㅋㅋ">#REF!</definedName>
     <definedName name="카" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="타" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
@@ -165,7 +165,7 @@
     <definedName name="하" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="한" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
     <definedName name="합계">#REF!</definedName>
-    <definedName name="협업포탈_1">'[3]예정(3)'!#REF!</definedName>
+    <definedName name="협업포탈_1">'[2]예정(3)'!#REF!</definedName>
     <definedName name="홎ㅅㄱ도" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="ㅏㄷ" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="ㅏ도">#REF!</definedName>
@@ -192,7 +192,7 @@
     <definedName name="ㄻㄹ" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
     <definedName name="A">#REF!</definedName>
     <definedName name="A000">#REF!</definedName>
-    <definedName name="a2121212">'[4]9GNG운반'!#REF!</definedName>
+    <definedName name="a2121212">'[3]9GNG운반'!#REF!</definedName>
     <definedName name="AA" hidden="1">#REF!</definedName>
     <definedName name="AAA">#REF!</definedName>
     <definedName name="AAAA">#REF!</definedName>
@@ -200,9 +200,9 @@
     <definedName name="add">#REF!</definedName>
     <definedName name="ARSCC">#REF!</definedName>
     <definedName name="ASIC">#REF!</definedName>
-    <definedName name="b">[6]단계별측정!#REF!</definedName>
-    <definedName name="baseline">[16]CSR납기분석!#REF!</definedName>
-    <definedName name="bb">'[4]9GNG운반'!#REF!</definedName>
+    <definedName name="b">[4]단계별측정!#REF!</definedName>
+    <definedName name="baseline">[10]CSR납기분석!#REF!</definedName>
+    <definedName name="bb">'[3]9GNG운반'!#REF!</definedName>
     <definedName name="BTSINFO_991Q">#REF!</definedName>
     <definedName name="BTSINFO_992Q">#REF!</definedName>
     <definedName name="BTSINFO_팀구분">#REF!</definedName>
@@ -220,8 +220,8 @@
     <definedName name="CHC_경기">#REF!</definedName>
     <definedName name="CHC_서울">#REF!</definedName>
     <definedName name="CHC_서울_COUNT">#REF!</definedName>
-    <definedName name="CHC산출_경기">'[18]Calc V1.2'!$H$1:$AC$65536</definedName>
-    <definedName name="CHC산출_서울">'[18]Calc V1.2 (2)'!$H$1:$AC$65536</definedName>
+    <definedName name="CHC산출_경기">'[11]Calc V1.2'!$H$1:$AC$65536</definedName>
+    <definedName name="CHC산출_서울">'[11]Calc V1.2 (2)'!$H$1:$AC$65536</definedName>
     <definedName name="Comments">#REF!</definedName>
     <definedName name="cost_a">#REF!</definedName>
     <definedName name="cost_b">#REF!</definedName>
@@ -239,9 +239,9 @@
     <definedName name="DocumentName">"OE-TS-UTR-001"</definedName>
     <definedName name="dsfga" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
     <definedName name="DTIC">#REF!</definedName>
-    <definedName name="e">[6]단계별측정!#REF!</definedName>
-    <definedName name="ee">[6]단계별측정!#REF!</definedName>
-    <definedName name="eeeeee">[6]단계별측정!#REF!</definedName>
+    <definedName name="e">[4]단계별측정!#REF!</definedName>
+    <definedName name="ee">[4]단계별측정!#REF!</definedName>
+    <definedName name="eeeeee">[4]단계별측정!#REF!</definedName>
     <definedName name="effort_a">#REF!</definedName>
     <definedName name="effort_change">#REF!</definedName>
     <definedName name="effort_e">#REF!</definedName>
@@ -261,7 +261,7 @@
     <definedName name="ENGDATA">#REF!</definedName>
     <definedName name="Entity_List">#REF!</definedName>
     <definedName name="er" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="Est_Eff_MDay">[20]FPA!#REF!</definedName>
+    <definedName name="Est_Eff_MDay">[12]FPA!#REF!</definedName>
     <definedName name="ex_rate">#REF!</definedName>
     <definedName name="FA_서울">#REF!</definedName>
     <definedName name="fdssdsdfds">#REF!</definedName>
@@ -278,12 +278,12 @@
     <definedName name="hejlkw" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="hsdgfjhf" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="ICPC">#REF!</definedName>
-    <definedName name="Index">'[22]Data Vol'!$B$6:$E$6816</definedName>
+    <definedName name="Index">'[13]Data Vol'!$B$6:$E$6816</definedName>
     <definedName name="IT_A">IF( OR(AND(#REF!&lt;2,#REF!&gt;15), AND(#REF!=2, AND(#REF!&gt;= 5,#REF!&lt;= 15)), AND(#REF!&gt;2, AND(#REF!&gt;=1,#REF!&lt;= 4)) ),1,0)</definedName>
     <definedName name="IT_C">IF( OR(AND(#REF!=2,#REF!&gt; 15), AND(#REF!&gt;2,#REF!&gt;=  5) ),1,0)</definedName>
     <definedName name="IT_S">IF( OR(AND(#REF!&lt;2, AND(#REF!&gt;= 1,#REF!&lt;= 15)), AND(#REF!=2, AND(#REF!&gt;= 1,#REF!&lt;= 4)) ),1,0)</definedName>
-    <definedName name="itsa_ratio_nrec">[23]공수견적!#REF!</definedName>
-    <definedName name="itsa_ratio_rec">[20]순수개발!#REF!</definedName>
+    <definedName name="itsa_ratio_nrec">[14]공수견적!#REF!</definedName>
+    <definedName name="itsa_ratio_rec">[12]순수개발!#REF!</definedName>
     <definedName name="IWFIC" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="jdkl" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="jeklw" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
@@ -305,12 +305,12 @@
     <definedName name="MSIC">#REF!</definedName>
     <definedName name="MSICC">#REF!</definedName>
     <definedName name="MTC">#REF!</definedName>
-    <definedName name="name">[11]IN!$D$5</definedName>
-    <definedName name="name1">[11]IN!$D$5</definedName>
+    <definedName name="name">[7]IN!$D$5</definedName>
+    <definedName name="name1">[7]IN!$D$5</definedName>
     <definedName name="NESC">#REF!</definedName>
     <definedName name="NO">#REF!</definedName>
     <definedName name="OCPC">#REF!</definedName>
-    <definedName name="oo">'[3]동원(3)'!#REF!</definedName>
+    <definedName name="oo">'[2]동원(3)'!#REF!</definedName>
     <definedName name="OT_A">IF( OR(AND(#REF!&lt;2,#REF!&gt;19), AND(AND(#REF!&gt;=2,#REF!&lt;= 3), AND(#REF!&gt;= 6,#REF!&lt;= 19)), AND(#REF!&gt;3, AND(#REF!&gt;= 1,#REF!&lt;= 5)) ),1,0)</definedName>
     <definedName name="OT_C">IF( OR(AND(AND(#REF!&gt;=2,#REF!&lt;=3),#REF!&gt; 19), AND(#REF!&gt;3,#REF!&gt;=  6) ),1,0)</definedName>
     <definedName name="OT_S">IF( OR(AND(#REF!&lt;2, AND(#REF!&gt;= 1,#REF!&lt;= 19)), AND(AND(#REF!&gt;=2,#REF!&lt;=3), AND(#REF!&gt;= 1,#REF!&lt;= 5)) ),1,0)</definedName>
@@ -331,7 +331,7 @@
     <definedName name="review_defect">#REF!</definedName>
     <definedName name="review_error">#REF!</definedName>
     <definedName name="RMS">#REF!</definedName>
-    <definedName name="rpt_date">[26]요약!$C$4</definedName>
+    <definedName name="rpt_date">[15]요약!$C$4</definedName>
     <definedName name="rr" hidden="1">#REF!</definedName>
     <definedName name="RRR" hidden="1">#REF!</definedName>
     <definedName name="s" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
@@ -342,7 +342,7 @@
     <definedName name="schedule_e_s">#REF!</definedName>
     <definedName name="SEC_서울">#REF!</definedName>
     <definedName name="Severity">#REF!</definedName>
-    <definedName name="size_code_e">[6]소스코드크기측정!#REF!</definedName>
+    <definedName name="size_code_e">[4]소스코드크기측정!#REF!</definedName>
     <definedName name="SS" hidden="1">#REF!</definedName>
     <definedName name="SSD">#REF!</definedName>
     <definedName name="SSN7C">#REF!</definedName>
@@ -350,7 +350,7 @@
     <definedName name="staffMonth">#REF!</definedName>
     <definedName name="staffWeek">#REF!</definedName>
     <definedName name="State_of_Origin">#REF!</definedName>
-    <definedName name="tol">'[16]규모,공수분석'!#REF!</definedName>
+    <definedName name="tol">'[10]규모,공수분석'!#REF!</definedName>
     <definedName name="TOTAL" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="tt" hidden="1">#REF!</definedName>
     <definedName name="TTT">#REF!</definedName>
@@ -401,38 +401,38 @@
     <definedName name="zzzzzzzzzzzzzzzzzzz">#REF!</definedName>
     <definedName name="_" localSheetId="0">#REF!</definedName>
     <definedName name="__" localSheetId="0">#REF!</definedName>
-    <definedName name="_80486SX_25" localSheetId="0">[2]COST!#REF!</definedName>
+    <definedName name="_80486SX_25" localSheetId="0">[16]COST!#REF!</definedName>
     <definedName name="_kwy1" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="_L80486SX_25" localSheetId="0">[2]COST!#REF!</definedName>
-    <definedName name="_SX25" localSheetId="0">[2]COST!#REF!</definedName>
+    <definedName name="_L80486SX_25" localSheetId="0">[16]COST!#REF!</definedName>
+    <definedName name="_SX25" localSheetId="0">[16]COST!#REF!</definedName>
     <definedName name="_Table1_In1" localSheetId="0" hidden="1">#REF!</definedName>
     <definedName name="_Table1_Out" localSheetId="0" hidden="1">#REF!</definedName>
-    <definedName name="_wo1" localSheetId="0">'[3]예정(3)'!#REF!</definedName>
-    <definedName name="\0" localSheetId="0">'[5]9GNG운반'!#REF!</definedName>
-    <definedName name="\A" localSheetId="0">'[5]9GNG운반'!#REF!</definedName>
-    <definedName name="\B" localSheetId="0">'[5]9GNG운반'!#REF!</definedName>
-    <definedName name="\I" localSheetId="0">'[5]9GNG운반'!#REF!</definedName>
-    <definedName name="\O" localSheetId="0">'[5]9GNG운반'!#REF!</definedName>
-    <definedName name="\P" localSheetId="0">'[5]9GNG운반'!#REF!</definedName>
-    <definedName name="\Q" localSheetId="0">'[5]9GNG운반'!#REF!</definedName>
+    <definedName name="_wo1" localSheetId="0">'[2]예정(3)'!#REF!</definedName>
+    <definedName name="\0" localSheetId="0">'[17]9GNG운반'!#REF!</definedName>
+    <definedName name="\A" localSheetId="0">'[17]9GNG운반'!#REF!</definedName>
+    <definedName name="\B" localSheetId="0">'[17]9GNG운반'!#REF!</definedName>
+    <definedName name="\I" localSheetId="0">'[17]9GNG운반'!#REF!</definedName>
+    <definedName name="\O" localSheetId="0">'[17]9GNG운반'!#REF!</definedName>
+    <definedName name="\P" localSheetId="0">'[17]9GNG운반'!#REF!</definedName>
+    <definedName name="\Q" localSheetId="0">'[17]9GNG운반'!#REF!</definedName>
     <definedName name="ㄱ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
     <definedName name="ㄱㅎㄷㄱㅎ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="가" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="계획표" localSheetId="0">#REF!</definedName>
     <definedName name="공사설명서" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="과업" localSheetId="0">[2]COST!#REF!</definedName>
+    <definedName name="과업" localSheetId="0">[16]COST!#REF!</definedName>
     <definedName name="과업대비표1" localSheetId="0">#REF!</definedName>
     <definedName name="국소수_서울" localSheetId="0">#REF!</definedName>
     <definedName name="기존프로그램" localSheetId="0">#REF!</definedName>
-    <definedName name="ㄴㄴ" localSheetId="0">[8]단계별측정!#REF!</definedName>
+    <definedName name="ㄴㄴ" localSheetId="0">[18]단계별측정!#REF!</definedName>
     <definedName name="ㄴㄴㄱ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="ㄴㄹ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="ㄴ아러" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="나" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="납기1" localSheetId="0">[10]IN!$B$5</definedName>
-    <definedName name="납기2" localSheetId="0">[12]IN!$B$5</definedName>
-    <definedName name="납기3" localSheetId="0">[10]IN!$D$5</definedName>
-    <definedName name="납기4" localSheetId="0">[12]IN!$D$5</definedName>
+    <definedName name="납기1" localSheetId="0">[19]IN!$B$5</definedName>
+    <definedName name="납기2" localSheetId="0">[20]IN!$B$5</definedName>
+    <definedName name="납기3" localSheetId="0">[19]IN!$D$5</definedName>
+    <definedName name="납기4" localSheetId="0">[20]IN!$D$5</definedName>
     <definedName name="ㄷ가" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="다" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="두지" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
@@ -486,7 +486,7 @@
     <definedName name="지두" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="차" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="총괄11" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="ㅋㅋ" localSheetId="0">[8]단계별측정!#REF!</definedName>
+    <definedName name="ㅋㅋ" localSheetId="0">[18]단계별측정!#REF!</definedName>
     <definedName name="ㅋㅋㅋ" localSheetId="0">#REF!</definedName>
     <definedName name="카" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="타" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
@@ -514,26 +514,26 @@
     <definedName name="ㄻㄹ" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
     <definedName name="A" localSheetId="0">#REF!</definedName>
     <definedName name="A000" localSheetId="0">#REF!</definedName>
-    <definedName name="a2121212" localSheetId="0">'[5]9GNG운반'!#REF!</definedName>
+    <definedName name="a2121212" localSheetId="0">'[17]9GNG운반'!#REF!</definedName>
     <definedName name="AA" localSheetId="0" hidden="1">#REF!</definedName>
     <definedName name="AAA" localSheetId="0">#REF!</definedName>
     <definedName name="AAAA" localSheetId="0">#REF!</definedName>
-    <definedName name="baseline" localSheetId="0">[15]CSR납기분석!#REF!</definedName>
-    <definedName name="bb" localSheetId="0">'[5]9GNG운반'!#REF!</definedName>
+    <definedName name="baseline" localSheetId="0">[21]CSR납기분석!#REF!</definedName>
+    <definedName name="bb" localSheetId="0">'[17]9GNG운반'!#REF!</definedName>
     <definedName name="BTSINFO_991Q" localSheetId="0">#REF!</definedName>
     <definedName name="BTSINFO_992Q" localSheetId="0">#REF!</definedName>
     <definedName name="BTSINFO_팀구분" localSheetId="0">#REF!</definedName>
-    <definedName name="C80486DX_33" localSheetId="0">[2]COST!#REF!</definedName>
-    <definedName name="C80486DX_50" localSheetId="0">[2]COST!#REF!</definedName>
-    <definedName name="C80486DX2_50" localSheetId="0">[2]COST!#REF!</definedName>
-    <definedName name="C80486DX2_66" localSheetId="0">[2]COST!#REF!</definedName>
-    <definedName name="C80486SX_25" localSheetId="0">[2]COST!#REF!</definedName>
-    <definedName name="C80486SX_33" localSheetId="0">[2]COST!#REF!</definedName>
+    <definedName name="C80486DX_33" localSheetId="0">[16]COST!#REF!</definedName>
+    <definedName name="C80486DX_50" localSheetId="0">[16]COST!#REF!</definedName>
+    <definedName name="C80486DX2_50" localSheetId="0">[16]COST!#REF!</definedName>
+    <definedName name="C80486DX2_66" localSheetId="0">[16]COST!#REF!</definedName>
+    <definedName name="C80486SX_25" localSheetId="0">[16]COST!#REF!</definedName>
+    <definedName name="C80486SX_33" localSheetId="0">[16]COST!#REF!</definedName>
     <definedName name="CAMPC" localSheetId="0">#REF!</definedName>
     <definedName name="cause" localSheetId="0">#REF!</definedName>
     <definedName name="CB_1" localSheetId="0">#REF!</definedName>
-    <definedName name="CHC산출_경기" localSheetId="0">'[17]Calc V1.2'!$H$1:$AC$65536</definedName>
-    <definedName name="CHC산출_서울" localSheetId="0">'[17]Calc V1.2 (2)'!$H$1:$AC$65536</definedName>
+    <definedName name="CHC산출_경기" localSheetId="0">'[22]Calc V1.2'!$H$1:$AC$65536</definedName>
+    <definedName name="CHC산출_서울" localSheetId="0">'[22]Calc V1.2 (2)'!$H$1:$AC$65536</definedName>
     <definedName name="Comments" localSheetId="0">#REF!</definedName>
     <definedName name="cost_a" localSheetId="0">#REF!</definedName>
     <definedName name="cost_b" localSheetId="0">#REF!</definedName>
@@ -552,7 +552,7 @@
     <definedName name="EI_C" localSheetId="0">IF( OR(AND(AND(#REF!&gt;=2,#REF!&lt;=5),#REF!&gt; 50), AND(#REF!&gt;5,#REF!&gt;=  20) ),1,0)</definedName>
     <definedName name="EI_S" localSheetId="0">IF( OR(AND(#REF!&lt;2, AND(#REF!&gt;= 1,#REF!&lt;= 50)), AND(AND(#REF!&gt;=2,#REF!&lt;=5), AND(#REF!&gt;= 1,#REF!&lt;= 19)) ),1,0)</definedName>
     <definedName name="er" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="Est_Eff_MDay" localSheetId="0">[19]FPA!#REF!</definedName>
+    <definedName name="Est_Eff_MDay" localSheetId="0">[23]FPA!#REF!</definedName>
     <definedName name="ex_rate" localSheetId="0">#REF!</definedName>
     <definedName name="FA_서울" localSheetId="0">#REF!</definedName>
     <definedName name="fdssdsdfds" localSheetId="0">#REF!</definedName>
@@ -565,12 +565,12 @@
     <definedName name="H" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
     <definedName name="hejlkw" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="hsdgfjhf" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="Index" localSheetId="0">'[21]Data Vol'!$B$6:$E$6816</definedName>
+    <definedName name="Index" localSheetId="0">'[24]Data Vol'!$B$6:$E$6816</definedName>
     <definedName name="IT_A" localSheetId="0">IF( OR(AND(#REF!&lt;2,#REF!&gt;15), AND(#REF!=2, AND(#REF!&gt;= 5,#REF!&lt;= 15)), AND(#REF!&gt;2, AND(#REF!&gt;=1,#REF!&lt;= 4)) ),1,0)</definedName>
     <definedName name="IT_C" localSheetId="0">IF( OR(AND(#REF!=2,#REF!&gt; 15), AND(#REF!&gt;2,#REF!&gt;=  5) ),1,0)</definedName>
     <definedName name="IT_S" localSheetId="0">IF( OR(AND(#REF!&lt;2, AND(#REF!&gt;= 1,#REF!&lt;= 15)), AND(#REF!=2, AND(#REF!&gt;= 1,#REF!&lt;= 4)) ),1,0)</definedName>
-    <definedName name="itsa_ratio_nrec" localSheetId="0">[24]공수견적!#REF!</definedName>
-    <definedName name="itsa_ratio_rec" localSheetId="0">[19]순수개발!#REF!</definedName>
+    <definedName name="itsa_ratio_nrec" localSheetId="0">[25]공수견적!#REF!</definedName>
+    <definedName name="itsa_ratio_rec" localSheetId="0">[23]순수개발!#REF!</definedName>
     <definedName name="IWFIC" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="jdkl" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="jeklw" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
@@ -582,38 +582,38 @@
     <definedName name="kljdklw" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="klwjdk" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="kwy" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="L80486SX_25" localSheetId="0">[2]COST!#REF!</definedName>
+    <definedName name="L80486SX_25" localSheetId="0">[16]COST!#REF!</definedName>
     <definedName name="LastRow" localSheetId="0">#REF!</definedName>
     <definedName name="LPA_서울" localSheetId="0">#REF!</definedName>
     <definedName name="LRIC" localSheetId="0">#REF!</definedName>
-    <definedName name="name" localSheetId="0">[10]IN!$D$5</definedName>
-    <definedName name="name1" localSheetId="0">[10]IN!$D$5</definedName>
+    <definedName name="name" localSheetId="0">[19]IN!$D$5</definedName>
+    <definedName name="name1" localSheetId="0">[19]IN!$D$5</definedName>
     <definedName name="NESC" localSheetId="0">#REF!</definedName>
     <definedName name="NO" localSheetId="0">#REF!</definedName>
     <definedName name="OCPC" localSheetId="0">#REF!</definedName>
-    <definedName name="oo" localSheetId="0">'[3]동원(3)'!#REF!</definedName>
+    <definedName name="oo" localSheetId="0">'[2]동원(3)'!#REF!</definedName>
     <definedName name="OT_A" localSheetId="0">IF( OR(AND(#REF!&lt;2,#REF!&gt;19), AND(AND(#REF!&gt;=2,#REF!&lt;= 3), AND(#REF!&gt;= 6,#REF!&lt;= 19)), AND(#REF!&gt;3, AND(#REF!&gt;= 1,#REF!&lt;= 5)) ),1,0)</definedName>
     <definedName name="OT_C" localSheetId="0">IF( OR(AND(AND(#REF!&gt;=2,#REF!&lt;=3),#REF!&gt; 19), AND(#REF!&gt;3,#REF!&gt;=  6) ),1,0)</definedName>
     <definedName name="OT_S" localSheetId="0">IF( OR(AND(#REF!&lt;2, AND(#REF!&gt;= 1,#REF!&lt;= 19)), AND(AND(#REF!&gt;=2,#REF!&lt;=3), AND(#REF!&gt;= 1,#REF!&lt;= 5)) ),1,0)</definedName>
     <definedName name="PAP" localSheetId="0">#REF!</definedName>
     <definedName name="PERT" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="PRICE" localSheetId="0">[2]COST!#REF!</definedName>
+    <definedName name="PRICE" localSheetId="0">[16]COST!#REF!</definedName>
     <definedName name="Q" localSheetId="0">#REF!</definedName>
     <definedName name="qq" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="QT_A" localSheetId="0">IF( OR(AND(#REF!&lt;2,#REF!&gt;19), AND(AND(#REF!&gt;=2,#REF!&lt;= 3), AND(#REF!&gt;= 6,#REF!&lt;= 19)), AND(#REF!&gt;3, AND(#REF!&gt;= 1,#REF!&lt;= 5)) ),1,0)</definedName>
     <definedName name="QT_C" localSheetId="0">IF( OR(AND(AND(#REF!&gt;=2,#REF!&lt;=3),#REF!&gt; 19), AND(#REF!&gt;3,#REF!&gt;=  6) ),1,0)</definedName>
     <definedName name="QT_S" localSheetId="0">IF( OR(AND(#REF!&lt;2, AND(#REF!&gt;= 1,#REF!&lt;= 19)), AND(AND(#REF!&gt;=2,#REF!&lt;=3), AND(#REF!&gt;= 1,#REF!&lt;= 5)) ),1,0)</definedName>
     <definedName name="RC0_서울" localSheetId="0">#REF!</definedName>
-    <definedName name="rpt_date" localSheetId="0">[25]요약!$C$4</definedName>
+    <definedName name="rpt_date" localSheetId="0">[26]요약!$C$4</definedName>
     <definedName name="rr" localSheetId="0" hidden="1">#REF!</definedName>
     <definedName name="RRR" localSheetId="0" hidden="1">#REF!</definedName>
     <definedName name="s" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
     <definedName name="SS" localSheetId="0" hidden="1">#REF!</definedName>
     <definedName name="SSD" localSheetId="0">#REF!</definedName>
     <definedName name="SSN7C" localSheetId="0">#REF!</definedName>
-    <definedName name="tol" localSheetId="0">'[15]규모,공수분석'!#REF!</definedName>
+    <definedName name="tol" localSheetId="0">'[21]규모,공수분석'!#REF!</definedName>
     <definedName name="TOTAL" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="US" localSheetId="0">[2]COST!$P$2</definedName>
+    <definedName name="US" localSheetId="0">[16]COST!$P$2</definedName>
     <definedName name="vbkjwhe" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="vdwf" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="vewtf" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
@@ -660,18 +660,18 @@
     <definedName name="_kwy1" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="_Table1_In1" localSheetId="1" hidden="1">#REF!</definedName>
     <definedName name="_Table1_Out" localSheetId="1" hidden="1">#REF!</definedName>
-    <definedName name="_wo1" localSheetId="1">'[3]예정(3)'!#REF!</definedName>
-    <definedName name="\0" localSheetId="1">'[4]9GNG운반'!#REF!</definedName>
+    <definedName name="_wo1" localSheetId="1">'[2]예정(3)'!#REF!</definedName>
+    <definedName name="\0" localSheetId="1">'[3]9GNG운반'!#REF!</definedName>
     <definedName name="ㄱ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
     <definedName name="ㄱㅎㄷㄱㅎ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="가" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="계획표" localSheetId="1">#REF!</definedName>
     <definedName name="공사설명서" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
-    <definedName name="과업" localSheetId="1">[2]COST!#REF!</definedName>
+    <definedName name="과업" localSheetId="1">[16]COST!#REF!</definedName>
     <definedName name="과업대비표1" localSheetId="1">#REF!</definedName>
     <definedName name="국소수_서울" localSheetId="1">#REF!</definedName>
     <definedName name="기존프로그램" localSheetId="1">#REF!</definedName>
-    <definedName name="ㄴㄴ" localSheetId="1">[8]단계별측정!#REF!</definedName>
+    <definedName name="ㄴㄴ" localSheetId="1">[18]단계별측정!#REF!</definedName>
     <definedName name="ㄴㄴㄱ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="ㄴㄹ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="ㄴ아러" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
@@ -726,7 +726,7 @@
     <definedName name="지두" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="차" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="총괄11" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
-    <definedName name="ㅋㅋ" localSheetId="1">[8]단계별측정!#REF!</definedName>
+    <definedName name="ㅋㅋ" localSheetId="1">[18]단계별측정!#REF!</definedName>
     <definedName name="ㅋㅋㅋ" localSheetId="1">#REF!</definedName>
     <definedName name="카" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="타" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
@@ -754,7 +754,7 @@
     <definedName name="ㄻㄹ" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"3가";#N/A,#N/A,FALSE,"3나";#N/A,#N/A,FALSE,"3다"}</definedName>
     <definedName name="A" localSheetId="1">#REF!</definedName>
     <definedName name="A000" localSheetId="1">#REF!</definedName>
-    <definedName name="a2121212" localSheetId="1">'[4]9GNG운반'!#REF!</definedName>
+    <definedName name="a2121212" localSheetId="1">'[3]9GNG운반'!#REF!</definedName>
     <definedName name="AA" localSheetId="1" hidden="1">#REF!</definedName>
     <definedName name="AAA" localSheetId="1">#REF!</definedName>
     <definedName name="AAAA" localSheetId="1">#REF!</definedName>
@@ -802,8 +802,8 @@
     <definedName name="IT_A" localSheetId="1">IF( OR(AND(#REF!&lt;2,#REF!&gt;15), AND(#REF!=2, AND(#REF!&gt;= 5,#REF!&lt;= 15)), AND(#REF!&gt;2, AND(#REF!&gt;=1,#REF!&lt;= 4)) ),1,0)</definedName>
     <definedName name="IT_C" localSheetId="1">IF( OR(AND(#REF!=2,#REF!&gt; 15), AND(#REF!&gt;2,#REF!&gt;=  5) ),1,0)</definedName>
     <definedName name="IT_S" localSheetId="1">IF( OR(AND(#REF!&lt;2, AND(#REF!&gt;= 1,#REF!&lt;= 15)), AND(#REF!=2, AND(#REF!&gt;= 1,#REF!&lt;= 4)) ),1,0)</definedName>
-    <definedName name="itsa_ratio_nrec" localSheetId="1">[23]공수견적!#REF!</definedName>
-    <definedName name="itsa_ratio_rec" localSheetId="1">[20]순수개발!#REF!</definedName>
+    <definedName name="itsa_ratio_nrec" localSheetId="1">[14]공수견적!#REF!</definedName>
+    <definedName name="itsa_ratio_rec" localSheetId="1">[12]순수개발!#REF!</definedName>
     <definedName name="IWFIC" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="jdkl" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
     <definedName name="jeklw" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
@@ -819,7 +819,7 @@
     <definedName name="NESC" localSheetId="1">#REF!</definedName>
     <definedName name="NO" localSheetId="1">#REF!</definedName>
     <definedName name="OCPC" localSheetId="1">#REF!</definedName>
-    <definedName name="oo" localSheetId="1">'[3]동원(3)'!#REF!</definedName>
+    <definedName name="oo" localSheetId="1">'[2]동원(3)'!#REF!</definedName>
     <definedName name="OT_A" localSheetId="1">IF( OR(AND(#REF!&lt;2,#REF!&gt;19), AND(AND(#REF!&gt;=2,#REF!&lt;= 3), AND(#REF!&gt;= 6,#REF!&lt;= 19)), AND(#REF!&gt;3, AND(#REF!&gt;= 1,#REF!&lt;= 5)) ),1,0)</definedName>
     <definedName name="OT_C" localSheetId="1">IF( OR(AND(AND(#REF!&gt;=2,#REF!&lt;=3),#REF!&gt; 19), AND(#REF!&gt;3,#REF!&gt;=  6) ),1,0)</definedName>
     <definedName name="PERT" localSheetId="1" hidden="1">{#N/A,#N/A,FALSE,"ALM-ASISC"}</definedName>
@@ -1676,16 +1676,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1704,13 +1711,6 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
       <alignment horizontal="center"/>
     </xf>
@@ -1906,89 +1906,6 @@
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
-      <sheetName val="산출"/>
-      <sheetName val="OUT"/>
-      <sheetName val="IN"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="산출"/>
-      <sheetName val="OUT"/>
-      <sheetName val="IN"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="IN"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="IN"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="main"/>
-      <sheetName val="DATA"/>
-      <sheetName val="ELEC"/>
-      <sheetName val="Raw"/>
-      <sheetName val="발생"/>
-      <sheetName val="평가"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
       <sheetName val="요약"/>
       <sheetName val="SIZE"/>
       <sheetName val="SIZE_DETAIL"/>
@@ -2050,72 +1967,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="요약"/>
-      <sheetName val="SIZE"/>
-      <sheetName val="SIZE_DETAIL"/>
-      <sheetName val="운영현황보고(6월)"/>
-      <sheetName val="Summary"/>
-      <sheetName val="유형별CSR처리현황"/>
-      <sheetName val="등급(처리시간)별 CSR 처리현황"/>
-      <sheetName val="주별 CSR 처리현황"/>
-      <sheetName val="유형별 CSR 분석(모듈)"/>
-      <sheetName val="규모,공수분석"/>
-      <sheetName val="기타 공수분석"/>
-      <sheetName val="CCR(최대CPU사용율)"/>
-      <sheetName val="CCR(평균CPU사용율)"/>
-      <sheetName val="CCR(최대PAGING SPACE IO"/>
-      <sheetName val="CCR(디스크사용량)"/>
-      <sheetName val="CSR납기분석"/>
-      <sheetName val="inspection_data(5월)"/>
-      <sheetName val="inspection_data(6월)"/>
-      <sheetName val="결함유형분석"/>
-      <sheetName val="결함종류별 분석"/>
-      <sheetName val="TEST결함관리"/>
-      <sheetName val="Inspection summary"/>
-      <sheetName val="위험문제관리"/>
-      <sheetName val="구성관리(실적)"/>
-      <sheetName val="SQA"/>
-      <sheetName val="교육"/>
-      <sheetName val="2003년도_교육계획(안)"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20"/>
-      <sheetData sheetId="21"/>
-      <sheetData sheetId="22"/>
-      <sheetData sheetId="23"/>
-      <sheetData sheetId="24"/>
-      <sheetData sheetId="25"/>
-      <sheetData sheetId="26"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2130,22 +1982,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Calc V1.2 (2)"/>
-      <sheetName val="Calc V1.2"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2196,71 +2033,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="COST"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink20.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="ILF &amp; EIF"/>
-      <sheetName val="EI"/>
-      <sheetName val="EQ"/>
-      <sheetName val="EO"/>
-      <sheetName val="FPA"/>
-      <sheetName val="Package (In-House)"/>
-      <sheetName val="In House"/>
-      <sheetName val="VAF"/>
-      <sheetName val="순수개발"/>
-      <sheetName val="Macro상수지정"/>
-      <sheetName val="Config"/>
-      <sheetName val="Package (by ITSA)"/>
-      <sheetName val="Dialog1"/>
-      <sheetName val="Module1"/>
-      <sheetName val="Module2"/>
-      <sheetName val="영남_1"/>
-      <sheetName val="견적990322"/>
-      <sheetName val="20관리비율"/>
-      <sheetName val="Sheet1"/>
-      <sheetName val="노임"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14" refreshError="1"/>
-      <sheetData sheetId="15" refreshError="1"/>
-      <sheetData sheetId="16" refreshError="1"/>
-      <sheetData sheetId="17" refreshError="1"/>
-      <sheetData sheetId="18" refreshError="1"/>
-      <sheetData sheetId="19" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2285,32 +2058,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink22.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="fpa_dev(dev)"/>
-      <sheetName val="Data Vol"/>
-      <sheetName val="FPA"/>
-      <sheetName val="순수개발"/>
-      <sheetName val="ilch"/>
-      <sheetName val="Galaxy 소비자가격표"/>
-      <sheetName val="공사내역"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2343,40 +2091,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="개정이력"/>
-      <sheetName val="기본정보"/>
-      <sheetName val="Data"/>
-      <sheetName val="Transaction"/>
-      <sheetName val="FPA_검증"/>
-      <sheetName val="VAF"/>
-      <sheetName val="공수견적"/>
-      <sheetName val="비용산정"/>
-      <sheetName val="품질항목"/>
-      <sheetName val="CountingTip"/>
-      <sheetName val="Macro상수"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2462,6 +2177,341 @@
       <sheetData sheetId="37"/>
       <sheetData sheetId="38"/>
       <sheetData sheetId="39"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="COST"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="9GNG운반"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="프로젝트정보"/>
+      <sheetName val="크기추정"/>
+      <sheetName val="공수추정"/>
+      <sheetName val="단계별측정"/>
+      <sheetName val="검토측정"/>
+      <sheetName val="변경측정"/>
+      <sheetName val="문서크기측정"/>
+      <sheetName val="소스코드크기측정"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="산출"/>
+      <sheetName val="OUT"/>
+      <sheetName val="IN"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="예정(3)"/>
+      <sheetName val="동원(3)"/>
+      <sheetName val="공사설명서"/>
+      <sheetName val="주요자재"/>
+      <sheetName val="예정공정표 (2)"/>
+      <sheetName val="동원인원 (2)"/>
+      <sheetName val="예정공정표"/>
+      <sheetName val="동원인원"/>
+      <sheetName val="가설공사"/>
+      <sheetName val="가설울타리"/>
+      <sheetName val="경고테이프"/>
+      <sheetName val="포장절단"/>
+      <sheetName val="FM공법 (2)"/>
+      <sheetName val="FM공법"/>
+      <sheetName val="인수공지수판"/>
+      <sheetName val="양수작업"/>
+      <sheetName val="상수도이설"/>
+      <sheetName val="포장복구(AS,CO)"/>
+      <sheetName val="압입공법"/>
+      <sheetName val="GR보호몰탈"/>
+      <sheetName val="교량첨가"/>
+      <sheetName val="피스표(수정)"/>
+      <sheetName val="피스표(수도)"/>
+      <sheetName val="피스표(4pe)"/>
+      <sheetName val="목차"/>
+      <sheetName val="소요노력"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="15" refreshError="1"/>
+      <sheetData sheetId="16" refreshError="1"/>
+      <sheetData sheetId="17" refreshError="1"/>
+      <sheetData sheetId="18" refreshError="1"/>
+      <sheetData sheetId="19" refreshError="1"/>
+      <sheetData sheetId="20" refreshError="1"/>
+      <sheetData sheetId="21" refreshError="1"/>
+      <sheetData sheetId="22" refreshError="1"/>
+      <sheetData sheetId="23" refreshError="1"/>
+      <sheetData sheetId="24" refreshError="1"/>
+      <sheetData sheetId="25" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink20.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="IN"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink21.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="요약"/>
+      <sheetName val="SIZE"/>
+      <sheetName val="SIZE_DETAIL"/>
+      <sheetName val="운영현황보고(6월)"/>
+      <sheetName val="Summary"/>
+      <sheetName val="유형별CSR처리현황"/>
+      <sheetName val="등급(처리시간)별 CSR 처리현황"/>
+      <sheetName val="주별 CSR 처리현황"/>
+      <sheetName val="유형별 CSR 분석(모듈)"/>
+      <sheetName val="규모,공수분석"/>
+      <sheetName val="기타 공수분석"/>
+      <sheetName val="CCR(최대CPU사용율)"/>
+      <sheetName val="CCR(평균CPU사용율)"/>
+      <sheetName val="CCR(최대PAGING SPACE IO"/>
+      <sheetName val="CCR(디스크사용량)"/>
+      <sheetName val="CSR납기분석"/>
+      <sheetName val="inspection_data(5월)"/>
+      <sheetName val="inspection_data(6월)"/>
+      <sheetName val="결함유형분석"/>
+      <sheetName val="결함종류별 분석"/>
+      <sheetName val="TEST결함관리"/>
+      <sheetName val="Inspection summary"/>
+      <sheetName val="위험문제관리"/>
+      <sheetName val="구성관리(실적)"/>
+      <sheetName val="SQA"/>
+      <sheetName val="교육"/>
+      <sheetName val="2003년도_교육계획(안)"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
+      <sheetData sheetId="22"/>
+      <sheetData sheetId="23"/>
+      <sheetData sheetId="24"/>
+      <sheetData sheetId="25"/>
+      <sheetData sheetId="26"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink22.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Calc V1.2 (2)"/>
+      <sheetName val="Calc V1.2"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="ILF &amp; EIF"/>
+      <sheetName val="EI"/>
+      <sheetName val="EQ"/>
+      <sheetName val="EO"/>
+      <sheetName val="FPA"/>
+      <sheetName val="Package (In-House)"/>
+      <sheetName val="In House"/>
+      <sheetName val="VAF"/>
+      <sheetName val="순수개발"/>
+      <sheetName val="Macro상수지정"/>
+      <sheetName val="Config"/>
+      <sheetName val="Package (by ITSA)"/>
+      <sheetName val="Dialog1"/>
+      <sheetName val="Module1"/>
+      <sheetName val="Module2"/>
+      <sheetName val="영남_1"/>
+      <sheetName val="견적990322"/>
+      <sheetName val="20관리비율"/>
+      <sheetName val="Sheet1"/>
+      <sheetName val="노임"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="15" refreshError="1"/>
+      <sheetData sheetId="16" refreshError="1"/>
+      <sheetData sheetId="17" refreshError="1"/>
+      <sheetData sheetId="18" refreshError="1"/>
+      <sheetData sheetId="19" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="fpa_dev(dev)"/>
+      <sheetName val="Data Vol"/>
+      <sheetName val="FPA"/>
+      <sheetName val="순수개발"/>
+      <sheetName val="ilch"/>
+      <sheetName val="Galaxy 소비자가격표"/>
+      <sheetName val="공사내역"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="개정이력"/>
+      <sheetName val="기본정보"/>
+      <sheetName val="Data"/>
+      <sheetName val="Transaction"/>
+      <sheetName val="FPA_검증"/>
+      <sheetName val="VAF"/>
+      <sheetName val="공수견적"/>
+      <sheetName val="비용산정"/>
+      <sheetName val="품질항목"/>
+      <sheetName val="CountingTip"/>
+      <sheetName val="Macro상수"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2562,69 +2612,6 @@
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
-      <sheetName val="예정(3)"/>
-      <sheetName val="동원(3)"/>
-      <sheetName val="공사설명서"/>
-      <sheetName val="주요자재"/>
-      <sheetName val="예정공정표 (2)"/>
-      <sheetName val="동원인원 (2)"/>
-      <sheetName val="예정공정표"/>
-      <sheetName val="동원인원"/>
-      <sheetName val="가설공사"/>
-      <sheetName val="가설울타리"/>
-      <sheetName val="경고테이프"/>
-      <sheetName val="포장절단"/>
-      <sheetName val="FM공법 (2)"/>
-      <sheetName val="FM공법"/>
-      <sheetName val="인수공지수판"/>
-      <sheetName val="양수작업"/>
-      <sheetName val="상수도이설"/>
-      <sheetName val="포장복구(AS,CO)"/>
-      <sheetName val="압입공법"/>
-      <sheetName val="GR보호몰탈"/>
-      <sheetName val="교량첨가"/>
-      <sheetName val="피스표(수정)"/>
-      <sheetName val="피스표(수도)"/>
-      <sheetName val="피스표(4pe)"/>
-      <sheetName val="목차"/>
-      <sheetName val="소요노력"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14" refreshError="1"/>
-      <sheetData sheetId="15" refreshError="1"/>
-      <sheetData sheetId="16" refreshError="1"/>
-      <sheetData sheetId="17" refreshError="1"/>
-      <sheetData sheetId="18" refreshError="1"/>
-      <sheetData sheetId="19" refreshError="1"/>
-      <sheetData sheetId="20" refreshError="1"/>
-      <sheetData sheetId="21" refreshError="1"/>
-      <sheetData sheetId="22" refreshError="1"/>
-      <sheetData sheetId="23" refreshError="1"/>
-      <sheetData sheetId="24" refreshError="1"/>
-      <sheetData sheetId="25" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
       <sheetName val="9GNG운반"/>
     </sheetNames>
     <sheetDataSet>
@@ -2634,20 +2621,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="9GNG운반"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2674,7 +2648,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2687,34 +2661,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="프로젝트정보"/>
-      <sheetName val="크기추정"/>
-      <sheetName val="공수추정"/>
-      <sheetName val="단계별측정"/>
-      <sheetName val="검토측정"/>
-      <sheetName val="변경측정"/>
-      <sheetName val="문서크기측정"/>
-      <sheetName val="소스코드크기측정"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2736,6 +2683,59 @@
       <sheetData sheetId="5"/>
       <sheetData sheetId="6"/>
       <sheetData sheetId="7"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="산출"/>
+      <sheetName val="OUT"/>
+      <sheetName val="IN"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="IN"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="main"/>
+      <sheetName val="DATA"/>
+      <sheetName val="ELEC"/>
+      <sheetName val="Raw"/>
+      <sheetName val="발생"/>
+      <sheetName val="평가"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3011,55 +3011,55 @@
   <dimension ref="A2:K30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
-    <col width="6.5" customWidth="1" style="65" min="1" max="1"/>
-    <col width="3.83203125" customWidth="1" style="65" min="2" max="2"/>
-    <col width="9.6640625" customWidth="1" style="65" min="3" max="4"/>
-    <col width="3.33203125" customWidth="1" style="65" min="5" max="5"/>
-    <col width="9.6640625" customWidth="1" style="65" min="6" max="7"/>
-    <col width="3.6640625" customWidth="1" style="65" min="8" max="8"/>
-    <col width="10.5" customWidth="1" style="65" min="9" max="9"/>
-    <col width="8.33203125" customWidth="1" style="65" min="10" max="10"/>
-    <col width="7.1640625" customWidth="1" style="65" min="11" max="11"/>
-    <col width="9" customWidth="1" style="65" min="12" max="13"/>
-    <col width="9" customWidth="1" style="65" min="14" max="16384"/>
+    <col width="6.5" customWidth="1" style="63" min="1" max="1"/>
+    <col width="3.83203125" customWidth="1" style="63" min="2" max="2"/>
+    <col width="9.6640625" customWidth="1" style="63" min="3" max="4"/>
+    <col width="3.33203125" customWidth="1" style="63" min="5" max="5"/>
+    <col width="9.6640625" customWidth="1" style="63" min="6" max="7"/>
+    <col width="3.6640625" customWidth="1" style="63" min="8" max="8"/>
+    <col width="10.5" customWidth="1" style="63" min="9" max="9"/>
+    <col width="8.33203125" customWidth="1" style="63" min="10" max="10"/>
+    <col width="7.1640625" customWidth="1" style="63" min="11" max="11"/>
+    <col width="9" customWidth="1" style="63" min="12" max="14"/>
+    <col width="9" customWidth="1" style="63" min="15" max="16384"/>
   </cols>
   <sheetData>
     <row r="2" ht="27.5" customHeight="1" s="60">
       <c r="E2" s="5" t="n"/>
       <c r="F2" s="5" t="n"/>
       <c r="G2" s="5" t="n"/>
-      <c r="H2" s="62" t="inlineStr">
+      <c r="H2" s="67" t="inlineStr">
         <is>
           <t>문서관리번호</t>
         </is>
       </c>
-      <c r="I2" s="63" t="n"/>
-      <c r="J2" s="67" t="inlineStr">
+      <c r="I2" s="68" t="n"/>
+      <c r="J2" s="70" t="inlineStr">
         <is>
           <t>버전</t>
         </is>
       </c>
-      <c r="K2" s="63" t="n"/>
+      <c r="K2" s="68" t="n"/>
     </row>
     <row r="3" ht="27.5" customHeight="1" s="60">
       <c r="E3" s="5" t="n"/>
       <c r="F3" s="5" t="n"/>
       <c r="G3" s="5" t="n"/>
-      <c r="H3" s="71" t="inlineStr">
+      <c r="H3" s="74" t="inlineStr">
         <is>
           <t>JJ_IP_A02</t>
         </is>
       </c>
-      <c r="I3" s="63" t="n"/>
-      <c r="J3" s="73" t="inlineStr">
+      <c r="I3" s="68" t="n"/>
+      <c r="J3" s="65" t="inlineStr">
         <is>
           <t>v1.5</t>
         </is>
       </c>
-      <c r="K3" s="74" t="n"/>
+      <c r="K3" s="66" t="n"/>
     </row>
     <row r="9" ht="26.25" customHeight="1" s="60">
-      <c r="A9" s="70" t="inlineStr">
+      <c r="A9" s="73" t="inlineStr">
         <is>
           <t>'25년 제주스마트도시 데이터허브 시범솔루션 발굴사업</t>
         </is>
@@ -3079,7 +3079,7 @@
       <c r="K10" s="6" t="n"/>
     </row>
     <row r="11" ht="50.25" customHeight="1" s="60">
-      <c r="A11" s="68" t="inlineStr">
+      <c r="A11" s="71" t="inlineStr">
         <is>
           <t>기능구조도</t>
         </is>
@@ -3112,32 +3112,32 @@
       <c r="K13" s="6" t="n"/>
     </row>
     <row r="14" ht="24.75" customHeight="1" s="60">
-      <c r="A14" s="69" t="inlineStr">
+      <c r="A14" s="72" t="inlineStr">
         <is>
           <t>공영주차장관련민원솔루션</t>
         </is>
       </c>
     </row>
     <row r="28" ht="43.5" customHeight="1" s="60">
-      <c r="B28" s="72" t="n"/>
-      <c r="E28" s="72" t="n"/>
-      <c r="H28" s="66" t="n"/>
+      <c r="B28" s="64" t="n"/>
+      <c r="E28" s="64" t="n"/>
+      <c r="H28" s="69" t="n"/>
     </row>
     <row r="29" ht="43.5" customHeight="1" s="60">
-      <c r="B29" s="66" t="n"/>
-      <c r="C29" s="64" t="n"/>
-      <c r="E29" s="66" t="n"/>
-      <c r="F29" s="64" t="n"/>
-      <c r="H29" s="66" t="n"/>
-      <c r="I29" s="64" t="n"/>
+      <c r="B29" s="69" t="n"/>
+      <c r="C29" s="62" t="n"/>
+      <c r="E29" s="69" t="n"/>
+      <c r="F29" s="62" t="n"/>
+      <c r="H29" s="69" t="n"/>
+      <c r="I29" s="62" t="n"/>
     </row>
     <row r="30" ht="43.5" customHeight="1" s="60">
-      <c r="B30" s="66" t="n"/>
-      <c r="C30" s="64" t="n"/>
-      <c r="E30" s="66" t="n"/>
-      <c r="F30" s="64" t="n"/>
-      <c r="H30" s="66" t="n"/>
-      <c r="I30" s="64" t="n"/>
+      <c r="B30" s="69" t="n"/>
+      <c r="C30" s="62" t="n"/>
+      <c r="E30" s="69" t="n"/>
+      <c r="F30" s="62" t="n"/>
+      <c r="H30" s="69" t="n"/>
+      <c r="I30" s="62" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -3178,8 +3178,8 @@
     <col width="8.5" customWidth="1" style="76" min="2" max="2"/>
     <col width="45.5" customWidth="1" style="76" min="3" max="3"/>
     <col width="8.33203125" customWidth="1" style="76" min="4" max="5"/>
-    <col width="9" customWidth="1" style="76" min="6" max="7"/>
-    <col width="9" customWidth="1" style="76" min="8" max="16384"/>
+    <col width="9" customWidth="1" style="76" min="6" max="8"/>
+    <col width="9" customWidth="1" style="76" min="9" max="16384"/>
   </cols>
   <sheetData>
     <row r="2" ht="26.25" customHeight="1" s="60">
@@ -3546,7 +3546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K76"/>
+  <dimension ref="A1:K77"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="68" customHeight="1"/>
   <cols>
     <col width="16" customWidth="1" style="60" min="1" max="1"/>
@@ -3747,118 +3747,118 @@
     <row r="6" ht="32" customHeight="1" s="60">
       <c r="A6" s="23" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>FN-PAR-00-01</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>로그인</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>통합 인증</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>D-Hub 통합 인증 로그인</t>
+        </is>
+      </c>
+      <c r="F6" s="16" t="inlineStr">
+        <is>
+          <t>UI-PAR-000</t>
+        </is>
+      </c>
+      <c r="G6" s="17" t="inlineStr">
+        <is>
+          <t>'통합 인증으로 로그인' 버튼 — 제주 데이터허브(D-Hub) 통합 인증(SSO) 로그인 창으로 이동, 인증 성공 시 대시보드 진입. 안내 문구 표시</t>
+        </is>
+      </c>
+      <c r="H6" s="16" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I6" s="37" t="inlineStr">
+        <is>
+          <t>D-Hub 통합 인증</t>
+        </is>
+      </c>
+      <c r="J6" s="16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K6" s="24" t="inlineStr"/>
+    </row>
+    <row r="7" ht="32" customHeight="1" s="60">
+      <c r="A7" s="23" t="inlineStr">
+        <is>
           <t>REQ-SFR-003-07</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>FN-PAR-01-01</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>대시보드</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>조회 단위 필터</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>기간 탭 및 상세 필터</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>UI-PAR-001</t>
         </is>
       </c>
-      <c r="G6" s="17" t="inlineStr">
+      <c r="G7" s="17" t="inlineStr">
         <is>
           <t>어제/주간/월간 탭 및 상세 필터(날짜 범위) 설정 기능</t>
         </is>
       </c>
-      <c r="H6" s="16" t="inlineStr">
+      <c r="H7" s="16" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I6" s="37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J6" s="16" t="inlineStr">
+      <c r="I7" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J7" s="16" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K6" s="24" t="n"/>
-    </row>
-    <row r="7" ht="32" customHeight="1" s="60">
-      <c r="A7" s="25" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-07</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>FN-PAR-01-02</t>
-        </is>
-      </c>
-      <c r="C7" s="31" t="inlineStr">
-        <is>
-          <t>대시보드</t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>KPI 요약</t>
-        </is>
-      </c>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>KPI 카드</t>
-        </is>
-      </c>
-      <c r="F7" s="14" t="inlineStr">
-        <is>
-          <t>UI-PAR-001</t>
-        </is>
-      </c>
-      <c r="G7" s="15" t="inlineStr">
-        <is>
-          <t>총 민원 건수·공영주차장 현황(개소)·위험단계알림 건수 카드</t>
-        </is>
-      </c>
-      <c r="H7" s="14" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I7" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J7" s="14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K7" s="26" t="n"/>
+      <c r="K7" s="24" t="n"/>
     </row>
     <row r="8" ht="32" customHeight="1" s="60">
       <c r="A8" s="25" t="inlineStr">
         <is>
-          <t>REQ-SFR-003-01</t>
+          <t>REQ-SFR-003-07</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>FN-PAR-01-03</t>
+          <t>FN-PAR-01-02</t>
         </is>
       </c>
       <c r="C8" s="31" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>민원 발생 추이</t>
+          <t>KPI 요약</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>시간대별 라인 차트</t>
+          <t>KPI 카드</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="G8" s="15" t="inlineStr">
         <is>
-          <t>시간대별 민원 유형 라인 차트 — 어제/주간/월간 조회 단위 모두 시간대별 집계, 단위에 따라 집계 규모 변경</t>
+          <t>총 민원 건수·공영주차장 현황(개소)·위험단계알림 건수 카드</t>
         </is>
       </c>
       <c r="H8" s="14" t="inlineStr">
@@ -3906,12 +3906,12 @@
     <row r="9" ht="32" customHeight="1" s="60">
       <c r="A9" s="25" t="inlineStr">
         <is>
-          <t>REQ-SFR-003-02</t>
+          <t>REQ-SFR-003-01</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>FN-PAR-01-04</t>
+          <t>FN-PAR-01-03</t>
         </is>
       </c>
       <c r="C9" s="31" t="inlineStr">
@@ -3921,12 +3921,12 @@
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>불법주차 집중구역 순위</t>
+          <t>민원 발생 추이</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>Top5 목록 + 자세히 보기</t>
+          <t>시간대별 라인 차트</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
-          <t>불법주차 집중구역 Top5 목록(최근 1개월 기준), 위험 등급 배지(심각/경고/주의), '자세히 보기'로 집중 구역 분석 이동</t>
+          <t>시간대별 민원 유형 라인 차트 — 어제/주간/월간 조회 단위 모두 시간대별 집계, 단위에 따라 집계 규모 변경</t>
         </is>
       </c>
       <c r="H9" s="14" t="inlineStr">
@@ -3959,12 +3959,12 @@
     <row r="10" ht="32" customHeight="1" s="60">
       <c r="A10" s="25" t="inlineStr">
         <is>
-          <t>REQ-SFR-003-03</t>
+          <t>REQ-SFR-003-02</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>FN-PAR-01-05</t>
+          <t>FN-PAR-01-04</t>
         </is>
       </c>
       <c r="C10" s="31" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>읍·면·동 민원 순위</t>
+          <t>불법주차 집중구역 순위</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>읍면동 Top5 카드</t>
+          <t>Top5 목록 + 자세히 보기</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="G10" s="15" t="inlineStr">
         <is>
-          <t>읍·면·동 Top5 민원 건수 카드, 전일 대비 증감률 · 순위 변동 · 호버 시 유형별 건수 및 스택바 표시. 전체 보기 링크</t>
+          <t>불법주차 집중구역 Top5 목록(최근 1개월 기준), 위험 등급 배지(심각/경고/주의), '자세히 보기'로 집중 구역 분석 이동</t>
         </is>
       </c>
       <c r="H10" s="14" t="inlineStr">
@@ -4012,12 +4012,12 @@
     <row r="11" ht="32" customHeight="1" s="60">
       <c r="A11" s="25" t="inlineStr">
         <is>
-          <t>REQ-SFR-003-10</t>
+          <t>REQ-SFR-003-03</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>FN-PAR-01-06</t>
+          <t>FN-PAR-01-05</t>
         </is>
       </c>
       <c r="C11" s="31" t="inlineStr">
@@ -4027,12 +4027,12 @@
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>최근 정책효과 시뮬레이션 목록</t>
+          <t>읍·면·동 민원 순위</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>분석 이력 목록</t>
+          <t>읍면동 Top5 카드</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>최근 정책 효과 시뮬레이션 목록 표시.  전체 → 정책 효과 시뮬레이션 이동</t>
+          <t>읍·면·동 Top5 민원 건수 카드, 전일 대비 증감률 · 순위 변동 · 호버 시 유형별 건수 및 스택바 표시. 전체 보기 링크</t>
         </is>
       </c>
       <c r="H11" s="14" t="inlineStr">
@@ -4065,302 +4065,302 @@
     <row r="12" ht="32" customHeight="1" s="60">
       <c r="A12" s="25" t="inlineStr">
         <is>
+          <t>REQ-SFR-003-10</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>FN-PAR-01-06</t>
+        </is>
+      </c>
+      <c r="C12" s="31" t="inlineStr">
+        <is>
+          <t>대시보드</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>최근 정책효과 시뮬레이션 목록</t>
+        </is>
+      </c>
+      <c r="E12" s="14" t="inlineStr">
+        <is>
+          <t>분석 이력 목록</t>
+        </is>
+      </c>
+      <c r="F12" s="14" t="inlineStr">
+        <is>
+          <t>UI-PAR-001</t>
+        </is>
+      </c>
+      <c r="G12" s="15" t="inlineStr">
+        <is>
+          <t>최근 정책 효과 시뮬레이션 목록 표시.  전체 → 정책 효과 시뮬레이션 이동</t>
+        </is>
+      </c>
+      <c r="H12" s="14" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I12" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J12" s="14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" s="26" t="n"/>
+    </row>
+    <row r="13" ht="32" customHeight="1" s="60">
+      <c r="A13" s="25" t="inlineStr">
+        <is>
           <t>REQ-SFR-005-05</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>FN-PAR-01-07</t>
         </is>
       </c>
-      <c r="C12" s="31" t="inlineStr">
+      <c r="C13" s="31" t="inlineStr">
         <is>
           <t>대시보드</t>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr">
+      <c r="D13" s="14" t="inlineStr">
         <is>
           <t>최근 보고서 목록</t>
         </is>
       </c>
-      <c r="E12" s="14" t="inlineStr">
+      <c r="E13" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">보고서 목록 </t>
         </is>
       </c>
-      <c r="F12" s="14" t="inlineStr">
+      <c r="F13" s="14" t="inlineStr">
         <is>
           <t>UI-PAR-001</t>
         </is>
       </c>
-      <c r="G12" s="15" t="inlineStr">
+      <c r="G13" s="15" t="inlineStr">
         <is>
           <t>최근 생성 보고서 목록(제목·일시). 항목 클릭 시 보고서 목록의 해당 행으로 이동</t>
         </is>
       </c>
-      <c r="H12" s="14" t="inlineStr">
+      <c r="H13" s="14" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I12" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J12" s="14" t="inlineStr">
+      <c r="I13" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J13" s="14" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K12" s="26" t="n"/>
-    </row>
-    <row r="13" ht="32" customHeight="1" s="60">
-      <c r="A13" s="27" t="inlineStr">
+      <c r="K13" s="26" t="n"/>
+    </row>
+    <row r="14" ht="32" customHeight="1" s="60">
+      <c r="A14" s="27" t="inlineStr">
         <is>
           <t>REQ-SFR-005-07</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>FN-PAR-01-08</t>
         </is>
       </c>
-      <c r="C13" s="33" t="inlineStr">
+      <c r="C14" s="33" t="inlineStr">
         <is>
           <t>대시보드</t>
         </is>
       </c>
-      <c r="D13" s="18" t="inlineStr">
+      <c r="D14" s="18" t="inlineStr">
         <is>
           <t>AI 어시스턴트 패널, 최근 질문 목록</t>
         </is>
       </c>
-      <c r="E13" s="18" t="inlineStr">
+      <c r="E14" s="18" t="inlineStr">
         <is>
           <t>빠른 질문 입력창</t>
         </is>
       </c>
-      <c r="F13" s="18" t="inlineStr">
+      <c r="F14" s="18" t="inlineStr">
         <is>
           <t>UI-PAR-001</t>
         </is>
       </c>
-      <c r="G13" s="19" t="inlineStr">
+      <c r="G14" s="19" t="inlineStr">
         <is>
           <t>AI 어시스턴트 빠른 질문 입력창 및 최근질문 3개 표시. 대화 열기 버튼 → AI 어시스턴트 화면 이동</t>
         </is>
       </c>
-      <c r="H13" s="18" t="inlineStr">
+      <c r="H14" s="18" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I13" s="39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J13" s="18" t="inlineStr">
+      <c r="I14" s="39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J14" s="18" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K13" s="28" t="n"/>
-    </row>
-    <row r="14" ht="32" customHeight="1" s="60">
-      <c r="A14" s="23" t="inlineStr">
+      <c r="K14" s="28" t="n"/>
+    </row>
+    <row r="15" ht="32" customHeight="1" s="60">
+      <c r="A15" s="23" t="inlineStr">
         <is>
           <t>REQ-SFR-003-03</t>
         </is>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>FN-PAR-02-01</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t>민원현황</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D15" s="16" t="inlineStr">
         <is>
           <t>조회 단위 필터</t>
         </is>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="E15" s="16" t="inlineStr">
         <is>
           <t>기간 탭 및 상세 필터</t>
         </is>
       </c>
-      <c r="F14" s="20" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>UI-PAR-002</t>
         </is>
       </c>
-      <c r="G14" s="17" t="inlineStr">
+      <c r="G15" s="17" t="inlineStr">
         <is>
           <t>어제/주간/월간 탭 및 상세 필터(행정구역/민원유형/위험단계) 설정</t>
         </is>
       </c>
-      <c r="H14" s="16" t="inlineStr">
+      <c r="H15" s="16" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I14" s="37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J14" s="16" t="inlineStr">
+      <c r="I15" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J15" s="16" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K14" s="24" t="n"/>
-    </row>
-    <row r="15" ht="32" customHeight="1" s="60">
-      <c r="A15" s="29" t="inlineStr">
+      <c r="K15" s="24" t="n"/>
+    </row>
+    <row r="16" ht="32" customHeight="1" s="60">
+      <c r="A16" s="29" t="inlineStr">
         <is>
           <t>REQ-SFR-003-07</t>
         </is>
       </c>
-      <c r="B15" s="20" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>FN-PAR-02-02</t>
         </is>
       </c>
-      <c r="C15" s="32" t="inlineStr">
+      <c r="C16" s="32" t="inlineStr">
         <is>
           <t>민원현황</t>
         </is>
       </c>
-      <c r="D15" s="20" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>KPI 요약</t>
         </is>
       </c>
-      <c r="E15" s="20" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>KPI 카드</t>
         </is>
       </c>
-      <c r="F15" s="20" t="inlineStr">
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>UI-PAR-002</t>
         </is>
       </c>
-      <c r="G15" s="21" t="inlineStr">
+      <c r="G16" s="21" t="inlineStr">
         <is>
           <t>KPI 카드(총 민원 건수 / 민원 감정 분석(긍정·보통·부정) / 단속 집중 지역 / 수요 부족 지역). 전기 대비 증감 표시</t>
         </is>
       </c>
-      <c r="H15" s="20" t="inlineStr">
+      <c r="H16" s="20" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I15" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J15" s="20" t="inlineStr">
+      <c r="I16" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J16" s="20" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K15" s="30" t="n"/>
-    </row>
-    <row r="16" ht="32" customHeight="1" s="60">
-      <c r="A16" s="25" t="inlineStr">
+      <c r="K16" s="30" t="n"/>
+    </row>
+    <row r="17" ht="61" customHeight="1" s="60">
+      <c r="A17" s="25" t="inlineStr">
         <is>
           <t>REQ-SFR-003-09</t>
         </is>
       </c>
-      <c r="B16" s="20" t="inlineStr">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>FN-PAR-02-03</t>
         </is>
       </c>
-      <c r="C16" s="32" t="inlineStr">
+      <c r="C17" s="32" t="inlineStr">
         <is>
           <t>민원현황</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="D17" s="14" t="inlineStr">
         <is>
           <t>GIS 지도</t>
         </is>
       </c>
-      <c r="E16" s="14" t="inlineStr">
+      <c r="E17" s="14" t="inlineStr">
         <is>
           <t>민원 분석 레이어</t>
         </is>
       </c>
-      <c r="F16" s="14" t="inlineStr">
+      <c r="F17" s="14" t="inlineStr">
         <is>
           <t>UI-PAR-002</t>
         </is>
       </c>
-      <c r="G16" s="15" t="inlineStr">
+      <c r="G17" s="15" t="inlineStr">
         <is>
           <t>분석레이어(민원다발지역/집중단속지역/수요부족지역 중 하나 선택 → 지도 데이터 시각화). 민원 다발·단속 집중 레이어는 히트맵 표현 시 민원 건수·단속 건수 기반 밀도 히트맵 표출</t>
-        </is>
-      </c>
-      <c r="H16" s="14" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I16" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J16" s="14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K16" s="26" t="n"/>
-    </row>
-    <row r="17" ht="32" customHeight="1" s="60">
-      <c r="A17" s="25" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-09</t>
-        </is>
-      </c>
-      <c r="B17" s="20" t="inlineStr">
-        <is>
-          <t>FN-PAR-02-04</t>
-        </is>
-      </c>
-      <c r="C17" s="32" t="inlineStr">
-        <is>
-          <t>민원현황</t>
-        </is>
-      </c>
-      <c r="D17" s="31" t="inlineStr">
-        <is>
-          <t>GIS 지도</t>
-        </is>
-      </c>
-      <c r="E17" s="14" t="inlineStr">
-        <is>
-          <t>레이어 설정 패널</t>
-        </is>
-      </c>
-      <c r="F17" s="14" t="inlineStr">
-        <is>
-          <t>UI-PAR-002</t>
-        </is>
-      </c>
-      <c r="G17" s="15" t="inlineStr">
-        <is>
-          <t>지도 레이어 패널 — 민원 다발/단속 집중/수요 부족(택1 라디오) + 공영주차장·행정동 경계 토글. 레이어 선택에 따라 우측 순위 패널 전환. 민원 다발·단속 집중 레이어는 읍면동(폴리곤) ↔ 히트맵(밀도) 표현 전환 지원(수요 부족 지역 제외)</t>
         </is>
       </c>
       <c r="H17" s="14" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>FN-PAR-02-05</t>
+          <t>FN-PAR-02-04</t>
         </is>
       </c>
       <c r="C18" s="32" t="inlineStr">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>지도 범례</t>
+          <t>레이어 설정 패널</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
@@ -4413,7 +4413,9 @@
       </c>
       <c r="G18" s="15" t="inlineStr">
         <is>
-          <t>색상 범례 표시 — 등급(심각·경고·주의) 범례, 히트맵 선택 시 그라데이션(낮음~높음) 범례로 전환</t>
+          <t xml:space="preserve">지도 레이어 패널 — 민원 다발/단속 집중/수요 부족(택1)레이어 선택에 따라 우측 순위 패널 전환. 
+민원 다발·단속 집중 레이어는 읍면동(폴리곤) ↔ 히트맵(밀도) 표현 전환 지원(수요 부족 지역 제외) 
+공영주차장·행정동 경계 토글. </t>
         </is>
       </c>
       <c r="H18" s="14" t="inlineStr">
@@ -4436,479 +4438,479 @@
     <row r="19" ht="32" customHeight="1" s="60">
       <c r="A19" s="25" t="inlineStr">
         <is>
+          <t>REQ-SFR-003-09</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>FN-PAR-02-05</t>
+        </is>
+      </c>
+      <c r="C19" s="32" t="inlineStr">
+        <is>
+          <t>민원현황</t>
+        </is>
+      </c>
+      <c r="D19" s="31" t="inlineStr">
+        <is>
+          <t>GIS 지도</t>
+        </is>
+      </c>
+      <c r="E19" s="14" t="inlineStr">
+        <is>
+          <t>지도 범례</t>
+        </is>
+      </c>
+      <c r="F19" s="14" t="inlineStr">
+        <is>
+          <t>UI-PAR-002</t>
+        </is>
+      </c>
+      <c r="G19" s="15" t="inlineStr">
+        <is>
+          <t>색상 범례 표시 — 등급(심각·경고·주의) 범례, 히트맵 선택 시 그라데이션(낮음~높음) 범례로 전환</t>
+        </is>
+      </c>
+      <c r="H19" s="14" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I19" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J19" s="14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K19" s="26" t="n"/>
+    </row>
+    <row r="20" ht="32" customHeight="1" s="60">
+      <c r="A20" s="25" t="inlineStr">
+        <is>
           <t>REQ-SFR-003-01</t>
         </is>
       </c>
-      <c r="B19" s="20" t="inlineStr">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>FN-PAR-02-06</t>
         </is>
       </c>
-      <c r="C19" s="32" t="inlineStr">
+      <c r="C20" s="32" t="inlineStr">
         <is>
           <t>민원현황</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
+      <c r="D20" s="14" t="inlineStr">
         <is>
           <t>민원/단속/수요부족 순위</t>
         </is>
       </c>
-      <c r="E19" s="14" t="inlineStr">
+      <c r="E20" s="14" t="inlineStr">
         <is>
           <t>읍면동 순위 목록</t>
         </is>
       </c>
-      <c r="F19" s="14" t="inlineStr">
+      <c r="F20" s="14" t="inlineStr">
         <is>
           <t>UI-PAR-002</t>
         </is>
       </c>
-      <c r="G19" s="15" t="inlineStr">
+      <c r="G20" s="15" t="inlineStr">
         <is>
           <t>읍·면·동 민원/단속/수요부족 순위(선택 레이어 연동). 범례 등급(심각·경고·주의)에 해당하는 지역만 표출, 행 클릭 시 지도 이동·팝업</t>
         </is>
       </c>
-      <c r="H19" s="14" t="inlineStr">
+      <c r="H20" s="14" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I19" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J19" s="14" t="inlineStr">
+      <c r="I20" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J20" s="14" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K19" s="26" t="n"/>
-    </row>
-    <row r="20" ht="32" customHeight="1" s="60">
-      <c r="A20" s="27" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-02</t>
-        </is>
-      </c>
-      <c r="B20" s="40" t="inlineStr">
-        <is>
-          <t>FN-PAR-02-07</t>
-        </is>
-      </c>
-      <c r="C20" s="34" t="inlineStr">
-        <is>
-          <t>민원현황</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>부정 민원 상위 지역</t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>읍면동 순위 목록</t>
-        </is>
-      </c>
-      <c r="F20" s="18" t="inlineStr">
-        <is>
-          <t>UI-PAR-002</t>
-        </is>
-      </c>
-      <c r="G20" s="19" t="inlineStr">
-        <is>
-          <t>읍·면·동 기준 부정 민원 상위 지역 순위. 긍정·보통·부정 구성비 막대 차트​. 더보기 클릭 하면 최대 15개 목록 노출</t>
-        </is>
-      </c>
-      <c r="H20" s="18" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I20" s="39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J20" s="18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K20" s="28" t="n"/>
+      <c r="K20" s="26" t="n"/>
     </row>
     <row r="21" ht="32" customHeight="1" s="60">
       <c r="A21" s="27" t="inlineStr">
         <is>
+          <t>REQ-SFR-003-02</t>
+        </is>
+      </c>
+      <c r="B21" s="40" t="inlineStr">
+        <is>
+          <t>FN-PAR-02-07</t>
+        </is>
+      </c>
+      <c r="C21" s="34" t="inlineStr">
+        <is>
+          <t>민원현황</t>
+        </is>
+      </c>
+      <c r="D21" s="18" t="inlineStr">
+        <is>
+          <t>부정 민원 상위 지역</t>
+        </is>
+      </c>
+      <c r="E21" s="18" t="inlineStr">
+        <is>
+          <t>읍면동 순위 목록</t>
+        </is>
+      </c>
+      <c r="F21" s="18" t="inlineStr">
+        <is>
+          <t>UI-PAR-002</t>
+        </is>
+      </c>
+      <c r="G21" s="19" t="inlineStr">
+        <is>
+          <t>읍·면·동 기준 부정 민원 상위 지역 순위. 긍정·보통·부정 구성비 막대 차트​. 더보기 클릭 하면 최대 15개 목록 노출</t>
+        </is>
+      </c>
+      <c r="H21" s="18" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I21" s="39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J21" s="18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K21" s="28" t="n"/>
+    </row>
+    <row r="22" ht="32" customHeight="1" s="60">
+      <c r="A22" s="27" t="inlineStr">
+        <is>
           <t>REQ-SFR-003-10</t>
         </is>
       </c>
-      <c r="B21" s="40" t="inlineStr">
+      <c r="B22" s="40" t="inlineStr">
         <is>
           <t>FN-PAR-02-08</t>
         </is>
       </c>
-      <c r="C21" s="34" t="inlineStr">
+      <c r="C22" s="34" t="inlineStr">
         <is>
           <t>민원현황</t>
         </is>
       </c>
-      <c r="D21" s="18" t="inlineStr">
+      <c r="D22" s="18" t="inlineStr">
         <is>
           <t>내보내기</t>
         </is>
       </c>
-      <c r="E21" s="18" t="inlineStr">
+      <c r="E22" s="18" t="inlineStr">
         <is>
           <t>PDF/DOCX 내보내기</t>
         </is>
       </c>
-      <c r="F21" s="18" t="inlineStr">
+      <c r="F22" s="18" t="inlineStr">
         <is>
           <t>UI-PAR-002</t>
         </is>
       </c>
-      <c r="G21" s="19" t="inlineStr">
+      <c r="G22" s="19" t="inlineStr">
         <is>
           <t>분석 결과를 PDF/DOCX 보고서로 내보내기 — 내보낸 보고서는 보고서 목록의 직접 생성 보고서 목록에 표시</t>
         </is>
       </c>
-      <c r="H21" s="18" t="inlineStr">
+      <c r="H22" s="18" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I21" s="39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J21" s="18" t="inlineStr">
+      <c r="I22" s="39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J22" s="18" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K21" s="28" t="n"/>
-    </row>
-    <row r="22" ht="32" customHeight="1" s="60">
-      <c r="A22" s="23" t="inlineStr">
+      <c r="K22" s="28" t="n"/>
+    </row>
+    <row r="23" ht="32" customHeight="1" s="60">
+      <c r="A23" s="23" t="inlineStr">
         <is>
           <t>REQ-SFR-003-02</t>
         </is>
       </c>
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>FN-PAR-03-01-01</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="C23" s="16" t="inlineStr">
         <is>
           <t>불법 주차 집중 구역 분석</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D23" s="16" t="inlineStr">
         <is>
           <t>집중구역 분석 GIS</t>
         </is>
       </c>
-      <c r="E22" s="16" t="inlineStr">
+      <c r="E23" s="16" t="inlineStr">
         <is>
           <t>GIS 지도 + 순위 마커</t>
         </is>
       </c>
-      <c r="F22" s="16" t="inlineStr">
+      <c r="F23" s="16" t="inlineStr">
         <is>
           <t>UI-PAR-003-01</t>
         </is>
       </c>
-      <c r="G22" s="17" t="inlineStr">
+      <c r="G23" s="17" t="inlineStr">
         <is>
           <t>제주 전역 GIS 지도에 불법 주차 집중 구역 순위 마커 표시. 목록 행 클릭 시 지도 확대 이동 및 팝업 표시</t>
         </is>
       </c>
-      <c r="H22" s="16" t="inlineStr">
+      <c r="H23" s="16" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I22" s="37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J22" s="16" t="inlineStr">
+      <c r="I23" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J23" s="16" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K22" s="24" t="n"/>
-    </row>
-    <row r="23" ht="32" customHeight="1" s="60">
-      <c r="A23" s="25" t="inlineStr">
+      <c r="K23" s="24" t="n"/>
+    </row>
+    <row r="24" ht="32" customHeight="1" s="60">
+      <c r="A24" s="25" t="inlineStr">
         <is>
           <t>REQ-SFR-003-02</t>
         </is>
       </c>
-      <c r="B23" s="14" t="inlineStr">
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>FN-PAR-03-01-02</t>
         </is>
       </c>
-      <c r="C23" s="32" t="inlineStr">
+      <c r="C24" s="32" t="inlineStr">
         <is>
           <t>불법 주차 집중 구역 분석</t>
         </is>
       </c>
-      <c r="D23" s="32" t="inlineStr">
+      <c r="D24" s="32" t="inlineStr">
         <is>
           <t>집중구역 분석 GIS</t>
         </is>
       </c>
-      <c r="E23" s="14" t="inlineStr">
+      <c r="E24" s="14" t="inlineStr">
         <is>
           <t>불법주차 집중구역 순위</t>
         </is>
       </c>
-      <c r="F23" s="14" t="inlineStr">
+      <c r="F24" s="14" t="inlineStr">
         <is>
           <t>UI-PAR-003-01</t>
         </is>
       </c>
-      <c r="G23" s="15" t="inlineStr">
+      <c r="G24" s="15" t="inlineStr">
         <is>
           <t>종합점수(민원 건수 60% + 단속 40%) 기준 우선순위 목록</t>
         </is>
       </c>
-      <c r="H23" s="14" t="inlineStr">
+      <c r="H24" s="14" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I23" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J23" s="14" t="inlineStr">
+      <c r="I24" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J24" s="14" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K23" s="26" t="n"/>
-    </row>
-    <row r="24" ht="32" customHeight="1" s="60">
-      <c r="A24" s="27" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-02</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>FN-PAR-03-01-03</t>
-        </is>
-      </c>
-      <c r="C24" s="34" t="inlineStr">
-        <is>
-          <t>불법 주차 집중 구역 분석</t>
-        </is>
-      </c>
-      <c r="D24" s="34" t="inlineStr">
-        <is>
-          <t>집중구역 분석 GIS</t>
-        </is>
-      </c>
-      <c r="E24" s="18" t="inlineStr">
-        <is>
-          <t>분석 설정 패널</t>
-        </is>
-      </c>
-      <c r="F24" s="18" t="inlineStr">
-        <is>
-          <t>UI-PAR-003-01</t>
-        </is>
-      </c>
-      <c r="G24" s="19" t="inlineStr">
-        <is>
-          <t>분석 지역·분석 기간(최근1/3/6개월, 월 단위 직접 설정) 조건 입력 후 분석 실행 — 분석 최소 단위는 월</t>
-        </is>
-      </c>
-      <c r="H24" s="18" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I24" s="39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J24" s="18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K24" s="28" t="n"/>
+      <c r="K24" s="26" t="n"/>
     </row>
     <row r="25" ht="32" customHeight="1" s="60">
       <c r="A25" s="27" t="inlineStr">
         <is>
+          <t>REQ-SFR-003-02</t>
+        </is>
+      </c>
+      <c r="B25" s="18" t="inlineStr">
+        <is>
+          <t>FN-PAR-03-01-03</t>
+        </is>
+      </c>
+      <c r="C25" s="34" t="inlineStr">
+        <is>
+          <t>불법 주차 집중 구역 분석</t>
+        </is>
+      </c>
+      <c r="D25" s="34" t="inlineStr">
+        <is>
+          <t>집중구역 분석 GIS</t>
+        </is>
+      </c>
+      <c r="E25" s="18" t="inlineStr">
+        <is>
+          <t>분석 설정 패널</t>
+        </is>
+      </c>
+      <c r="F25" s="18" t="inlineStr">
+        <is>
+          <t>UI-PAR-003-01</t>
+        </is>
+      </c>
+      <c r="G25" s="19" t="inlineStr">
+        <is>
+          <t>분석 지역·분석 기간(최근1/3/6개월, 월 단위 직접 설정) 조건 입력 후 분석 실행 — 분석 최소 단위는 월</t>
+        </is>
+      </c>
+      <c r="H25" s="18" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I25" s="39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J25" s="18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K25" s="28" t="n"/>
+    </row>
+    <row r="26" ht="32" customHeight="1" s="60">
+      <c r="A26" s="27" t="inlineStr">
+        <is>
           <t>REQ-SFR-003-10</t>
         </is>
       </c>
-      <c r="B25" s="18" t="inlineStr">
+      <c r="B26" s="18" t="inlineStr">
         <is>
           <t>FN-PAR-03-01-05</t>
         </is>
       </c>
-      <c r="C25" s="34" t="inlineStr">
+      <c r="C26" s="34" t="inlineStr">
         <is>
           <t>불법 주차 집중 구역 분석</t>
         </is>
       </c>
-      <c r="D25" s="34" t="inlineStr">
+      <c r="D26" s="34" t="inlineStr">
         <is>
           <t>내보내기</t>
         </is>
       </c>
-      <c r="E25" s="18" t="inlineStr">
+      <c r="E26" s="18" t="inlineStr">
         <is>
           <t>PDF/DOCX 내보내기</t>
         </is>
       </c>
-      <c r="F25" s="18" t="inlineStr">
+      <c r="F26" s="18" t="inlineStr">
         <is>
           <t>UI-PAR-003-01</t>
         </is>
       </c>
-      <c r="G25" s="19" t="inlineStr">
+      <c r="G26" s="19" t="inlineStr">
         <is>
           <t>분석 결과를 PDF/DOCX 보고서로 내보내기 — 내보낸 보고서는 보고서 목록의 직접 생성 보고서 목록에 표시</t>
         </is>
       </c>
-      <c r="H25" s="18" t="inlineStr">
+      <c r="H26" s="18" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I25" s="39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J25" s="18" t="inlineStr">
+      <c r="I26" s="39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J26" s="18" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K25" s="28" t="n"/>
-    </row>
-    <row r="26" ht="32" customHeight="1" s="60">
-      <c r="A26" s="23" t="inlineStr">
+      <c r="K26" s="28" t="n"/>
+    </row>
+    <row r="27" ht="32" customHeight="1" s="60">
+      <c r="A27" s="23" t="inlineStr">
         <is>
           <t>REQ-SFR-003-05</t>
         </is>
       </c>
-      <c r="B26" s="16" t="inlineStr">
+      <c r="B27" s="16" t="inlineStr">
         <is>
           <t>FN-PAR-03-02-01</t>
         </is>
       </c>
-      <c r="C26" s="16" t="inlineStr">
+      <c r="C27" s="16" t="inlineStr">
         <is>
           <t>정책 효과 시뮬레이션</t>
         </is>
       </c>
-      <c r="D26" s="16" t="inlineStr">
+      <c r="D27" s="16" t="inlineStr">
         <is>
           <t>정책 변수 설정</t>
         </is>
       </c>
-      <c r="E26" s="16" t="inlineStr">
+      <c r="E27" s="16" t="inlineStr">
         <is>
           <t>정책 유형 탭 선택</t>
         </is>
       </c>
-      <c r="F26" s="16" t="inlineStr">
+      <c r="F27" s="16" t="inlineStr">
         <is>
           <t>UI-PAR-003-02</t>
         </is>
       </c>
-      <c r="G26" s="17" t="inlineStr">
+      <c r="G27" s="17" t="inlineStr">
         <is>
           <t>정책 유형 탭 전환: 주차장 확충 / 이면도로 정비 / 요금제 적용 3종 탭 선택</t>
         </is>
       </c>
-      <c r="H26" s="16" t="inlineStr">
+      <c r="H27" s="16" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I26" s="37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J26" s="16" t="inlineStr">
+      <c r="I27" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J27" s="16" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K26" s="24" t="n"/>
-    </row>
-    <row r="27" ht="32" customHeight="1" s="60">
-      <c r="A27" s="25" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-05</t>
-        </is>
-      </c>
-      <c r="B27" s="14" t="inlineStr">
-        <is>
-          <t>FN-PAR-03-02-02</t>
-        </is>
-      </c>
-      <c r="C27" s="32" t="inlineStr">
-        <is>
-          <t>정책 효과 시뮬레이션</t>
-        </is>
-      </c>
-      <c r="D27" s="32" t="inlineStr">
-        <is>
-          <t>정책 변수 설정</t>
-        </is>
-      </c>
-      <c r="E27" s="14" t="inlineStr">
-        <is>
-          <t>주차장 확충 파라미터</t>
-        </is>
-      </c>
-      <c r="F27" s="14" t="inlineStr">
-        <is>
-          <t>UI-PAR-003-02</t>
-        </is>
-      </c>
-      <c r="G27" s="15" t="inlineStr">
-        <is>
-          <t>[주차장 확충] 대상 지역·확충 방식(공한지 조성/복층화/신규 조성)·주차면 증설 수 입력 후 시뮬레이션 실행</t>
-        </is>
-      </c>
-      <c r="H27" s="14" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I27" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J27" s="14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K27" s="26" t="n"/>
+      <c r="K27" s="24" t="n"/>
     </row>
     <row r="28" ht="32" customHeight="1" s="60">
       <c r="A28" s="25" t="inlineStr">
@@ -4918,7 +4920,7 @@
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>FN-PAR-03-02-03</t>
+          <t>FN-PAR-03-02-02</t>
         </is>
       </c>
       <c r="C28" s="32" t="inlineStr">
@@ -4933,17 +4935,17 @@
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>이면도로 정비 파라미터</t>
+          <t>주차장 확충 파라미터</t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
         <is>
-          <t>UI-PAR-003-02-1</t>
+          <t>UI-PAR-003-02</t>
         </is>
       </c>
       <c r="G28" s="15" t="inlineStr">
         <is>
-          <t>[이면도로 정비] 대상 지역·정비 방식(상업지역형(주차환경개선지구)/주거지역형(주민참여형))·정비 구간 연장(m) 입력</t>
+          <t>[주차장 확충] 대상 지역·확충 방식(공한지 조성/복층화/신규 조성)·주차면 증설 수 입력 후 시뮬레이션 실행</t>
         </is>
       </c>
       <c r="H28" s="14" t="inlineStr">
@@ -4971,7 +4973,7 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>FN-PAR-03-02-04</t>
+          <t>FN-PAR-03-02-03</t>
         </is>
       </c>
       <c r="C29" s="32" t="inlineStr">
@@ -4986,7 +4988,7 @@
       </c>
       <c r="E29" s="14" t="inlineStr">
         <is>
-          <t>요금제 적용 파라미터</t>
+          <t>이면도로 정비 파라미터</t>
         </is>
       </c>
       <c r="F29" s="14" t="inlineStr">
@@ -4996,7 +4998,7 @@
       </c>
       <c r="G29" s="15" t="inlineStr">
         <is>
-          <t>[요금제 적용] 대상 지역·적용 방식(요금 인상/무료→유료 전환)·적용 급지(전체/1급지(동)/2급지(읍·면), 제주 전체·시 전체 선택 시에만)·인상률(+10/20/30%, 요금 인상 시)</t>
+          <t>[이면도로 정비] 대상 지역·정비 방식(상업지역형(주차환경개선지구)/주거지역형(주민참여형))·정비 구간 연장(m) 입력</t>
         </is>
       </c>
       <c r="H29" s="14" t="inlineStr">
@@ -5014,21 +5016,17 @@
           <t>O</t>
         </is>
       </c>
-      <c r="K29" s="26" t="inlineStr">
-        <is>
-          <t>설계감리 시정 완료</t>
-        </is>
-      </c>
+      <c r="K29" s="26" t="n"/>
     </row>
     <row r="30" ht="32" customHeight="1" s="60" thickBot="1">
       <c r="A30" s="25" t="inlineStr">
         <is>
-          <t>REQ-SFR-003-10</t>
+          <t>REQ-SFR-003-05</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>FN-PAR-03-02-05</t>
+          <t>FN-PAR-03-02-04</t>
         </is>
       </c>
       <c r="C30" s="32" t="inlineStr">
@@ -5036,24 +5034,24 @@
           <t>정책 효과 시뮬레이션</t>
         </is>
       </c>
-      <c r="D30" s="14" t="inlineStr">
-        <is>
-          <t>효과 예측 결과</t>
+      <c r="D30" s="32" t="inlineStr">
+        <is>
+          <t>정책 변수 설정</t>
         </is>
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>효과 예측 KPI 카드</t>
+          <t>요금제 적용 파라미터</t>
         </is>
       </c>
       <c r="F30" s="14" t="inlineStr">
         <is>
-          <t>UI-PAR-003-02</t>
+          <t>UI-PAR-003-02-1</t>
         </is>
       </c>
       <c r="G30" s="15" t="inlineStr">
         <is>
-          <t>효과 예측 KPI: 민원 감소 예측·혼잡도 개선(혼잡 지수 = (정상 이용+불법주차)÷공급 면수). 분석 근거 ⓘ 팝오버(가정값 기반 고지 포함)</t>
+          <t>[요금제 적용] 대상 지역·적용 방식(요금 인상/무료→유료 전환)·적용 급지(전체/1급지(동)/2급지(읍·면), 제주 전체·시 전체 선택 시에만)·인상률(+10/20/30%, 요금 인상 시)</t>
         </is>
       </c>
       <c r="H30" s="14" t="inlineStr">
@@ -5071,180 +5069,184 @@
           <t>O</t>
         </is>
       </c>
-      <c r="K30" s="26" t="n"/>
+      <c r="K30" s="26" t="inlineStr">
+        <is>
+          <t>설계감리 시정 완료</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="32" customHeight="1" s="60">
       <c r="A31" s="25" t="inlineStr">
         <is>
+          <t>REQ-SFR-003-10</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>FN-PAR-03-02-05</t>
+        </is>
+      </c>
+      <c r="C31" s="32" t="inlineStr">
+        <is>
+          <t>정책 효과 시뮬레이션</t>
+        </is>
+      </c>
+      <c r="D31" s="14" t="inlineStr">
+        <is>
+          <t>효과 예측 결과</t>
+        </is>
+      </c>
+      <c r="E31" s="14" t="inlineStr">
+        <is>
+          <t>효과 예측 KPI 카드</t>
+        </is>
+      </c>
+      <c r="F31" s="14" t="inlineStr">
+        <is>
+          <t>UI-PAR-003-02</t>
+        </is>
+      </c>
+      <c r="G31" s="15" t="inlineStr">
+        <is>
+          <t>효과 예측 KPI: 민원 감소 예측·혼잡도 개선(혼잡 지수 = (정상 이용+불법주차)÷공급 면수). 분석 근거 ⓘ 팝오버(가정값 기반 고지 포함)</t>
+        </is>
+      </c>
+      <c r="H31" s="14" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I31" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J31" s="14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K31" s="26" t="n"/>
+    </row>
+    <row r="32" ht="32" customHeight="1" s="60">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
           <t>REQ-SFR-003-12</t>
         </is>
       </c>
-      <c r="B31" s="14" t="inlineStr">
+      <c r="B32" s="14" t="inlineStr">
         <is>
           <t>FN-PAR-03-02-06</t>
         </is>
       </c>
-      <c r="C31" s="32" t="inlineStr">
+      <c r="C32" s="32" t="inlineStr">
         <is>
           <t>정책 효과 시뮬레이션</t>
         </is>
       </c>
-      <c r="D31" s="14" t="inlineStr">
+      <c r="D32" s="14" t="inlineStr">
         <is>
           <t>시나리오 비교 테이블</t>
         </is>
       </c>
-      <c r="E31" s="14" t="inlineStr">
+      <c r="E32" s="14" t="inlineStr">
         <is>
           <t>비교 결과 PDF 다운로드</t>
         </is>
       </c>
-      <c r="F31" s="14" t="inlineStr">
+      <c r="F32" s="14" t="inlineStr">
         <is>
           <t>UI-PAR-003-02</t>
         </is>
       </c>
-      <c r="G31" s="15" t="inlineStr">
+      <c r="G32" s="15" t="inlineStr">
         <is>
           <t>시나리오 비교 테이블 — 정책 유형 필터 칩(건수 표시), 체크박스 선택 내보내기(PDF/DOCX, 비교 차트 포함), 행 삭제(확인 모달)</t>
         </is>
       </c>
-      <c r="H31" s="14" t="inlineStr">
+      <c r="H32" s="14" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I31" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J31" s="14" t="inlineStr">
+      <c r="I32" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J32" s="14" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K31" s="26" t="inlineStr">
+      <c r="K32" s="26" t="inlineStr">
         <is>
           <t>설계감리 시정 완료</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="32" customHeight="1" s="60">
-      <c r="A32" s="23" t="inlineStr">
+    <row r="33" ht="32" customHeight="1" s="60">
+      <c r="A33" s="23" t="inlineStr">
         <is>
           <t>REQ-SFR-003-04</t>
         </is>
       </c>
-      <c r="B32" s="16" t="inlineStr">
+      <c r="B33" s="16" t="inlineStr">
         <is>
           <t>FN-PAR-03-03-01</t>
         </is>
       </c>
-      <c r="C32" s="16" t="inlineStr">
+      <c r="C33" s="16" t="inlineStr">
         <is>
           <t>생활권 시뮬레이션</t>
         </is>
       </c>
-      <c r="D32" s="16" t="inlineStr">
+      <c r="D33" s="16" t="inlineStr">
         <is>
           <t>생활권 분석 설정</t>
         </is>
       </c>
-      <c r="E32" s="16" t="inlineStr">
+      <c r="E33" s="16" t="inlineStr">
         <is>
           <t>분석 조건 설정 패널</t>
         </is>
       </c>
-      <c r="F32" s="16" t="inlineStr">
+      <c r="F33" s="16" t="inlineStr">
         <is>
           <t>UI-PAR-003-03</t>
         </is>
       </c>
-      <c r="G32" s="17" t="inlineStr">
+      <c r="G33" s="17" t="inlineStr">
         <is>
           <t>분석 내용 선택·분석 지역·분석 기간(최근1/3/6개월·직접 설정·날짜 범위)·격자 크기(1km/500m/250m/100m) 설정 후 생활권 분석 실행</t>
         </is>
       </c>
-      <c r="H32" s="16" t="inlineStr">
+      <c r="H33" s="16" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I32" s="37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J32" s="16" t="inlineStr">
+      <c r="I33" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J33" s="16" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K32" s="24" t="n"/>
-    </row>
-    <row r="33" ht="32" customHeight="1" s="60">
-      <c r="A33" s="25" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-09</t>
-        </is>
-      </c>
-      <c r="B33" s="14" t="inlineStr">
-        <is>
-          <t>FN-PAR-03-03-02</t>
-        </is>
-      </c>
-      <c r="C33" s="32" t="inlineStr">
-        <is>
-          <t>생활권 시뮬레이션</t>
-        </is>
-      </c>
-      <c r="D33" s="14" t="inlineStr">
-        <is>
-          <t>격자 GIS 지도</t>
-        </is>
-      </c>
-      <c r="E33" s="14" t="inlineStr">
-        <is>
-          <t>격자 히트맵 시각화</t>
-        </is>
-      </c>
-      <c r="F33" s="14" t="inlineStr">
-        <is>
-          <t>UI-PAR-003-03</t>
-        </is>
-      </c>
-      <c r="G33" s="15" t="inlineStr">
-        <is>
-          <t>격자(100m~1km) 기반 GIS 히트맵 — 5단계 색상(심각/경고/주의/보통/낮음). 민원·수급은 백분위, 혼잡도는 절대 기준(지수 1.0=100점)</t>
-        </is>
-      </c>
-      <c r="H33" s="14" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I33" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J33" s="14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K33" s="26" t="n"/>
+      <c r="K33" s="24" t="n"/>
     </row>
     <row r="34" ht="32" customHeight="1" s="60">
       <c r="A34" s="25" t="inlineStr">
         <is>
-          <t>REQ-SFR-003-04</t>
+          <t>REQ-SFR-003-09</t>
         </is>
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>FN-PAR-03-03-03</t>
+          <t>FN-PAR-03-03-02</t>
         </is>
       </c>
       <c r="C34" s="32" t="inlineStr">
@@ -5252,14 +5254,14 @@
           <t>생활권 시뮬레이션</t>
         </is>
       </c>
-      <c r="D34" s="32" t="inlineStr">
+      <c r="D34" s="14" t="inlineStr">
         <is>
           <t>격자 GIS 지도</t>
         </is>
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>격자 팝업</t>
+          <t>격자 히트맵 시각화</t>
         </is>
       </c>
       <c r="F34" s="14" t="inlineStr">
@@ -5269,7 +5271,7 @@
       </c>
       <c r="G34" s="15" t="inlineStr">
         <is>
-          <t>선택 격자 클릭 시 팝업: 위치명·총 건수·기간· 유형별 건수 상세 표시</t>
+          <t>격자(100m~1km) 기반 GIS 히트맵 — 5단계 색상(심각/경고/주의/보통/낮음). 민원·수급은 백분위, 혼잡도는 절대 기준(지수 1.0=100점)</t>
         </is>
       </c>
       <c r="H34" s="14" t="inlineStr">
@@ -5297,482 +5299,478 @@
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
+          <t>FN-PAR-03-03-03</t>
+        </is>
+      </c>
+      <c r="C35" s="32" t="inlineStr">
+        <is>
+          <t>생활권 시뮬레이션</t>
+        </is>
+      </c>
+      <c r="D35" s="32" t="inlineStr">
+        <is>
+          <t>격자 GIS 지도</t>
+        </is>
+      </c>
+      <c r="E35" s="14" t="inlineStr">
+        <is>
+          <t>격자 팝업</t>
+        </is>
+      </c>
+      <c r="F35" s="14" t="inlineStr">
+        <is>
+          <t>UI-PAR-003-03</t>
+        </is>
+      </c>
+      <c r="G35" s="15" t="inlineStr">
+        <is>
+          <t>선택 격자 클릭 시 팝업: 위치명·총 건수·기간· 유형별 건수 상세 표시</t>
+        </is>
+      </c>
+      <c r="H35" s="14" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I35" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J35" s="14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K35" s="26" t="n"/>
+    </row>
+    <row r="36" ht="32" customHeight="1" s="60">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>REQ-SFR-003-04</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
           <t>FN-PAR-03-03-04</t>
         </is>
       </c>
-      <c r="C35" s="32" t="inlineStr">
+      <c r="C36" s="32" t="inlineStr">
         <is>
           <t>생활권 시뮬레이션</t>
         </is>
       </c>
-      <c r="D35" s="14" t="inlineStr">
+      <c r="D36" s="14" t="inlineStr">
         <is>
           <t>분석 결과 요약</t>
         </is>
       </c>
-      <c r="E35" s="14" t="inlineStr">
+      <c r="E36" s="14" t="inlineStr">
         <is>
           <t>격자 기반 분석 요약 패널</t>
         </is>
       </c>
-      <c r="F35" s="14" t="inlineStr">
+      <c r="F36" s="14" t="inlineStr">
         <is>
           <t>UI-PAR-003-03</t>
         </is>
       </c>
-      <c r="G35" s="15" t="inlineStr">
+      <c r="G36" s="15" t="inlineStr">
         <is>
           <t>총 분석 격자 수 + 5단계 격자 수 요약, 격자 크기 칩·등급 산정 기준 ⓘ 팝오버</t>
         </is>
       </c>
-      <c r="H35" s="14" t="inlineStr">
+      <c r="H36" s="14" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I35" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J35" s="14" t="inlineStr">
+      <c r="I36" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J36" s="14" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K35" s="26" t="inlineStr">
+      <c r="K36" s="26" t="inlineStr">
         <is>
           <t>설계감리 시정 완료</t>
         </is>
       </c>
-    </row>
-    <row r="36" ht="32" customHeight="1" s="60">
-      <c r="A36" s="27" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-04</t>
-        </is>
-      </c>
-      <c r="B36" s="18" t="inlineStr">
-        <is>
-          <t>FN-PAR-03-03-05</t>
-        </is>
-      </c>
-      <c r="C36" s="34" t="inlineStr">
-        <is>
-          <t>생활권 시뮬레이션</t>
-        </is>
-      </c>
-      <c r="D36" s="18" t="inlineStr">
-        <is>
-          <t>민원 집중구역 목록</t>
-        </is>
-      </c>
-      <c r="E36" s="18" t="inlineStr">
-        <is>
-          <t>격자 기반 집중구역 Top 목록</t>
-        </is>
-      </c>
-      <c r="F36" s="18" t="inlineStr">
-        <is>
-          <t>UI-PAR-003-03</t>
-        </is>
-      </c>
-      <c r="G36" s="19" t="inlineStr">
-        <is>
-          <t>격자 분석 집중 구역 Top8(심각·경고·주의) 목록 — 동 + 격자 중심 POI 명칭으로 표시. 행 클릭 시 지도 이동·팝업. 혼잡도 모드는 혼잡 점수 안내 ⓘ 제공</t>
-        </is>
-      </c>
-      <c r="H36" s="18" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I36" s="39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J36" s="18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K36" s="28" t="n"/>
     </row>
     <row r="37" ht="32" customHeight="1" s="60">
       <c r="A37" s="27" t="inlineStr">
         <is>
+          <t>REQ-SFR-003-04</t>
+        </is>
+      </c>
+      <c r="B37" s="18" t="inlineStr">
+        <is>
+          <t>FN-PAR-03-03-05</t>
+        </is>
+      </c>
+      <c r="C37" s="34" t="inlineStr">
+        <is>
+          <t>생활권 시뮬레이션</t>
+        </is>
+      </c>
+      <c r="D37" s="18" t="inlineStr">
+        <is>
+          <t>민원 집중구역 목록</t>
+        </is>
+      </c>
+      <c r="E37" s="18" t="inlineStr">
+        <is>
+          <t>격자 기반 집중구역 Top 목록</t>
+        </is>
+      </c>
+      <c r="F37" s="18" t="inlineStr">
+        <is>
+          <t>UI-PAR-003-03</t>
+        </is>
+      </c>
+      <c r="G37" s="19" t="inlineStr">
+        <is>
+          <t>격자 분석 집중 구역 Top8(심각·경고·주의) 목록 — 동 + 격자 중심 POI 명칭으로 표시. 행 클릭 시 지도 이동·팝업. 혼잡도 모드는 혼잡 점수 안내 ⓘ 제공</t>
+        </is>
+      </c>
+      <c r="H37" s="18" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I37" s="39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J37" s="18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K37" s="28" t="n"/>
+    </row>
+    <row r="38" ht="32" customHeight="1" s="60">
+      <c r="A38" s="27" t="inlineStr">
+        <is>
           <t>REQ-SFR-003-10</t>
         </is>
       </c>
-      <c r="B37" s="18" t="inlineStr">
+      <c r="B38" s="18" t="inlineStr">
         <is>
           <t>FN-PAR-03-03-06</t>
         </is>
       </c>
-      <c r="C37" s="34" t="inlineStr">
+      <c r="C38" s="34" t="inlineStr">
         <is>
           <t>생활권 시뮬레이션</t>
         </is>
       </c>
-      <c r="D37" s="18" t="inlineStr">
+      <c r="D38" s="18" t="inlineStr">
         <is>
           <t>내보내기</t>
         </is>
       </c>
-      <c r="E37" s="18" t="inlineStr">
+      <c r="E38" s="18" t="inlineStr">
         <is>
           <t>PDF/DOCX 내보내기</t>
         </is>
       </c>
-      <c r="F37" s="18" t="inlineStr">
+      <c r="F38" s="18" t="inlineStr">
         <is>
           <t>UI-PAR-003-03</t>
         </is>
       </c>
-      <c r="G37" s="19" t="inlineStr">
+      <c r="G38" s="19" t="inlineStr">
         <is>
           <t>분석 결과를 PDF/DOCX 보고서로 내보내기 — 내보낸 보고서는 보고서 목록의 직접 생성 보고서 목록에 표시</t>
         </is>
       </c>
-      <c r="H37" s="18" t="inlineStr">
+      <c r="H38" s="18" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I37" s="39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J37" s="18" t="inlineStr">
+      <c r="I38" s="39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J38" s="18" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K37" s="28" t="n"/>
-    </row>
-    <row r="38" ht="32" customHeight="1" s="60">
-      <c r="A38" s="23" t="inlineStr">
+      <c r="K38" s="28" t="n"/>
+    </row>
+    <row r="39" ht="32" customHeight="1" s="60">
+      <c r="A39" s="23" t="inlineStr">
         <is>
           <t>REQ-SFR-003-06</t>
         </is>
       </c>
-      <c r="B38" s="16" t="inlineStr">
+      <c r="B39" s="16" t="inlineStr">
         <is>
           <t>FN-PAR-03-04-01</t>
         </is>
       </c>
-      <c r="C38" s="16" t="inlineStr">
+      <c r="C39" s="16" t="inlineStr">
         <is>
           <t>구역추천</t>
         </is>
       </c>
-      <c r="D38" s="16" t="inlineStr">
+      <c r="D39" s="16" t="inlineStr">
         <is>
           <t>구역 추천 설정</t>
         </is>
       </c>
-      <c r="E38" s="16" t="inlineStr">
+      <c r="E39" s="16" t="inlineStr">
         <is>
           <t>추천 조건 설정 패널</t>
         </is>
       </c>
-      <c r="F38" s="16" t="inlineStr">
+      <c r="F39" s="16" t="inlineStr">
         <is>
           <t>UI-PAR-003-04</t>
         </is>
       </c>
-      <c r="G38" s="17" t="inlineStr">
+      <c r="G39" s="17" t="inlineStr">
         <is>
           <t>분석 내용(요금제 적용/공유주차제 적용)·분석 지역·분석 기간(월 단위) 설정 후 구역 추천 실행</t>
         </is>
       </c>
-      <c r="H38" s="16" t="inlineStr">
+      <c r="H39" s="16" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I38" s="37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J38" s="16" t="inlineStr">
+      <c r="I39" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J39" s="16" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K38" s="24" t="n"/>
-    </row>
-    <row r="39" ht="32" customHeight="1" s="60">
-      <c r="A39" s="25" t="inlineStr">
+      <c r="K39" s="24" t="n"/>
+    </row>
+    <row r="40" ht="32" customHeight="1" s="60">
+      <c r="A40" s="25" t="inlineStr">
         <is>
           <t>REQ-SFR-003-06</t>
         </is>
       </c>
-      <c r="B39" s="14" t="inlineStr">
+      <c r="B40" s="14" t="inlineStr">
         <is>
           <t>FN-PAR-03-04-02</t>
         </is>
       </c>
-      <c r="C39" s="32" t="inlineStr">
+      <c r="C40" s="32" t="inlineStr">
         <is>
           <t>구역추천</t>
         </is>
       </c>
-      <c r="D39" s="14" t="inlineStr">
+      <c r="D40" s="14" t="inlineStr">
         <is>
           <t>구역 추천 GIS</t>
         </is>
       </c>
-      <c r="E39" s="14" t="inlineStr">
+      <c r="E40" s="14" t="inlineStr">
         <is>
           <t>GIS 지도 + 순위 마커</t>
         </is>
       </c>
-      <c r="F39" s="14" t="inlineStr">
+      <c r="F40" s="14" t="inlineStr">
         <is>
           <t>UI-PAR-003-04</t>
         </is>
       </c>
-      <c r="G39" s="15" t="inlineStr">
+      <c r="G40" s="15" t="inlineStr">
         <is>
           <t>GIS 지도에 추천 구역 순위 핀 마커 표시 — 핀 클릭 시 상세 팝업</t>
         </is>
       </c>
-      <c r="H39" s="14" t="inlineStr">
+      <c r="H40" s="14" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I39" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J39" s="14" t="inlineStr">
+      <c r="I40" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J40" s="14" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K39" s="26" t="n"/>
-    </row>
-    <row r="40" ht="32" customHeight="1" s="60">
-      <c r="A40" s="50" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-06</t>
-        </is>
-      </c>
-      <c r="B40" s="51" t="inlineStr">
-        <is>
-          <t>FN-PAR-03-04-03</t>
-        </is>
-      </c>
-      <c r="C40" s="52" t="inlineStr">
-        <is>
-          <t>구역추천</t>
-        </is>
-      </c>
-      <c r="D40" s="51" t="inlineStr">
-        <is>
-          <t>요금제 적용 추천 구역 순위</t>
-        </is>
-      </c>
-      <c r="E40" s="51" t="inlineStr">
-        <is>
-          <t>구역 추천 결과 목록</t>
-        </is>
-      </c>
-      <c r="F40" s="51" t="inlineStr">
-        <is>
-          <t>UI-PAR-003-04</t>
-        </is>
-      </c>
-      <c r="G40" s="53" t="inlineStr">
-        <is>
-          <t>민원 증가 추세를 분석하여 요금제·공유주차제 적용 추천 구역 순위 표시 — 산정 기준 ⓘ 팝오버 제공, 목록과 지도 연동</t>
-        </is>
-      </c>
-      <c r="H40" s="51" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I40" s="54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J40" s="51" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K40" s="55" t="n"/>
+      <c r="K40" s="26" t="n"/>
     </row>
     <row r="41" ht="32" customHeight="1" s="60">
       <c r="A41" s="50" t="inlineStr">
         <is>
+          <t>REQ-SFR-003-06</t>
+        </is>
+      </c>
+      <c r="B41" s="51" t="inlineStr">
+        <is>
+          <t>FN-PAR-03-04-03</t>
+        </is>
+      </c>
+      <c r="C41" s="52" t="inlineStr">
+        <is>
+          <t>구역추천</t>
+        </is>
+      </c>
+      <c r="D41" s="51" t="inlineStr">
+        <is>
+          <t>요금제 적용 추천 구역 순위</t>
+        </is>
+      </c>
+      <c r="E41" s="51" t="inlineStr">
+        <is>
+          <t>구역 추천 결과 목록</t>
+        </is>
+      </c>
+      <c r="F41" s="51" t="inlineStr">
+        <is>
+          <t>UI-PAR-003-04</t>
+        </is>
+      </c>
+      <c r="G41" s="53" t="inlineStr">
+        <is>
+          <t>민원 증가 추세를 분석하여 요금제·공유주차제 적용 추천 구역 순위 표시 — 산정 기준 ⓘ 팝오버 제공, 목록과 지도 연동</t>
+        </is>
+      </c>
+      <c r="H41" s="51" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I41" s="54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J41" s="51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K41" s="55" t="n"/>
+    </row>
+    <row r="42" ht="32" customHeight="1" s="60" thickBot="1">
+      <c r="A42" s="50" t="inlineStr">
+        <is>
           <t>REQ-SFR-003-10</t>
         </is>
       </c>
-      <c r="B41" s="51" t="inlineStr">
+      <c r="B42" s="51" t="inlineStr">
         <is>
           <t>FN-PAR-03-04-04</t>
         </is>
       </c>
-      <c r="C41" s="52" t="inlineStr">
+      <c r="C42" s="52" t="inlineStr">
         <is>
           <t>구역추천</t>
         </is>
       </c>
-      <c r="D41" s="51" t="inlineStr">
+      <c r="D42" s="51" t="inlineStr">
         <is>
           <t>내보내기</t>
         </is>
       </c>
-      <c r="E41" s="51" t="inlineStr">
+      <c r="E42" s="51" t="inlineStr">
         <is>
           <t>PDF/DOCX 내보내기</t>
         </is>
       </c>
-      <c r="F41" s="51" t="inlineStr">
+      <c r="F42" s="51" t="inlineStr">
         <is>
           <t>UI-PAR-003-04</t>
         </is>
       </c>
-      <c r="G41" s="53" t="inlineStr">
+      <c r="G42" s="53" t="inlineStr">
         <is>
           <t>분석 결과를 PDF/DOCX 보고서로 내보내기 — 내보낸 보고서는 보고서 목록의 직접 생성 보고서 목록에 표시</t>
         </is>
       </c>
-      <c r="H41" s="51" t="inlineStr">
+      <c r="H42" s="51" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I41" s="54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J41" s="51" t="inlineStr">
+      <c r="I42" s="54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J42" s="51" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K41" s="55" t="n"/>
-    </row>
-    <row r="42" ht="32" customHeight="1" s="60" thickBot="1">
-      <c r="A42" s="23" t="inlineStr">
+      <c r="K42" s="55" t="n"/>
+    </row>
+    <row r="43" ht="32" customHeight="1" s="60">
+      <c r="A43" s="23" t="inlineStr">
         <is>
           <t>REQ-SFR-005-04</t>
         </is>
       </c>
-      <c r="B42" s="16" t="inlineStr">
+      <c r="B43" s="16" t="inlineStr">
         <is>
           <t>FN-PAR-03-05-01</t>
         </is>
       </c>
-      <c r="C42" s="16" t="inlineStr">
+      <c r="C43" s="16" t="inlineStr">
         <is>
           <t>투자우선순위 보드</t>
         </is>
       </c>
-      <c r="D42" s="16" t="inlineStr">
+      <c r="D43" s="16" t="inlineStr">
         <is>
           <t>KPI 요약</t>
         </is>
       </c>
-      <c r="E42" s="16" t="inlineStr">
+      <c r="E43" s="16" t="inlineStr">
         <is>
           <t>KPI 카드</t>
         </is>
       </c>
-      <c r="F42" s="16" t="inlineStr">
+      <c r="F43" s="16" t="inlineStr">
         <is>
           <t>UI-PAR-003-05</t>
         </is>
       </c>
-      <c r="G42" s="17" t="inlineStr">
+      <c r="G43" s="17" t="inlineStr">
         <is>
           <t>분석 대상 주차장 수·높음 우선순위 개소·최근 3개월 사고 건수 KPI 카드 표시</t>
         </is>
       </c>
-      <c r="H42" s="16" t="inlineStr">
+      <c r="H43" s="16" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I42" s="37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J42" s="16" t="inlineStr">
+      <c r="I43" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J43" s="16" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K42" s="24" t="inlineStr">
-        <is>
-          <t>설계감리 시정 완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="32" customHeight="1" s="60">
-      <c r="A43" s="25" t="inlineStr">
-        <is>
-          <t>REQ-SFR-005-04</t>
-        </is>
-      </c>
-      <c r="B43" s="14" t="inlineStr">
-        <is>
-          <t>FN-PAR-03-05-02</t>
-        </is>
-      </c>
-      <c r="C43" s="31" t="inlineStr">
-        <is>
-          <t>투자우선순위 보드</t>
-        </is>
-      </c>
-      <c r="D43" s="14" t="inlineStr">
-        <is>
-          <t>투자우선순위 GIS</t>
-        </is>
-      </c>
-      <c r="E43" s="14" t="inlineStr">
-        <is>
-          <t>GIS 지도 + 우선순위 마커</t>
-        </is>
-      </c>
-      <c r="F43" s="14" t="inlineStr">
-        <is>
-          <t>UI-PAR-003-05</t>
-        </is>
-      </c>
-      <c r="G43" s="15" t="inlineStr">
-        <is>
-          <t>제주 전역 GIS 지도에 우선순위 공영주차장 마커 표시(높음, 중간만 표시). 선택 시 주차장 상세 팝업(위치·총 면수·준공연도·경과연수)</t>
-        </is>
-      </c>
-      <c r="H43" s="14" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I43" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J43" s="14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K43" s="26" t="inlineStr">
+      <c r="K43" s="24" t="inlineStr">
         <is>
           <t>설계감리 시정 완료</t>
         </is>
@@ -5786,107 +5784,107 @@
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
+          <t>FN-PAR-03-05-02</t>
+        </is>
+      </c>
+      <c r="C44" s="31" t="inlineStr">
+        <is>
+          <t>투자우선순위 보드</t>
+        </is>
+      </c>
+      <c r="D44" s="14" t="inlineStr">
+        <is>
+          <t>투자우선순위 GIS</t>
+        </is>
+      </c>
+      <c r="E44" s="14" t="inlineStr">
+        <is>
+          <t>GIS 지도 + 우선순위 마커</t>
+        </is>
+      </c>
+      <c r="F44" s="14" t="inlineStr">
+        <is>
+          <t>UI-PAR-003-05</t>
+        </is>
+      </c>
+      <c r="G44" s="15" t="inlineStr">
+        <is>
+          <t>제주 전역 GIS 지도에 우선순위 공영주차장 마커 표시(높음, 중간만 표시). 선택 시 주차장 상세 팝업(위치·총 면수·준공연도·경과연수)</t>
+        </is>
+      </c>
+      <c r="H44" s="14" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I44" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J44" s="14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K44" s="26" t="inlineStr">
+        <is>
+          <t>설계감리 시정 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="32" customHeight="1" s="60">
+      <c r="A45" s="25" t="inlineStr">
+        <is>
+          <t>REQ-SFR-005-04</t>
+        </is>
+      </c>
+      <c r="B45" s="14" t="inlineStr">
+        <is>
           <t>FN-PAR-03-05-03</t>
         </is>
       </c>
-      <c r="C44" s="31" t="inlineStr">
+      <c r="C45" s="31" t="inlineStr">
         <is>
           <t>투자우선순위 보드</t>
         </is>
       </c>
-      <c r="D44" s="31" t="inlineStr">
+      <c r="D45" s="31" t="inlineStr">
         <is>
           <t>투자우선순위 GIS</t>
         </is>
       </c>
-      <c r="E44" s="14" t="inlineStr">
+      <c r="E45" s="14" t="inlineStr">
         <is>
           <t>주차장 상세 팝업</t>
         </is>
       </c>
-      <c r="F44" s="14" t="inlineStr">
+      <c r="F45" s="14" t="inlineStr">
         <is>
           <t>UI-PAR-003-05</t>
         </is>
       </c>
-      <c r="G44" s="15" t="inlineStr">
+      <c r="G45" s="15" t="inlineStr">
         <is>
           <t>선택 주차장 팝업: 주차장명·주소·총 면수·준공연도·경과연수 및 안전위험도·민원 빈도·이용 패턴·단속 건수 4개 지표 게이지 표시</t>
         </is>
       </c>
-      <c r="H44" s="14" t="inlineStr">
+      <c r="H45" s="14" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I44" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J44" s="14" t="inlineStr">
+      <c r="I45" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J45" s="14" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K44" s="26" t="inlineStr">
-        <is>
-          <t>설계감리 시정 완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="32" customHeight="1" s="60">
-      <c r="A45" s="27" t="inlineStr">
-        <is>
-          <t>REQ-SFR-005-04</t>
-        </is>
-      </c>
-      <c r="B45" s="18" t="inlineStr">
-        <is>
-          <t>FN-PAR-03-05-04</t>
-        </is>
-      </c>
-      <c r="C45" s="33" t="inlineStr">
-        <is>
-          <t>투자우선순위 보드</t>
-        </is>
-      </c>
-      <c r="D45" s="18" t="inlineStr">
-        <is>
-          <t>투자·보강 우선순위 목록</t>
-        </is>
-      </c>
-      <c r="E45" s="18" t="inlineStr">
-        <is>
-          <t>종합점수 기반 순위 Top 목록</t>
-        </is>
-      </c>
-      <c r="F45" s="18" t="inlineStr">
-        <is>
-          <t>UI-PAR-003-05</t>
-        </is>
-      </c>
-      <c r="G45" s="19" t="inlineStr">
-        <is>
-          <t>종합점수(안전위험도 25%·민원 빈도 25%·이용 패턴 20%·단속 건수 25% — 설정에서 가중치 변경 가능) 기준 우선순위 목록 — 행 클릭 시 지도 확대 이동·팝업, 등급(높음/중간/낮음) 점 표시</t>
-        </is>
-      </c>
-      <c r="H45" s="18" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I45" s="39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J45" s="18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K45" s="28" t="inlineStr">
+      <c r="K45" s="26" t="inlineStr">
         <is>
           <t>설계감리 시정 완료</t>
         </is>
@@ -5895,378 +5893,386 @@
     <row r="46" ht="32" customHeight="1" s="60">
       <c r="A46" s="27" t="inlineStr">
         <is>
+          <t>REQ-SFR-005-04</t>
+        </is>
+      </c>
+      <c r="B46" s="18" t="inlineStr">
+        <is>
+          <t>FN-PAR-03-05-04</t>
+        </is>
+      </c>
+      <c r="C46" s="33" t="inlineStr">
+        <is>
+          <t>투자우선순위 보드</t>
+        </is>
+      </c>
+      <c r="D46" s="18" t="inlineStr">
+        <is>
+          <t>투자·보강 우선순위 목록</t>
+        </is>
+      </c>
+      <c r="E46" s="18" t="inlineStr">
+        <is>
+          <t>종합점수 기반 순위 Top 목록</t>
+        </is>
+      </c>
+      <c r="F46" s="18" t="inlineStr">
+        <is>
+          <t>UI-PAR-003-05</t>
+        </is>
+      </c>
+      <c r="G46" s="19" t="inlineStr">
+        <is>
+          <t>종합점수(안전위험도 25%·민원 빈도 25%·이용 패턴 20%·단속 건수 25% — 설정에서 가중치 변경 가능) 기준 우선순위 목록 — 행 클릭 시 지도 확대 이동·팝업, 등급(높음/중간/낮음) 점 표시</t>
+        </is>
+      </c>
+      <c r="H46" s="18" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I46" s="39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J46" s="18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K46" s="28" t="inlineStr">
+        <is>
+          <t>설계감리 시정 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="32" customHeight="1" s="60">
+      <c r="A47" s="27" t="inlineStr">
+        <is>
           <t>REQ-SFR-003-10</t>
         </is>
       </c>
-      <c r="B46" s="18" t="inlineStr">
+      <c r="B47" s="18" t="inlineStr">
         <is>
           <t>FN-PAR-03-05-05</t>
         </is>
       </c>
-      <c r="C46" s="33" t="inlineStr">
+      <c r="C47" s="33" t="inlineStr">
         <is>
           <t>투자우선순위 보드</t>
         </is>
       </c>
-      <c r="D46" s="18" t="inlineStr">
+      <c r="D47" s="18" t="inlineStr">
         <is>
           <t>내보내기</t>
         </is>
       </c>
-      <c r="E46" s="18" t="inlineStr">
+      <c r="E47" s="18" t="inlineStr">
         <is>
           <t>PDF/DOCX 내보내기</t>
         </is>
       </c>
-      <c r="F46" s="18" t="inlineStr">
+      <c r="F47" s="18" t="inlineStr">
         <is>
           <t>UI-PAR-003-05</t>
         </is>
       </c>
-      <c r="G46" s="19" t="inlineStr">
+      <c r="G47" s="19" t="inlineStr">
         <is>
           <t>분석 결과를 PDF/DOCX 보고서로 내보내기 — 내보낸 보고서는 보고서 목록의 직접 생성 보고서 목록에 표시</t>
         </is>
       </c>
-      <c r="H46" s="18" t="inlineStr">
+      <c r="H47" s="18" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I46" s="39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J46" s="18" t="inlineStr">
+      <c r="I47" s="39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J47" s="18" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K46" s="28" t="n"/>
-    </row>
-    <row r="47" ht="32" customHeight="1" s="60">
-      <c r="A47" s="29" t="inlineStr">
+      <c r="K47" s="28" t="n"/>
+    </row>
+    <row r="48" ht="32" customHeight="1" s="60">
+      <c r="A48" s="29" t="inlineStr">
         <is>
           <t>REQ-SFR-005-05</t>
         </is>
       </c>
-      <c r="B47" s="20" t="inlineStr">
+      <c r="B48" s="20" t="inlineStr">
         <is>
           <t>FN-PAR-04-01-01</t>
         </is>
       </c>
-      <c r="C47" s="20" t="inlineStr">
+      <c r="C48" s="20" t="inlineStr">
         <is>
           <t>보고서 목록</t>
         </is>
       </c>
-      <c r="D47" s="20" t="inlineStr">
+      <c r="D48" s="20" t="inlineStr">
         <is>
           <t>자동 생성 보고서 목록</t>
         </is>
       </c>
-      <c r="E47" s="20" t="inlineStr">
+      <c r="E48" s="20" t="inlineStr">
         <is>
           <t>자동 생성 보고서 목록</t>
         </is>
       </c>
-      <c r="F47" s="20" t="inlineStr">
+      <c r="F48" s="20" t="inlineStr">
         <is>
           <t>UI-PAR-004-01</t>
         </is>
       </c>
-      <c r="G47" s="21" t="inlineStr">
+      <c r="G48" s="21" t="inlineStr">
         <is>
           <t>자동 생성된 보고서 목록 조회.</t>
         </is>
       </c>
-      <c r="H47" s="20" t="inlineStr">
+      <c r="H48" s="20" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I47" s="56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J47" s="20" t="inlineStr">
+      <c r="I48" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J48" s="20" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K47" s="30" t="n"/>
-    </row>
-    <row r="48" ht="32" customHeight="1" s="60">
-      <c r="A48" s="25" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-11</t>
-        </is>
-      </c>
-      <c r="B48" s="14" t="inlineStr">
-        <is>
-          <t>FN-PAR-04-01-02</t>
-        </is>
-      </c>
-      <c r="C48" s="31" t="inlineStr">
-        <is>
-          <t>보고서 목록</t>
-        </is>
-      </c>
-      <c r="D48" s="14" t="inlineStr">
-        <is>
-          <t>직접 생성 보고서 목록</t>
-        </is>
-      </c>
-      <c r="E48" s="14" t="inlineStr">
-        <is>
-          <t>직접 생성 보고서 목록</t>
-        </is>
-      </c>
-      <c r="F48" s="14" t="inlineStr">
-        <is>
-          <t>UI-PAR-004-01</t>
-        </is>
-      </c>
-      <c r="G48" s="15" t="inlineStr">
-        <is>
-          <t>직접 생성 보고서 목록 — 보고서명 검색·출처·생성일 필터, 행 삭제(확인 모달)</t>
-        </is>
-      </c>
-      <c r="H48" s="14" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I48" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J48" s="14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K48" s="26" t="inlineStr">
-        <is>
-          <t>설계감리 시정 완료</t>
-        </is>
-      </c>
+      <c r="K48" s="30" t="n"/>
     </row>
     <row r="49" ht="32" customHeight="1" s="60">
       <c r="A49" s="25" t="inlineStr">
         <is>
+          <t>REQ-SFR-003-11</t>
+        </is>
+      </c>
+      <c r="B49" s="14" t="inlineStr">
+        <is>
+          <t>FN-PAR-04-01-02</t>
+        </is>
+      </c>
+      <c r="C49" s="31" t="inlineStr">
+        <is>
+          <t>보고서 목록</t>
+        </is>
+      </c>
+      <c r="D49" s="14" t="inlineStr">
+        <is>
+          <t>직접 생성 보고서 목록</t>
+        </is>
+      </c>
+      <c r="E49" s="14" t="inlineStr">
+        <is>
+          <t>직접 생성 보고서 목록</t>
+        </is>
+      </c>
+      <c r="F49" s="14" t="inlineStr">
+        <is>
+          <t>UI-PAR-004-01</t>
+        </is>
+      </c>
+      <c r="G49" s="15" t="inlineStr">
+        <is>
+          <t>직접 생성 보고서 목록 — 보고서명 검색·출처·생성일 필터, 행 삭제(확인 모달)</t>
+        </is>
+      </c>
+      <c r="H49" s="14" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I49" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J49" s="14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K49" s="26" t="inlineStr">
+        <is>
+          <t>설계감리 시정 완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="32" customHeight="1" s="60">
+      <c r="A50" s="25" t="inlineStr">
+        <is>
           <t>REQ-SFR-005-05</t>
         </is>
       </c>
-      <c r="B49" s="14" t="inlineStr">
+      <c r="B50" s="14" t="inlineStr">
         <is>
           <t>FN-PAR-04-02-01</t>
         </is>
       </c>
-      <c r="C49" s="14" t="inlineStr">
+      <c r="C50" s="14" t="inlineStr">
         <is>
           <t>보고서 관리</t>
         </is>
       </c>
-      <c r="D49" s="14" t="inlineStr">
+      <c r="D50" s="14" t="inlineStr">
         <is>
           <t>자동 생성 설정 목록</t>
         </is>
       </c>
-      <c r="E49" s="14" t="inlineStr">
+      <c r="E50" s="14" t="inlineStr">
         <is>
           <t>자동 생성 설정 목록</t>
         </is>
       </c>
-      <c r="F49" s="14" t="inlineStr">
+      <c r="F50" s="14" t="inlineStr">
         <is>
           <t>UI-PAR-004-02</t>
         </is>
       </c>
-      <c r="G49" s="15" t="inlineStr">
+      <c r="G50" s="15" t="inlineStr">
         <is>
           <t>보고서 자동 생성 설정에서 확인된 목록 조회, 수정 버튼 클릭시 배포부서/배포주기/배포일자 수정</t>
         </is>
       </c>
-      <c r="H49" s="14" t="inlineStr">
+      <c r="H50" s="14" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I49" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J49" s="14" t="inlineStr">
+      <c r="I50" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J50" s="14" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K49" s="26" t="n"/>
-    </row>
-    <row r="50" ht="32" customHeight="1" s="60">
-      <c r="A50" s="27" t="inlineStr">
+      <c r="K50" s="26" t="n"/>
+    </row>
+    <row r="51" ht="32" customHeight="1" s="60">
+      <c r="A51" s="27" t="inlineStr">
         <is>
           <t>REQ-SFR-005-06</t>
         </is>
       </c>
-      <c r="B50" s="18" t="inlineStr">
+      <c r="B51" s="18" t="inlineStr">
         <is>
           <t>FN-PAR-04-02-02</t>
         </is>
       </c>
-      <c r="C50" s="33" t="inlineStr">
+      <c r="C51" s="33" t="inlineStr">
         <is>
           <t>보고서 관리</t>
         </is>
       </c>
-      <c r="D50" s="18" t="inlineStr">
+      <c r="D51" s="18" t="inlineStr">
         <is>
           <t>보고서 자동 생성 설정</t>
         </is>
       </c>
-      <c r="E50" s="18" t="inlineStr">
+      <c r="E51" s="18" t="inlineStr">
         <is>
           <t>배포 부서·배포 주기·배포 일자 설정</t>
         </is>
       </c>
-      <c r="F50" s="18" t="inlineStr">
+      <c r="F51" s="18" t="inlineStr">
         <is>
           <t>UI-PAR-004-02</t>
         </is>
       </c>
-      <c r="G50" s="19" t="inlineStr">
+      <c r="G51" s="19" t="inlineStr">
         <is>
           <t>배포 부서, 배포 주기, 배포 일자, 보고서 자동생성버튼</t>
         </is>
       </c>
-      <c r="H50" s="18" t="inlineStr">
+      <c r="H51" s="18" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I50" s="39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J50" s="18" t="inlineStr">
+      <c r="I51" s="39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J51" s="18" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K50" s="28" t="inlineStr">
+      <c r="K51" s="28" t="inlineStr">
         <is>
           <t>REQ-SFR-005-05 
 설계감리 시정 완료</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="32" customHeight="1" s="60">
-      <c r="A51" s="29" t="inlineStr">
+    <row r="52" ht="32" customHeight="1" s="60">
+      <c r="A52" s="29" t="inlineStr">
         <is>
           <t>REQ-SFR-003-08</t>
         </is>
       </c>
-      <c r="B51" s="20" t="inlineStr">
+      <c r="B52" s="20" t="inlineStr">
         <is>
           <t>FN-PAR-04-03-01</t>
         </is>
       </c>
-      <c r="C51" s="20" t="inlineStr">
+      <c r="C52" s="20" t="inlineStr">
         <is>
           <t>위험단계 알림 조회</t>
         </is>
       </c>
-      <c r="D51" s="20" t="inlineStr">
+      <c r="D52" s="20" t="inlineStr">
         <is>
           <t>조회 단위 필터</t>
         </is>
       </c>
-      <c r="E51" s="20" t="inlineStr">
+      <c r="E52" s="20" t="inlineStr">
         <is>
           <t>기간 탭 및 상세 필터</t>
         </is>
       </c>
-      <c r="F51" s="20" t="inlineStr">
+      <c r="F52" s="20" t="inlineStr">
         <is>
           <t>UI-PAR-004-03</t>
         </is>
       </c>
-      <c r="G51" s="21" t="inlineStr">
+      <c r="G52" s="21" t="inlineStr">
         <is>
           <t>단계(전체/심각/경고/주의), 지역,기간 선택</t>
         </is>
       </c>
-      <c r="H51" s="20" t="inlineStr">
+      <c r="H52" s="20" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I51" s="56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J51" s="20" t="inlineStr">
+      <c r="I52" s="56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J52" s="20" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K51" s="30" t="n"/>
-    </row>
-    <row r="52" ht="32" customHeight="1" s="60">
-      <c r="A52" s="25" t="inlineStr">
-        <is>
-          <t>REQ-SFR-003-08</t>
-        </is>
-      </c>
-      <c r="B52" s="14" t="inlineStr">
-        <is>
-          <t>FN-PAR-04-03-02</t>
-        </is>
-      </c>
-      <c r="C52" s="32" t="inlineStr">
-        <is>
-          <t>위험단계 알림 조회</t>
-        </is>
-      </c>
-      <c r="D52" s="14" t="inlineStr">
-        <is>
-          <t>KPI 요약</t>
-        </is>
-      </c>
-      <c r="E52" s="14" t="inlineStr">
-        <is>
-          <t>KPI 카드</t>
-        </is>
-      </c>
-      <c r="F52" s="14" t="inlineStr">
-        <is>
-          <t>UI-PAR-004-03</t>
-        </is>
-      </c>
-      <c r="G52" s="15" t="inlineStr">
-        <is>
-          <t>KPI 카드(조회 알림 건수/위험 알림 건수/누적 민원 수) 표시</t>
-        </is>
-      </c>
-      <c r="H52" s="14" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I52" s="14" t="n"/>
-      <c r="J52" s="14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K52" s="26" t="n"/>
+      <c r="K52" s="30" t="n"/>
     </row>
     <row r="53" ht="32" customHeight="1" s="60">
       <c r="A53" s="25" t="inlineStr">
@@ -6276,7 +6282,7 @@
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>FN-PAR-04-03-03</t>
+          <t>FN-PAR-04-03-02</t>
         </is>
       </c>
       <c r="C53" s="32" t="inlineStr">
@@ -6286,12 +6292,12 @@
       </c>
       <c r="D53" s="14" t="inlineStr">
         <is>
-          <t>알림 이력 조회</t>
+          <t>KPI 요약</t>
         </is>
       </c>
       <c r="E53" s="14" t="inlineStr">
         <is>
-          <t>알림 이력 테이블</t>
+          <t>KPI 카드</t>
         </is>
       </c>
       <c r="F53" s="14" t="inlineStr">
@@ -6301,7 +6307,7 @@
       </c>
       <c r="G53" s="15" t="inlineStr">
         <is>
-          <t>발송된 위험단계 알림 이력 테이블 — 단계(심각/경고/주의 배지)·지역·내용·일시·민원 수</t>
+          <t>KPI 카드(조회 알림 건수/위험 알림 건수/누적 민원 수) 표시</t>
         </is>
       </c>
       <c r="H53" s="14" t="inlineStr">
@@ -6309,11 +6315,7 @@
           <t>신규</t>
         </is>
       </c>
-      <c r="I53" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="I53" s="14" t="n"/>
       <c r="J53" s="14" t="inlineStr">
         <is>
           <t>O</t>
@@ -6329,272 +6331,272 @@
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
+          <t>FN-PAR-04-03-03</t>
+        </is>
+      </c>
+      <c r="C54" s="32" t="inlineStr">
+        <is>
+          <t>위험단계 알림 조회</t>
+        </is>
+      </c>
+      <c r="D54" s="14" t="inlineStr">
+        <is>
+          <t>알림 이력 조회</t>
+        </is>
+      </c>
+      <c r="E54" s="14" t="inlineStr">
+        <is>
+          <t>알림 이력 테이블</t>
+        </is>
+      </c>
+      <c r="F54" s="14" t="inlineStr">
+        <is>
+          <t>UI-PAR-004-03</t>
+        </is>
+      </c>
+      <c r="G54" s="15" t="inlineStr">
+        <is>
+          <t>발송된 위험단계 알림 이력 테이블 — 단계(심각/경고/주의 배지)·지역·내용·일시·민원 수</t>
+        </is>
+      </c>
+      <c r="H54" s="14" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I54" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J54" s="14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K54" s="26" t="n"/>
+    </row>
+    <row r="55" ht="32" customHeight="1" s="60">
+      <c r="A55" s="25" t="inlineStr">
+        <is>
+          <t>REQ-SFR-003-08</t>
+        </is>
+      </c>
+      <c r="B55" s="14" t="inlineStr">
+        <is>
           <t>FN-PAR-04-04-01</t>
         </is>
       </c>
-      <c r="C54" s="14" t="inlineStr">
+      <c r="C55" s="14" t="inlineStr">
         <is>
           <t>위험단계 알림 관리</t>
         </is>
       </c>
-      <c r="D54" s="14" t="inlineStr">
+      <c r="D55" s="14" t="inlineStr">
         <is>
           <t>알림 기준 설정</t>
         </is>
       </c>
-      <c r="E54" s="14" t="inlineStr">
+      <c r="E55" s="14" t="inlineStr">
         <is>
           <t>단계별 임계값 설정</t>
         </is>
       </c>
-      <c r="F54" s="14" t="inlineStr">
+      <c r="F55" s="14" t="inlineStr">
         <is>
           <t>UI-PAR-004-04</t>
         </is>
       </c>
-      <c r="G54" s="15" t="inlineStr">
+      <c r="G55" s="15" t="inlineStr">
         <is>
           <t>민원 증가율 기준 단계별 알림 기준 카드 — 심각 30%/경고 20%/주의 10% 이상 + 최소 건수 10건 표시. 설정 버튼 → 알림 기준 설정 팝업에서 단계별 증가율(%)·최소 건수 입력 후 저장(서비스 공통 반영, 다음날부터 적용, 민원 건수가 최소 건수 미만이면 알림 미발생)</t>
         </is>
       </c>
-      <c r="H54" s="14" t="inlineStr">
+      <c r="H55" s="14" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I54" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J54" s="14" t="inlineStr">
+      <c r="I55" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J55" s="14" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K54" s="26" t="n"/>
-    </row>
-    <row r="55" ht="32" customHeight="1" s="60">
-      <c r="A55" s="27" t="inlineStr">
+      <c r="K55" s="26" t="n"/>
+    </row>
+    <row r="56" ht="32" customHeight="1" s="60">
+      <c r="A56" s="27" t="inlineStr">
         <is>
           <t>REQ-SFR-003-08</t>
         </is>
       </c>
-      <c r="B55" s="18" t="inlineStr">
+      <c r="B56" s="18" t="inlineStr">
         <is>
           <t>FN-PAR-04-04-02</t>
         </is>
       </c>
-      <c r="C55" s="34" t="inlineStr">
+      <c r="C56" s="34" t="inlineStr">
         <is>
           <t>위험단계 알림 관리</t>
         </is>
       </c>
-      <c r="D55" s="18" t="inlineStr">
+      <c r="D56" s="18" t="inlineStr">
         <is>
           <t>수신자 관리</t>
         </is>
       </c>
-      <c r="E55" s="18" t="inlineStr">
+      <c r="E56" s="18" t="inlineStr">
         <is>
           <t>수신자 목록</t>
         </is>
       </c>
-      <c r="F55" s="18" t="inlineStr">
+      <c r="F56" s="18" t="inlineStr">
         <is>
           <t>UI-PAR-004-04</t>
         </is>
       </c>
-      <c r="G55" s="19" t="inlineStr">
+      <c r="G56" s="19" t="inlineStr">
         <is>
           <t>수신자 목록 및 추가 팝업 — 기본 정보는 로그인 사용자 자동 입력(사용자 목록 불러오기 전환 가능), 지역 다중 추가(+버튼·칩), 알림 단계 누적 선택. 삭제 시 확인 모달</t>
         </is>
       </c>
-      <c r="H55" s="18" t="inlineStr">
+      <c r="H56" s="18" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I55" s="39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J55" s="18" t="inlineStr">
+      <c r="I56" s="39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J56" s="18" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K55" s="28" t="n"/>
-    </row>
-    <row r="56" ht="32" customHeight="1" s="60">
-      <c r="A56" s="23" t="inlineStr">
+      <c r="K56" s="28" t="n"/>
+    </row>
+    <row r="57" ht="32" customHeight="1" s="60">
+      <c r="A57" s="23" t="inlineStr">
         <is>
           <t>REQ-SFR-005-07</t>
         </is>
       </c>
-      <c r="B56" s="16" t="inlineStr">
+      <c r="B57" s="16" t="inlineStr">
         <is>
           <t>FN-PAR-05-01-01</t>
         </is>
       </c>
-      <c r="C56" s="16" t="inlineStr">
+      <c r="C57" s="16" t="inlineStr">
         <is>
           <t>AI 어시스턴트</t>
         </is>
       </c>
-      <c r="D56" s="16" t="inlineStr">
+      <c r="D57" s="16" t="inlineStr">
         <is>
           <t>AI 채팅</t>
         </is>
       </c>
-      <c r="E56" s="16" t="inlineStr">
+      <c r="E57" s="16" t="inlineStr">
         <is>
           <t>질문·답변 인터페이스</t>
         </is>
       </c>
-      <c r="F56" s="16" t="inlineStr">
+      <c r="F57" s="16" t="inlineStr">
         <is>
           <t>UI-PAR-005-01</t>
         </is>
       </c>
-      <c r="G56" s="17" t="inlineStr">
+      <c r="G57" s="17" t="inlineStr">
         <is>
           <t>sLLM 기반 대화형 인터페이스. 인사말 그리팅 표시. 자연어 질의응답·파일 첨부 지원. 행정 정보 검색·민원 분석 요청 처리</t>
         </is>
       </c>
-      <c r="H56" s="16" t="inlineStr">
+      <c r="H57" s="16" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I56" s="16" t="inlineStr">
+      <c r="I57" s="16" t="inlineStr">
         <is>
           <t>sLLM(EXAONE)</t>
         </is>
       </c>
-      <c r="J56" s="16" t="inlineStr">
+      <c r="J57" s="16" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K56" s="24" t="n"/>
-    </row>
-    <row r="57" ht="32" customHeight="1" s="60">
-      <c r="A57" s="25" t="inlineStr">
+      <c r="K57" s="24" t="n"/>
+    </row>
+    <row r="58" ht="32" customHeight="1" s="60">
+      <c r="A58" s="25" t="inlineStr">
         <is>
           <t>REQ-SFR-005-08</t>
         </is>
       </c>
-      <c r="B57" s="14" t="inlineStr">
+      <c r="B58" s="14" t="inlineStr">
         <is>
           <t>FN-PAR-05-01-02</t>
         </is>
       </c>
-      <c r="C57" s="32" t="inlineStr">
+      <c r="C58" s="32" t="inlineStr">
         <is>
           <t>AI 어시스턴트</t>
         </is>
       </c>
-      <c r="D57" s="32" t="inlineStr">
+      <c r="D58" s="32" t="inlineStr">
         <is>
           <t>AI 채팅</t>
         </is>
       </c>
-      <c r="E57" s="14" t="inlineStr">
+      <c r="E58" s="14" t="inlineStr">
         <is>
           <t>조례 검색·RAG 연계 답변</t>
         </is>
       </c>
-      <c r="F57" s="14" t="inlineStr">
+      <c r="F58" s="14" t="inlineStr">
         <is>
           <t>UI-PAR-005-01</t>
         </is>
       </c>
-      <c r="G57" s="15" t="inlineStr">
+      <c r="G58" s="15" t="inlineStr">
         <is>
           <t>민원 관련 행정 정보(조례 등) RAG 기반 검색 및 답변 생성. 조례명·원문 보기 링크 카드 형태 응답</t>
         </is>
       </c>
-      <c r="H57" s="14" t="inlineStr">
+      <c r="H58" s="14" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I57" s="14" t="inlineStr">
+      <c r="I58" s="14" t="inlineStr">
         <is>
           <t>RAG·Vector DB</t>
         </is>
       </c>
-      <c r="J57" s="14" t="inlineStr">
+      <c r="J58" s="14" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K57" s="26" t="n"/>
-    </row>
-    <row r="58" ht="32" customHeight="1" s="60">
-      <c r="A58" s="41" t="inlineStr">
-        <is>
-          <t>REQ-SFR-005-09</t>
-        </is>
-      </c>
-      <c r="B58" s="42" t="inlineStr">
-        <is>
-          <t>FN-PAR-05-05</t>
-        </is>
-      </c>
-      <c r="C58" s="57" t="inlineStr">
-        <is>
-          <t>AI 어시스턴트</t>
-        </is>
-      </c>
-      <c r="D58" s="32" t="inlineStr">
-        <is>
-          <t>AI 채팅</t>
-        </is>
-      </c>
-      <c r="E58" s="42" t="inlineStr">
-        <is>
-          <t>대량 민원 자동 요약</t>
-        </is>
-      </c>
-      <c r="F58" s="42" t="inlineStr">
-        <is>
-          <t>UI-PAR-005-02</t>
-        </is>
-      </c>
-      <c r="G58" s="43" t="inlineStr">
-        <is>
-          <t>대량 민원 내용을 sLLM으로 자동 요약하여 보고용 리포트 생성. AI 응답 하단 리포트 생성 버튼 제공</t>
-        </is>
-      </c>
-      <c r="H58" s="42" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I58" s="42" t="inlineStr">
-        <is>
-          <t>sLLM(EXAONE)</t>
-        </is>
-      </c>
-      <c r="J58" s="42" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K58" s="44" t="n"/>
+      <c r="K58" s="26" t="n"/>
     </row>
     <row r="59" ht="32" customHeight="1" s="60">
       <c r="A59" s="41" t="inlineStr">
         <is>
-          <t>REQ-SFR-005-05</t>
+          <t>REQ-SFR-005-09</t>
         </is>
       </c>
       <c r="B59" s="42" t="inlineStr">
         <is>
-          <t>FN-PAR-05-06</t>
+          <t>FN-PAR-05-05</t>
         </is>
       </c>
       <c r="C59" s="57" t="inlineStr">
@@ -6609,17 +6611,17 @@
       </c>
       <c r="E59" s="42" t="inlineStr">
         <is>
-          <t>리포트 미리보기·다운로드</t>
+          <t>대량 민원 자동 요약</t>
         </is>
       </c>
       <c r="F59" s="42" t="inlineStr">
         <is>
-          <t>UI-PAR-005-03</t>
+          <t>UI-PAR-005-02</t>
         </is>
       </c>
       <c r="G59" s="43" t="inlineStr">
         <is>
-          <t>AI 생성 민원 요약 보고서 미리보기 및 다운로드(PDF/DOCX)</t>
+          <t>대량 민원 내용을 sLLM으로 자동 요약하여 보고용 리포트 생성. AI 응답 하단 리포트 생성 버튼 제공</t>
         </is>
       </c>
       <c r="H59" s="42" t="inlineStr">
@@ -6629,7 +6631,7 @@
       </c>
       <c r="I59" s="42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>sLLM(EXAONE)</t>
         </is>
       </c>
       <c r="J59" s="42" t="inlineStr">
@@ -6642,271 +6644,267 @@
     <row r="60" ht="31" customHeight="1" s="60">
       <c r="A60" s="41" t="inlineStr">
         <is>
+          <t>REQ-SFR-005-05</t>
+        </is>
+      </c>
+      <c r="B60" s="42" t="inlineStr">
+        <is>
+          <t>FN-PAR-05-06</t>
+        </is>
+      </c>
+      <c r="C60" s="57" t="inlineStr">
+        <is>
+          <t>AI 어시스턴트</t>
+        </is>
+      </c>
+      <c r="D60" s="32" t="inlineStr">
+        <is>
+          <t>AI 채팅</t>
+        </is>
+      </c>
+      <c r="E60" s="42" t="inlineStr">
+        <is>
+          <t>리포트 미리보기·다운로드</t>
+        </is>
+      </c>
+      <c r="F60" s="42" t="inlineStr">
+        <is>
+          <t>UI-PAR-005-03</t>
+        </is>
+      </c>
+      <c r="G60" s="43" t="inlineStr">
+        <is>
+          <t>AI 생성 민원 요약 보고서 미리보기 및 다운로드(PDF/DOCX)</t>
+        </is>
+      </c>
+      <c r="H60" s="42" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I60" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J60" s="42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K60" s="44" t="n"/>
+    </row>
+    <row r="61" ht="31" customHeight="1" s="60">
+      <c r="A61" s="41" t="inlineStr">
+        <is>
           <t>REQ-SFR-005-01</t>
         </is>
       </c>
-      <c r="B60" s="42" t="inlineStr">
+      <c r="B61" s="42" t="inlineStr">
         <is>
           <t>FN-PAR-05-07</t>
         </is>
       </c>
-      <c r="C60" s="57" t="inlineStr">
+      <c r="C61" s="57" t="inlineStr">
         <is>
           <t>AI 어시스턴트</t>
         </is>
       </c>
-      <c r="D60" s="32" t="inlineStr">
+      <c r="D61" s="32" t="inlineStr">
         <is>
           <t>AI 채팅</t>
         </is>
       </c>
-      <c r="E60" s="42" t="inlineStr">
+      <c r="E61" s="42" t="inlineStr">
         <is>
           <t>융합 데이터 통합 분석 답변</t>
         </is>
       </c>
-      <c r="F60" s="42" t="inlineStr">
+      <c r="F61" s="42" t="inlineStr">
         <is>
           <t>UI-PAR-005-04</t>
         </is>
       </c>
-      <c r="G60" s="43" t="inlineStr">
+      <c r="G61" s="43" t="inlineStr">
         <is>
           <t>민원 데이터와 감시(화재·안전) 데이터를 결합해야 답이 나오는 질문에 AI 에이전트를 호출, 융합 데이터에서 종합 인사이트를 도출하여 AI 어시스턴트 답변으로 표시. 리포트 생성 버튼 제공</t>
         </is>
       </c>
-      <c r="H60" s="42" t="inlineStr">
+      <c r="H61" s="42" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I60" s="42" t="inlineStr">
+      <c r="I61" s="42" t="inlineStr">
         <is>
           <t>AI 에이전트</t>
         </is>
       </c>
-      <c r="J60" s="42" t="inlineStr">
+      <c r="J61" s="42" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K60" s="44" t="n"/>
-    </row>
-    <row r="61" ht="31" customHeight="1" s="60">
-      <c r="A61" s="25" t="inlineStr">
-        <is>
-          <t>REQ-SFR-005-07</t>
-        </is>
-      </c>
-      <c r="B61" s="14" t="inlineStr">
-        <is>
-          <t>FN-PAR-05-02</t>
-        </is>
-      </c>
-      <c r="C61" s="32" t="inlineStr">
-        <is>
-          <t>AI 어시스턴트</t>
-        </is>
-      </c>
-      <c r="D61" s="14" t="inlineStr">
-        <is>
-          <t>최근 대화</t>
-        </is>
-      </c>
-      <c r="E61" s="14" t="inlineStr">
-        <is>
-          <t>대화 이력 목록</t>
-        </is>
-      </c>
-      <c r="F61" s="14" t="inlineStr">
-        <is>
-          <t>UI-PAR-005-01</t>
-        </is>
-      </c>
-      <c r="G61" s="15" t="inlineStr">
-        <is>
-          <t>최근 대화 목록(제목·일시) — 항목 클릭 시 대화 재개, 새 대화 버튼, 행별 X 삭제(확인 모달)</t>
-        </is>
-      </c>
-      <c r="H61" s="14" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I61" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J61" s="14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K61" s="26" t="n"/>
+      <c r="K61" s="44" t="n"/>
     </row>
     <row r="62" ht="31" customHeight="1" s="60">
       <c r="A62" s="25" t="inlineStr">
         <is>
+          <t>REQ-SFR-005-07</t>
+        </is>
+      </c>
+      <c r="B62" s="14" t="inlineStr">
+        <is>
+          <t>FN-PAR-05-02</t>
+        </is>
+      </c>
+      <c r="C62" s="32" t="inlineStr">
+        <is>
+          <t>AI 어시스턴트</t>
+        </is>
+      </c>
+      <c r="D62" s="14" t="inlineStr">
+        <is>
+          <t>최근 대화</t>
+        </is>
+      </c>
+      <c r="E62" s="14" t="inlineStr">
+        <is>
+          <t>대화 이력 목록</t>
+        </is>
+      </c>
+      <c r="F62" s="14" t="inlineStr">
+        <is>
+          <t>UI-PAR-005-01</t>
+        </is>
+      </c>
+      <c r="G62" s="15" t="inlineStr">
+        <is>
+          <t>최근 대화 목록(제목·일시) — 항목 클릭 시 대화 재개, 새 대화 버튼, 행별 X 삭제(확인 모달)</t>
+        </is>
+      </c>
+      <c r="H62" s="14" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I62" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J62" s="14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K62" s="26" t="n"/>
+    </row>
+    <row r="63" ht="31" customHeight="1" s="60">
+      <c r="A63" s="25" t="inlineStr">
+        <is>
           <t>REQ-SFR-005-09</t>
         </is>
       </c>
-      <c r="B62" s="14" t="inlineStr">
+      <c r="B63" s="14" t="inlineStr">
         <is>
           <t>FN-PAR-05-03</t>
         </is>
       </c>
-      <c r="C62" s="32" t="inlineStr">
+      <c r="C63" s="32" t="inlineStr">
         <is>
           <t>AI 어시스턴트</t>
         </is>
       </c>
-      <c r="D62" s="14" t="inlineStr">
+      <c r="D63" s="14" t="inlineStr">
         <is>
           <t>최근 리포트</t>
         </is>
       </c>
-      <c r="E62" s="14" t="inlineStr">
+      <c r="E63" s="14" t="inlineStr">
         <is>
           <t>리포트 목록 및 다운로드</t>
         </is>
       </c>
-      <c r="F62" s="14" t="inlineStr">
+      <c r="F63" s="14" t="inlineStr">
         <is>
           <t>UI-PAR-005-01</t>
         </is>
       </c>
-      <c r="G62" s="15" t="inlineStr">
+      <c r="G63" s="15" t="inlineStr">
         <is>
           <t>AI 생성 민원 요약 리포트 목록(제목·날짜) 조회 및 개별 다운로드(↓) 기능</t>
         </is>
       </c>
-      <c r="H62" s="14" t="inlineStr">
+      <c r="H63" s="14" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I62" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J62" s="14" t="inlineStr">
+      <c r="I63" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J63" s="14" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K62" s="26" t="n"/>
-    </row>
-    <row r="63" ht="31" customHeight="1" s="60">
-      <c r="A63" s="50" t="inlineStr">
+      <c r="K63" s="26" t="n"/>
+    </row>
+    <row r="64" ht="31" customHeight="1" s="60">
+      <c r="A64" s="50" t="inlineStr">
         <is>
           <t>REQ-SFR-005-07</t>
         </is>
       </c>
-      <c r="B63" s="51" t="inlineStr">
+      <c r="B64" s="51" t="inlineStr">
         <is>
           <t>FN-PAR-05-04</t>
         </is>
       </c>
-      <c r="C63" s="52" t="inlineStr">
+      <c r="C64" s="52" t="inlineStr">
         <is>
           <t>AI 어시스턴트</t>
         </is>
       </c>
-      <c r="D63" s="51" t="inlineStr">
+      <c r="D64" s="51" t="inlineStr">
         <is>
           <t>자주 하는 질문(FAQ)</t>
         </is>
       </c>
-      <c r="E63" s="51" t="inlineStr">
+      <c r="E64" s="51" t="inlineStr">
         <is>
           <t>FAQ 목록</t>
         </is>
       </c>
-      <c r="F63" s="14" t="inlineStr">
+      <c r="F64" s="14" t="inlineStr">
         <is>
           <t>UI-PAR-005-01</t>
         </is>
       </c>
-      <c r="G63" s="53" t="inlineStr">
+      <c r="G64" s="53" t="inlineStr">
         <is>
           <t>이번 달 민원 현황 요약·불법주차 단속 관련 행정 절차·공유주차제 도입 요건 등 자주 사용 질문 목록. 클릭 시 입력창 자동 입력</t>
         </is>
       </c>
-      <c r="H63" s="51" t="inlineStr">
+      <c r="H64" s="51" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I63" s="54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J63" s="51" t="inlineStr">
+      <c r="I64" s="54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J64" s="51" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K63" s="55" t="n"/>
-    </row>
-    <row r="64" ht="31" customHeight="1" s="60">
-      <c r="A64" s="41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B64" s="42" t="inlineStr">
-        <is>
-          <t>FN-PAR-06-01</t>
-        </is>
-      </c>
-      <c r="C64" s="32" t="inlineStr">
-        <is>
-          <t>설정</t>
-        </is>
-      </c>
-      <c r="D64" s="42" t="inlineStr">
-        <is>
-          <t>메뉴 권한 관리</t>
-        </is>
-      </c>
-      <c r="E64" s="42" t="inlineStr">
-        <is>
-          <t>메뉴별 권한 그룹 지정</t>
-        </is>
-      </c>
-      <c r="F64" s="42" t="inlineStr">
-        <is>
-          <t>UI-PAR-006-01</t>
-        </is>
-      </c>
-      <c r="G64" s="43" t="inlineStr">
-        <is>
-          <t>메뉴별 권한 그룹 지정 — 시스템 관리자 항상 허용(해제 불가), 일반 사용자는 관리 메뉴 부여 불가, 서비스 관리자 해제 시 일반 사용자 동시 해제</t>
-        </is>
-      </c>
-      <c r="H64" s="42" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I64" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J64" s="42" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K64" s="44" t="inlineStr">
-        <is>
-          <t>관리자</t>
-        </is>
-      </c>
+      <c r="K64" s="55" t="n"/>
     </row>
     <row r="65" ht="31" customHeight="1" s="60">
       <c r="A65" s="41" t="inlineStr">
@@ -6916,10 +6914,10 @@
       </c>
       <c r="B65" s="42" t="inlineStr">
         <is>
-          <t>FN-PAR-06-02</t>
-        </is>
-      </c>
-      <c r="C65" s="31" t="inlineStr">
+          <t>FN-PAR-06-01</t>
+        </is>
+      </c>
+      <c r="C65" s="32" t="inlineStr">
         <is>
           <t>설정</t>
         </is>
@@ -6931,7 +6929,7 @@
       </c>
       <c r="E65" s="42" t="inlineStr">
         <is>
-          <t>권한 저장</t>
+          <t>메뉴별 권한 그룹 지정</t>
         </is>
       </c>
       <c r="F65" s="42" t="inlineStr">
@@ -6941,7 +6939,7 @@
       </c>
       <c r="G65" s="43" t="inlineStr">
         <is>
-          <t>메뉴별 권한 설정 저장(메뉴 단위 저장)</t>
+          <t>메뉴별 권한 그룹 지정 — 시스템 관리자 항상 허용(해제 불가), 일반 사용자는 관리 메뉴 부여 불가, 서비스 관리자 해제 시 일반 사용자 동시 해제</t>
         </is>
       </c>
       <c r="H65" s="42" t="inlineStr">
@@ -6968,12 +6966,12 @@
     <row r="66" ht="45" customHeight="1" s="60">
       <c r="A66" s="41" t="inlineStr">
         <is>
-          <t>REQ-SFR-005-10</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B66" s="42" t="inlineStr">
         <is>
-          <t>FN-PAR-06-03</t>
+          <t>FN-PAR-06-02</t>
         </is>
       </c>
       <c r="C66" s="31" t="inlineStr">
@@ -6983,22 +6981,22 @@
       </c>
       <c r="D66" s="42" t="inlineStr">
         <is>
-          <t>분석 지표 가중치 설정</t>
+          <t>메뉴 권한 관리</t>
         </is>
       </c>
       <c r="E66" s="42" t="inlineStr">
         <is>
-          <t>종합점수 가중치</t>
+          <t>권한 저장</t>
         </is>
       </c>
       <c r="F66" s="42" t="inlineStr">
         <is>
-          <t>UI-PAR-006-02</t>
+          <t>UI-PAR-006-01</t>
         </is>
       </c>
       <c r="G66" s="43" t="inlineStr">
         <is>
-          <t>집중구역 분석/구역 추천/투자·보강 우선순위 3개 모델의 가중치 조정(합 100% 검증)</t>
+          <t>메뉴별 권한 설정 저장(메뉴 단위 저장)</t>
         </is>
       </c>
       <c r="H66" s="42" t="inlineStr">
@@ -7030,7 +7028,7 @@
       </c>
       <c r="B67" s="42" t="inlineStr">
         <is>
-          <t>FN-PAR-06-04</t>
+          <t>FN-PAR-06-03</t>
         </is>
       </c>
       <c r="C67" s="31" t="inlineStr">
@@ -7045,7 +7043,7 @@
       </c>
       <c r="E67" s="42" t="inlineStr">
         <is>
-          <t>설정 변경 이력</t>
+          <t>종합점수 가중치</t>
         </is>
       </c>
       <c r="F67" s="42" t="inlineStr">
@@ -7055,7 +7053,7 @@
       </c>
       <c r="G67" s="43" t="inlineStr">
         <is>
-          <t>변경일시, 변경자, 변경 항목, 변경 내용에 대한 목록 조회</t>
+          <t>집중구역 분석/구역 추천/투자·보강 우선순위 3개 모델의 가중치 조정(합 100% 검증)</t>
         </is>
       </c>
       <c r="H67" s="42" t="inlineStr">
@@ -7087,107 +7085,107 @@
       </c>
       <c r="B68" s="42" t="inlineStr">
         <is>
+          <t>FN-PAR-06-04</t>
+        </is>
+      </c>
+      <c r="C68" s="31" t="inlineStr">
+        <is>
+          <t>설정</t>
+        </is>
+      </c>
+      <c r="D68" s="42" t="inlineStr">
+        <is>
+          <t>분석 지표 가중치 설정</t>
+        </is>
+      </c>
+      <c r="E68" s="42" t="inlineStr">
+        <is>
+          <t>설정 변경 이력</t>
+        </is>
+      </c>
+      <c r="F68" s="42" t="inlineStr">
+        <is>
+          <t>UI-PAR-006-02</t>
+        </is>
+      </c>
+      <c r="G68" s="43" t="inlineStr">
+        <is>
+          <t>변경일시, 변경자, 변경 항목, 변경 내용에 대한 목록 조회</t>
+        </is>
+      </c>
+      <c r="H68" s="42" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I68" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J68" s="42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K68" s="44" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="30" customHeight="1" s="60">
+      <c r="A69" s="41" t="inlineStr">
+        <is>
+          <t>REQ-SFR-005-10</t>
+        </is>
+      </c>
+      <c r="B69" s="42" t="inlineStr">
+        <is>
           <t>FN-PAR-06-05</t>
         </is>
       </c>
-      <c r="C68" s="31" t="inlineStr">
+      <c r="C69" s="31" t="inlineStr">
         <is>
           <t>설정</t>
         </is>
       </c>
-      <c r="D68" s="42" t="inlineStr">
+      <c r="D69" s="42" t="inlineStr">
         <is>
           <t>분석 지표 가중치 설정</t>
         </is>
       </c>
-      <c r="E68" s="42" t="inlineStr">
+      <c r="E69" s="42" t="inlineStr">
         <is>
           <t>기본값 초기화</t>
         </is>
       </c>
-      <c r="F68" s="42" t="inlineStr">
+      <c r="F69" s="42" t="inlineStr">
         <is>
           <t>UI-PAR-006-02</t>
         </is>
       </c>
-      <c r="G68" s="43" t="inlineStr">
+      <c r="G69" s="43" t="inlineStr">
         <is>
           <t>기존 종합점수 가중치로 초기화</t>
         </is>
       </c>
-      <c r="H68" s="42" t="inlineStr">
+      <c r="H69" s="42" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I68" s="42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J68" s="42" t="inlineStr">
+      <c r="I69" s="42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J69" s="42" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K68" s="44" t="inlineStr">
-        <is>
-          <t>관리자</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="30" customHeight="1" s="60">
-      <c r="A69" s="48" t="inlineStr">
-        <is>
-          <t>REQ-SFR-005-10</t>
-        </is>
-      </c>
-      <c r="B69" s="46" t="inlineStr">
-        <is>
-          <t>FN-PAR-06-06</t>
-        </is>
-      </c>
-      <c r="C69" s="33" t="inlineStr">
-        <is>
-          <t>설정</t>
-        </is>
-      </c>
-      <c r="D69" s="46" t="inlineStr">
-        <is>
-          <t>분석 지표 가중치 설정</t>
-        </is>
-      </c>
-      <c r="E69" s="46" t="inlineStr">
-        <is>
-          <t>설정 저장</t>
-        </is>
-      </c>
-      <c r="F69" s="46" t="inlineStr">
-        <is>
-          <t>UI-PAR-006-02</t>
-        </is>
-      </c>
-      <c r="G69" s="47" t="inlineStr">
-        <is>
-          <t>변경한 가중치 설정 저장 버튼</t>
-        </is>
-      </c>
-      <c r="H69" s="46" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I69" s="46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J69" s="46" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K69" s="49" t="inlineStr">
+      <c r="K69" s="44" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
@@ -7196,37 +7194,37 @@
     <row r="70" ht="31" customHeight="1" s="60" thickBot="1">
       <c r="A70" s="48" t="inlineStr">
         <is>
-          <t>REQ-SFR-003-07</t>
+          <t>REQ-SFR-005-10</t>
         </is>
       </c>
       <c r="B70" s="46" t="inlineStr">
         <is>
-          <t>FN-PAR-C01-04</t>
-        </is>
-      </c>
-      <c r="C70" s="58" t="inlineStr">
-        <is>
-          <t>공통</t>
+          <t>FN-PAR-06-06</t>
+        </is>
+      </c>
+      <c r="C70" s="33" t="inlineStr">
+        <is>
+          <t>설정</t>
         </is>
       </c>
       <c r="D70" s="46" t="inlineStr">
         <is>
-          <t>데이터 기준일 안내</t>
+          <t>분석 지표 가중치 설정</t>
         </is>
       </c>
       <c r="E70" s="46" t="inlineStr">
         <is>
-          <t>데이터 기준일 팝오버</t>
+          <t>설정 저장</t>
         </is>
       </c>
       <c r="F70" s="46" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>UI-PAR-006-02</t>
         </is>
       </c>
       <c r="G70" s="47" t="inlineStr">
         <is>
-          <t>헤더 '최근 갱신' 문구의 ⓘ 호버 시 데이터별 기준일·갱신 주기 팝오버 표시(민원 3종·단속·공영주차장)</t>
+          <t>변경한 가중치 설정 저장 버튼</t>
         </is>
       </c>
       <c r="H70" s="46" t="inlineStr">
@@ -7246,168 +7244,168 @@
       </c>
       <c r="K70" s="49" t="inlineStr">
         <is>
-          <t>대시보드·민원현황</t>
+          <t>관리자</t>
         </is>
       </c>
     </row>
     <row r="71" ht="30" customHeight="1" s="60">
       <c r="A71" s="48" t="inlineStr">
         <is>
+          <t>REQ-SFR-003-07</t>
+        </is>
+      </c>
+      <c r="B71" s="46" t="inlineStr">
+        <is>
+          <t>FN-PAR-C01-04</t>
+        </is>
+      </c>
+      <c r="C71" s="58" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="D71" s="46" t="inlineStr">
+        <is>
+          <t>데이터 기준일 안내</t>
+        </is>
+      </c>
+      <c r="E71" s="46" t="inlineStr">
+        <is>
+          <t>데이터 기준일 팝오버</t>
+        </is>
+      </c>
+      <c r="F71" s="46" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="G71" s="47" t="inlineStr">
+        <is>
+          <t>헤더 '최근 갱신' 문구의 ⓘ 호버 시 데이터별 기준일·갱신 주기 팝오버 표시(민원 3종·단속·공영주차장)</t>
+        </is>
+      </c>
+      <c r="H71" s="46" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I71" s="46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J71" s="46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K71" s="49" t="inlineStr">
+        <is>
+          <t>대시보드·민원현황</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="45" customHeight="1" s="60">
+      <c r="A72" s="48" t="inlineStr">
+        <is>
           <t>REQ-SFR-003-10</t>
         </is>
       </c>
-      <c r="B71" s="46" t="inlineStr">
+      <c r="B72" s="46" t="inlineStr">
         <is>
           <t>FN-PAR-C01-05</t>
         </is>
       </c>
-      <c r="C71" s="58" t="inlineStr">
+      <c r="C72" s="58" t="inlineStr">
         <is>
           <t>공통</t>
         </is>
       </c>
-      <c r="D71" s="46" t="inlineStr">
+      <c r="D72" s="46" t="inlineStr">
         <is>
           <t>삭제 확인</t>
         </is>
       </c>
-      <c r="E71" s="46" t="inlineStr">
+      <c r="E72" s="46" t="inlineStr">
         <is>
           <t>삭제 확인 모달</t>
         </is>
       </c>
-      <c r="F71" s="46" t="inlineStr">
+      <c r="F72" s="46" t="inlineStr">
         <is>
           <t>공통</t>
         </is>
       </c>
-      <c r="G71" s="47" t="inlineStr">
+      <c r="G72" s="47" t="inlineStr">
         <is>
           <t>모든 삭제 동작(시나리오·보고서·자동 생성 설정·수신자·최근 대화)에 확인 모달 적용 — '삭제하면 되돌릴 수 없습니다' 경고 및 취소/삭제 버튼</t>
         </is>
       </c>
-      <c r="H71" s="46" t="inlineStr">
+      <c r="H72" s="46" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I71" s="46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J71" s="46" t="inlineStr">
+      <c r="I72" s="46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J72" s="46" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K71" s="49" t="n"/>
-    </row>
-    <row r="72" ht="45" customHeight="1" s="60">
-      <c r="A72" s="29" t="inlineStr">
+      <c r="K72" s="49" t="n"/>
+    </row>
+    <row r="73" ht="30" customHeight="1" s="60">
+      <c r="A73" s="29" t="inlineStr">
         <is>
           <t>REQ-SFR-003-14</t>
         </is>
       </c>
-      <c r="B72" s="20" t="inlineStr">
+      <c r="B73" s="20" t="inlineStr">
         <is>
           <t>FN-PAR-SYS-01</t>
         </is>
       </c>
-      <c r="C72" s="20" t="n"/>
-      <c r="D72" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E72" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F72" s="20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G72" s="45" t="inlineStr">
+      <c r="C73" s="20" t="n"/>
+      <c r="D73" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E73" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F73" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G73" s="45" t="inlineStr">
         <is>
           <t>분석 모델 재학습은 AI 어시스턴트(sLLM+RAG) 학습으로 대체 수행. 신규 민원 유형·정책 변화·도시 환경 변화 발생 시 조례·정책문서 재색인(Vector DB 갱신), 첨부문서 학습, 대화 이력·FAQ 축적을 통해 지속 고도화. 모델 개선 프로세스는 AI 어시스턴트 운영 절차에 포함</t>
         </is>
       </c>
-      <c r="H72" s="20" t="inlineStr">
+      <c r="H73" s="20" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I72" s="20" t="inlineStr">
+      <c r="I73" s="20" t="inlineStr">
         <is>
           <t>sLLM(EXAONE)·RAG·Vector DB</t>
         </is>
       </c>
-      <c r="J72" s="20" t="inlineStr">
+      <c r="J73" s="20" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K72" s="30" t="inlineStr">
-        <is>
-          <t>비화면</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="30" customHeight="1" s="60">
-      <c r="A73" s="25" t="inlineStr">
-        <is>
-          <t>REQ-SFR-005-02</t>
-        </is>
-      </c>
-      <c r="B73" s="14" t="inlineStr">
-        <is>
-          <t>FN-PAR-SYS-02</t>
-        </is>
-      </c>
-      <c r="C73" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D73" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E73" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F73" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G73" s="35" t="inlineStr">
-        <is>
-          <t>D-hub에 적제된 통합데이터 활용하여 민원 3종 이상·정책행정문서 12종 이상 데이터의 수집→정제→구조화→적용 전 과정 관리. 데이터 유형별 적용 목적·활용 시나리오 관리</t>
-        </is>
-      </c>
-      <c r="H73" s="14" t="inlineStr">
-        <is>
-          <t>신규</t>
-        </is>
-      </c>
-      <c r="I73" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J73" s="14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K73" s="26" t="inlineStr">
+      <c r="K73" s="30" t="inlineStr">
         <is>
           <t>비화면</t>
         </is>
@@ -7416,12 +7414,12 @@
     <row r="74" ht="30" customHeight="1" s="60">
       <c r="A74" s="25" t="inlineStr">
         <is>
-          <t>REQ-SFR-005-03</t>
+          <t>REQ-SFR-005-02</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>FN-PAR-SYS-03</t>
+          <t>FN-PAR-SYS-02</t>
         </is>
       </c>
       <c r="C74" s="14" t="inlineStr">
@@ -7446,7 +7444,7 @@
       </c>
       <c r="G74" s="35" t="inlineStr">
         <is>
-          <t>비정형 문서·스캔 문서·이미지 기반 행정자료를 AI RPA로 자동 수집하고 AI OCR로 텍스트 추출·정형화·구조화 적재</t>
+          <t>D-hub에 적제된 통합데이터 활용하여 민원 3종 이상·정책행정문서 12종 이상 데이터의 수집→정제→구조화→적용 전 과정 관리. 데이터 유형별 적용 목적·활용 시나리오 관리</t>
         </is>
       </c>
       <c r="H74" s="14" t="inlineStr">
@@ -7454,9 +7452,9 @@
           <t>신규</t>
         </is>
       </c>
-      <c r="I74" s="14" t="inlineStr">
-        <is>
-          <t>AI RPA·AI OCR</t>
+      <c r="I74" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="J74" s="14" t="inlineStr">
@@ -7473,112 +7471,169 @@
     <row r="75" ht="30" customHeight="1" s="60">
       <c r="A75" s="25" t="inlineStr">
         <is>
+          <t>REQ-SFR-005-03</t>
+        </is>
+      </c>
+      <c r="B75" s="14" t="inlineStr">
+        <is>
+          <t>FN-PAR-SYS-03</t>
+        </is>
+      </c>
+      <c r="C75" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D75" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E75" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F75" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G75" s="35" t="inlineStr">
+        <is>
+          <t>비정형 문서·스캔 문서·이미지 기반 행정자료를 AI RPA로 자동 수집하고 AI OCR로 텍스트 추출·정형화·구조화 적재</t>
+        </is>
+      </c>
+      <c r="H75" s="14" t="inlineStr">
+        <is>
+          <t>신규</t>
+        </is>
+      </c>
+      <c r="I75" s="14" t="inlineStr">
+        <is>
+          <t>AI RPA·AI OCR</t>
+        </is>
+      </c>
+      <c r="J75" s="14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K75" s="26" t="inlineStr">
+        <is>
+          <t>비화면</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="30" customHeight="1" s="60">
+      <c r="A76" s="25" t="inlineStr">
+        <is>
           <t>REQ-SFR-005-01</t>
         </is>
       </c>
-      <c r="B75" s="14" t="inlineStr">
+      <c r="B76" s="14" t="inlineStr">
         <is>
           <t>FN-PAR-SYS-04</t>
         </is>
       </c>
-      <c r="C75" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D75" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E75" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F75" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G75" s="35" t="inlineStr">
+      <c r="C76" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D76" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E76" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F76" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G76" s="35" t="inlineStr">
         <is>
           <t>민원 분석 대응 솔루션과 실시간 공영주차장 감시 대응 솔루션의 수집·분석 데이터를 결합·융합하여 상관관계 분석 및 종합 인사이트 도출. 대시보드·보고서로 반영</t>
         </is>
       </c>
-      <c r="H75" s="14" t="inlineStr">
+      <c r="H76" s="14" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I75" s="38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J75" s="14" t="inlineStr">
+      <c r="I76" s="38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J76" s="14" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K75" s="26" t="inlineStr">
+      <c r="K76" s="26" t="inlineStr">
         <is>
           <t>비화면</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="30" customHeight="1" s="60">
-      <c r="A76" s="27" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="27" t="inlineStr">
         <is>
           <t>REQ-SFR-005-10</t>
         </is>
       </c>
-      <c r="B76" s="18" t="inlineStr">
+      <c r="B77" s="18" t="inlineStr">
         <is>
           <t>FN-PAR-SYS-05</t>
         </is>
       </c>
-      <c r="C76" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D76" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E76" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F76" s="18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G76" s="36" t="inlineStr">
+      <c r="C77" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D77" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E77" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F77" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G77" s="36" t="inlineStr">
         <is>
           <t>타 지자체 확산 적용을 위해 데이터 구조·분석 지표·가중치·기능 구성을 지역 여건에 맞게 설정·조정. 오픈 소스 활용. 공통코드 및 지표 가중치 관리</t>
         </is>
       </c>
-      <c r="H76" s="18" t="inlineStr">
+      <c r="H77" s="18" t="inlineStr">
         <is>
           <t>신규</t>
         </is>
       </c>
-      <c r="I76" s="39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J76" s="18" t="inlineStr">
+      <c r="I77" s="39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J77" s="18" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="K76" s="28" t="inlineStr">
+      <c r="K77" s="28" t="inlineStr">
         <is>
           <t>비화면</t>
         </is>

--- a/Audit/JJ_PD_IP_A02_기능구조도_v1.5_이노팸.xlsx
+++ b/Audit/JJ_PD_IP_A02_기능구조도_v1.5_이노팸.xlsx
@@ -1462,7 +1462,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="5"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
@@ -1715,6 +1715,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="5"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="5">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3020,8 +3024,8 @@
     <col width="10.5" customWidth="1" style="63" min="9" max="9"/>
     <col width="8.33203125" customWidth="1" style="63" min="10" max="10"/>
     <col width="7.1640625" customWidth="1" style="63" min="11" max="11"/>
-    <col width="9" customWidth="1" style="63" min="12" max="14"/>
-    <col width="9" customWidth="1" style="63" min="15" max="16384"/>
+    <col width="9" customWidth="1" style="63" min="12" max="15"/>
+    <col width="9" customWidth="1" style="63" min="16" max="16384"/>
   </cols>
   <sheetData>
     <row r="2" ht="27.5" customHeight="1" s="60">
@@ -3178,8 +3182,8 @@
     <col width="8.5" customWidth="1" style="76" min="2" max="2"/>
     <col width="45.5" customWidth="1" style="76" min="3" max="3"/>
     <col width="8.33203125" customWidth="1" style="76" min="4" max="5"/>
-    <col width="9" customWidth="1" style="76" min="6" max="8"/>
-    <col width="9" customWidth="1" style="76" min="9" max="16384"/>
+    <col width="9" customWidth="1" style="76" min="6" max="9"/>
+    <col width="9" customWidth="1" style="76" min="10" max="16384"/>
   </cols>
   <sheetData>
     <row r="2" ht="26.25" customHeight="1" s="60">
@@ -3390,133 +3394,133 @@
       <c r="E11" s="3" t="n"/>
     </row>
     <row r="12" ht="24.75" customHeight="1" s="60">
-      <c r="A12" s="77" t="n"/>
+      <c r="A12" s="78" t="n"/>
       <c r="B12" s="3" t="n"/>
       <c r="C12" s="3" t="n"/>
       <c r="D12" s="3" t="n"/>
       <c r="E12" s="3" t="n"/>
     </row>
     <row r="13" ht="24.75" customHeight="1" s="60">
-      <c r="A13" s="77" t="n"/>
+      <c r="A13" s="78" t="n"/>
       <c r="B13" s="3" t="n"/>
       <c r="C13" s="3" t="n"/>
       <c r="D13" s="3" t="n"/>
       <c r="E13" s="3" t="n"/>
     </row>
     <row r="14" ht="24.75" customHeight="1" s="60">
-      <c r="A14" s="77" t="n"/>
+      <c r="A14" s="78" t="n"/>
       <c r="B14" s="3" t="n"/>
       <c r="C14" s="3" t="n"/>
       <c r="D14" s="3" t="n"/>
       <c r="E14" s="3" t="n"/>
     </row>
     <row r="15" ht="24.75" customHeight="1" s="60">
-      <c r="A15" s="77" t="n"/>
+      <c r="A15" s="78" t="n"/>
       <c r="B15" s="3" t="n"/>
       <c r="C15" s="3" t="n"/>
       <c r="D15" s="3" t="n"/>
       <c r="E15" s="3" t="n"/>
     </row>
     <row r="16" ht="24.75" customHeight="1" s="60">
-      <c r="A16" s="77" t="n"/>
+      <c r="A16" s="78" t="n"/>
       <c r="B16" s="3" t="n"/>
       <c r="C16" s="3" t="n"/>
       <c r="D16" s="3" t="n"/>
       <c r="E16" s="3" t="n"/>
     </row>
     <row r="17" ht="24.75" customHeight="1" s="60">
-      <c r="A17" s="77" t="n"/>
+      <c r="A17" s="78" t="n"/>
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="n"/>
       <c r="D17" s="3" t="n"/>
       <c r="E17" s="3" t="n"/>
     </row>
     <row r="18" ht="24.75" customHeight="1" s="60">
-      <c r="A18" s="77" t="n"/>
+      <c r="A18" s="78" t="n"/>
       <c r="B18" s="3" t="n"/>
       <c r="C18" s="3" t="n"/>
       <c r="D18" s="3" t="n"/>
       <c r="E18" s="3" t="n"/>
     </row>
     <row r="19" ht="24.75" customHeight="1" s="60">
-      <c r="A19" s="77" t="n"/>
+      <c r="A19" s="78" t="n"/>
       <c r="B19" s="3" t="n"/>
       <c r="C19" s="3" t="n"/>
       <c r="D19" s="3" t="n"/>
       <c r="E19" s="3" t="n"/>
     </row>
     <row r="20" ht="24.75" customHeight="1" s="60">
-      <c r="A20" s="77" t="n"/>
+      <c r="A20" s="78" t="n"/>
       <c r="B20" s="3" t="n"/>
       <c r="C20" s="3" t="n"/>
       <c r="D20" s="3" t="n"/>
       <c r="E20" s="3" t="n"/>
     </row>
     <row r="21" ht="24.75" customHeight="1" s="60">
-      <c r="A21" s="77" t="n"/>
+      <c r="A21" s="78" t="n"/>
       <c r="B21" s="3" t="n"/>
       <c r="C21" s="3" t="n"/>
       <c r="D21" s="3" t="n"/>
       <c r="E21" s="3" t="n"/>
     </row>
     <row r="22" ht="24.75" customHeight="1" s="60">
-      <c r="A22" s="77" t="n"/>
+      <c r="A22" s="78" t="n"/>
       <c r="B22" s="3" t="n"/>
       <c r="C22" s="3" t="n"/>
       <c r="D22" s="3" t="n"/>
       <c r="E22" s="3" t="n"/>
     </row>
     <row r="23" ht="24.75" customHeight="1" s="60">
-      <c r="A23" s="77" t="n"/>
+      <c r="A23" s="78" t="n"/>
       <c r="B23" s="3" t="n"/>
       <c r="C23" s="3" t="n"/>
       <c r="D23" s="3" t="n"/>
       <c r="E23" s="3" t="n"/>
     </row>
     <row r="24" ht="24.75" customHeight="1" s="60">
-      <c r="A24" s="77" t="n"/>
+      <c r="A24" s="78" t="n"/>
       <c r="B24" s="3" t="n"/>
       <c r="C24" s="3" t="n"/>
       <c r="D24" s="3" t="n"/>
       <c r="E24" s="3" t="n"/>
     </row>
     <row r="25" ht="24.75" customHeight="1" s="60">
-      <c r="A25" s="77" t="n"/>
+      <c r="A25" s="78" t="n"/>
       <c r="B25" s="3" t="n"/>
       <c r="C25" s="3" t="n"/>
       <c r="D25" s="3" t="n"/>
       <c r="E25" s="3" t="n"/>
     </row>
     <row r="26" ht="24.75" customHeight="1" s="60">
-      <c r="A26" s="77" t="n"/>
+      <c r="A26" s="78" t="n"/>
       <c r="B26" s="3" t="n"/>
       <c r="C26" s="3" t="n"/>
       <c r="D26" s="3" t="n"/>
       <c r="E26" s="3" t="n"/>
     </row>
     <row r="27" ht="24.75" customHeight="1" s="60">
-      <c r="A27" s="77" t="n"/>
+      <c r="A27" s="78" t="n"/>
       <c r="B27" s="3" t="n"/>
       <c r="C27" s="3" t="n"/>
       <c r="D27" s="3" t="n"/>
       <c r="E27" s="3" t="n"/>
     </row>
     <row r="28" ht="24.75" customHeight="1" s="60">
-      <c r="A28" s="77" t="n"/>
+      <c r="A28" s="78" t="n"/>
       <c r="B28" s="3" t="n"/>
       <c r="C28" s="3" t="n"/>
       <c r="D28" s="3" t="n"/>
       <c r="E28" s="3" t="n"/>
     </row>
     <row r="29" ht="24.75" customHeight="1" s="60">
-      <c r="A29" s="77" t="n"/>
+      <c r="A29" s="78" t="n"/>
       <c r="B29" s="3" t="n"/>
       <c r="C29" s="3" t="n"/>
       <c r="D29" s="3" t="n"/>
       <c r="E29" s="3" t="n"/>
     </row>
     <row r="30" ht="24.75" customHeight="1" s="60">
-      <c r="A30" s="77" t="n"/>
+      <c r="A30" s="78" t="n"/>
       <c r="B30" s="3" t="n"/>
       <c r="C30" s="3" t="n"/>
       <c r="D30" s="3" t="n"/>
@@ -3775,9 +3779,9 @@
           <t>UI-PAR-000</t>
         </is>
       </c>
-      <c r="G6" s="17" t="inlineStr">
-        <is>
-          <t>'통합 인증으로 로그인' 버튼 — 제주 데이터허브(D-Hub) 통합 인증(SSO) 로그인 창으로 이동, 인증 성공 시 대시보드 진입. 안내 문구 표시</t>
+      <c r="G6" s="77" t="inlineStr">
+        <is>
+          <t>통합 인증으로 로그인' 버튼 — 제주 데이터허브(D-Hub) 통합 인증(SSO) 로그인 창으로 이동, 인증 성공 시 대시보드 진입</t>
         </is>
       </c>
       <c r="H6" s="16" t="inlineStr">
@@ -3795,7 +3799,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="K6" s="24" t="inlineStr"/>
+      <c r="K6" s="24" t="n"/>
     </row>
     <row r="7" ht="32" customHeight="1" s="60">
       <c r="A7" s="23" t="inlineStr">
@@ -6568,7 +6572,7 @@
       </c>
       <c r="G58" s="15" t="inlineStr">
         <is>
-          <t>민원 관련 행정 정보(조례 등) RAG 기반 검색 및 답변 생성. 조례명·원문 보기 링크 카드 형태 응답</t>
+          <t>민원 관련 행정 정보(조례 등) RAG 기반 검색 및 답변 생성 — 조례명·관련 조문 발췌 카드 형태 응답</t>
         </is>
       </c>
       <c r="H58" s="14" t="inlineStr">
@@ -7582,7 +7586,7 @@
         </is>
       </c>
     </row>
-    <row r="77">
+    <row r="77" ht="30" customHeight="1" s="60">
       <c r="A77" s="27" t="inlineStr">
         <is>
           <t>REQ-SFR-005-10</t>

--- a/Audit/JJ_PD_IP_A02_기능구조도_v1.5_이노팸.xlsx
+++ b/Audit/JJ_PD_IP_A02_기능구조도_v1.5_이노팸.xlsx
@@ -6572,7 +6572,7 @@
       </c>
       <c r="G58" s="15" t="inlineStr">
         <is>
-          <t>민원 관련 행정 정보(조례 등) RAG 기반 검색 및 답변 생성 — 조례명·관련 조문 발췌 카드 형태 응답</t>
+          <t>민원 관련 행정 정보(조례 등) RAG 기반 검색 및 답변 생성 — 조례명·관련 조문 발췌 응답</t>
         </is>
       </c>
       <c r="H58" s="14" t="inlineStr">

--- a/Audit/JJ_PD_IP_A02_기능구조도_v1.5_이노팸.xlsx
+++ b/Audit/JJ_PD_IP_A02_기능구조도_v1.5_이노팸.xlsx
@@ -5870,7 +5870,7 @@
       </c>
       <c r="G45" s="15" t="inlineStr">
         <is>
-          <t>선택 주차장 팝업: 주차장명·주소·총 면수·준공연도·경과연수 및 안전위험도·민원 빈도·이용 패턴·단속 건수 4개 지표 게이지 표시</t>
+          <t>선택 주차장 팝업: 주차장명·주소·총 면수·준공연도·경과연수 및 안전위험도·민원 빈도·이용 패턴·사고 이력 4개 지표 게이지 표시</t>
         </is>
       </c>
       <c r="H45" s="14" t="inlineStr">
@@ -5927,7 +5927,7 @@
       </c>
       <c r="G46" s="19" t="inlineStr">
         <is>
-          <t>종합점수(안전위험도 25%·민원 빈도 25%·이용 패턴 20%·단속 건수 25% — 설정에서 가중치 변경 가능) 기준 우선순위 목록 — 행 클릭 시 지도 확대 이동·팝업, 등급(높음/중간/낮음) 점 표시</t>
+          <t>종합점수(안전위험도 25%·민원 빈도 25%·이용 패턴 25%·사고 이력 25% — 설정에서 가중치 변경 가능) 기준 우선순위 목록 — 행 클릭 시 지도 확대 이동·팝업, 등급(높음/중간/낮음) 점 표시</t>
         </is>
       </c>
       <c r="H46" s="18" t="inlineStr">

--- a/Audit/JJ_PD_IP_A02_기능구조도_v1.5_이노팸.xlsx
+++ b/Audit/JJ_PD_IP_A02_기능구조도_v1.5_이노팸.xlsx
@@ -7057,7 +7057,7 @@
       </c>
       <c r="G67" s="43" t="inlineStr">
         <is>
-          <t>집중구역 분석/구역 추천/투자·보강 우선순위 3개 모델의 가중치 조정(합 100% 검증)</t>
+          <t>집중구역 분석/구역 추천/투자·보강 우선순위 3개 모델의 가중치 조정</t>
         </is>
       </c>
       <c r="H67" s="42" t="inlineStr">
